--- a/docs/設計/部品在庫管理/機能仕様書_部品入荷API.xlsx
+++ b/docs/設計/部品在庫管理/機能仕様書_部品入荷API.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ryota\Downloads\Java-apiCourse-feature\Java-apiCourse-feature\docs\設計\部品在庫管理\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Application\git\Java-API-Course\docs\設計\部品在庫管理\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20BBF29D-7D36-434C-969A-5D86F9ED2D22}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E99C01AF-96C0-43EC-AF89-5CC6CAF216D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="改訂履歴" sheetId="19" r:id="rId1"/>
@@ -20,15 +20,16 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="2">リクエスト!$A$1:$Y$27</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">レスポンス!$A$1:$V$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">機能概要!$A$1:$AH$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">レスポンス!$A$1:$V$27</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">機能概要!$A$1:$AH$29</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
+  <fileRecoveryPr repairLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="261" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="270" uniqueCount="143">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -141,15 +142,9 @@
     <t>共通機能</t>
   </si>
   <si>
-    <t>部品在庫テーブル</t>
-  </si>
-  <si>
     <t>◯</t>
   </si>
   <si>
-    <t>部品入出庫履歴テーブル</t>
-  </si>
-  <si>
     <t>リクエスト</t>
   </si>
   <si>
@@ -198,9 +193,6 @@
     <t>トークン発行済みであること</t>
   </si>
   <si>
-    <t>クエリパラメータ</t>
-  </si>
-  <si>
     <t>項目名</t>
   </si>
   <si>
@@ -216,9 +208,6 @@
     <t>取引種別</t>
   </si>
   <si>
-    <t>transaction_type</t>
-  </si>
-  <si>
     <t>String</t>
   </si>
   <si>
@@ -228,27 +217,12 @@
     <t>"RECEIVE"</t>
   </si>
   <si>
-    <t>入荷日時</t>
-  </si>
-  <si>
-    <t>transaction_date</t>
-  </si>
-  <si>
     <t>業務上の処理日時（入荷日時）</t>
   </si>
   <si>
     <t>ISO 8601</t>
   </si>
   <si>
-    <t>"2024-12-15T14:30:00Z"</t>
-  </si>
-  <si>
-    <t xml:space="preserve">仕入先名 </t>
-  </si>
-  <si>
-    <t>supplier_name</t>
-  </si>
-  <si>
     <t>仕入先企業名</t>
   </si>
   <si>
@@ -258,30 +232,15 @@
     <t>発注書番号</t>
   </si>
   <si>
-    <t>purchase_order_no</t>
-  </si>
-  <si>
     <t>"PO-2024-001234"</t>
   </si>
   <si>
-    <t>入荷作業者名</t>
-  </si>
-  <si>
-    <t>operator_name</t>
-  </si>
-  <si>
     <t>処理担当者名</t>
   </si>
   <si>
     <t>"購買太郎"</t>
   </si>
   <si>
-    <t>入荷部品リスト</t>
-  </si>
-  <si>
-    <t>items</t>
-  </si>
-  <si>
     <t>Array</t>
   </si>
   <si>
@@ -291,57 +250,21 @@
     <t>-</t>
   </si>
   <si>
-    <t>入荷部品リスト（items）配列仕様</t>
-  </si>
-  <si>
-    <t>在庫ID</t>
-  </si>
-  <si>
-    <t>stock_id</t>
-  </si>
-  <si>
     <t>製品在庫のID</t>
   </si>
   <si>
-    <t>入荷先センター ID</t>
-  </si>
-  <si>
-    <t>center_id</t>
-  </si>
-  <si>
     <t>Integer</t>
   </si>
   <si>
     <t>カテゴリID</t>
   </si>
   <si>
-    <t>カテゴリ ID</t>
-  </si>
-  <si>
-    <t>category_id</t>
-  </si>
-  <si>
     <t>部品名</t>
   </si>
   <si>
-    <t>parts_name</t>
-  </si>
-  <si>
     <t>“ボールベアリング”</t>
   </si>
   <si>
-    <t>入荷数量</t>
-  </si>
-  <si>
-    <t>receive_amount</t>
-  </si>
-  <si>
-    <t>部品説明</t>
-  </si>
-  <si>
-    <t>description</t>
-  </si>
-  <si>
     <t>部品在庫に関する説明</t>
   </si>
   <si>
@@ -370,9 +293,6 @@
   </si>
   <si>
     <t>正常系メッセージ</t>
-  </si>
-  <si>
-    <t>"部品入荷情報を正常に登録しました"</t>
   </si>
   <si>
     <t>エラーレスポンス（HTTP 401 Unauthorized）</t>
@@ -434,12 +354,160 @@
     </rPh>
     <phoneticPr fontId="8"/>
   </si>
+  <si>
+    <t>/api/parts/stock/receive</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>transaction_type</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>transaction_date</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>supplier_name</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>purchase_order_no</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>operator_name</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>items</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>取引種別</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>入荷日時</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t xml:space="preserve">仕入先名 </t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>発注書番号</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>入荷作業者名</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>入荷部品リスト</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>在庫ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>入荷先センター ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>カテゴリ ID</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>部品名</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>入荷数量</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>部品説明</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>String</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>stock_id</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>center_id</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>category_id</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>parts_name</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>receive_amount</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>description</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>部品在庫テーブル</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>部品入出庫履歴テーブル</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>"部品入荷情報を正常に登録しました"</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>"2024-12-10"</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>部品入荷 API</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>入荷部品リスト（items）配列仕様</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>クエリパラメータ</t>
+    <phoneticPr fontId="9"/>
+  </si>
+  <si>
+    <t>◯</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>部品カテゴリ情報テーブル</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>在庫センター情報テーブル</t>
+    <phoneticPr fontId="8"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="9"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -504,6 +572,25 @@
     <font>
       <sz val="14"/>
       <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Meiryo UI"/>
+      <family val="3"/>
+      <charset val="128"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <name val="Meiryo UI"/>
       <family val="3"/>
       <charset val="128"/>
@@ -697,7 +784,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="132">
+  <cellXfs count="142">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -836,8 +923,23 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -854,6 +956,51 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -863,54 +1010,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="4" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1005,6 +1104,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1037,6 +1139,12 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1046,12 +1154,18 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="1" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1067,6 +1181,9 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1091,8 +1208,8 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1209,15 +1326,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>168910</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>99695</xdr:rowOff>
+      <xdr:colOff>216535</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>22</xdr:col>
-      <xdr:colOff>301625</xdr:colOff>
-      <xdr:row>21</xdr:row>
-      <xdr:rowOff>245745</xdr:rowOff>
+      <xdr:colOff>295275</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>179069</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1232,8 +1349,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5512435" y="4439285"/>
-          <a:ext cx="1892935" cy="1167130"/>
+          <a:off x="5560060" y="4114800"/>
+          <a:ext cx="1840865" cy="588644"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartMagneticDisk">
           <a:avLst/>
@@ -1271,27 +1388,7 @@
               <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
               <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
             </a:rPr>
-            <a:t>部品在庫</a:t>
-          </a:r>
-          <a:endParaRPr kumimoji="1" lang="en-US" altLang="ja-JP" sz="1100">
-            <a:solidFill>
-              <a:schemeClr val="tx1"/>
-            </a:solidFill>
-            <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
-            <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
-          <a:r>
-            <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-              <a:solidFill>
-                <a:schemeClr val="tx1"/>
-              </a:solidFill>
-              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
-              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="34" charset="-128"/>
-            </a:rPr>
-            <a:t>テーブル</a:t>
+            <a:t>部品在庫テーブル</a:t>
           </a:r>
         </a:p>
       </xdr:txBody>
@@ -1435,14 +1532,14 @@
     <xdr:from>
       <xdr:col>14</xdr:col>
       <xdr:colOff>224155</xdr:colOff>
-      <xdr:row>17</xdr:row>
-      <xdr:rowOff>111760</xdr:rowOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>132397</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>168910</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>172720</xdr:rowOff>
+      <xdr:colOff>216535</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>111125</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1459,9 +1556,9 @@
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
-        <a:xfrm>
-          <a:off x="4624705" y="4451350"/>
-          <a:ext cx="887730" cy="571500"/>
+        <a:xfrm flipV="1">
+          <a:off x="4624705" y="4409122"/>
+          <a:ext cx="935355" cy="474028"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -1492,15 +1589,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>168275</xdr:colOff>
+      <xdr:colOff>206375</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>187960</xdr:rowOff>
+      <xdr:rowOff>102235</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>300990</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>78740</xdr:rowOff>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>24765</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>219075</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
@@ -1515,8 +1612,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5511800" y="2995930"/>
-          <a:ext cx="1892935" cy="1167130"/>
+          <a:off x="5549900" y="3388360"/>
+          <a:ext cx="1894840" cy="612140"/>
         </a:xfrm>
         <a:prstGeom prst="flowChartMagneticDisk">
           <a:avLst/>
@@ -1654,9 +1751,6 @@
             </a:rPr>
             <a:t> 部品入出庫履歴</a:t>
           </a:r>
-        </a:p>
-        <a:p>
-          <a:pPr algn="ctr"/>
           <a:r>
             <a:rPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
               <a:solidFill>
@@ -1675,15 +1769,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>14</xdr:col>
-      <xdr:colOff>227330</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>10160</xdr:rowOff>
+      <xdr:colOff>224155</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>160655</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>17</xdr:col>
-      <xdr:colOff>168275</xdr:colOff>
+      <xdr:colOff>206375</xdr:colOff>
       <xdr:row>17</xdr:row>
-      <xdr:rowOff>60325</xdr:rowOff>
+      <xdr:rowOff>111125</xdr:rowOff>
     </xdr:to>
     <xdr:cxnSp macro="">
       <xdr:nvCxnSpPr>
@@ -1695,13 +1789,277 @@
           </a:extLst>
         </xdr:cNvPr>
         <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="3"/>
           <a:endCxn id="3" idx="2"/>
         </xdr:cNvCxnSpPr>
       </xdr:nvCxnSpPr>
       <xdr:spPr>
         <a:xfrm flipV="1">
-          <a:off x="4627880" y="3583940"/>
-          <a:ext cx="883920" cy="815975"/>
+          <a:off x="4624705" y="3694430"/>
+          <a:ext cx="925195" cy="1188720"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>2540</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>150494</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="15" name="フローチャート: 磁気ディスク 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CC2837C1-A091-4470-BC94-571E99A6AAE6}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5581650" y="4829175"/>
+          <a:ext cx="1840865" cy="588644"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartMagneticDisk">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>在庫センター情報テーブル</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>307340</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>102869</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="16" name="フローチャート: 磁気ディスク 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D9337D0E-BB89-430C-AF35-61BC73C89D41}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5572125" y="5524500"/>
+          <a:ext cx="1840865" cy="588644"/>
+        </a:xfrm>
+        <a:prstGeom prst="flowChartMagneticDisk">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="bg1"/>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="2">
+          <a:schemeClr val="accent1">
+            <a:shade val="15000"/>
+          </a:schemeClr>
+        </a:lnRef>
+        <a:fillRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="lt1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="ctr"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr algn="ctr"/>
+          <a:r>
+            <a:rPr lang="ja-JP" altLang="en-US" sz="1100" b="0" i="0">
+              <a:solidFill>
+                <a:sysClr val="windowText" lastClr="000000"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:ea typeface="Meiryo UI" panose="020B0604030504040204" pitchFamily="50" charset="-128"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>部品カテゴリ情報テーブル</a:t>
+          </a:r>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>224155</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>111125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>103822</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="19" name="直線コネクタ 18">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4567B5B6-2711-4733-9CAD-EC6A3C3E2FF7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="3"/>
+          <a:endCxn id="15" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4624705" y="4883150"/>
+          <a:ext cx="956945" cy="240347"/>
+        </a:xfrm>
+        <a:prstGeom prst="line">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln>
+          <a:solidFill>
+            <a:schemeClr val="tx1"/>
+          </a:solidFill>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>228600</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>56197</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="23" name="直線コネクタ 22">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9BEB4DD2-043E-470E-877B-817EF7E53B3F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:endCxn id="16" idx="2"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4629150" y="4905375"/>
+          <a:ext cx="942975" cy="913447"/>
         </a:xfrm>
         <a:prstGeom prst="line">
           <a:avLst/>
@@ -2438,7 +2796,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:AH26"/>
+  <dimension ref="A1:AH28"/>
   <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="20" width="3.6640625" style="29"/>
@@ -2449,452 +2807,452 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="81" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="78"/>
-      <c r="K1" s="79"/>
-      <c r="L1" s="86" t="s">
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="82"/>
+      <c r="K1" s="83"/>
+      <c r="L1" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="87"/>
-      <c r="N1" s="87"/>
-      <c r="O1" s="87"/>
-      <c r="P1" s="88"/>
-      <c r="Q1" s="92" t="s">
+      <c r="M1" s="91"/>
+      <c r="N1" s="91"/>
+      <c r="O1" s="91"/>
+      <c r="P1" s="92"/>
+      <c r="Q1" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="93"/>
-      <c r="S1" s="93"/>
-      <c r="T1" s="93"/>
-      <c r="U1" s="93"/>
-      <c r="V1" s="66" t="s">
+      <c r="R1" s="97"/>
+      <c r="S1" s="97"/>
+      <c r="T1" s="97"/>
+      <c r="U1" s="97"/>
+      <c r="V1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="66"/>
-      <c r="X1" s="66"/>
-      <c r="Y1" s="96" t="s">
+      <c r="W1" s="61"/>
+      <c r="X1" s="61"/>
+      <c r="Y1" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="97"/>
-      <c r="AA1" s="97"/>
-      <c r="AB1" s="98"/>
-      <c r="AC1" s="71" t="s">
+      <c r="Z1" s="101"/>
+      <c r="AA1" s="101"/>
+      <c r="AB1" s="102"/>
+      <c r="AC1" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="AD1" s="72"/>
-      <c r="AE1" s="73"/>
-      <c r="AF1" s="67" t="s">
+      <c r="AD1" s="76"/>
+      <c r="AE1" s="77"/>
+      <c r="AF1" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="68"/>
-      <c r="AH1" s="68"/>
+      <c r="AG1" s="63"/>
+      <c r="AH1" s="63"/>
     </row>
     <row r="2" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="80"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="81"/>
-      <c r="K2" s="82"/>
-      <c r="L2" s="89"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="90"/>
-      <c r="O2" s="90"/>
-      <c r="P2" s="91"/>
-      <c r="Q2" s="94"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="95"/>
-      <c r="T2" s="95"/>
-      <c r="U2" s="95"/>
-      <c r="V2" s="66"/>
-      <c r="W2" s="66"/>
-      <c r="X2" s="66"/>
-      <c r="Y2" s="99"/>
-      <c r="Z2" s="100"/>
-      <c r="AA2" s="100"/>
-      <c r="AB2" s="101"/>
-      <c r="AC2" s="74"/>
-      <c r="AD2" s="75"/>
-      <c r="AE2" s="76"/>
-      <c r="AF2" s="69"/>
-      <c r="AG2" s="70"/>
-      <c r="AH2" s="70"/>
+      <c r="A2" s="84"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="85"/>
+      <c r="K2" s="86"/>
+      <c r="L2" s="93"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="94"/>
+      <c r="O2" s="94"/>
+      <c r="P2" s="95"/>
+      <c r="Q2" s="98"/>
+      <c r="R2" s="99"/>
+      <c r="S2" s="99"/>
+      <c r="T2" s="99"/>
+      <c r="U2" s="99"/>
+      <c r="V2" s="61"/>
+      <c r="W2" s="61"/>
+      <c r="X2" s="61"/>
+      <c r="Y2" s="103"/>
+      <c r="Z2" s="104"/>
+      <c r="AA2" s="104"/>
+      <c r="AB2" s="105"/>
+      <c r="AC2" s="78"/>
+      <c r="AD2" s="79"/>
+      <c r="AE2" s="80"/>
+      <c r="AF2" s="64"/>
+      <c r="AG2" s="65"/>
+      <c r="AH2" s="65"/>
     </row>
     <row r="3" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="81"/>
-      <c r="K3" s="82"/>
-      <c r="L3" s="86" t="s">
+      <c r="A3" s="84"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="85"/>
+      <c r="K3" s="86"/>
+      <c r="L3" s="90" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="87"/>
-      <c r="N3" s="87"/>
-      <c r="O3" s="87"/>
-      <c r="P3" s="88"/>
-      <c r="Q3" s="92" t="s">
+      <c r="M3" s="91"/>
+      <c r="N3" s="91"/>
+      <c r="O3" s="91"/>
+      <c r="P3" s="92"/>
+      <c r="Q3" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="93"/>
-      <c r="S3" s="93"/>
-      <c r="T3" s="93"/>
-      <c r="U3" s="93"/>
-      <c r="V3" s="66" t="s">
+      <c r="R3" s="97"/>
+      <c r="S3" s="97"/>
+      <c r="T3" s="97"/>
+      <c r="U3" s="97"/>
+      <c r="V3" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="W3" s="66"/>
-      <c r="X3" s="66"/>
-      <c r="Y3" s="96" t="s">
+      <c r="W3" s="61"/>
+      <c r="X3" s="61"/>
+      <c r="Y3" s="100" t="s">
         <v>16</v>
       </c>
-      <c r="Z3" s="97"/>
-      <c r="AA3" s="97"/>
-      <c r="AB3" s="98"/>
-      <c r="AC3" s="66" t="s">
+      <c r="Z3" s="101"/>
+      <c r="AA3" s="101"/>
+      <c r="AB3" s="102"/>
+      <c r="AC3" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="AD3" s="66"/>
-      <c r="AE3" s="66"/>
-      <c r="AF3" s="67" t="s">
+      <c r="AD3" s="61"/>
+      <c r="AE3" s="61"/>
+      <c r="AF3" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="AG3" s="68"/>
-      <c r="AH3" s="68"/>
+      <c r="AG3" s="63"/>
+      <c r="AH3" s="63"/>
     </row>
     <row r="4" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="84"/>
-      <c r="K4" s="85"/>
-      <c r="L4" s="89"/>
-      <c r="M4" s="90"/>
-      <c r="N4" s="90"/>
-      <c r="O4" s="90"/>
-      <c r="P4" s="91"/>
-      <c r="Q4" s="94"/>
-      <c r="R4" s="95"/>
-      <c r="S4" s="95"/>
-      <c r="T4" s="95"/>
-      <c r="U4" s="95"/>
-      <c r="V4" s="66"/>
-      <c r="W4" s="66"/>
-      <c r="X4" s="66"/>
-      <c r="Y4" s="99"/>
-      <c r="Z4" s="100"/>
-      <c r="AA4" s="100"/>
-      <c r="AB4" s="101"/>
-      <c r="AC4" s="66"/>
-      <c r="AD4" s="66"/>
-      <c r="AE4" s="66"/>
-      <c r="AF4" s="69"/>
-      <c r="AG4" s="70"/>
-      <c r="AH4" s="70"/>
+      <c r="A4" s="87"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="88"/>
+      <c r="K4" s="89"/>
+      <c r="L4" s="93"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="94"/>
+      <c r="O4" s="94"/>
+      <c r="P4" s="95"/>
+      <c r="Q4" s="98"/>
+      <c r="R4" s="99"/>
+      <c r="S4" s="99"/>
+      <c r="T4" s="99"/>
+      <c r="U4" s="99"/>
+      <c r="V4" s="61"/>
+      <c r="W4" s="61"/>
+      <c r="X4" s="61"/>
+      <c r="Y4" s="103"/>
+      <c r="Z4" s="104"/>
+      <c r="AA4" s="104"/>
+      <c r="AB4" s="105"/>
+      <c r="AC4" s="61"/>
+      <c r="AD4" s="61"/>
+      <c r="AE4" s="61"/>
+      <c r="AF4" s="64"/>
+      <c r="AG4" s="65"/>
+      <c r="AH4" s="65"/>
     </row>
     <row r="5" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="47" t="s">
+      <c r="A5" s="52" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="48"/>
-      <c r="C5" s="48"/>
-      <c r="D5" s="48"/>
-      <c r="E5" s="48"/>
-      <c r="F5" s="48"/>
-      <c r="G5" s="49"/>
-      <c r="H5" s="50" t="s">
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="53"/>
+      <c r="E5" s="53"/>
+      <c r="F5" s="53"/>
+      <c r="G5" s="54"/>
+      <c r="H5" s="55" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="51"/>
-      <c r="J5" s="51"/>
-      <c r="K5" s="51"/>
-      <c r="L5" s="51"/>
-      <c r="M5" s="51"/>
-      <c r="N5" s="51"/>
-      <c r="O5" s="51"/>
-      <c r="P5" s="51"/>
-      <c r="Q5" s="51"/>
-      <c r="R5" s="51"/>
-      <c r="S5" s="51"/>
-      <c r="T5" s="51"/>
-      <c r="U5" s="51"/>
-      <c r="V5" s="51"/>
-      <c r="W5" s="51"/>
-      <c r="X5" s="51"/>
-      <c r="Y5" s="51"/>
-      <c r="Z5" s="51"/>
-      <c r="AA5" s="51"/>
-      <c r="AB5" s="51"/>
-      <c r="AC5" s="51"/>
-      <c r="AD5" s="51"/>
-      <c r="AE5" s="51"/>
-      <c r="AF5" s="51"/>
-      <c r="AG5" s="51"/>
-      <c r="AH5" s="51"/>
+      <c r="I5" s="56"/>
+      <c r="J5" s="56"/>
+      <c r="K5" s="56"/>
+      <c r="L5" s="56"/>
+      <c r="M5" s="56"/>
+      <c r="N5" s="56"/>
+      <c r="O5" s="56"/>
+      <c r="P5" s="56"/>
+      <c r="Q5" s="56"/>
+      <c r="R5" s="56"/>
+      <c r="S5" s="56"/>
+      <c r="T5" s="56"/>
+      <c r="U5" s="56"/>
+      <c r="V5" s="56"/>
+      <c r="W5" s="56"/>
+      <c r="X5" s="56"/>
+      <c r="Y5" s="56"/>
+      <c r="Z5" s="56"/>
+      <c r="AA5" s="56"/>
+      <c r="AB5" s="56"/>
+      <c r="AC5" s="56"/>
+      <c r="AD5" s="56"/>
+      <c r="AE5" s="56"/>
+      <c r="AF5" s="56"/>
+      <c r="AG5" s="56"/>
+      <c r="AH5" s="56"/>
     </row>
     <row r="6" spans="1:34" customFormat="1" ht="63.75" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="47" t="s">
+      <c r="A6" s="52" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="48"/>
-      <c r="C6" s="48"/>
-      <c r="D6" s="48"/>
-      <c r="E6" s="48"/>
-      <c r="F6" s="48"/>
-      <c r="G6" s="49"/>
-      <c r="H6" s="131" t="s">
-        <v>132</v>
-      </c>
-      <c r="I6" s="51"/>
-      <c r="J6" s="51"/>
-      <c r="K6" s="51"/>
-      <c r="L6" s="51"/>
-      <c r="M6" s="51"/>
-      <c r="N6" s="51"/>
-      <c r="O6" s="51"/>
-      <c r="P6" s="51"/>
-      <c r="Q6" s="51"/>
-      <c r="R6" s="51"/>
-      <c r="S6" s="51"/>
-      <c r="T6" s="51"/>
-      <c r="U6" s="51"/>
-      <c r="V6" s="51"/>
-      <c r="W6" s="51"/>
-      <c r="X6" s="51"/>
-      <c r="Y6" s="51"/>
-      <c r="Z6" s="51"/>
-      <c r="AA6" s="51"/>
-      <c r="AB6" s="51"/>
-      <c r="AC6" s="51"/>
-      <c r="AD6" s="51"/>
-      <c r="AE6" s="51"/>
-      <c r="AF6" s="51"/>
-      <c r="AG6" s="51"/>
-      <c r="AH6" s="51"/>
+      <c r="B6" s="53"/>
+      <c r="C6" s="53"/>
+      <c r="D6" s="53"/>
+      <c r="E6" s="53"/>
+      <c r="F6" s="53"/>
+      <c r="G6" s="54"/>
+      <c r="H6" s="57" t="s">
+        <v>105</v>
+      </c>
+      <c r="I6" s="56"/>
+      <c r="J6" s="56"/>
+      <c r="K6" s="56"/>
+      <c r="L6" s="56"/>
+      <c r="M6" s="56"/>
+      <c r="N6" s="56"/>
+      <c r="O6" s="56"/>
+      <c r="P6" s="56"/>
+      <c r="Q6" s="56"/>
+      <c r="R6" s="56"/>
+      <c r="S6" s="56"/>
+      <c r="T6" s="56"/>
+      <c r="U6" s="56"/>
+      <c r="V6" s="56"/>
+      <c r="W6" s="56"/>
+      <c r="X6" s="56"/>
+      <c r="Y6" s="56"/>
+      <c r="Z6" s="56"/>
+      <c r="AA6" s="56"/>
+      <c r="AB6" s="56"/>
+      <c r="AC6" s="56"/>
+      <c r="AD6" s="56"/>
+      <c r="AE6" s="56"/>
+      <c r="AF6" s="56"/>
+      <c r="AG6" s="56"/>
+      <c r="AH6" s="56"/>
     </row>
     <row r="7" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="47" t="s">
+      <c r="A7" s="52" t="s">
         <v>21</v>
       </c>
-      <c r="B7" s="48"/>
-      <c r="C7" s="48"/>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="49"/>
-      <c r="H7" s="50" t="s">
+      <c r="B7" s="53"/>
+      <c r="C7" s="53"/>
+      <c r="D7" s="53"/>
+      <c r="E7" s="53"/>
+      <c r="F7" s="53"/>
+      <c r="G7" s="54"/>
+      <c r="H7" s="55" t="s">
         <v>22</v>
       </c>
-      <c r="I7" s="51"/>
-      <c r="J7" s="51"/>
-      <c r="K7" s="51"/>
-      <c r="L7" s="51"/>
-      <c r="M7" s="51"/>
-      <c r="N7" s="51"/>
-      <c r="O7" s="51"/>
-      <c r="P7" s="51"/>
-      <c r="Q7" s="51"/>
-      <c r="R7" s="51"/>
-      <c r="S7" s="51"/>
-      <c r="T7" s="51"/>
-      <c r="U7" s="51"/>
-      <c r="V7" s="51"/>
-      <c r="W7" s="51"/>
-      <c r="X7" s="51"/>
-      <c r="Y7" s="51"/>
-      <c r="Z7" s="51"/>
-      <c r="AA7" s="51"/>
-      <c r="AB7" s="51"/>
-      <c r="AC7" s="51"/>
-      <c r="AD7" s="51"/>
-      <c r="AE7" s="51"/>
-      <c r="AF7" s="51"/>
-      <c r="AG7" s="51"/>
-      <c r="AH7" s="51"/>
+      <c r="I7" s="56"/>
+      <c r="J7" s="56"/>
+      <c r="K7" s="56"/>
+      <c r="L7" s="56"/>
+      <c r="M7" s="56"/>
+      <c r="N7" s="56"/>
+      <c r="O7" s="56"/>
+      <c r="P7" s="56"/>
+      <c r="Q7" s="56"/>
+      <c r="R7" s="56"/>
+      <c r="S7" s="56"/>
+      <c r="T7" s="56"/>
+      <c r="U7" s="56"/>
+      <c r="V7" s="56"/>
+      <c r="W7" s="56"/>
+      <c r="X7" s="56"/>
+      <c r="Y7" s="56"/>
+      <c r="Z7" s="56"/>
+      <c r="AA7" s="56"/>
+      <c r="AB7" s="56"/>
+      <c r="AC7" s="56"/>
+      <c r="AD7" s="56"/>
+      <c r="AE7" s="56"/>
+      <c r="AF7" s="56"/>
+      <c r="AG7" s="56"/>
+      <c r="AH7" s="56"/>
     </row>
     <row r="8" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="47" t="s">
+      <c r="A8" s="52" t="s">
         <v>23</v>
       </c>
-      <c r="B8" s="48"/>
-      <c r="C8" s="48"/>
-      <c r="D8" s="48"/>
-      <c r="E8" s="48"/>
-      <c r="F8" s="48"/>
-      <c r="G8" s="49"/>
-      <c r="H8" s="50" t="s">
+      <c r="B8" s="53"/>
+      <c r="C8" s="53"/>
+      <c r="D8" s="53"/>
+      <c r="E8" s="53"/>
+      <c r="F8" s="53"/>
+      <c r="G8" s="54"/>
+      <c r="H8" s="55" t="s">
         <v>24</v>
       </c>
-      <c r="I8" s="51"/>
-      <c r="J8" s="51"/>
-      <c r="K8" s="51"/>
-      <c r="L8" s="51"/>
-      <c r="M8" s="51"/>
-      <c r="N8" s="51"/>
-      <c r="O8" s="51"/>
-      <c r="P8" s="51"/>
-      <c r="Q8" s="51"/>
-      <c r="R8" s="51"/>
-      <c r="S8" s="51"/>
-      <c r="T8" s="51"/>
-      <c r="U8" s="51"/>
-      <c r="V8" s="51"/>
-      <c r="W8" s="51"/>
-      <c r="X8" s="51"/>
-      <c r="Y8" s="51"/>
-      <c r="Z8" s="51"/>
-      <c r="AA8" s="51"/>
-      <c r="AB8" s="51"/>
-      <c r="AC8" s="51"/>
-      <c r="AD8" s="51"/>
-      <c r="AE8" s="51"/>
-      <c r="AF8" s="51"/>
-      <c r="AG8" s="51"/>
-      <c r="AH8" s="51"/>
+      <c r="I8" s="56"/>
+      <c r="J8" s="56"/>
+      <c r="K8" s="56"/>
+      <c r="L8" s="56"/>
+      <c r="M8" s="56"/>
+      <c r="N8" s="56"/>
+      <c r="O8" s="56"/>
+      <c r="P8" s="56"/>
+      <c r="Q8" s="56"/>
+      <c r="R8" s="56"/>
+      <c r="S8" s="56"/>
+      <c r="T8" s="56"/>
+      <c r="U8" s="56"/>
+      <c r="V8" s="56"/>
+      <c r="W8" s="56"/>
+      <c r="X8" s="56"/>
+      <c r="Y8" s="56"/>
+      <c r="Z8" s="56"/>
+      <c r="AA8" s="56"/>
+      <c r="AB8" s="56"/>
+      <c r="AC8" s="56"/>
+      <c r="AD8" s="56"/>
+      <c r="AE8" s="56"/>
+      <c r="AF8" s="56"/>
+      <c r="AG8" s="56"/>
+      <c r="AH8" s="56"/>
     </row>
     <row r="9" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="47" t="s">
+      <c r="A9" s="52" t="s">
         <v>25</v>
       </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="49"/>
-      <c r="H9" s="50" t="s">
+      <c r="B9" s="53"/>
+      <c r="C9" s="53"/>
+      <c r="D9" s="53"/>
+      <c r="E9" s="53"/>
+      <c r="F9" s="53"/>
+      <c r="G9" s="54"/>
+      <c r="H9" s="55" t="s">
         <v>26</v>
       </c>
-      <c r="I9" s="51"/>
-      <c r="J9" s="51"/>
-      <c r="K9" s="51"/>
-      <c r="L9" s="51"/>
-      <c r="M9" s="51"/>
-      <c r="N9" s="51"/>
-      <c r="O9" s="51"/>
-      <c r="P9" s="51"/>
-      <c r="Q9" s="51"/>
-      <c r="R9" s="51"/>
-      <c r="S9" s="51"/>
-      <c r="T9" s="51"/>
-      <c r="U9" s="51"/>
-      <c r="V9" s="51"/>
-      <c r="W9" s="51"/>
-      <c r="X9" s="51"/>
-      <c r="Y9" s="51"/>
-      <c r="Z9" s="51"/>
-      <c r="AA9" s="51"/>
-      <c r="AB9" s="51"/>
-      <c r="AC9" s="51"/>
-      <c r="AD9" s="51"/>
-      <c r="AE9" s="51"/>
-      <c r="AF9" s="51"/>
-      <c r="AG9" s="51"/>
-      <c r="AH9" s="51"/>
+      <c r="I9" s="56"/>
+      <c r="J9" s="56"/>
+      <c r="K9" s="56"/>
+      <c r="L9" s="56"/>
+      <c r="M9" s="56"/>
+      <c r="N9" s="56"/>
+      <c r="O9" s="56"/>
+      <c r="P9" s="56"/>
+      <c r="Q9" s="56"/>
+      <c r="R9" s="56"/>
+      <c r="S9" s="56"/>
+      <c r="T9" s="56"/>
+      <c r="U9" s="56"/>
+      <c r="V9" s="56"/>
+      <c r="W9" s="56"/>
+      <c r="X9" s="56"/>
+      <c r="Y9" s="56"/>
+      <c r="Z9" s="56"/>
+      <c r="AA9" s="56"/>
+      <c r="AB9" s="56"/>
+      <c r="AC9" s="56"/>
+      <c r="AD9" s="56"/>
+      <c r="AE9" s="56"/>
+      <c r="AF9" s="56"/>
+      <c r="AG9" s="56"/>
+      <c r="AH9" s="56"/>
     </row>
     <row r="10" spans="1:34" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="52" t="s">
+      <c r="A10" s="72" t="s">
         <v>27</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="53"/>
-      <c r="D10" s="53"/>
-      <c r="E10" s="53"/>
-      <c r="F10" s="53"/>
-      <c r="G10" s="54"/>
-      <c r="H10" s="55" t="s">
+      <c r="B10" s="73"/>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="74"/>
+      <c r="H10" s="50" t="s">
         <v>28</v>
       </c>
-      <c r="I10" s="56"/>
-      <c r="J10" s="56"/>
-      <c r="K10" s="56"/>
-      <c r="L10" s="56"/>
-      <c r="M10" s="56"/>
-      <c r="N10" s="56"/>
-      <c r="O10" s="56"/>
-      <c r="P10" s="56"/>
-      <c r="Q10" s="56"/>
-      <c r="R10" s="56"/>
-      <c r="S10" s="56"/>
-      <c r="T10" s="56"/>
-      <c r="U10" s="56"/>
-      <c r="V10" s="56"/>
-      <c r="W10" s="56"/>
-      <c r="X10" s="56"/>
-      <c r="Y10" s="56"/>
-      <c r="Z10" s="56"/>
-      <c r="AA10" s="56"/>
-      <c r="AB10" s="56"/>
-      <c r="AC10" s="56"/>
-      <c r="AD10" s="56"/>
-      <c r="AE10" s="56"/>
-      <c r="AF10" s="56"/>
-      <c r="AG10" s="56"/>
-      <c r="AH10" s="56"/>
+      <c r="I10" s="51"/>
+      <c r="J10" s="51"/>
+      <c r="K10" s="51"/>
+      <c r="L10" s="51"/>
+      <c r="M10" s="51"/>
+      <c r="N10" s="51"/>
+      <c r="O10" s="51"/>
+      <c r="P10" s="51"/>
+      <c r="Q10" s="51"/>
+      <c r="R10" s="51"/>
+      <c r="S10" s="51"/>
+      <c r="T10" s="51"/>
+      <c r="U10" s="51"/>
+      <c r="V10" s="51"/>
+      <c r="W10" s="51"/>
+      <c r="X10" s="51"/>
+      <c r="Y10" s="51"/>
+      <c r="Z10" s="51"/>
+      <c r="AA10" s="51"/>
+      <c r="AB10" s="51"/>
+      <c r="AC10" s="51"/>
+      <c r="AD10" s="51"/>
+      <c r="AE10" s="51"/>
+      <c r="AF10" s="51"/>
+      <c r="AG10" s="51"/>
+      <c r="AH10" s="51"/>
     </row>
     <row r="11" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="57" t="s">
+      <c r="A11" s="66" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
-      <c r="J11" s="58"/>
-      <c r="K11" s="58"/>
-      <c r="L11" s="58"/>
-      <c r="M11" s="58"/>
-      <c r="N11" s="58"/>
-      <c r="O11" s="58"/>
-      <c r="P11" s="58"/>
-      <c r="Q11" s="58"/>
-      <c r="R11" s="58"/>
-      <c r="S11" s="58"/>
-      <c r="T11" s="58"/>
-      <c r="U11" s="58"/>
-      <c r="V11" s="58"/>
-      <c r="W11" s="58"/>
-      <c r="X11" s="58"/>
-      <c r="Y11" s="58"/>
-      <c r="Z11" s="58"/>
-      <c r="AA11" s="58"/>
-      <c r="AB11" s="58"/>
-      <c r="AC11" s="58"/>
-      <c r="AD11" s="58"/>
-      <c r="AE11" s="58"/>
-      <c r="AF11" s="58"/>
-      <c r="AG11" s="58"/>
-      <c r="AH11" s="58"/>
+      <c r="B11" s="67"/>
+      <c r="C11" s="67"/>
+      <c r="D11" s="67"/>
+      <c r="E11" s="67"/>
+      <c r="F11" s="67"/>
+      <c r="G11" s="67"/>
+      <c r="H11" s="67"/>
+      <c r="I11" s="67"/>
+      <c r="J11" s="67"/>
+      <c r="K11" s="67"/>
+      <c r="L11" s="67"/>
+      <c r="M11" s="67"/>
+      <c r="N11" s="67"/>
+      <c r="O11" s="67"/>
+      <c r="P11" s="67"/>
+      <c r="Q11" s="67"/>
+      <c r="R11" s="67"/>
+      <c r="S11" s="67"/>
+      <c r="T11" s="67"/>
+      <c r="U11" s="67"/>
+      <c r="V11" s="67"/>
+      <c r="W11" s="67"/>
+      <c r="X11" s="67"/>
+      <c r="Y11" s="67"/>
+      <c r="Z11" s="67"/>
+      <c r="AA11" s="67"/>
+      <c r="AB11" s="67"/>
+      <c r="AC11" s="67"/>
+      <c r="AD11" s="67"/>
+      <c r="AE11" s="67"/>
+      <c r="AF11" s="67"/>
+      <c r="AG11" s="67"/>
+      <c r="AH11" s="67"/>
     </row>
     <row r="12" spans="1:34" s="4" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A12" s="30"/>
@@ -2966,20 +3324,20 @@
       <c r="AH23" s="32"/>
     </row>
     <row r="24" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="59" t="s">
+      <c r="A24" s="68" t="s">
         <v>30</v>
       </c>
-      <c r="B24" s="60"/>
-      <c r="C24" s="59" t="s">
+      <c r="B24" s="69"/>
+      <c r="C24" s="68" t="s">
         <v>31</v>
       </c>
-      <c r="D24" s="61"/>
-      <c r="E24" s="61"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="61"/>
-      <c r="J24" s="60"/>
+      <c r="D24" s="70"/>
+      <c r="E24" s="70"/>
+      <c r="F24" s="70"/>
+      <c r="G24" s="70"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="70"/>
+      <c r="J24" s="69"/>
       <c r="K24" s="36" t="s">
         <v>32</v>
       </c>
@@ -2992,36 +3350,36 @@
       <c r="N24" s="33" t="s">
         <v>35</v>
       </c>
-      <c r="O24" s="62" t="s">
+      <c r="O24" s="71" t="s">
         <v>36</v>
       </c>
-      <c r="P24" s="62"/>
-      <c r="Q24" s="62"/>
-      <c r="R24" s="62"/>
-      <c r="S24" s="62"/>
-      <c r="T24" s="62"/>
-      <c r="U24" s="62"/>
-      <c r="V24" s="62"/>
-      <c r="W24" s="62"/>
-      <c r="X24" s="62"/>
-      <c r="Y24" s="62"/>
-      <c r="Z24" s="62"/>
-      <c r="AA24" s="62"/>
-      <c r="AB24" s="62"/>
-      <c r="AC24" s="62"/>
-      <c r="AD24" s="62"/>
-      <c r="AE24" s="62"/>
-      <c r="AF24" s="62"/>
-      <c r="AG24" s="62"/>
-      <c r="AH24" s="62"/>
+      <c r="P24" s="71"/>
+      <c r="Q24" s="71"/>
+      <c r="R24" s="71"/>
+      <c r="S24" s="71"/>
+      <c r="T24" s="71"/>
+      <c r="U24" s="71"/>
+      <c r="V24" s="71"/>
+      <c r="W24" s="71"/>
+      <c r="X24" s="71"/>
+      <c r="Y24" s="71"/>
+      <c r="Z24" s="71"/>
+      <c r="AA24" s="71"/>
+      <c r="AB24" s="71"/>
+      <c r="AC24" s="71"/>
+      <c r="AD24" s="71"/>
+      <c r="AE24" s="71"/>
+      <c r="AF24" s="71"/>
+      <c r="AG24" s="71"/>
+      <c r="AH24" s="71"/>
     </row>
     <row r="25" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="63">
+      <c r="A25" s="58">
         <v>1</v>
       </c>
-      <c r="B25" s="64"/>
-      <c r="C25" s="34" t="s">
-        <v>37</v>
+      <c r="B25" s="59"/>
+      <c r="C25" s="46" t="s">
+        <v>132</v>
       </c>
       <c r="D25" s="35"/>
       <c r="E25" s="35"/>
@@ -3031,43 +3389,43 @@
       <c r="I25" s="35"/>
       <c r="J25" s="35"/>
       <c r="K25" s="37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="L25" s="37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M25" s="37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="N25" s="34"/>
-      <c r="O25" s="65"/>
-      <c r="P25" s="65"/>
-      <c r="Q25" s="65"/>
-      <c r="R25" s="65"/>
-      <c r="S25" s="65"/>
-      <c r="T25" s="65"/>
-      <c r="U25" s="65"/>
-      <c r="V25" s="65"/>
-      <c r="W25" s="65"/>
-      <c r="X25" s="65"/>
-      <c r="Y25" s="65"/>
-      <c r="Z25" s="65"/>
-      <c r="AA25" s="65"/>
-      <c r="AB25" s="65"/>
-      <c r="AC25" s="65"/>
-      <c r="AD25" s="65"/>
-      <c r="AE25" s="65"/>
-      <c r="AF25" s="65"/>
-      <c r="AG25" s="65"/>
-      <c r="AH25" s="65"/>
+      <c r="O25" s="60"/>
+      <c r="P25" s="60"/>
+      <c r="Q25" s="60"/>
+      <c r="R25" s="60"/>
+      <c r="S25" s="60"/>
+      <c r="T25" s="60"/>
+      <c r="U25" s="60"/>
+      <c r="V25" s="60"/>
+      <c r="W25" s="60"/>
+      <c r="X25" s="60"/>
+      <c r="Y25" s="60"/>
+      <c r="Z25" s="60"/>
+      <c r="AA25" s="60"/>
+      <c r="AB25" s="60"/>
+      <c r="AC25" s="60"/>
+      <c r="AD25" s="60"/>
+      <c r="AE25" s="60"/>
+      <c r="AF25" s="60"/>
+      <c r="AG25" s="60"/>
+      <c r="AH25" s="60"/>
     </row>
     <row r="26" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="63">
+      <c r="A26" s="58">
         <v>2</v>
       </c>
-      <c r="B26" s="64"/>
-      <c r="C26" s="46" t="s">
-        <v>39</v>
+      <c r="B26" s="59"/>
+      <c r="C26" s="47" t="s">
+        <v>133</v>
       </c>
       <c r="D26" s="35"/>
       <c r="E26" s="35"/>
@@ -3076,35 +3434,125 @@
       <c r="H26" s="35"/>
       <c r="I26" s="35"/>
       <c r="J26" s="35"/>
-      <c r="K26" s="37"/>
+      <c r="K26" s="141" t="s">
+        <v>139</v>
+      </c>
       <c r="L26" s="37" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M26" s="37"/>
       <c r="N26" s="34"/>
-      <c r="O26" s="65"/>
-      <c r="P26" s="65"/>
-      <c r="Q26" s="65"/>
-      <c r="R26" s="65"/>
-      <c r="S26" s="65"/>
-      <c r="T26" s="65"/>
-      <c r="U26" s="65"/>
-      <c r="V26" s="65"/>
-      <c r="W26" s="65"/>
-      <c r="X26" s="65"/>
-      <c r="Y26" s="65"/>
-      <c r="Z26" s="65"/>
-      <c r="AA26" s="65"/>
-      <c r="AB26" s="65"/>
-      <c r="AC26" s="65"/>
-      <c r="AD26" s="65"/>
-      <c r="AE26" s="65"/>
-      <c r="AF26" s="65"/>
-      <c r="AG26" s="65"/>
-      <c r="AH26" s="65"/>
+      <c r="O26" s="60"/>
+      <c r="P26" s="60"/>
+      <c r="Q26" s="60"/>
+      <c r="R26" s="60"/>
+      <c r="S26" s="60"/>
+      <c r="T26" s="60"/>
+      <c r="U26" s="60"/>
+      <c r="V26" s="60"/>
+      <c r="W26" s="60"/>
+      <c r="X26" s="60"/>
+      <c r="Y26" s="60"/>
+      <c r="Z26" s="60"/>
+      <c r="AA26" s="60"/>
+      <c r="AB26" s="60"/>
+      <c r="AC26" s="60"/>
+      <c r="AD26" s="60"/>
+      <c r="AE26" s="60"/>
+      <c r="AF26" s="60"/>
+      <c r="AG26" s="60"/>
+      <c r="AH26" s="60"/>
+    </row>
+    <row r="27" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A27" s="58">
+        <v>3</v>
+      </c>
+      <c r="B27" s="59"/>
+      <c r="C27" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" s="35"/>
+      <c r="E27" s="35"/>
+      <c r="F27" s="35"/>
+      <c r="G27" s="35"/>
+      <c r="H27" s="35"/>
+      <c r="I27" s="35"/>
+      <c r="J27" s="35"/>
+      <c r="K27" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="L27" s="37"/>
+      <c r="M27" s="37"/>
+      <c r="N27" s="34"/>
+      <c r="O27" s="60"/>
+      <c r="P27" s="60"/>
+      <c r="Q27" s="60"/>
+      <c r="R27" s="60"/>
+      <c r="S27" s="60"/>
+      <c r="T27" s="60"/>
+      <c r="U27" s="60"/>
+      <c r="V27" s="60"/>
+      <c r="W27" s="60"/>
+      <c r="X27" s="60"/>
+      <c r="Y27" s="60"/>
+      <c r="Z27" s="60"/>
+      <c r="AA27" s="60"/>
+      <c r="AB27" s="60"/>
+      <c r="AC27" s="60"/>
+      <c r="AD27" s="60"/>
+      <c r="AE27" s="60"/>
+      <c r="AF27" s="60"/>
+      <c r="AG27" s="60"/>
+      <c r="AH27" s="60"/>
+    </row>
+    <row r="28" spans="1:34" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="58">
+        <v>4</v>
+      </c>
+      <c r="B28" s="59"/>
+      <c r="C28" s="47" t="s">
+        <v>140</v>
+      </c>
+      <c r="D28" s="35"/>
+      <c r="E28" s="35"/>
+      <c r="F28" s="35"/>
+      <c r="G28" s="35"/>
+      <c r="H28" s="35"/>
+      <c r="I28" s="35"/>
+      <c r="J28" s="35"/>
+      <c r="K28" s="37" t="s">
+        <v>37</v>
+      </c>
+      <c r="L28" s="37"/>
+      <c r="M28" s="37"/>
+      <c r="N28" s="34"/>
+      <c r="O28" s="60"/>
+      <c r="P28" s="60"/>
+      <c r="Q28" s="60"/>
+      <c r="R28" s="60"/>
+      <c r="S28" s="60"/>
+      <c r="T28" s="60"/>
+      <c r="U28" s="60"/>
+      <c r="V28" s="60"/>
+      <c r="W28" s="60"/>
+      <c r="X28" s="60"/>
+      <c r="Y28" s="60"/>
+      <c r="Z28" s="60"/>
+      <c r="AA28" s="60"/>
+      <c r="AB28" s="60"/>
+      <c r="AC28" s="60"/>
+      <c r="AD28" s="60"/>
+      <c r="AE28" s="60"/>
+      <c r="AF28" s="60"/>
+      <c r="AG28" s="60"/>
+      <c r="AH28" s="60"/>
     </row>
   </sheetData>
-  <mergeCells count="33">
+  <mergeCells count="37">
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="O27:AH27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="O28:AH28"/>
     <mergeCell ref="V1:X2"/>
     <mergeCell ref="AC1:AE2"/>
     <mergeCell ref="AF1:AH2"/>
@@ -3169,565 +3617,565 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="77" t="s">
+      <c r="A1" s="81" t="s">
+        <v>38</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="82"/>
+      <c r="J1" s="90" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="91"/>
+      <c r="N1" s="92"/>
+      <c r="O1" s="96" t="s">
+        <v>10</v>
+      </c>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="97"/>
+      <c r="R1" s="97"/>
+      <c r="S1" s="97"/>
+      <c r="T1" s="61" t="s">
+        <v>3</v>
+      </c>
+      <c r="U1" s="100" t="s">
+        <v>6</v>
+      </c>
+      <c r="V1" s="101"/>
+      <c r="W1" s="75" t="s">
+        <v>11</v>
+      </c>
+      <c r="X1" s="62" t="s">
+        <v>12</v>
+      </c>
+      <c r="Y1" s="63"/>
+    </row>
+    <row r="2" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="84"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="85"/>
+      <c r="J2" s="93"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="94"/>
+      <c r="M2" s="94"/>
+      <c r="N2" s="95"/>
+      <c r="O2" s="98"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="99"/>
+      <c r="R2" s="99"/>
+      <c r="S2" s="99"/>
+      <c r="T2" s="61"/>
+      <c r="U2" s="103"/>
+      <c r="V2" s="104"/>
+      <c r="W2" s="78"/>
+      <c r="X2" s="64"/>
+      <c r="Y2" s="65"/>
+    </row>
+    <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="84"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="85"/>
+      <c r="J3" s="90" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="91"/>
+      <c r="N3" s="92"/>
+      <c r="O3" s="132" t="s">
+        <v>136</v>
+      </c>
+      <c r="P3" s="97"/>
+      <c r="Q3" s="97"/>
+      <c r="R3" s="97"/>
+      <c r="S3" s="97"/>
+      <c r="T3" s="61" t="s">
+        <v>15</v>
+      </c>
+      <c r="U3" s="100" t="s">
+        <v>16</v>
+      </c>
+      <c r="V3" s="101"/>
+      <c r="W3" s="61" t="s">
+        <v>17</v>
+      </c>
+      <c r="X3" s="62" t="s">
+        <v>18</v>
+      </c>
+      <c r="Y3" s="63"/>
+    </row>
+    <row r="4" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="87"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="88"/>
+      <c r="J4" s="93"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="94"/>
+      <c r="M4" s="94"/>
+      <c r="N4" s="95"/>
+      <c r="O4" s="98"/>
+      <c r="P4" s="99"/>
+      <c r="Q4" s="99"/>
+      <c r="R4" s="99"/>
+      <c r="S4" s="99"/>
+      <c r="T4" s="61"/>
+      <c r="U4" s="103"/>
+      <c r="V4" s="104"/>
+      <c r="W4" s="61"/>
+      <c r="X4" s="64"/>
+      <c r="Y4" s="65"/>
+    </row>
+    <row r="5" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="106" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="106"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="106"/>
+      <c r="F5" s="107" t="s">
+        <v>106</v>
+      </c>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="108"/>
+      <c r="J5" s="106" t="s">
         <v>40</v>
       </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="78"/>
-      <c r="J1" s="86" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="87"/>
-      <c r="N1" s="88"/>
-      <c r="O1" s="92" t="s">
-        <v>10</v>
-      </c>
-      <c r="P1" s="93"/>
-      <c r="Q1" s="93"/>
-      <c r="R1" s="93"/>
-      <c r="S1" s="93"/>
-      <c r="T1" s="66" t="s">
-        <v>3</v>
-      </c>
-      <c r="U1" s="96" t="s">
-        <v>6</v>
-      </c>
-      <c r="V1" s="97"/>
-      <c r="W1" s="71" t="s">
-        <v>11</v>
-      </c>
-      <c r="X1" s="67" t="s">
-        <v>12</v>
-      </c>
-      <c r="Y1" s="68"/>
-    </row>
-    <row r="2" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="80"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="81"/>
-      <c r="J2" s="89"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="90"/>
-      <c r="N2" s="91"/>
-      <c r="O2" s="94"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="95"/>
-      <c r="R2" s="95"/>
-      <c r="S2" s="95"/>
-      <c r="T2" s="66"/>
-      <c r="U2" s="99"/>
-      <c r="V2" s="100"/>
-      <c r="W2" s="74"/>
-      <c r="X2" s="69"/>
-      <c r="Y2" s="70"/>
-    </row>
-    <row r="3" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="81"/>
-      <c r="J3" s="86" t="s">
-        <v>13</v>
-      </c>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="87"/>
-      <c r="N3" s="88"/>
-      <c r="O3" s="92" t="s">
-        <v>14</v>
-      </c>
-      <c r="P3" s="93"/>
-      <c r="Q3" s="93"/>
-      <c r="R3" s="93"/>
-      <c r="S3" s="93"/>
-      <c r="T3" s="66" t="s">
-        <v>15</v>
-      </c>
-      <c r="U3" s="96" t="s">
-        <v>16</v>
-      </c>
-      <c r="V3" s="97"/>
-      <c r="W3" s="66" t="s">
-        <v>17</v>
-      </c>
-      <c r="X3" s="67" t="s">
-        <v>18</v>
-      </c>
-      <c r="Y3" s="68"/>
-    </row>
-    <row r="4" spans="1:25" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="84"/>
-      <c r="J4" s="89"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="90"/>
-      <c r="N4" s="91"/>
-      <c r="O4" s="94"/>
-      <c r="P4" s="95"/>
-      <c r="Q4" s="95"/>
-      <c r="R4" s="95"/>
-      <c r="S4" s="95"/>
-      <c r="T4" s="66"/>
-      <c r="U4" s="99"/>
-      <c r="V4" s="100"/>
-      <c r="W4" s="66"/>
-      <c r="X4" s="69"/>
-      <c r="Y4" s="70"/>
-    </row>
-    <row r="5" spans="1:25" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="102" t="s">
+      <c r="K5" s="106"/>
+      <c r="L5" s="106"/>
+      <c r="M5" s="106"/>
+      <c r="N5" s="106"/>
+      <c r="O5" s="108" t="s">
+        <v>22</v>
+      </c>
+      <c r="P5" s="108"/>
+      <c r="Q5" s="108"/>
+      <c r="R5" s="108"/>
+      <c r="S5" s="108"/>
+      <c r="T5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="102"/>
-      <c r="F5" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="103"/>
-      <c r="J5" s="102" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="102"/>
-      <c r="N5" s="102"/>
-      <c r="O5" s="103" t="s">
-        <v>22</v>
-      </c>
-      <c r="P5" s="103"/>
-      <c r="Q5" s="103"/>
-      <c r="R5" s="103"/>
-      <c r="S5" s="103"/>
-      <c r="T5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="U5" s="103" t="s">
+      <c r="U5" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="V5" s="103"/>
-      <c r="W5" s="103"/>
-      <c r="X5" s="103"/>
-      <c r="Y5" s="103"/>
+      <c r="V5" s="108"/>
+      <c r="W5" s="108"/>
+      <c r="X5" s="108"/>
+      <c r="Y5" s="108"/>
     </row>
     <row r="6" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A6" s="24" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="7" spans="1:25" s="2" customFormat="1" ht="23.1" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A7" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B7" s="66" t="s">
+      <c r="B7" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="C7" s="61"/>
+      <c r="D7" s="61"/>
+      <c r="E7" s="61"/>
+      <c r="F7" s="61"/>
+      <c r="G7" s="61"/>
+      <c r="H7" s="61"/>
+      <c r="I7" s="61"/>
+      <c r="J7" s="28" t="s">
+        <v>44</v>
+      </c>
+      <c r="K7" s="109" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="66"/>
-      <c r="D7" s="66"/>
-      <c r="E7" s="66"/>
-      <c r="F7" s="66"/>
-      <c r="G7" s="66"/>
-      <c r="H7" s="66"/>
-      <c r="I7" s="66"/>
-      <c r="J7" s="28" t="s">
+      <c r="L7" s="110"/>
+      <c r="M7" s="110"/>
+      <c r="N7" s="111"/>
+      <c r="O7" s="61" t="s">
         <v>46</v>
       </c>
-      <c r="K7" s="104" t="s">
+      <c r="P7" s="61"/>
+      <c r="Q7" s="61"/>
+      <c r="R7" s="61"/>
+      <c r="S7" s="61" t="s">
         <v>47</v>
       </c>
-      <c r="L7" s="105"/>
-      <c r="M7" s="105"/>
-      <c r="N7" s="106"/>
-      <c r="O7" s="66" t="s">
+      <c r="T7" s="61"/>
+      <c r="U7" s="109" t="s">
         <v>48</v>
       </c>
-      <c r="P7" s="66"/>
-      <c r="Q7" s="66"/>
-      <c r="R7" s="66"/>
-      <c r="S7" s="66" t="s">
-        <v>49</v>
-      </c>
-      <c r="T7" s="66"/>
-      <c r="U7" s="104" t="s">
-        <v>50</v>
-      </c>
-      <c r="V7" s="105"/>
-      <c r="W7" s="105"/>
-      <c r="X7" s="105"/>
-      <c r="Y7" s="105"/>
+      <c r="V7" s="110"/>
+      <c r="W7" s="110"/>
+      <c r="X7" s="110"/>
+      <c r="Y7" s="110"/>
     </row>
     <row r="8" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A8" s="11">
         <v>1</v>
       </c>
-      <c r="B8" s="107" t="s">
+      <c r="B8" s="112" t="s">
+        <v>49</v>
+      </c>
+      <c r="C8" s="112"/>
+      <c r="D8" s="112"/>
+      <c r="E8" s="112"/>
+      <c r="F8" s="112"/>
+      <c r="G8" s="112"/>
+      <c r="H8" s="112"/>
+      <c r="I8" s="112"/>
+      <c r="J8" s="25" t="s">
+        <v>50</v>
+      </c>
+      <c r="K8" s="113" t="s">
         <v>51</v>
       </c>
-      <c r="C8" s="107"/>
-      <c r="D8" s="107"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="107"/>
-      <c r="G8" s="107"/>
-      <c r="H8" s="107"/>
-      <c r="I8" s="107"/>
-      <c r="J8" s="25" t="s">
+      <c r="L8" s="114"/>
+      <c r="M8" s="114"/>
+      <c r="N8" s="115"/>
+      <c r="O8" s="116">
+        <v>4000</v>
+      </c>
+      <c r="P8" s="116"/>
+      <c r="Q8" s="116"/>
+      <c r="R8" s="116"/>
+      <c r="S8" s="116" t="s">
         <v>52</v>
       </c>
-      <c r="K8" s="108" t="s">
+      <c r="T8" s="116"/>
+      <c r="U8" s="113" t="s">
         <v>53</v>
       </c>
-      <c r="L8" s="109"/>
-      <c r="M8" s="109"/>
-      <c r="N8" s="110"/>
-      <c r="O8" s="111">
-        <v>4000</v>
-      </c>
-      <c r="P8" s="111"/>
-      <c r="Q8" s="111"/>
-      <c r="R8" s="111"/>
-      <c r="S8" s="111" t="s">
-        <v>54</v>
-      </c>
-      <c r="T8" s="111"/>
-      <c r="U8" s="108" t="s">
-        <v>55</v>
-      </c>
-      <c r="V8" s="109"/>
-      <c r="W8" s="109"/>
-      <c r="X8" s="109"/>
-      <c r="Y8" s="109"/>
+      <c r="V8" s="114"/>
+      <c r="W8" s="114"/>
+      <c r="X8" s="114"/>
+      <c r="Y8" s="114"/>
     </row>
     <row r="9" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="24"/>
     </row>
     <row r="10" spans="1:25" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="24" t="s">
-        <v>56</v>
+      <c r="A10" s="49" t="s">
+        <v>138</v>
       </c>
     </row>
     <row r="11" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A11" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="66" t="s">
+      <c r="B11" s="61" t="s">
+        <v>54</v>
+      </c>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
+      <c r="F11" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="G11" s="61"/>
+      <c r="H11" s="61"/>
+      <c r="I11" s="61"/>
+      <c r="J11" s="61"/>
+      <c r="K11" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="L11" s="61"/>
+      <c r="M11" s="61"/>
+      <c r="N11" s="61"/>
+      <c r="O11" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="P11" s="61"/>
+      <c r="Q11" s="117" t="s">
+        <v>47</v>
+      </c>
+      <c r="R11" s="117"/>
+      <c r="S11" s="117"/>
+      <c r="T11" s="117"/>
+      <c r="U11" s="61" t="s">
+        <v>56</v>
+      </c>
+      <c r="V11" s="61"/>
+      <c r="W11" s="61"/>
+      <c r="X11" s="109" t="s">
         <v>57</v>
       </c>
-      <c r="C11" s="66"/>
-      <c r="D11" s="66"/>
-      <c r="E11" s="66"/>
-      <c r="F11" s="66" t="s">
-        <v>45</v>
-      </c>
-      <c r="G11" s="66"/>
-      <c r="H11" s="66"/>
-      <c r="I11" s="66"/>
-      <c r="J11" s="66"/>
-      <c r="K11" s="66" t="s">
-        <v>58</v>
-      </c>
-      <c r="L11" s="66"/>
-      <c r="M11" s="66"/>
-      <c r="N11" s="66"/>
-      <c r="O11" s="66" t="s">
-        <v>46</v>
-      </c>
-      <c r="P11" s="66"/>
-      <c r="Q11" s="112" t="s">
-        <v>49</v>
-      </c>
-      <c r="R11" s="112"/>
-      <c r="S11" s="112"/>
-      <c r="T11" s="112"/>
-      <c r="U11" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="V11" s="66"/>
-      <c r="W11" s="66"/>
-      <c r="X11" s="104" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y11" s="105"/>
+      <c r="Y11" s="110"/>
     </row>
     <row r="12" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A12" s="11">
         <v>1</v>
       </c>
-      <c r="B12" s="111" t="s">
+      <c r="B12" s="118" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="116"/>
+      <c r="D12" s="116"/>
+      <c r="E12" s="116"/>
+      <c r="F12" s="118" t="s">
+        <v>107</v>
+      </c>
+      <c r="G12" s="116"/>
+      <c r="H12" s="116"/>
+      <c r="I12" s="116"/>
+      <c r="J12" s="116"/>
+      <c r="K12" s="119" t="s">
+        <v>125</v>
+      </c>
+      <c r="L12" s="114"/>
+      <c r="M12" s="114"/>
+      <c r="N12" s="115"/>
+      <c r="O12" s="120" t="s">
+        <v>50</v>
+      </c>
+      <c r="P12" s="121"/>
+      <c r="Q12" s="116" t="s">
+        <v>58</v>
+      </c>
+      <c r="R12" s="116"/>
+      <c r="S12" s="116"/>
+      <c r="T12" s="116"/>
+      <c r="U12" s="122" t="s">
+        <v>60</v>
+      </c>
+      <c r="V12" s="116"/>
+      <c r="W12" s="116"/>
+      <c r="X12" s="116" t="s">
         <v>61</v>
       </c>
-      <c r="C12" s="111"/>
-      <c r="D12" s="111"/>
-      <c r="E12" s="111"/>
-      <c r="F12" s="111" t="s">
-        <v>62</v>
-      </c>
-      <c r="G12" s="111"/>
-      <c r="H12" s="111"/>
-      <c r="I12" s="111"/>
-      <c r="J12" s="111"/>
-      <c r="K12" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="L12" s="109"/>
-      <c r="M12" s="109"/>
-      <c r="N12" s="110"/>
-      <c r="O12" s="113" t="s">
-        <v>52</v>
-      </c>
-      <c r="P12" s="114"/>
-      <c r="Q12" s="111" t="s">
-        <v>61</v>
-      </c>
-      <c r="R12" s="111"/>
-      <c r="S12" s="111"/>
-      <c r="T12" s="111"/>
-      <c r="U12" s="115" t="s">
-        <v>64</v>
-      </c>
-      <c r="V12" s="111"/>
-      <c r="W12" s="111"/>
-      <c r="X12" s="111" t="s">
-        <v>65</v>
-      </c>
-      <c r="Y12" s="111"/>
+      <c r="Y12" s="116"/>
     </row>
     <row r="13" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A13" s="11">
         <v>2</v>
       </c>
-      <c r="B13" s="111" t="s">
-        <v>66</v>
-      </c>
-      <c r="C13" s="111"/>
-      <c r="D13" s="111"/>
-      <c r="E13" s="111"/>
-      <c r="F13" s="116" t="s">
-        <v>67</v>
-      </c>
-      <c r="G13" s="116"/>
-      <c r="H13" s="116"/>
-      <c r="I13" s="116"/>
-      <c r="J13" s="116"/>
-      <c r="K13" s="108" t="s">
+      <c r="B13" s="118" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="116"/>
+      <c r="D13" s="116"/>
+      <c r="E13" s="116"/>
+      <c r="F13" s="123" t="s">
+        <v>108</v>
+      </c>
+      <c r="G13" s="124"/>
+      <c r="H13" s="124"/>
+      <c r="I13" s="124"/>
+      <c r="J13" s="124"/>
+      <c r="K13" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="L13" s="114"/>
+      <c r="M13" s="114"/>
+      <c r="N13" s="115"/>
+      <c r="O13" s="120" t="s">
+        <v>50</v>
+      </c>
+      <c r="P13" s="121"/>
+      <c r="Q13" s="125" t="s">
+        <v>62</v>
+      </c>
+      <c r="R13" s="116"/>
+      <c r="S13" s="116"/>
+      <c r="T13" s="116"/>
+      <c r="U13" s="122" t="s">
         <v>63</v>
       </c>
-      <c r="L13" s="109"/>
-      <c r="M13" s="109"/>
-      <c r="N13" s="110"/>
-      <c r="O13" s="113" t="s">
-        <v>52</v>
-      </c>
-      <c r="P13" s="114"/>
-      <c r="Q13" s="117" t="s">
-        <v>68</v>
-      </c>
-      <c r="R13" s="111"/>
-      <c r="S13" s="111"/>
-      <c r="T13" s="111"/>
-      <c r="U13" s="115" t="s">
-        <v>69</v>
-      </c>
-      <c r="V13" s="111"/>
-      <c r="W13" s="111"/>
-      <c r="X13" s="111" t="s">
-        <v>70</v>
-      </c>
-      <c r="Y13" s="111"/>
+      <c r="V13" s="116"/>
+      <c r="W13" s="116"/>
+      <c r="X13" s="118" t="s">
+        <v>135</v>
+      </c>
+      <c r="Y13" s="116"/>
     </row>
     <row r="14" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A14" s="11">
         <v>3</v>
       </c>
-      <c r="B14" s="117" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="111"/>
-      <c r="D14" s="111"/>
-      <c r="E14" s="111"/>
-      <c r="F14" s="111" t="s">
-        <v>72</v>
-      </c>
-      <c r="G14" s="111"/>
-      <c r="H14" s="111"/>
-      <c r="I14" s="111"/>
-      <c r="J14" s="111"/>
-      <c r="K14" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="L14" s="109"/>
-      <c r="M14" s="109"/>
-      <c r="N14" s="110"/>
-      <c r="O14" s="113" t="s">
-        <v>52</v>
-      </c>
-      <c r="P14" s="114"/>
-      <c r="Q14" s="111" t="s">
-        <v>73</v>
-      </c>
-      <c r="R14" s="111"/>
-      <c r="S14" s="111"/>
-      <c r="T14" s="111"/>
-      <c r="U14" s="115"/>
-      <c r="V14" s="111"/>
-      <c r="W14" s="111"/>
-      <c r="X14" s="118" t="s">
-        <v>74</v>
-      </c>
-      <c r="Y14" s="119"/>
+      <c r="B14" s="126" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="116"/>
+      <c r="D14" s="116"/>
+      <c r="E14" s="116"/>
+      <c r="F14" s="118" t="s">
+        <v>109</v>
+      </c>
+      <c r="G14" s="116"/>
+      <c r="H14" s="116"/>
+      <c r="I14" s="116"/>
+      <c r="J14" s="116"/>
+      <c r="K14" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="L14" s="114"/>
+      <c r="M14" s="114"/>
+      <c r="N14" s="115"/>
+      <c r="O14" s="120" t="s">
+        <v>50</v>
+      </c>
+      <c r="P14" s="121"/>
+      <c r="Q14" s="116" t="s">
+        <v>64</v>
+      </c>
+      <c r="R14" s="116"/>
+      <c r="S14" s="116"/>
+      <c r="T14" s="116"/>
+      <c r="U14" s="122"/>
+      <c r="V14" s="116"/>
+      <c r="W14" s="116"/>
+      <c r="X14" s="127" t="s">
+        <v>65</v>
+      </c>
+      <c r="Y14" s="128"/>
     </row>
     <row r="15" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A15" s="11">
         <v>4</v>
       </c>
-      <c r="B15" s="111" t="s">
-        <v>75</v>
-      </c>
-      <c r="C15" s="111"/>
-      <c r="D15" s="111"/>
-      <c r="E15" s="111"/>
-      <c r="F15" s="111" t="s">
-        <v>76</v>
-      </c>
-      <c r="G15" s="111"/>
-      <c r="H15" s="111"/>
-      <c r="I15" s="111"/>
-      <c r="J15" s="111"/>
-      <c r="K15" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="L15" s="109"/>
-      <c r="M15" s="109"/>
-      <c r="N15" s="110"/>
-      <c r="O15" s="113" t="s">
-        <v>52</v>
-      </c>
-      <c r="P15" s="114"/>
-      <c r="Q15" s="111" t="s">
-        <v>75</v>
-      </c>
-      <c r="R15" s="111"/>
-      <c r="S15" s="111"/>
-      <c r="T15" s="111"/>
-      <c r="U15" s="111"/>
-      <c r="V15" s="111"/>
-      <c r="W15" s="111"/>
-      <c r="X15" s="108" t="s">
-        <v>77</v>
-      </c>
-      <c r="Y15" s="110"/>
+      <c r="B15" s="118" t="s">
+        <v>116</v>
+      </c>
+      <c r="C15" s="116"/>
+      <c r="D15" s="116"/>
+      <c r="E15" s="116"/>
+      <c r="F15" s="118" t="s">
+        <v>110</v>
+      </c>
+      <c r="G15" s="116"/>
+      <c r="H15" s="116"/>
+      <c r="I15" s="116"/>
+      <c r="J15" s="116"/>
+      <c r="K15" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="L15" s="114"/>
+      <c r="M15" s="114"/>
+      <c r="N15" s="115"/>
+      <c r="O15" s="120" t="s">
+        <v>50</v>
+      </c>
+      <c r="P15" s="121"/>
+      <c r="Q15" s="116" t="s">
+        <v>66</v>
+      </c>
+      <c r="R15" s="116"/>
+      <c r="S15" s="116"/>
+      <c r="T15" s="116"/>
+      <c r="U15" s="116"/>
+      <c r="V15" s="116"/>
+      <c r="W15" s="116"/>
+      <c r="X15" s="113" t="s">
+        <v>67</v>
+      </c>
+      <c r="Y15" s="115"/>
     </row>
     <row r="16" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A16" s="11">
         <v>5</v>
       </c>
-      <c r="B16" s="111" t="s">
-        <v>78</v>
-      </c>
-      <c r="C16" s="111"/>
-      <c r="D16" s="111"/>
-      <c r="E16" s="111"/>
-      <c r="F16" s="111" t="s">
-        <v>79</v>
-      </c>
-      <c r="G16" s="111"/>
-      <c r="H16" s="111"/>
-      <c r="I16" s="111"/>
-      <c r="J16" s="111"/>
-      <c r="K16" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="L16" s="109"/>
-      <c r="M16" s="109"/>
-      <c r="N16" s="110"/>
-      <c r="O16" s="113" t="s">
-        <v>52</v>
-      </c>
-      <c r="P16" s="114"/>
-      <c r="Q16" s="111" t="s">
-        <v>80</v>
-      </c>
-      <c r="R16" s="111"/>
-      <c r="S16" s="111"/>
-      <c r="T16" s="111"/>
-      <c r="U16" s="111"/>
-      <c r="V16" s="111"/>
-      <c r="W16" s="111"/>
-      <c r="X16" s="108" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y16" s="110"/>
+      <c r="B16" s="118" t="s">
+        <v>117</v>
+      </c>
+      <c r="C16" s="116"/>
+      <c r="D16" s="116"/>
+      <c r="E16" s="116"/>
+      <c r="F16" s="118" t="s">
+        <v>111</v>
+      </c>
+      <c r="G16" s="116"/>
+      <c r="H16" s="116"/>
+      <c r="I16" s="116"/>
+      <c r="J16" s="116"/>
+      <c r="K16" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="L16" s="114"/>
+      <c r="M16" s="114"/>
+      <c r="N16" s="115"/>
+      <c r="O16" s="120" t="s">
+        <v>50</v>
+      </c>
+      <c r="P16" s="121"/>
+      <c r="Q16" s="116" t="s">
+        <v>68</v>
+      </c>
+      <c r="R16" s="116"/>
+      <c r="S16" s="116"/>
+      <c r="T16" s="116"/>
+      <c r="U16" s="116"/>
+      <c r="V16" s="116"/>
+      <c r="W16" s="116"/>
+      <c r="X16" s="113" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y16" s="115"/>
     </row>
     <row r="17" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A17" s="11">
         <v>6</v>
       </c>
-      <c r="B17" s="111" t="s">
-        <v>82</v>
-      </c>
-      <c r="C17" s="111"/>
-      <c r="D17" s="111"/>
-      <c r="E17" s="111"/>
-      <c r="F17" s="111" t="s">
-        <v>83</v>
-      </c>
-      <c r="G17" s="111"/>
-      <c r="H17" s="111"/>
-      <c r="I17" s="111"/>
-      <c r="J17" s="111"/>
-      <c r="K17" s="108" t="s">
-        <v>84</v>
-      </c>
-      <c r="L17" s="109"/>
-      <c r="M17" s="109"/>
-      <c r="N17" s="110"/>
-      <c r="O17" s="113" t="s">
-        <v>52</v>
-      </c>
-      <c r="P17" s="114"/>
-      <c r="Q17" s="120" t="s">
-        <v>85</v>
-      </c>
-      <c r="R17" s="109"/>
-      <c r="S17" s="109"/>
-      <c r="T17" s="109"/>
-      <c r="U17" s="109"/>
-      <c r="V17" s="109"/>
-      <c r="W17" s="110"/>
-      <c r="X17" s="108" t="s">
-        <v>86</v>
-      </c>
-      <c r="Y17" s="110"/>
+      <c r="B17" s="118" t="s">
+        <v>118</v>
+      </c>
+      <c r="C17" s="116"/>
+      <c r="D17" s="116"/>
+      <c r="E17" s="116"/>
+      <c r="F17" s="118" t="s">
+        <v>112</v>
+      </c>
+      <c r="G17" s="116"/>
+      <c r="H17" s="116"/>
+      <c r="I17" s="116"/>
+      <c r="J17" s="116"/>
+      <c r="K17" s="113" t="s">
+        <v>70</v>
+      </c>
+      <c r="L17" s="114"/>
+      <c r="M17" s="114"/>
+      <c r="N17" s="115"/>
+      <c r="O17" s="120" t="s">
+        <v>50</v>
+      </c>
+      <c r="P17" s="121"/>
+      <c r="Q17" s="129" t="s">
+        <v>71</v>
+      </c>
+      <c r="R17" s="114"/>
+      <c r="S17" s="114"/>
+      <c r="T17" s="114"/>
+      <c r="U17" s="114"/>
+      <c r="V17" s="114"/>
+      <c r="W17" s="115"/>
+      <c r="X17" s="113" t="s">
+        <v>72</v>
+      </c>
+      <c r="Y17" s="115"/>
     </row>
     <row r="18" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A18" s="26"/>
@@ -3757,8 +4205,8 @@
       <c r="Y18" s="27"/>
     </row>
     <row r="19" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
-      <c r="A19" s="26" t="s">
-        <v>87</v>
+      <c r="A19" s="48" t="s">
+        <v>137</v>
       </c>
       <c r="B19" s="27"/>
       <c r="C19" s="27"/>
@@ -3789,298 +4237,296 @@
       <c r="A20" s="21" t="s">
         <v>30</v>
       </c>
-      <c r="B20" s="66" t="s">
+      <c r="B20" s="61" t="s">
+        <v>54</v>
+      </c>
+      <c r="C20" s="61"/>
+      <c r="D20" s="61"/>
+      <c r="E20" s="61"/>
+      <c r="F20" s="61" t="s">
+        <v>43</v>
+      </c>
+      <c r="G20" s="61"/>
+      <c r="H20" s="61"/>
+      <c r="I20" s="61"/>
+      <c r="J20" s="61"/>
+      <c r="K20" s="61" t="s">
+        <v>55</v>
+      </c>
+      <c r="L20" s="61"/>
+      <c r="M20" s="61"/>
+      <c r="N20" s="61"/>
+      <c r="O20" s="61" t="s">
+        <v>44</v>
+      </c>
+      <c r="P20" s="61"/>
+      <c r="Q20" s="117" t="s">
+        <v>47</v>
+      </c>
+      <c r="R20" s="117"/>
+      <c r="S20" s="117"/>
+      <c r="T20" s="117"/>
+      <c r="U20" s="61" t="s">
+        <v>56</v>
+      </c>
+      <c r="V20" s="61"/>
+      <c r="W20" s="61"/>
+      <c r="X20" s="109" t="s">
         <v>57</v>
       </c>
-      <c r="C20" s="66"/>
-      <c r="D20" s="66"/>
-      <c r="E20" s="66"/>
-      <c r="F20" s="66" t="s">
-        <v>45</v>
-      </c>
-      <c r="G20" s="66"/>
-      <c r="H20" s="66"/>
-      <c r="I20" s="66"/>
-      <c r="J20" s="66"/>
-      <c r="K20" s="66" t="s">
-        <v>58</v>
-      </c>
-      <c r="L20" s="66"/>
-      <c r="M20" s="66"/>
-      <c r="N20" s="66"/>
-      <c r="O20" s="66" t="s">
-        <v>46</v>
-      </c>
-      <c r="P20" s="66"/>
-      <c r="Q20" s="112" t="s">
-        <v>49</v>
-      </c>
-      <c r="R20" s="112"/>
-      <c r="S20" s="112"/>
-      <c r="T20" s="112"/>
-      <c r="U20" s="66" t="s">
-        <v>59</v>
-      </c>
-      <c r="V20" s="66"/>
-      <c r="W20" s="66"/>
-      <c r="X20" s="104" t="s">
-        <v>60</v>
-      </c>
-      <c r="Y20" s="105"/>
+      <c r="Y20" s="110"/>
     </row>
     <row r="21" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A21" s="11">
         <v>1</v>
       </c>
-      <c r="B21" s="111" t="s">
-        <v>88</v>
-      </c>
-      <c r="C21" s="111"/>
-      <c r="D21" s="111"/>
-      <c r="E21" s="111"/>
-      <c r="F21" s="116" t="s">
-        <v>89</v>
-      </c>
-      <c r="G21" s="116"/>
-      <c r="H21" s="116"/>
-      <c r="I21" s="116"/>
-      <c r="J21" s="116"/>
-      <c r="K21" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="L21" s="109"/>
-      <c r="M21" s="109"/>
-      <c r="N21" s="110"/>
-      <c r="O21" s="113" t="s">
-        <v>52</v>
-      </c>
-      <c r="P21" s="114"/>
-      <c r="Q21" s="111" t="s">
-        <v>90</v>
-      </c>
-      <c r="R21" s="111"/>
-      <c r="S21" s="111"/>
-      <c r="T21" s="111"/>
-      <c r="U21" s="111" t="s">
-        <v>86</v>
-      </c>
-      <c r="V21" s="111"/>
-      <c r="W21" s="111"/>
-      <c r="X21" s="121">
+      <c r="B21" s="118" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" s="116"/>
+      <c r="D21" s="116"/>
+      <c r="E21" s="116"/>
+      <c r="F21" s="123" t="s">
+        <v>126</v>
+      </c>
+      <c r="G21" s="124"/>
+      <c r="H21" s="124"/>
+      <c r="I21" s="124"/>
+      <c r="J21" s="124"/>
+      <c r="K21" s="113" t="s">
+        <v>74</v>
+      </c>
+      <c r="L21" s="114"/>
+      <c r="M21" s="114"/>
+      <c r="N21" s="115"/>
+      <c r="O21" s="120"/>
+      <c r="P21" s="121"/>
+      <c r="Q21" s="116" t="s">
+        <v>73</v>
+      </c>
+      <c r="R21" s="116"/>
+      <c r="S21" s="116"/>
+      <c r="T21" s="116"/>
+      <c r="U21" s="116" t="s">
+        <v>72</v>
+      </c>
+      <c r="V21" s="116"/>
+      <c r="W21" s="116"/>
+      <c r="X21" s="130">
         <v>5</v>
       </c>
-      <c r="Y21" s="122"/>
+      <c r="Y21" s="131"/>
     </row>
     <row r="22" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A22" s="11">
         <v>2</v>
       </c>
-      <c r="B22" s="111" t="s">
-        <v>91</v>
-      </c>
-      <c r="C22" s="111"/>
-      <c r="D22" s="111"/>
-      <c r="E22" s="111"/>
-      <c r="F22" s="111" t="s">
-        <v>92</v>
-      </c>
-      <c r="G22" s="111"/>
-      <c r="H22" s="111"/>
-      <c r="I22" s="111"/>
-      <c r="J22" s="111"/>
-      <c r="K22" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="L22" s="109"/>
-      <c r="M22" s="109"/>
-      <c r="N22" s="110"/>
-      <c r="O22" s="113" t="s">
-        <v>52</v>
-      </c>
-      <c r="P22" s="114"/>
-      <c r="Q22" s="117" t="s">
-        <v>94</v>
-      </c>
-      <c r="R22" s="111"/>
-      <c r="S22" s="111"/>
-      <c r="T22" s="111"/>
-      <c r="U22" s="111" t="s">
-        <v>86</v>
-      </c>
-      <c r="V22" s="111"/>
-      <c r="W22" s="111"/>
-      <c r="X22" s="111">
+      <c r="B22" s="118" t="s">
+        <v>120</v>
+      </c>
+      <c r="C22" s="116"/>
+      <c r="D22" s="116"/>
+      <c r="E22" s="116"/>
+      <c r="F22" s="118" t="s">
+        <v>127</v>
+      </c>
+      <c r="G22" s="116"/>
+      <c r="H22" s="116"/>
+      <c r="I22" s="116"/>
+      <c r="J22" s="116"/>
+      <c r="K22" s="113" t="s">
+        <v>74</v>
+      </c>
+      <c r="L22" s="114"/>
+      <c r="M22" s="114"/>
+      <c r="N22" s="115"/>
+      <c r="O22" s="120" t="s">
+        <v>50</v>
+      </c>
+      <c r="P22" s="121"/>
+      <c r="Q22" s="125" t="s">
+        <v>75</v>
+      </c>
+      <c r="R22" s="116"/>
+      <c r="S22" s="116"/>
+      <c r="T22" s="116"/>
+      <c r="U22" s="116" t="s">
+        <v>72</v>
+      </c>
+      <c r="V22" s="116"/>
+      <c r="W22" s="116"/>
+      <c r="X22" s="116">
         <v>2</v>
       </c>
-      <c r="Y22" s="111"/>
+      <c r="Y22" s="116"/>
     </row>
     <row r="23" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A23" s="11">
         <v>3</v>
       </c>
-      <c r="B23" s="111" t="s">
-        <v>95</v>
-      </c>
-      <c r="C23" s="111"/>
-      <c r="D23" s="111"/>
-      <c r="E23" s="111"/>
-      <c r="F23" s="111" t="s">
-        <v>96</v>
-      </c>
-      <c r="G23" s="111"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="111"/>
-      <c r="J23" s="111"/>
-      <c r="K23" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="L23" s="109"/>
-      <c r="M23" s="109"/>
-      <c r="N23" s="110"/>
-      <c r="O23" s="113" t="s">
-        <v>52</v>
-      </c>
-      <c r="P23" s="114"/>
-      <c r="Q23" s="117" t="s">
-        <v>94</v>
-      </c>
-      <c r="R23" s="111"/>
-      <c r="S23" s="111"/>
-      <c r="T23" s="111"/>
-      <c r="U23" s="111" t="s">
-        <v>86</v>
-      </c>
-      <c r="V23" s="111"/>
-      <c r="W23" s="111"/>
-      <c r="X23" s="121">
+      <c r="B23" s="118" t="s">
+        <v>121</v>
+      </c>
+      <c r="C23" s="116"/>
+      <c r="D23" s="116"/>
+      <c r="E23" s="116"/>
+      <c r="F23" s="118" t="s">
+        <v>128</v>
+      </c>
+      <c r="G23" s="116"/>
+      <c r="H23" s="116"/>
+      <c r="I23" s="116"/>
+      <c r="J23" s="116"/>
+      <c r="K23" s="113" t="s">
+        <v>74</v>
+      </c>
+      <c r="L23" s="114"/>
+      <c r="M23" s="114"/>
+      <c r="N23" s="115"/>
+      <c r="O23" s="120" t="s">
+        <v>50</v>
+      </c>
+      <c r="P23" s="121"/>
+      <c r="Q23" s="125" t="s">
+        <v>75</v>
+      </c>
+      <c r="R23" s="116"/>
+      <c r="S23" s="116"/>
+      <c r="T23" s="116"/>
+      <c r="U23" s="116" t="s">
+        <v>72</v>
+      </c>
+      <c r="V23" s="116"/>
+      <c r="W23" s="116"/>
+      <c r="X23" s="130">
         <v>1</v>
       </c>
-      <c r="Y23" s="122"/>
+      <c r="Y23" s="131"/>
     </row>
     <row r="24" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A24" s="11">
         <v>4</v>
       </c>
-      <c r="B24" s="111" t="s">
-        <v>97</v>
-      </c>
-      <c r="C24" s="111"/>
-      <c r="D24" s="111"/>
-      <c r="E24" s="111"/>
-      <c r="F24" s="116" t="s">
-        <v>98</v>
-      </c>
-      <c r="G24" s="116"/>
-      <c r="H24" s="116"/>
-      <c r="I24" s="116"/>
-      <c r="J24" s="116"/>
-      <c r="K24" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="L24" s="109"/>
-      <c r="M24" s="109"/>
-      <c r="N24" s="110"/>
-      <c r="O24" s="113" t="s">
-        <v>52</v>
-      </c>
-      <c r="P24" s="114"/>
-      <c r="Q24" s="111" t="s">
-        <v>97</v>
-      </c>
-      <c r="R24" s="111"/>
-      <c r="S24" s="111"/>
-      <c r="T24" s="111"/>
-      <c r="U24" s="111" t="s">
-        <v>86</v>
-      </c>
-      <c r="V24" s="111"/>
-      <c r="W24" s="111"/>
-      <c r="X24" s="111" t="s">
-        <v>99</v>
-      </c>
-      <c r="Y24" s="111"/>
+      <c r="B24" s="118" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="116"/>
+      <c r="D24" s="116"/>
+      <c r="E24" s="116"/>
+      <c r="F24" s="123" t="s">
+        <v>129</v>
+      </c>
+      <c r="G24" s="124"/>
+      <c r="H24" s="124"/>
+      <c r="I24" s="124"/>
+      <c r="J24" s="124"/>
+      <c r="K24" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="L24" s="114"/>
+      <c r="M24" s="114"/>
+      <c r="N24" s="115"/>
+      <c r="O24" s="120" t="s">
+        <v>50</v>
+      </c>
+      <c r="P24" s="121"/>
+      <c r="Q24" s="116" t="s">
+        <v>76</v>
+      </c>
+      <c r="R24" s="116"/>
+      <c r="S24" s="116"/>
+      <c r="T24" s="116"/>
+      <c r="U24" s="116" t="s">
+        <v>72</v>
+      </c>
+      <c r="V24" s="116"/>
+      <c r="W24" s="116"/>
+      <c r="X24" s="116" t="s">
+        <v>77</v>
+      </c>
+      <c r="Y24" s="116"/>
     </row>
     <row r="25" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A25" s="11">
         <v>5</v>
       </c>
-      <c r="B25" s="111" t="s">
-        <v>100</v>
-      </c>
-      <c r="C25" s="111"/>
-      <c r="D25" s="111"/>
-      <c r="E25" s="111"/>
-      <c r="F25" s="111" t="s">
-        <v>101</v>
-      </c>
-      <c r="G25" s="111"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="111"/>
-      <c r="J25" s="111"/>
-      <c r="K25" s="108" t="s">
-        <v>93</v>
-      </c>
-      <c r="L25" s="109"/>
-      <c r="M25" s="109"/>
-      <c r="N25" s="110"/>
-      <c r="O25" s="113" t="s">
-        <v>52</v>
-      </c>
-      <c r="P25" s="114"/>
-      <c r="Q25" s="111"/>
-      <c r="R25" s="111"/>
-      <c r="S25" s="111"/>
-      <c r="T25" s="111"/>
-      <c r="U25" s="111" t="s">
-        <v>86</v>
-      </c>
-      <c r="V25" s="111"/>
-      <c r="W25" s="111"/>
-      <c r="X25" s="118">
+      <c r="B25" s="118" t="s">
+        <v>123</v>
+      </c>
+      <c r="C25" s="116"/>
+      <c r="D25" s="116"/>
+      <c r="E25" s="116"/>
+      <c r="F25" s="118" t="s">
+        <v>130</v>
+      </c>
+      <c r="G25" s="116"/>
+      <c r="H25" s="116"/>
+      <c r="I25" s="116"/>
+      <c r="J25" s="116"/>
+      <c r="K25" s="113" t="s">
+        <v>74</v>
+      </c>
+      <c r="L25" s="114"/>
+      <c r="M25" s="114"/>
+      <c r="N25" s="115"/>
+      <c r="O25" s="120" t="s">
+        <v>50</v>
+      </c>
+      <c r="P25" s="121"/>
+      <c r="Q25" s="116"/>
+      <c r="R25" s="116"/>
+      <c r="S25" s="116"/>
+      <c r="T25" s="116"/>
+      <c r="U25" s="116" t="s">
+        <v>72</v>
+      </c>
+      <c r="V25" s="116"/>
+      <c r="W25" s="116"/>
+      <c r="X25" s="127">
         <v>20</v>
       </c>
-      <c r="Y25" s="119"/>
+      <c r="Y25" s="128"/>
     </row>
     <row r="26" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A26" s="11">
         <v>6</v>
       </c>
-      <c r="B26" s="111" t="s">
-        <v>102</v>
-      </c>
-      <c r="C26" s="111"/>
-      <c r="D26" s="111"/>
-      <c r="E26" s="111"/>
-      <c r="F26" s="111" t="s">
-        <v>103</v>
-      </c>
-      <c r="G26" s="111"/>
-      <c r="H26" s="111"/>
-      <c r="I26" s="111"/>
-      <c r="J26" s="111"/>
-      <c r="K26" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="L26" s="109"/>
-      <c r="M26" s="109"/>
-      <c r="N26" s="110"/>
-      <c r="O26" s="113"/>
-      <c r="P26" s="114"/>
-      <c r="Q26" s="111" t="s">
-        <v>104</v>
-      </c>
-      <c r="R26" s="111"/>
-      <c r="S26" s="111"/>
-      <c r="T26" s="111"/>
-      <c r="U26" s="111" t="s">
-        <v>86</v>
-      </c>
-      <c r="V26" s="111"/>
-      <c r="W26" s="111"/>
-      <c r="X26" s="108" t="s">
-        <v>105</v>
-      </c>
-      <c r="Y26" s="110"/>
+      <c r="B26" s="118" t="s">
+        <v>124</v>
+      </c>
+      <c r="C26" s="116"/>
+      <c r="D26" s="116"/>
+      <c r="E26" s="116"/>
+      <c r="F26" s="118" t="s">
+        <v>131</v>
+      </c>
+      <c r="G26" s="116"/>
+      <c r="H26" s="116"/>
+      <c r="I26" s="116"/>
+      <c r="J26" s="116"/>
+      <c r="K26" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="L26" s="114"/>
+      <c r="M26" s="114"/>
+      <c r="N26" s="115"/>
+      <c r="O26" s="120"/>
+      <c r="P26" s="121"/>
+      <c r="Q26" s="116" t="s">
+        <v>78</v>
+      </c>
+      <c r="R26" s="116"/>
+      <c r="S26" s="116"/>
+      <c r="T26" s="116"/>
+      <c r="U26" s="116" t="s">
+        <v>72</v>
+      </c>
+      <c r="V26" s="116"/>
+      <c r="W26" s="116"/>
+      <c r="X26" s="113" t="s">
+        <v>79</v>
+      </c>
+      <c r="Y26" s="115"/>
     </row>
     <row r="27" spans="1:25" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A27" s="26"/>
@@ -4223,7 +4669,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:V24"/>
+  <dimension ref="A1:V25"/>
   <sheetFormatPr defaultColWidth="3.6640625" defaultRowHeight="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="6.44140625" style="4" customWidth="1"/>
@@ -4244,162 +4690,162 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="77" t="s">
-        <v>106</v>
-      </c>
-      <c r="B1" s="78"/>
-      <c r="C1" s="78"/>
-      <c r="D1" s="78"/>
-      <c r="E1" s="78"/>
-      <c r="F1" s="78"/>
-      <c r="G1" s="78"/>
-      <c r="H1" s="78"/>
-      <c r="I1" s="86" t="s">
+      <c r="A1" s="81" t="s">
+        <v>80</v>
+      </c>
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
+      <c r="F1" s="82"/>
+      <c r="G1" s="82"/>
+      <c r="H1" s="82"/>
+      <c r="I1" s="90" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="87"/>
-      <c r="K1" s="87"/>
-      <c r="L1" s="87"/>
-      <c r="M1" s="92" t="s">
+      <c r="J1" s="91"/>
+      <c r="K1" s="91"/>
+      <c r="L1" s="91"/>
+      <c r="M1" s="96" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="93"/>
-      <c r="O1" s="93"/>
-      <c r="P1" s="93"/>
-      <c r="Q1" s="66" t="s">
+      <c r="N1" s="97"/>
+      <c r="O1" s="97"/>
+      <c r="P1" s="97"/>
+      <c r="Q1" s="61" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="96" t="s">
+      <c r="R1" s="100" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="97"/>
-      <c r="T1" s="71" t="s">
+      <c r="S1" s="101"/>
+      <c r="T1" s="75" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="67" t="s">
+      <c r="U1" s="62" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="129"/>
+      <c r="V1" s="139"/>
     </row>
     <row r="2" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="80"/>
-      <c r="B2" s="81"/>
-      <c r="C2" s="81"/>
-      <c r="D2" s="81"/>
-      <c r="E2" s="81"/>
-      <c r="F2" s="81"/>
-      <c r="G2" s="81"/>
-      <c r="H2" s="81"/>
-      <c r="I2" s="89"/>
-      <c r="J2" s="90"/>
-      <c r="K2" s="90"/>
-      <c r="L2" s="90"/>
-      <c r="M2" s="94"/>
-      <c r="N2" s="95"/>
-      <c r="O2" s="95"/>
-      <c r="P2" s="95"/>
-      <c r="Q2" s="66"/>
-      <c r="R2" s="99"/>
-      <c r="S2" s="100"/>
-      <c r="T2" s="74"/>
-      <c r="U2" s="69"/>
-      <c r="V2" s="130"/>
+      <c r="A2" s="84"/>
+      <c r="B2" s="85"/>
+      <c r="C2" s="85"/>
+      <c r="D2" s="85"/>
+      <c r="E2" s="85"/>
+      <c r="F2" s="85"/>
+      <c r="G2" s="85"/>
+      <c r="H2" s="85"/>
+      <c r="I2" s="93"/>
+      <c r="J2" s="94"/>
+      <c r="K2" s="94"/>
+      <c r="L2" s="94"/>
+      <c r="M2" s="98"/>
+      <c r="N2" s="99"/>
+      <c r="O2" s="99"/>
+      <c r="P2" s="99"/>
+      <c r="Q2" s="61"/>
+      <c r="R2" s="103"/>
+      <c r="S2" s="104"/>
+      <c r="T2" s="78"/>
+      <c r="U2" s="64"/>
+      <c r="V2" s="140"/>
     </row>
     <row r="3" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="80"/>
-      <c r="B3" s="81"/>
-      <c r="C3" s="81"/>
-      <c r="D3" s="81"/>
-      <c r="E3" s="81"/>
-      <c r="F3" s="81"/>
-      <c r="G3" s="81"/>
-      <c r="H3" s="81"/>
-      <c r="I3" s="86" t="s">
+      <c r="A3" s="84"/>
+      <c r="B3" s="85"/>
+      <c r="C3" s="85"/>
+      <c r="D3" s="85"/>
+      <c r="E3" s="85"/>
+      <c r="F3" s="85"/>
+      <c r="G3" s="85"/>
+      <c r="H3" s="85"/>
+      <c r="I3" s="90" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="87"/>
-      <c r="K3" s="87"/>
-      <c r="L3" s="87"/>
-      <c r="M3" s="92" t="s">
+      <c r="J3" s="91"/>
+      <c r="K3" s="91"/>
+      <c r="L3" s="91"/>
+      <c r="M3" s="96" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="93"/>
-      <c r="O3" s="93"/>
-      <c r="P3" s="93"/>
-      <c r="Q3" s="66" t="s">
+      <c r="N3" s="97"/>
+      <c r="O3" s="97"/>
+      <c r="P3" s="97"/>
+      <c r="Q3" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="96" t="s">
+      <c r="R3" s="100" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="97"/>
-      <c r="T3" s="66" t="s">
+      <c r="S3" s="101"/>
+      <c r="T3" s="61" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="67" t="s">
+      <c r="U3" s="62" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="129"/>
+      <c r="V3" s="139"/>
     </row>
     <row r="4" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="83"/>
-      <c r="B4" s="84"/>
-      <c r="C4" s="84"/>
-      <c r="D4" s="84"/>
-      <c r="E4" s="84"/>
-      <c r="F4" s="84"/>
-      <c r="G4" s="84"/>
-      <c r="H4" s="84"/>
-      <c r="I4" s="89"/>
-      <c r="J4" s="90"/>
-      <c r="K4" s="90"/>
-      <c r="L4" s="90"/>
-      <c r="M4" s="94"/>
-      <c r="N4" s="95"/>
-      <c r="O4" s="95"/>
-      <c r="P4" s="95"/>
-      <c r="Q4" s="66"/>
-      <c r="R4" s="99"/>
-      <c r="S4" s="100"/>
-      <c r="T4" s="66"/>
-      <c r="U4" s="69"/>
-      <c r="V4" s="130"/>
+      <c r="A4" s="87"/>
+      <c r="B4" s="88"/>
+      <c r="C4" s="88"/>
+      <c r="D4" s="88"/>
+      <c r="E4" s="88"/>
+      <c r="F4" s="88"/>
+      <c r="G4" s="88"/>
+      <c r="H4" s="88"/>
+      <c r="I4" s="93"/>
+      <c r="J4" s="94"/>
+      <c r="K4" s="94"/>
+      <c r="L4" s="94"/>
+      <c r="M4" s="98"/>
+      <c r="N4" s="99"/>
+      <c r="O4" s="99"/>
+      <c r="P4" s="99"/>
+      <c r="Q4" s="61"/>
+      <c r="R4" s="103"/>
+      <c r="S4" s="104"/>
+      <c r="T4" s="61"/>
+      <c r="U4" s="64"/>
+      <c r="V4" s="140"/>
     </row>
     <row r="5" spans="1:22" s="1" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="102" t="s">
+      <c r="A5" s="106" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" s="106"/>
+      <c r="C5" s="106"/>
+      <c r="D5" s="106"/>
+      <c r="E5" s="108" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" s="108"/>
+      <c r="G5" s="108"/>
+      <c r="H5" s="108"/>
+      <c r="I5" s="106" t="s">
+        <v>40</v>
+      </c>
+      <c r="J5" s="106"/>
+      <c r="K5" s="106"/>
+      <c r="L5" s="106"/>
+      <c r="M5" s="108" t="s">
+        <v>22</v>
+      </c>
+      <c r="N5" s="108"/>
+      <c r="O5" s="108"/>
+      <c r="P5" s="108"/>
+      <c r="Q5" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" s="102"/>
-      <c r="C5" s="102"/>
-      <c r="D5" s="102"/>
-      <c r="E5" s="103" t="s">
-        <v>24</v>
-      </c>
-      <c r="F5" s="103"/>
-      <c r="G5" s="103"/>
-      <c r="H5" s="103"/>
-      <c r="I5" s="102" t="s">
-        <v>42</v>
-      </c>
-      <c r="J5" s="102"/>
-      <c r="K5" s="102"/>
-      <c r="L5" s="102"/>
-      <c r="M5" s="103" t="s">
-        <v>22</v>
-      </c>
-      <c r="N5" s="103"/>
-      <c r="O5" s="103"/>
-      <c r="P5" s="103"/>
-      <c r="Q5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="R5" s="103" t="s">
+      <c r="R5" s="108" t="s">
         <v>28</v>
       </c>
-      <c r="S5" s="103"/>
-      <c r="T5" s="103"/>
-      <c r="U5" s="103"/>
-      <c r="V5" s="103"/>
+      <c r="S5" s="108"/>
+      <c r="T5" s="108"/>
+      <c r="U5" s="108"/>
+      <c r="V5" s="108"/>
     </row>
     <row r="6" spans="1:22" s="2" customFormat="1" ht="19.5" x14ac:dyDescent="0.4">
       <c r="A6" s="6"/>
@@ -4427,7 +4873,7 @@
     </row>
     <row r="7" spans="1:22" s="2" customFormat="1" ht="16.5" x14ac:dyDescent="0.4">
       <c r="A7" s="8" t="s">
-        <v>107</v>
+        <v>81</v>
       </c>
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
@@ -4455,80 +4901,80 @@
       <c r="A8" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B8" s="123" t="s">
-        <v>45</v>
-      </c>
-      <c r="C8" s="123"/>
-      <c r="D8" s="123"/>
-      <c r="E8" s="123"/>
-      <c r="F8" s="123"/>
-      <c r="G8" s="123"/>
-      <c r="H8" s="123"/>
-      <c r="I8" s="123" t="s">
-        <v>58</v>
-      </c>
-      <c r="J8" s="123"/>
-      <c r="K8" s="123"/>
-      <c r="L8" s="123"/>
-      <c r="M8" s="123" t="s">
-        <v>46</v>
-      </c>
-      <c r="N8" s="123"/>
-      <c r="O8" s="123"/>
-      <c r="P8" s="124" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q8" s="124"/>
-      <c r="R8" s="124"/>
-      <c r="S8" s="124"/>
-      <c r="T8" s="74" t="s">
-        <v>108</v>
-      </c>
-      <c r="U8" s="75"/>
-      <c r="V8" s="76"/>
+      <c r="B8" s="133" t="s">
+        <v>43</v>
+      </c>
+      <c r="C8" s="133"/>
+      <c r="D8" s="133"/>
+      <c r="E8" s="133"/>
+      <c r="F8" s="133"/>
+      <c r="G8" s="133"/>
+      <c r="H8" s="133"/>
+      <c r="I8" s="133" t="s">
+        <v>55</v>
+      </c>
+      <c r="J8" s="133"/>
+      <c r="K8" s="133"/>
+      <c r="L8" s="133"/>
+      <c r="M8" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="N8" s="133"/>
+      <c r="O8" s="133"/>
+      <c r="P8" s="134" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q8" s="134"/>
+      <c r="R8" s="134"/>
+      <c r="S8" s="134"/>
+      <c r="T8" s="78" t="s">
+        <v>82</v>
+      </c>
+      <c r="U8" s="79"/>
+      <c r="V8" s="80"/>
     </row>
     <row r="9" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A9" s="11">
         <v>1</v>
       </c>
-      <c r="B9" s="125" t="s">
-        <v>109</v>
-      </c>
-      <c r="C9" s="126"/>
-      <c r="D9" s="126"/>
-      <c r="E9" s="126"/>
-      <c r="F9" s="126"/>
-      <c r="G9" s="126"/>
-      <c r="H9" s="126"/>
-      <c r="I9" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J9" s="109"/>
-      <c r="K9" s="109"/>
-      <c r="L9" s="110"/>
-      <c r="M9" s="117" t="s">
-        <v>52</v>
-      </c>
-      <c r="N9" s="111"/>
-      <c r="O9" s="111"/>
-      <c r="P9" s="117" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q9" s="111"/>
-      <c r="R9" s="111"/>
-      <c r="S9" s="111"/>
-      <c r="T9" s="111" t="s">
-        <v>111</v>
-      </c>
-      <c r="U9" s="111"/>
-      <c r="V9" s="111"/>
+      <c r="B9" s="135" t="s">
+        <v>83</v>
+      </c>
+      <c r="C9" s="136"/>
+      <c r="D9" s="136"/>
+      <c r="E9" s="136"/>
+      <c r="F9" s="136"/>
+      <c r="G9" s="136"/>
+      <c r="H9" s="136"/>
+      <c r="I9" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="J9" s="114"/>
+      <c r="K9" s="114"/>
+      <c r="L9" s="115"/>
+      <c r="M9" s="125" t="s">
+        <v>50</v>
+      </c>
+      <c r="N9" s="116"/>
+      <c r="O9" s="116"/>
+      <c r="P9" s="125" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q9" s="116"/>
+      <c r="R9" s="116"/>
+      <c r="S9" s="116"/>
+      <c r="T9" s="116" t="s">
+        <v>85</v>
+      </c>
+      <c r="U9" s="116"/>
+      <c r="V9" s="116"/>
     </row>
     <row r="10" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A10" s="11">
         <v>2</v>
       </c>
       <c r="B10" s="14" t="s">
-        <v>112</v>
+        <v>86</v>
       </c>
       <c r="C10" s="13"/>
       <c r="D10" s="13"/>
@@ -4536,399 +4982,399 @@
       <c r="F10" s="13"/>
       <c r="G10" s="13"/>
       <c r="H10" s="13"/>
-      <c r="I10" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J10" s="109"/>
-      <c r="K10" s="109"/>
-      <c r="L10" s="110"/>
-      <c r="M10" s="117" t="s">
-        <v>52</v>
-      </c>
-      <c r="N10" s="111"/>
-      <c r="O10" s="111"/>
-      <c r="P10" s="117" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q10" s="111"/>
-      <c r="R10" s="111"/>
-      <c r="S10" s="111"/>
-      <c r="T10" s="111" t="s">
-        <v>114</v>
-      </c>
-      <c r="U10" s="111"/>
-      <c r="V10" s="111"/>
-    </row>
-    <row r="11" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="6"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
-      <c r="Q11" s="7"/>
-      <c r="R11" s="7"/>
-      <c r="S11" s="7"/>
-      <c r="T11" s="7"/>
-      <c r="U11" s="7"/>
-      <c r="V11" s="7"/>
-    </row>
-    <row r="12" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="15" t="s">
-        <v>115</v>
-      </c>
-      <c r="B12" s="16"/>
-      <c r="C12" s="16"/>
-      <c r="D12" s="16"/>
-      <c r="E12" s="16"/>
-      <c r="F12" s="16"/>
-      <c r="G12" s="16"/>
-      <c r="H12" s="16"/>
-      <c r="I12" s="16"/>
-      <c r="J12" s="16"/>
-      <c r="K12" s="16"/>
-      <c r="L12" s="16"/>
-      <c r="M12" s="16"/>
-      <c r="N12" s="16"/>
-      <c r="O12" s="16"/>
-      <c r="P12" s="16"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="23"/>
+      <c r="I10" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="J10" s="114"/>
+      <c r="K10" s="114"/>
+      <c r="L10" s="115"/>
+      <c r="M10" s="125" t="s">
+        <v>50</v>
+      </c>
+      <c r="N10" s="116"/>
+      <c r="O10" s="116"/>
+      <c r="P10" s="125" t="s">
+        <v>87</v>
+      </c>
+      <c r="Q10" s="116"/>
+      <c r="R10" s="116"/>
+      <c r="S10" s="116"/>
+      <c r="T10" s="118" t="s">
+        <v>134</v>
+      </c>
+      <c r="U10" s="116"/>
+      <c r="V10" s="116"/>
+    </row>
+    <row r="11" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="11">
+        <v>3</v>
+      </c>
+      <c r="B11" s="137" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="136"/>
+      <c r="D11" s="136"/>
+      <c r="E11" s="136"/>
+      <c r="F11" s="136"/>
+      <c r="G11" s="136"/>
+      <c r="H11" s="138"/>
+      <c r="I11" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="J11" s="114"/>
+      <c r="K11" s="114"/>
+      <c r="L11" s="115"/>
+      <c r="M11" s="125" t="s">
+        <v>50</v>
+      </c>
+      <c r="N11" s="116"/>
+      <c r="O11" s="116"/>
+      <c r="P11" s="118" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q11" s="116"/>
+      <c r="R11" s="116"/>
+      <c r="S11" s="116"/>
+      <c r="T11" s="116" t="s">
+        <v>94</v>
+      </c>
+      <c r="U11" s="116"/>
+      <c r="V11" s="116"/>
+    </row>
+    <row r="12" spans="1:22" s="2" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="6"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
+      <c r="Q12" s="7"/>
+      <c r="R12" s="7"/>
+      <c r="S12" s="7"/>
+      <c r="T12" s="7"/>
+      <c r="U12" s="7"/>
+      <c r="V12" s="7"/>
     </row>
     <row r="13" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="10" t="s">
+      <c r="A13" s="15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B13" s="16"/>
+      <c r="C13" s="16"/>
+      <c r="D13" s="16"/>
+      <c r="E13" s="16"/>
+      <c r="F13" s="16"/>
+      <c r="G13" s="16"/>
+      <c r="H13" s="16"/>
+      <c r="I13" s="16"/>
+      <c r="J13" s="16"/>
+      <c r="K13" s="16"/>
+      <c r="L13" s="16"/>
+      <c r="M13" s="16"/>
+      <c r="N13" s="16"/>
+      <c r="O13" s="16"/>
+      <c r="P13" s="16"/>
+      <c r="Q13" s="16"/>
+      <c r="R13" s="16"/>
+      <c r="S13" s="16"/>
+      <c r="T13" s="16"/>
+      <c r="U13" s="16"/>
+      <c r="V13" s="23"/>
+    </row>
+    <row r="14" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B13" s="123" t="s">
-        <v>45</v>
-      </c>
-      <c r="C13" s="123"/>
-      <c r="D13" s="123"/>
-      <c r="E13" s="123"/>
-      <c r="F13" s="123"/>
-      <c r="G13" s="123"/>
-      <c r="H13" s="123"/>
-      <c r="I13" s="123" t="s">
-        <v>58</v>
-      </c>
-      <c r="J13" s="123"/>
-      <c r="K13" s="123"/>
-      <c r="L13" s="123"/>
-      <c r="M13" s="123" t="s">
-        <v>46</v>
-      </c>
-      <c r="N13" s="123"/>
-      <c r="O13" s="123"/>
-      <c r="P13" s="124" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q13" s="124"/>
-      <c r="R13" s="124"/>
-      <c r="S13" s="124"/>
-      <c r="T13" s="74" t="s">
-        <v>108</v>
-      </c>
-      <c r="U13" s="75"/>
-      <c r="V13" s="76"/>
-    </row>
-    <row r="14" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="11">
-        <v>1</v>
-      </c>
-      <c r="B14" s="125" t="s">
-        <v>112</v>
-      </c>
-      <c r="C14" s="126"/>
-      <c r="D14" s="126"/>
-      <c r="E14" s="126"/>
-      <c r="F14" s="126"/>
-      <c r="G14" s="126"/>
-      <c r="H14" s="126"/>
-      <c r="I14" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J14" s="109"/>
-      <c r="K14" s="109"/>
-      <c r="L14" s="110"/>
-      <c r="M14" s="117" t="s">
-        <v>52</v>
-      </c>
-      <c r="N14" s="111"/>
-      <c r="O14" s="111"/>
-      <c r="P14" s="117" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q14" s="111"/>
-      <c r="R14" s="111"/>
-      <c r="S14" s="111"/>
-      <c r="T14" s="111" t="s">
-        <v>116</v>
-      </c>
-      <c r="U14" s="111"/>
-      <c r="V14" s="111"/>
+      <c r="B14" s="133" t="s">
+        <v>43</v>
+      </c>
+      <c r="C14" s="133"/>
+      <c r="D14" s="133"/>
+      <c r="E14" s="133"/>
+      <c r="F14" s="133"/>
+      <c r="G14" s="133"/>
+      <c r="H14" s="133"/>
+      <c r="I14" s="133" t="s">
+        <v>55</v>
+      </c>
+      <c r="J14" s="133"/>
+      <c r="K14" s="133"/>
+      <c r="L14" s="133"/>
+      <c r="M14" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="N14" s="133"/>
+      <c r="O14" s="133"/>
+      <c r="P14" s="134" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q14" s="134"/>
+      <c r="R14" s="134"/>
+      <c r="S14" s="134"/>
+      <c r="T14" s="78" t="s">
+        <v>82</v>
+      </c>
+      <c r="U14" s="79"/>
+      <c r="V14" s="80"/>
     </row>
     <row r="15" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A15" s="11">
-        <v>2</v>
-      </c>
-      <c r="B15" s="125" t="s">
-        <v>109</v>
-      </c>
-      <c r="C15" s="126"/>
-      <c r="D15" s="126"/>
-      <c r="E15" s="126"/>
-      <c r="F15" s="126"/>
-      <c r="G15" s="126"/>
-      <c r="H15" s="126"/>
-      <c r="I15" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J15" s="109"/>
-      <c r="K15" s="109"/>
-      <c r="L15" s="110"/>
-      <c r="M15" s="117" t="s">
-        <v>52</v>
-      </c>
-      <c r="N15" s="111"/>
-      <c r="O15" s="111"/>
-      <c r="P15" s="117" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q15" s="111"/>
-      <c r="R15" s="111"/>
-      <c r="S15" s="111"/>
-      <c r="T15" s="111" t="s">
-        <v>118</v>
-      </c>
-      <c r="U15" s="111"/>
-      <c r="V15" s="111"/>
+        <v>1</v>
+      </c>
+      <c r="B15" s="135" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="136"/>
+      <c r="D15" s="136"/>
+      <c r="E15" s="136"/>
+      <c r="F15" s="136"/>
+      <c r="G15" s="136"/>
+      <c r="H15" s="136"/>
+      <c r="I15" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="J15" s="114"/>
+      <c r="K15" s="114"/>
+      <c r="L15" s="115"/>
+      <c r="M15" s="125" t="s">
+        <v>50</v>
+      </c>
+      <c r="N15" s="116"/>
+      <c r="O15" s="116"/>
+      <c r="P15" s="125" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q15" s="116"/>
+      <c r="R15" s="116"/>
+      <c r="S15" s="116"/>
+      <c r="T15" s="116" t="s">
+        <v>89</v>
+      </c>
+      <c r="U15" s="116"/>
+      <c r="V15" s="116"/>
     </row>
     <row r="16" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A16" s="11">
+        <v>2</v>
+      </c>
+      <c r="B16" s="135" t="s">
+        <v>83</v>
+      </c>
+      <c r="C16" s="136"/>
+      <c r="D16" s="136"/>
+      <c r="E16" s="136"/>
+      <c r="F16" s="136"/>
+      <c r="G16" s="136"/>
+      <c r="H16" s="136"/>
+      <c r="I16" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="J16" s="114"/>
+      <c r="K16" s="114"/>
+      <c r="L16" s="115"/>
+      <c r="M16" s="125" t="s">
+        <v>50</v>
+      </c>
+      <c r="N16" s="116"/>
+      <c r="O16" s="116"/>
+      <c r="P16" s="125" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q16" s="116"/>
+      <c r="R16" s="116"/>
+      <c r="S16" s="116"/>
+      <c r="T16" s="116" t="s">
+        <v>91</v>
+      </c>
+      <c r="U16" s="116"/>
+      <c r="V16" s="116"/>
+    </row>
+    <row r="17" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="11">
         <v>3</v>
       </c>
-      <c r="B16" s="127" t="s">
-        <v>119</v>
-      </c>
-      <c r="C16" s="126"/>
-      <c r="D16" s="126"/>
-      <c r="E16" s="126"/>
-      <c r="F16" s="126"/>
-      <c r="G16" s="126"/>
-      <c r="H16" s="128"/>
-      <c r="I16" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J16" s="109"/>
-      <c r="K16" s="109"/>
-      <c r="L16" s="110"/>
-      <c r="M16" s="117" t="s">
-        <v>52</v>
-      </c>
-      <c r="N16" s="111"/>
-      <c r="O16" s="111"/>
-      <c r="P16" s="111" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q16" s="111"/>
-      <c r="R16" s="111"/>
-      <c r="S16" s="111"/>
-      <c r="T16" s="111" t="s">
-        <v>121</v>
-      </c>
-      <c r="U16" s="111"/>
-      <c r="V16" s="111"/>
-    </row>
-    <row r="18" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="15" t="s">
-        <v>122</v>
-      </c>
-      <c r="B18" s="16"/>
-      <c r="C18" s="16"/>
-      <c r="D18" s="16"/>
-      <c r="E18" s="16"/>
-      <c r="F18" s="16"/>
-      <c r="G18" s="16"/>
-      <c r="H18" s="16"/>
-      <c r="I18" s="16"/>
-      <c r="J18" s="16"/>
-      <c r="K18" s="16"/>
-      <c r="L18" s="16"/>
-      <c r="M18" s="16"/>
-      <c r="N18" s="16"/>
-      <c r="O18" s="16"/>
-      <c r="P18" s="16"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="16"/>
-      <c r="V18" s="23"/>
+      <c r="B17" s="137" t="s">
+        <v>92</v>
+      </c>
+      <c r="C17" s="136"/>
+      <c r="D17" s="136"/>
+      <c r="E17" s="136"/>
+      <c r="F17" s="136"/>
+      <c r="G17" s="136"/>
+      <c r="H17" s="138"/>
+      <c r="I17" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="J17" s="114"/>
+      <c r="K17" s="114"/>
+      <c r="L17" s="115"/>
+      <c r="M17" s="125" t="s">
+        <v>50</v>
+      </c>
+      <c r="N17" s="116"/>
+      <c r="O17" s="116"/>
+      <c r="P17" s="118" t="s">
+        <v>142</v>
+      </c>
+      <c r="Q17" s="116"/>
+      <c r="R17" s="116"/>
+      <c r="S17" s="116"/>
+      <c r="T17" s="116" t="s">
+        <v>94</v>
+      </c>
+      <c r="U17" s="116"/>
+      <c r="V17" s="116"/>
     </row>
     <row r="19" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="10" t="s">
+      <c r="A19" s="15" t="s">
+        <v>95</v>
+      </c>
+      <c r="B19" s="16"/>
+      <c r="C19" s="16"/>
+      <c r="D19" s="16"/>
+      <c r="E19" s="16"/>
+      <c r="F19" s="16"/>
+      <c r="G19" s="16"/>
+      <c r="H19" s="16"/>
+      <c r="I19" s="16"/>
+      <c r="J19" s="16"/>
+      <c r="K19" s="16"/>
+      <c r="L19" s="16"/>
+      <c r="M19" s="16"/>
+      <c r="N19" s="16"/>
+      <c r="O19" s="16"/>
+      <c r="P19" s="16"/>
+      <c r="Q19" s="16"/>
+      <c r="R19" s="16"/>
+      <c r="S19" s="16"/>
+      <c r="T19" s="16"/>
+      <c r="U19" s="16"/>
+      <c r="V19" s="23"/>
+    </row>
+    <row r="20" spans="1:22" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="123" t="s">
-        <v>45</v>
-      </c>
-      <c r="C19" s="123"/>
-      <c r="D19" s="123"/>
-      <c r="E19" s="123"/>
-      <c r="F19" s="123"/>
-      <c r="G19" s="123"/>
-      <c r="H19" s="123"/>
-      <c r="I19" s="123" t="s">
-        <v>58</v>
-      </c>
-      <c r="J19" s="123"/>
-      <c r="K19" s="123"/>
-      <c r="L19" s="123"/>
-      <c r="M19" s="123" t="s">
-        <v>46</v>
-      </c>
-      <c r="N19" s="123"/>
-      <c r="O19" s="123"/>
-      <c r="P19" s="124" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q19" s="124"/>
-      <c r="R19" s="124"/>
-      <c r="S19" s="124"/>
-      <c r="T19" s="74" t="s">
-        <v>108</v>
-      </c>
-      <c r="U19" s="75"/>
-      <c r="V19" s="76"/>
-    </row>
-    <row r="20" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="11">
-        <v>1</v>
-      </c>
-      <c r="B20" s="125" t="s">
-        <v>109</v>
-      </c>
-      <c r="C20" s="126"/>
-      <c r="D20" s="126"/>
-      <c r="E20" s="126"/>
-      <c r="F20" s="126"/>
-      <c r="G20" s="126"/>
-      <c r="H20" s="126"/>
-      <c r="I20" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J20" s="109"/>
-      <c r="K20" s="109"/>
-      <c r="L20" s="110"/>
-      <c r="M20" s="117" t="s">
-        <v>52</v>
-      </c>
-      <c r="N20" s="111"/>
-      <c r="O20" s="111"/>
-      <c r="P20" s="117" t="s">
-        <v>110</v>
-      </c>
-      <c r="Q20" s="111"/>
-      <c r="R20" s="111"/>
-      <c r="S20" s="111"/>
-      <c r="T20" s="111" t="s">
-        <v>116</v>
-      </c>
-      <c r="U20" s="111"/>
-      <c r="V20" s="111"/>
+      <c r="B20" s="133" t="s">
+        <v>43</v>
+      </c>
+      <c r="C20" s="133"/>
+      <c r="D20" s="133"/>
+      <c r="E20" s="133"/>
+      <c r="F20" s="133"/>
+      <c r="G20" s="133"/>
+      <c r="H20" s="133"/>
+      <c r="I20" s="133" t="s">
+        <v>55</v>
+      </c>
+      <c r="J20" s="133"/>
+      <c r="K20" s="133"/>
+      <c r="L20" s="133"/>
+      <c r="M20" s="133" t="s">
+        <v>44</v>
+      </c>
+      <c r="N20" s="133"/>
+      <c r="O20" s="133"/>
+      <c r="P20" s="134" t="s">
+        <v>47</v>
+      </c>
+      <c r="Q20" s="134"/>
+      <c r="R20" s="134"/>
+      <c r="S20" s="134"/>
+      <c r="T20" s="78" t="s">
+        <v>82</v>
+      </c>
+      <c r="U20" s="79"/>
+      <c r="V20" s="80"/>
     </row>
     <row r="21" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A21" s="11">
-        <v>2</v>
-      </c>
-      <c r="B21" s="12" t="s">
-        <v>112</v>
-      </c>
-      <c r="C21" s="17"/>
-      <c r="D21" s="17"/>
-      <c r="E21" s="17"/>
-      <c r="F21" s="17"/>
-      <c r="G21" s="17"/>
-      <c r="H21" s="17"/>
-      <c r="I21" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J21" s="109"/>
-      <c r="K21" s="109"/>
-      <c r="L21" s="110"/>
-      <c r="M21" s="117" t="s">
-        <v>52</v>
-      </c>
-      <c r="N21" s="111"/>
-      <c r="O21" s="111"/>
-      <c r="P21" s="117" t="s">
-        <v>117</v>
-      </c>
-      <c r="Q21" s="111"/>
-      <c r="R21" s="111"/>
-      <c r="S21" s="111"/>
-      <c r="T21" s="111" t="s">
-        <v>123</v>
-      </c>
-      <c r="U21" s="111"/>
-      <c r="V21" s="111"/>
+        <v>1</v>
+      </c>
+      <c r="B21" s="135" t="s">
+        <v>83</v>
+      </c>
+      <c r="C21" s="136"/>
+      <c r="D21" s="136"/>
+      <c r="E21" s="136"/>
+      <c r="F21" s="136"/>
+      <c r="G21" s="136"/>
+      <c r="H21" s="136"/>
+      <c r="I21" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="J21" s="114"/>
+      <c r="K21" s="114"/>
+      <c r="L21" s="115"/>
+      <c r="M21" s="125" t="s">
+        <v>50</v>
+      </c>
+      <c r="N21" s="116"/>
+      <c r="O21" s="116"/>
+      <c r="P21" s="125" t="s">
+        <v>84</v>
+      </c>
+      <c r="Q21" s="116"/>
+      <c r="R21" s="116"/>
+      <c r="S21" s="116"/>
+      <c r="T21" s="116" t="s">
+        <v>89</v>
+      </c>
+      <c r="U21" s="116"/>
+      <c r="V21" s="116"/>
     </row>
     <row r="22" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A22" s="11">
-        <v>3</v>
-      </c>
-      <c r="B22" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="C22" s="19"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="19"/>
-      <c r="H22" s="20"/>
-      <c r="I22" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J22" s="109"/>
-      <c r="K22" s="109"/>
-      <c r="L22" s="110"/>
-      <c r="M22" s="117" t="s">
-        <v>52</v>
-      </c>
-      <c r="N22" s="111"/>
-      <c r="O22" s="111"/>
-      <c r="P22" s="111" t="s">
-        <v>120</v>
-      </c>
-      <c r="Q22" s="111"/>
-      <c r="R22" s="111"/>
-      <c r="S22" s="111"/>
-      <c r="T22" s="117" t="s">
-        <v>125</v>
-      </c>
-      <c r="U22" s="111"/>
-      <c r="V22" s="111"/>
+        <v>2</v>
+      </c>
+      <c r="B22" s="12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C22" s="17"/>
+      <c r="D22" s="17"/>
+      <c r="E22" s="17"/>
+      <c r="F22" s="17"/>
+      <c r="G22" s="17"/>
+      <c r="H22" s="17"/>
+      <c r="I22" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="J22" s="114"/>
+      <c r="K22" s="114"/>
+      <c r="L22" s="115"/>
+      <c r="M22" s="125" t="s">
+        <v>50</v>
+      </c>
+      <c r="N22" s="116"/>
+      <c r="O22" s="116"/>
+      <c r="P22" s="125" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q22" s="116"/>
+      <c r="R22" s="116"/>
+      <c r="S22" s="116"/>
+      <c r="T22" s="116" t="s">
+        <v>96</v>
+      </c>
+      <c r="U22" s="116"/>
+      <c r="V22" s="116"/>
     </row>
     <row r="23" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A23" s="11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B23" s="18" t="s">
-        <v>126</v>
+        <v>97</v>
       </c>
       <c r="C23" s="19"/>
       <c r="D23" s="19"/>
@@ -4936,35 +5382,35 @@
       <c r="F23" s="19"/>
       <c r="G23" s="19"/>
       <c r="H23" s="20"/>
-      <c r="I23" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J23" s="109"/>
-      <c r="K23" s="109"/>
-      <c r="L23" s="110"/>
-      <c r="M23" s="117" t="s">
-        <v>52</v>
-      </c>
-      <c r="N23" s="111"/>
-      <c r="O23" s="111"/>
-      <c r="P23" s="111" t="s">
-        <v>127</v>
-      </c>
-      <c r="Q23" s="111"/>
-      <c r="R23" s="111"/>
-      <c r="S23" s="111"/>
-      <c r="T23" s="111" t="s">
-        <v>128</v>
-      </c>
-      <c r="U23" s="111"/>
-      <c r="V23" s="111"/>
+      <c r="I23" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="J23" s="114"/>
+      <c r="K23" s="114"/>
+      <c r="L23" s="115"/>
+      <c r="M23" s="125" t="s">
+        <v>50</v>
+      </c>
+      <c r="N23" s="116"/>
+      <c r="O23" s="116"/>
+      <c r="P23" s="116" t="s">
+        <v>93</v>
+      </c>
+      <c r="Q23" s="116"/>
+      <c r="R23" s="116"/>
+      <c r="S23" s="116"/>
+      <c r="T23" s="125" t="s">
+        <v>98</v>
+      </c>
+      <c r="U23" s="116"/>
+      <c r="V23" s="116"/>
     </row>
     <row r="24" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
       <c r="A24" s="11">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B24" s="18" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="C24" s="19"/>
       <c r="D24" s="19"/>
@@ -4972,31 +5418,67 @@
       <c r="F24" s="19"/>
       <c r="G24" s="19"/>
       <c r="H24" s="20"/>
-      <c r="I24" s="108" t="s">
-        <v>63</v>
-      </c>
-      <c r="J24" s="109"/>
-      <c r="K24" s="109"/>
-      <c r="L24" s="110"/>
-      <c r="M24" s="117" t="s">
-        <v>52</v>
-      </c>
-      <c r="N24" s="111"/>
-      <c r="O24" s="111"/>
-      <c r="P24" s="111" t="s">
-        <v>130</v>
-      </c>
-      <c r="Q24" s="111"/>
-      <c r="R24" s="111"/>
-      <c r="S24" s="111"/>
-      <c r="T24" s="111" t="s">
-        <v>131</v>
-      </c>
-      <c r="U24" s="111"/>
-      <c r="V24" s="111"/>
+      <c r="I24" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="J24" s="114"/>
+      <c r="K24" s="114"/>
+      <c r="L24" s="115"/>
+      <c r="M24" s="125" t="s">
+        <v>50</v>
+      </c>
+      <c r="N24" s="116"/>
+      <c r="O24" s="116"/>
+      <c r="P24" s="116" t="s">
+        <v>100</v>
+      </c>
+      <c r="Q24" s="116"/>
+      <c r="R24" s="116"/>
+      <c r="S24" s="116"/>
+      <c r="T24" s="116" t="s">
+        <v>101</v>
+      </c>
+      <c r="U24" s="116"/>
+      <c r="V24" s="116"/>
+    </row>
+    <row r="25" spans="1:22" s="3" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="11">
+        <v>5</v>
+      </c>
+      <c r="B25" s="18" t="s">
+        <v>102</v>
+      </c>
+      <c r="C25" s="19"/>
+      <c r="D25" s="19"/>
+      <c r="E25" s="19"/>
+      <c r="F25" s="19"/>
+      <c r="G25" s="19"/>
+      <c r="H25" s="20"/>
+      <c r="I25" s="113" t="s">
+        <v>59</v>
+      </c>
+      <c r="J25" s="114"/>
+      <c r="K25" s="114"/>
+      <c r="L25" s="115"/>
+      <c r="M25" s="125" t="s">
+        <v>50</v>
+      </c>
+      <c r="N25" s="116"/>
+      <c r="O25" s="116"/>
+      <c r="P25" s="116" t="s">
+        <v>103</v>
+      </c>
+      <c r="Q25" s="116"/>
+      <c r="R25" s="116"/>
+      <c r="S25" s="116"/>
+      <c r="T25" s="116" t="s">
+        <v>104</v>
+      </c>
+      <c r="U25" s="116"/>
+      <c r="V25" s="116"/>
     </row>
   </sheetData>
-  <mergeCells count="78">
+  <mergeCells count="83">
     <mergeCell ref="A1:H4"/>
     <mergeCell ref="I1:L2"/>
     <mergeCell ref="M1:P2"/>
@@ -5010,32 +5492,37 @@
     <mergeCell ref="U1:V2"/>
     <mergeCell ref="R3:S4"/>
     <mergeCell ref="R1:S2"/>
+    <mergeCell ref="I24:L24"/>
+    <mergeCell ref="M24:O24"/>
+    <mergeCell ref="P24:S24"/>
+    <mergeCell ref="T24:V24"/>
+    <mergeCell ref="I25:L25"/>
+    <mergeCell ref="M25:O25"/>
+    <mergeCell ref="P25:S25"/>
+    <mergeCell ref="T25:V25"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="M22:O22"/>
+    <mergeCell ref="P22:S22"/>
+    <mergeCell ref="T22:V22"/>
     <mergeCell ref="I23:L23"/>
     <mergeCell ref="M23:O23"/>
     <mergeCell ref="P23:S23"/>
     <mergeCell ref="T23:V23"/>
-    <mergeCell ref="I24:L24"/>
-    <mergeCell ref="M24:O24"/>
-    <mergeCell ref="P24:S24"/>
-    <mergeCell ref="T24:V24"/>
+    <mergeCell ref="B21:H21"/>
     <mergeCell ref="I21:L21"/>
     <mergeCell ref="M21:O21"/>
     <mergeCell ref="P21:S21"/>
     <mergeCell ref="T21:V21"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="M22:O22"/>
-    <mergeCell ref="P22:S22"/>
-    <mergeCell ref="T22:V22"/>
     <mergeCell ref="B20:H20"/>
     <mergeCell ref="I20:L20"/>
     <mergeCell ref="M20:O20"/>
     <mergeCell ref="P20:S20"/>
     <mergeCell ref="T20:V20"/>
-    <mergeCell ref="B19:H19"/>
-    <mergeCell ref="I19:L19"/>
-    <mergeCell ref="M19:O19"/>
-    <mergeCell ref="P19:S19"/>
-    <mergeCell ref="T19:V19"/>
+    <mergeCell ref="B17:H17"/>
+    <mergeCell ref="I17:L17"/>
+    <mergeCell ref="M17:O17"/>
+    <mergeCell ref="P17:S17"/>
+    <mergeCell ref="T17:V17"/>
     <mergeCell ref="B16:H16"/>
     <mergeCell ref="I16:L16"/>
     <mergeCell ref="M16:O16"/>
@@ -5046,20 +5533,20 @@
     <mergeCell ref="M15:O15"/>
     <mergeCell ref="P15:S15"/>
     <mergeCell ref="T15:V15"/>
+    <mergeCell ref="I10:L10"/>
+    <mergeCell ref="M10:O10"/>
+    <mergeCell ref="P10:S10"/>
+    <mergeCell ref="T10:V10"/>
     <mergeCell ref="B14:H14"/>
     <mergeCell ref="I14:L14"/>
     <mergeCell ref="M14:O14"/>
     <mergeCell ref="P14:S14"/>
     <mergeCell ref="T14:V14"/>
-    <mergeCell ref="I10:L10"/>
-    <mergeCell ref="M10:O10"/>
-    <mergeCell ref="P10:S10"/>
-    <mergeCell ref="T10:V10"/>
-    <mergeCell ref="B13:H13"/>
-    <mergeCell ref="I13:L13"/>
-    <mergeCell ref="M13:O13"/>
-    <mergeCell ref="P13:S13"/>
-    <mergeCell ref="T13:V13"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="I11:L11"/>
+    <mergeCell ref="M11:O11"/>
+    <mergeCell ref="P11:S11"/>
+    <mergeCell ref="T11:V11"/>
     <mergeCell ref="B9:H9"/>
     <mergeCell ref="I9:L9"/>
     <mergeCell ref="M9:O9"/>

--- a/docs/設計/部品在庫管理/機能仕様書_部品入荷API.xlsx
+++ b/docs/設計/部品在庫管理/機能仕様書_部品入荷API.xlsx
@@ -19,14 +19,14 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">レスポンス!$A$1:$V$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">機能概要!$A$1:$AH$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">シーケンス!$A$1:$V$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">処理詳細!$A$1:$P$137</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">処理詳細!$A$1:$P$134</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="276">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="278">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -642,9 +642,6 @@
     <t>入荷部品リスト.stock_id　＝　部品在庫テーブル.stock_id</t>
   </si>
   <si>
-    <t>※在庫IDが入荷部品リストに含まれる場合、絞り込み検索を行う</t>
-  </si>
-  <si>
     <t>＜取得項目＞</t>
   </si>
   <si>
@@ -669,13 +666,25 @@
     <t>4.1 UPSERT処理実行</t>
   </si>
   <si>
-    <t>＜返却値＞</t>
-  </si>
-  <si>
-    <t>SELECT LAST_INSERT_ID() により取得した実際の stock_id（新規または既存）</t>
-  </si>
-  <si>
-    <t>4.2 設定値</t>
+    <t>部品在庫テーブルに対して、在庫IDをキーとした挿入・更新処理を実行する。</t>
+  </si>
+  <si>
+    <t>＜実行内容＞</t>
+  </si>
+  <si>
+    <t>在庫IDが存在しない場合</t>
+  </si>
+  <si>
+    <t>：新規レコードを挿入</t>
+  </si>
+  <si>
+    <t>在庫IDが既に存在する場合</t>
+  </si>
+  <si>
+    <t>：既存レコードの数量を加算更新</t>
+  </si>
+  <si>
+    <t>4.2 UPSERT処理実行</t>
   </si>
   <si>
     <t>＜新規登録＞（stock_id = null）</t>
@@ -741,7 +750,7 @@
     <t>3.で取得した既存数量　＋　入荷部品リスト.入荷数量</t>
   </si>
   <si>
-    <t>4.3 SELECT LAST_INSERT_ID() により 実際の stock_id（新規または既存） を取得</t>
+    <t>4.3 LAST_INSERT_ID関数により実際の stock_id（新規または既存）を取得（新規挿入の場合は自動採番されたID、更新の場合は既存のIDを取得）</t>
   </si>
   <si>
     <t>4.4 　処理中にエラーが発生した場合、以下のログを出力して例外をスロー</t>
@@ -765,19 +774,16 @@
     <t>PartsStockReceiveService.insertPartsStockHistory()</t>
   </si>
   <si>
-    <t>5.1 入荷日時の形式変更</t>
-  </si>
-  <si>
-    <t>　　String形式で受け取った「入荷日時」をLocalDateTimeに変更</t>
-  </si>
-  <si>
-    <t>　　DateTimeParseExceptionが発生した場合、以下のログを出力して、例外をスロー</t>
-  </si>
-  <si>
-    <t>　　※"入荷日時の形式が不正です: " + transactionDateStr</t>
-  </si>
-  <si>
-    <t>5.2 設定値</t>
+    <t>5.1 「入荷日時」を文字列形式（yyyy-MM-dd）を日時オブジェクト（yyyy-MM-dd 00:00:00）に変換</t>
+  </si>
+  <si>
+    <t>　DateTimeParseExceptionが発生した場合、以下のログを出力して、例外をスロー</t>
+  </si>
+  <si>
+    <t>　※"入荷日時の形式が不正です: " + transactionDateStr</t>
+  </si>
+  <si>
+    <t>5.2 履歴登録実行</t>
   </si>
   <si>
     <t>部品在庫履歴テーブル</t>
@@ -864,11 +870,11 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="31">
+  <fonts count="27">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -911,32 +917,10 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="12"/>
-      <name val="Meiryo UI"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="12"/>
+      <sz val="11"/>
       <color theme="1"/>
-      <name val="Meiryo UI"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <name val="Meiryo UI"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="14"/>
-      <color theme="1"/>
-      <name val="Meiryo UI"/>
-      <charset val="128"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="游ゴシック"/>
-      <charset val="0"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -948,37 +932,22 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color theme="0"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF0000FF"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -992,30 +961,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1038,6 +984,14 @@
     </font>
     <font>
       <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
@@ -1045,32 +999,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <i/>
       <sz val="11"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF7F7F7F"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1083,8 +1014,61 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="36">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1111,7 +1095,145 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1123,169 +1245,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1474,6 +1440,15 @@
       <diagonal/>
     </border>
     <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
       <left style="thin">
         <color rgb="FF7F7F7F"/>
       </left>
@@ -1485,6 +1460,56 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1507,67 +1532,8 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
       <bottom style="medium">
         <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1576,155 +1542,155 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="14" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="22" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="19" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="30" fillId="23" borderId="23" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="186">
+  <cellXfs count="154">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1794,9 +1760,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="49" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1842,9 +1805,6 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="12" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -1854,7 +1814,7 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1869,9 +1829,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1884,28 +1841,19 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1914,40 +1862,28 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="49" applyFont="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="9" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1971,33 +1907,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
@@ -2010,9 +1931,6 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2028,9 +1946,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -2049,24 +1964,12 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="8" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="14" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="9" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2079,36 +1982,21 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="9" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="6" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -2121,9 +2009,6 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="9" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2169,7 +2054,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -2184,12 +2069,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="7" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="8" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="49" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
@@ -2214,7 +2093,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1">
@@ -2244,15 +2123,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2286,13 +2156,10 @@
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" quotePrefix="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" quotePrefix="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1" quotePrefix="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3500,442 +3367,442 @@
   <dimension ref="A1:E69"/>
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="3.66666666666667" style="40"/>
-    <col min="2" max="2" width="5.11111111111111" style="179" customWidth="1"/>
-    <col min="3" max="3" width="12.3333333333333" style="40" customWidth="1"/>
-    <col min="4" max="4" width="10.3333333333333" style="40" customWidth="1"/>
-    <col min="5" max="5" width="66.1111111111111" style="40" customWidth="1"/>
-    <col min="6" max="16384" width="3.66666666666667" style="40"/>
+    <col min="1" max="1" width="3.66666666666667" style="38"/>
+    <col min="2" max="2" width="5.11111111111111" style="147" customWidth="1"/>
+    <col min="3" max="3" width="12.3333333333333" style="38" customWidth="1"/>
+    <col min="4" max="4" width="10.3333333333333" style="38" customWidth="1"/>
+    <col min="5" max="5" width="66.1111111111111" style="38" customWidth="1"/>
+    <col min="6" max="16384" width="3.66666666666667" style="38"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="38" t="s">
         <v>0</v>
       </c>
     </row>
     <row r="2" spans="2:5">
-      <c r="B2" s="180" t="s">
+      <c r="B2" s="148" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="181" t="s">
+      <c r="C2" s="149" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="181" t="s">
+      <c r="D2" s="149" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="181" t="s">
+      <c r="E2" s="149" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="182" t="s">
+      <c r="B3" s="150" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="183">
+      <c r="C3" s="151">
         <v>45636</v>
       </c>
-      <c r="D3" s="184" t="s">
+      <c r="D3" s="152" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="184" t="s">
+      <c r="E3" s="152" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="2:5">
-      <c r="B4" s="182"/>
-      <c r="C4" s="183"/>
-      <c r="D4" s="184"/>
-      <c r="E4" s="185"/>
+      <c r="B4" s="150"/>
+      <c r="C4" s="151"/>
+      <c r="D4" s="152"/>
+      <c r="E4" s="153"/>
     </row>
     <row r="5" spans="2:5">
-      <c r="B5" s="182"/>
-      <c r="C5" s="183"/>
-      <c r="D5" s="184"/>
-      <c r="E5" s="185"/>
+      <c r="B5" s="150"/>
+      <c r="C5" s="151"/>
+      <c r="D5" s="152"/>
+      <c r="E5" s="153"/>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="182"/>
-      <c r="C6" s="184"/>
-      <c r="D6" s="184"/>
-      <c r="E6" s="184"/>
+      <c r="B6" s="150"/>
+      <c r="C6" s="152"/>
+      <c r="D6" s="152"/>
+      <c r="E6" s="152"/>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="182"/>
-      <c r="C7" s="184"/>
-      <c r="D7" s="184"/>
-      <c r="E7" s="184"/>
+      <c r="B7" s="150"/>
+      <c r="C7" s="152"/>
+      <c r="D7" s="152"/>
+      <c r="E7" s="152"/>
     </row>
     <row r="8" spans="2:5">
-      <c r="B8" s="182"/>
-      <c r="C8" s="184"/>
-      <c r="D8" s="184"/>
-      <c r="E8" s="184"/>
+      <c r="B8" s="150"/>
+      <c r="C8" s="152"/>
+      <c r="D8" s="152"/>
+      <c r="E8" s="152"/>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="182"/>
-      <c r="C9" s="184"/>
-      <c r="D9" s="184"/>
-      <c r="E9" s="184"/>
+      <c r="B9" s="150"/>
+      <c r="C9" s="152"/>
+      <c r="D9" s="152"/>
+      <c r="E9" s="152"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="182"/>
-      <c r="C10" s="184"/>
-      <c r="D10" s="184"/>
-      <c r="E10" s="184"/>
+      <c r="B10" s="150"/>
+      <c r="C10" s="152"/>
+      <c r="D10" s="152"/>
+      <c r="E10" s="152"/>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="182"/>
-      <c r="C11" s="184"/>
-      <c r="D11" s="184"/>
-      <c r="E11" s="184"/>
+      <c r="B11" s="150"/>
+      <c r="C11" s="152"/>
+      <c r="D11" s="152"/>
+      <c r="E11" s="152"/>
     </row>
     <row r="12" spans="2:5">
-      <c r="B12" s="182"/>
-      <c r="C12" s="184"/>
-      <c r="D12" s="184"/>
-      <c r="E12" s="184"/>
+      <c r="B12" s="150"/>
+      <c r="C12" s="152"/>
+      <c r="D12" s="152"/>
+      <c r="E12" s="152"/>
     </row>
     <row r="13" spans="2:5">
-      <c r="B13" s="182"/>
-      <c r="C13" s="184"/>
-      <c r="D13" s="184"/>
-      <c r="E13" s="184"/>
+      <c r="B13" s="150"/>
+      <c r="C13" s="152"/>
+      <c r="D13" s="152"/>
+      <c r="E13" s="152"/>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="182"/>
-      <c r="C14" s="184"/>
-      <c r="D14" s="184"/>
-      <c r="E14" s="184"/>
+      <c r="B14" s="150"/>
+      <c r="C14" s="152"/>
+      <c r="D14" s="152"/>
+      <c r="E14" s="152"/>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="182"/>
-      <c r="C15" s="184"/>
-      <c r="D15" s="184"/>
-      <c r="E15" s="184"/>
+      <c r="B15" s="150"/>
+      <c r="C15" s="152"/>
+      <c r="D15" s="152"/>
+      <c r="E15" s="152"/>
     </row>
     <row r="16" spans="2:5">
-      <c r="B16" s="182"/>
-      <c r="C16" s="184"/>
-      <c r="D16" s="184"/>
-      <c r="E16" s="184"/>
+      <c r="B16" s="150"/>
+      <c r="C16" s="152"/>
+      <c r="D16" s="152"/>
+      <c r="E16" s="152"/>
     </row>
     <row r="17" spans="2:5">
-      <c r="B17" s="182"/>
-      <c r="C17" s="184"/>
-      <c r="D17" s="184"/>
-      <c r="E17" s="184"/>
+      <c r="B17" s="150"/>
+      <c r="C17" s="152"/>
+      <c r="D17" s="152"/>
+      <c r="E17" s="152"/>
     </row>
     <row r="18" spans="2:5">
-      <c r="B18" s="182"/>
-      <c r="C18" s="184"/>
-      <c r="D18" s="184"/>
-      <c r="E18" s="184"/>
+      <c r="B18" s="150"/>
+      <c r="C18" s="152"/>
+      <c r="D18" s="152"/>
+      <c r="E18" s="152"/>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="182"/>
-      <c r="C19" s="184"/>
-      <c r="D19" s="184"/>
-      <c r="E19" s="184"/>
+      <c r="B19" s="150"/>
+      <c r="C19" s="152"/>
+      <c r="D19" s="152"/>
+      <c r="E19" s="152"/>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="182"/>
-      <c r="C20" s="184"/>
-      <c r="D20" s="184"/>
-      <c r="E20" s="184"/>
+      <c r="B20" s="150"/>
+      <c r="C20" s="152"/>
+      <c r="D20" s="152"/>
+      <c r="E20" s="152"/>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="182"/>
-      <c r="C21" s="184"/>
-      <c r="D21" s="184"/>
-      <c r="E21" s="184"/>
+      <c r="B21" s="150"/>
+      <c r="C21" s="152"/>
+      <c r="D21" s="152"/>
+      <c r="E21" s="152"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="182"/>
-      <c r="C22" s="184"/>
-      <c r="D22" s="184"/>
-      <c r="E22" s="184"/>
+      <c r="B22" s="150"/>
+      <c r="C22" s="152"/>
+      <c r="D22" s="152"/>
+      <c r="E22" s="152"/>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="182"/>
-      <c r="C23" s="184"/>
-      <c r="D23" s="184"/>
-      <c r="E23" s="184"/>
+      <c r="B23" s="150"/>
+      <c r="C23" s="152"/>
+      <c r="D23" s="152"/>
+      <c r="E23" s="152"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="182"/>
-      <c r="C24" s="184"/>
-      <c r="D24" s="184"/>
-      <c r="E24" s="184"/>
+      <c r="B24" s="150"/>
+      <c r="C24" s="152"/>
+      <c r="D24" s="152"/>
+      <c r="E24" s="152"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="182"/>
-      <c r="C25" s="184"/>
-      <c r="D25" s="184"/>
-      <c r="E25" s="184"/>
+      <c r="B25" s="150"/>
+      <c r="C25" s="152"/>
+      <c r="D25" s="152"/>
+      <c r="E25" s="152"/>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="182"/>
-      <c r="C26" s="184"/>
-      <c r="D26" s="184"/>
-      <c r="E26" s="184"/>
+      <c r="B26" s="150"/>
+      <c r="C26" s="152"/>
+      <c r="D26" s="152"/>
+      <c r="E26" s="152"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="182"/>
-      <c r="C27" s="184"/>
-      <c r="D27" s="184"/>
-      <c r="E27" s="184"/>
+      <c r="B27" s="150"/>
+      <c r="C27" s="152"/>
+      <c r="D27" s="152"/>
+      <c r="E27" s="152"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="182"/>
-      <c r="C28" s="184"/>
-      <c r="D28" s="184"/>
-      <c r="E28" s="184"/>
+      <c r="B28" s="150"/>
+      <c r="C28" s="152"/>
+      <c r="D28" s="152"/>
+      <c r="E28" s="152"/>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="182"/>
-      <c r="C29" s="184"/>
-      <c r="D29" s="184"/>
-      <c r="E29" s="184"/>
+      <c r="B29" s="150"/>
+      <c r="C29" s="152"/>
+      <c r="D29" s="152"/>
+      <c r="E29" s="152"/>
     </row>
     <row r="30" spans="2:5">
-      <c r="B30" s="182"/>
-      <c r="C30" s="184"/>
-      <c r="D30" s="184"/>
-      <c r="E30" s="184"/>
+      <c r="B30" s="150"/>
+      <c r="C30" s="152"/>
+      <c r="D30" s="152"/>
+      <c r="E30" s="152"/>
     </row>
     <row r="31" spans="2:5">
-      <c r="B31" s="182"/>
-      <c r="C31" s="184"/>
-      <c r="D31" s="184"/>
-      <c r="E31" s="184"/>
+      <c r="B31" s="150"/>
+      <c r="C31" s="152"/>
+      <c r="D31" s="152"/>
+      <c r="E31" s="152"/>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="182"/>
-      <c r="C32" s="184"/>
-      <c r="D32" s="184"/>
-      <c r="E32" s="184"/>
+      <c r="B32" s="150"/>
+      <c r="C32" s="152"/>
+      <c r="D32" s="152"/>
+      <c r="E32" s="152"/>
     </row>
     <row r="33" spans="2:5">
-      <c r="B33" s="182"/>
-      <c r="C33" s="184"/>
-      <c r="D33" s="184"/>
-      <c r="E33" s="184"/>
+      <c r="B33" s="150"/>
+      <c r="C33" s="152"/>
+      <c r="D33" s="152"/>
+      <c r="E33" s="152"/>
     </row>
     <row r="34" spans="2:5">
-      <c r="B34" s="182"/>
-      <c r="C34" s="184"/>
-      <c r="D34" s="184"/>
-      <c r="E34" s="184"/>
+      <c r="B34" s="150"/>
+      <c r="C34" s="152"/>
+      <c r="D34" s="152"/>
+      <c r="E34" s="152"/>
     </row>
     <row r="35" spans="2:5">
-      <c r="B35" s="182"/>
-      <c r="C35" s="184"/>
-      <c r="D35" s="184"/>
-      <c r="E35" s="184"/>
+      <c r="B35" s="150"/>
+      <c r="C35" s="152"/>
+      <c r="D35" s="152"/>
+      <c r="E35" s="152"/>
     </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="182"/>
-      <c r="C36" s="184"/>
-      <c r="D36" s="184"/>
-      <c r="E36" s="184"/>
+      <c r="B36" s="150"/>
+      <c r="C36" s="152"/>
+      <c r="D36" s="152"/>
+      <c r="E36" s="152"/>
     </row>
     <row r="37" spans="2:5">
-      <c r="B37" s="182"/>
-      <c r="C37" s="184"/>
-      <c r="D37" s="184"/>
-      <c r="E37" s="184"/>
+      <c r="B37" s="150"/>
+      <c r="C37" s="152"/>
+      <c r="D37" s="152"/>
+      <c r="E37" s="152"/>
     </row>
     <row r="38" spans="2:5">
-      <c r="B38" s="182"/>
-      <c r="C38" s="184"/>
-      <c r="D38" s="184"/>
-      <c r="E38" s="184"/>
+      <c r="B38" s="150"/>
+      <c r="C38" s="152"/>
+      <c r="D38" s="152"/>
+      <c r="E38" s="152"/>
     </row>
     <row r="39" spans="2:5">
-      <c r="B39" s="182"/>
-      <c r="C39" s="184"/>
-      <c r="D39" s="184"/>
-      <c r="E39" s="184"/>
+      <c r="B39" s="150"/>
+      <c r="C39" s="152"/>
+      <c r="D39" s="152"/>
+      <c r="E39" s="152"/>
     </row>
     <row r="40" spans="2:5">
-      <c r="B40" s="182"/>
-      <c r="C40" s="184"/>
-      <c r="D40" s="184"/>
-      <c r="E40" s="184"/>
+      <c r="B40" s="150"/>
+      <c r="C40" s="152"/>
+      <c r="D40" s="152"/>
+      <c r="E40" s="152"/>
     </row>
     <row r="41" spans="2:5">
-      <c r="B41" s="182"/>
-      <c r="C41" s="184"/>
-      <c r="D41" s="184"/>
-      <c r="E41" s="184"/>
+      <c r="B41" s="150"/>
+      <c r="C41" s="152"/>
+      <c r="D41" s="152"/>
+      <c r="E41" s="152"/>
     </row>
     <row r="42" spans="2:5">
-      <c r="B42" s="182"/>
-      <c r="C42" s="184"/>
-      <c r="D42" s="184"/>
-      <c r="E42" s="184"/>
+      <c r="B42" s="150"/>
+      <c r="C42" s="152"/>
+      <c r="D42" s="152"/>
+      <c r="E42" s="152"/>
     </row>
     <row r="43" spans="2:5">
-      <c r="B43" s="182"/>
-      <c r="C43" s="184"/>
-      <c r="D43" s="184"/>
-      <c r="E43" s="184"/>
+      <c r="B43" s="150"/>
+      <c r="C43" s="152"/>
+      <c r="D43" s="152"/>
+      <c r="E43" s="152"/>
     </row>
     <row r="44" spans="2:5">
-      <c r="B44" s="182"/>
-      <c r="C44" s="184"/>
-      <c r="D44" s="184"/>
-      <c r="E44" s="184"/>
+      <c r="B44" s="150"/>
+      <c r="C44" s="152"/>
+      <c r="D44" s="152"/>
+      <c r="E44" s="152"/>
     </row>
     <row r="45" spans="2:5">
-      <c r="B45" s="182"/>
-      <c r="C45" s="184"/>
-      <c r="D45" s="184"/>
-      <c r="E45" s="184"/>
+      <c r="B45" s="150"/>
+      <c r="C45" s="152"/>
+      <c r="D45" s="152"/>
+      <c r="E45" s="152"/>
     </row>
     <row r="46" spans="2:5">
-      <c r="B46" s="182"/>
-      <c r="C46" s="184"/>
-      <c r="D46" s="184"/>
-      <c r="E46" s="184"/>
+      <c r="B46" s="150"/>
+      <c r="C46" s="152"/>
+      <c r="D46" s="152"/>
+      <c r="E46" s="152"/>
     </row>
     <row r="47" spans="2:5">
-      <c r="B47" s="182"/>
-      <c r="C47" s="184"/>
-      <c r="D47" s="184"/>
-      <c r="E47" s="184"/>
+      <c r="B47" s="150"/>
+      <c r="C47" s="152"/>
+      <c r="D47" s="152"/>
+      <c r="E47" s="152"/>
     </row>
     <row r="48" spans="2:5">
-      <c r="B48" s="182"/>
-      <c r="C48" s="184"/>
-      <c r="D48" s="184"/>
-      <c r="E48" s="184"/>
+      <c r="B48" s="150"/>
+      <c r="C48" s="152"/>
+      <c r="D48" s="152"/>
+      <c r="E48" s="152"/>
     </row>
     <row r="49" spans="2:5">
-      <c r="B49" s="182"/>
-      <c r="C49" s="184"/>
-      <c r="D49" s="184"/>
-      <c r="E49" s="184"/>
+      <c r="B49" s="150"/>
+      <c r="C49" s="152"/>
+      <c r="D49" s="152"/>
+      <c r="E49" s="152"/>
     </row>
     <row r="50" spans="2:5">
-      <c r="B50" s="182"/>
-      <c r="C50" s="184"/>
-      <c r="D50" s="184"/>
-      <c r="E50" s="184"/>
+      <c r="B50" s="150"/>
+      <c r="C50" s="152"/>
+      <c r="D50" s="152"/>
+      <c r="E50" s="152"/>
     </row>
     <row r="51" spans="2:5">
-      <c r="B51" s="182"/>
-      <c r="C51" s="184"/>
-      <c r="D51" s="184"/>
-      <c r="E51" s="184"/>
+      <c r="B51" s="150"/>
+      <c r="C51" s="152"/>
+      <c r="D51" s="152"/>
+      <c r="E51" s="152"/>
     </row>
     <row r="52" spans="2:5">
-      <c r="B52" s="182"/>
-      <c r="C52" s="184"/>
-      <c r="D52" s="184"/>
-      <c r="E52" s="184"/>
+      <c r="B52" s="150"/>
+      <c r="C52" s="152"/>
+      <c r="D52" s="152"/>
+      <c r="E52" s="152"/>
     </row>
     <row r="53" spans="2:5">
-      <c r="B53" s="182"/>
-      <c r="C53" s="184"/>
-      <c r="D53" s="184"/>
-      <c r="E53" s="184"/>
+      <c r="B53" s="150"/>
+      <c r="C53" s="152"/>
+      <c r="D53" s="152"/>
+      <c r="E53" s="152"/>
     </row>
     <row r="54" spans="2:5">
-      <c r="B54" s="182"/>
-      <c r="C54" s="184"/>
-      <c r="D54" s="184"/>
-      <c r="E54" s="184"/>
+      <c r="B54" s="150"/>
+      <c r="C54" s="152"/>
+      <c r="D54" s="152"/>
+      <c r="E54" s="152"/>
     </row>
     <row r="55" spans="2:5">
-      <c r="B55" s="182"/>
-      <c r="C55" s="184"/>
-      <c r="D55" s="184"/>
-      <c r="E55" s="184"/>
+      <c r="B55" s="150"/>
+      <c r="C55" s="152"/>
+      <c r="D55" s="152"/>
+      <c r="E55" s="152"/>
     </row>
     <row r="56" spans="2:5">
-      <c r="B56" s="182"/>
-      <c r="C56" s="184"/>
-      <c r="D56" s="184"/>
-      <c r="E56" s="184"/>
+      <c r="B56" s="150"/>
+      <c r="C56" s="152"/>
+      <c r="D56" s="152"/>
+      <c r="E56" s="152"/>
     </row>
     <row r="57" spans="2:5">
-      <c r="B57" s="182"/>
-      <c r="C57" s="184"/>
-      <c r="D57" s="184"/>
-      <c r="E57" s="184"/>
+      <c r="B57" s="150"/>
+      <c r="C57" s="152"/>
+      <c r="D57" s="152"/>
+      <c r="E57" s="152"/>
     </row>
     <row r="58" spans="2:5">
-      <c r="B58" s="182"/>
-      <c r="C58" s="184"/>
-      <c r="D58" s="184"/>
-      <c r="E58" s="184"/>
+      <c r="B58" s="150"/>
+      <c r="C58" s="152"/>
+      <c r="D58" s="152"/>
+      <c r="E58" s="152"/>
     </row>
     <row r="59" spans="2:5">
-      <c r="B59" s="182"/>
-      <c r="C59" s="184"/>
-      <c r="D59" s="184"/>
-      <c r="E59" s="184"/>
+      <c r="B59" s="150"/>
+      <c r="C59" s="152"/>
+      <c r="D59" s="152"/>
+      <c r="E59" s="152"/>
     </row>
     <row r="60" spans="2:5">
-      <c r="B60" s="182"/>
-      <c r="C60" s="184"/>
-      <c r="D60" s="184"/>
-      <c r="E60" s="184"/>
+      <c r="B60" s="150"/>
+      <c r="C60" s="152"/>
+      <c r="D60" s="152"/>
+      <c r="E60" s="152"/>
     </row>
     <row r="61" spans="2:5">
-      <c r="B61" s="182"/>
-      <c r="C61" s="184"/>
-      <c r="D61" s="184"/>
-      <c r="E61" s="184"/>
+      <c r="B61" s="150"/>
+      <c r="C61" s="152"/>
+      <c r="D61" s="152"/>
+      <c r="E61" s="152"/>
     </row>
     <row r="62" spans="2:5">
-      <c r="B62" s="182"/>
-      <c r="C62" s="184"/>
-      <c r="D62" s="184"/>
-      <c r="E62" s="184"/>
+      <c r="B62" s="150"/>
+      <c r="C62" s="152"/>
+      <c r="D62" s="152"/>
+      <c r="E62" s="152"/>
     </row>
     <row r="63" spans="2:5">
-      <c r="B63" s="182"/>
-      <c r="C63" s="184"/>
-      <c r="D63" s="184"/>
-      <c r="E63" s="184"/>
+      <c r="B63" s="150"/>
+      <c r="C63" s="152"/>
+      <c r="D63" s="152"/>
+      <c r="E63" s="152"/>
     </row>
     <row r="64" spans="2:5">
-      <c r="B64" s="182"/>
-      <c r="C64" s="184"/>
-      <c r="D64" s="184"/>
-      <c r="E64" s="184"/>
+      <c r="B64" s="150"/>
+      <c r="C64" s="152"/>
+      <c r="D64" s="152"/>
+      <c r="E64" s="152"/>
     </row>
     <row r="65" spans="2:5">
-      <c r="B65" s="182"/>
-      <c r="C65" s="184"/>
-      <c r="D65" s="184"/>
-      <c r="E65" s="184"/>
+      <c r="B65" s="150"/>
+      <c r="C65" s="152"/>
+      <c r="D65" s="152"/>
+      <c r="E65" s="152"/>
     </row>
     <row r="66" spans="2:5">
-      <c r="B66" s="182"/>
-      <c r="C66" s="184"/>
-      <c r="D66" s="184"/>
-      <c r="E66" s="184"/>
+      <c r="B66" s="150"/>
+      <c r="C66" s="152"/>
+      <c r="D66" s="152"/>
+      <c r="E66" s="152"/>
     </row>
     <row r="67" spans="2:5">
-      <c r="B67" s="182"/>
-      <c r="C67" s="184"/>
-      <c r="D67" s="184"/>
-      <c r="E67" s="184"/>
+      <c r="B67" s="150"/>
+      <c r="C67" s="152"/>
+      <c r="D67" s="152"/>
+      <c r="E67" s="152"/>
     </row>
     <row r="68" spans="2:5">
-      <c r="B68" s="182"/>
-      <c r="C68" s="184"/>
-      <c r="D68" s="184"/>
-      <c r="E68" s="184"/>
+      <c r="B68" s="150"/>
+      <c r="C68" s="152"/>
+      <c r="D68" s="152"/>
+      <c r="E68" s="152"/>
     </row>
     <row r="69" spans="2:5">
-      <c r="B69" s="182"/>
-      <c r="C69" s="184"/>
-      <c r="D69" s="184"/>
-      <c r="E69" s="184"/>
+      <c r="B69" s="150"/>
+      <c r="C69" s="152"/>
+      <c r="D69" s="152"/>
+      <c r="E69" s="152"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3949,11 +3816,11 @@
   <dimension ref="A1:AH28"/>
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
-    <col min="1" max="20" width="3.66666666666667" style="143"/>
-    <col min="21" max="21" width="5.88888888888889" style="143" customWidth="1"/>
-    <col min="22" max="33" width="3.66666666666667" style="143"/>
-    <col min="34" max="34" width="13" style="143" customWidth="1"/>
-    <col min="35" max="16384" width="3.66666666666667" style="143"/>
+    <col min="1" max="20" width="3.66666666666667" style="116"/>
+    <col min="21" max="21" width="5.88888888888889" style="116" customWidth="1"/>
+    <col min="22" max="33" width="3.66666666666667" style="116"/>
+    <col min="34" max="34" width="13" style="116" customWidth="1"/>
+    <col min="35" max="16384" width="3.66666666666667" style="116"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:34">
@@ -3969,42 +3836,42 @@
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
-      <c r="K1" s="165"/>
-      <c r="L1" s="24" t="s">
+      <c r="K1" s="136"/>
+      <c r="L1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="M1" s="25"/>
-      <c r="N1" s="25"/>
-      <c r="O1" s="25"/>
-      <c r="P1" s="125"/>
-      <c r="Q1" s="26" t="s">
+      <c r="M1" s="24"/>
+      <c r="N1" s="24"/>
+      <c r="O1" s="24"/>
+      <c r="P1" s="100"/>
+      <c r="Q1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="93"/>
-      <c r="S1" s="93"/>
-      <c r="T1" s="93"/>
-      <c r="U1" s="93"/>
-      <c r="V1" s="27" t="s">
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="78"/>
+      <c r="U1" s="78"/>
+      <c r="V1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="W1" s="27"/>
-      <c r="X1" s="27"/>
-      <c r="Y1" s="28" t="s">
+      <c r="W1" s="26"/>
+      <c r="X1" s="26"/>
+      <c r="Y1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="Z1" s="95"/>
-      <c r="AA1" s="95"/>
-      <c r="AB1" s="175"/>
-      <c r="AC1" s="29" t="s">
+      <c r="Z1" s="16"/>
+      <c r="AA1" s="16"/>
+      <c r="AB1" s="17"/>
+      <c r="AC1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="AD1" s="176"/>
-      <c r="AE1" s="177"/>
-      <c r="AF1" s="186" t="s">
+      <c r="AD1" s="144"/>
+      <c r="AE1" s="145"/>
+      <c r="AF1" s="154" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="139"/>
-      <c r="AH1" s="139"/>
+      <c r="AG1" s="112"/>
+      <c r="AH1" s="112"/>
     </row>
     <row r="2" customHeight="1" spans="1:34">
       <c r="A2" s="6"/>
@@ -4017,30 +3884,30 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
-      <c r="K2" s="166"/>
-      <c r="L2" s="32"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="33"/>
-      <c r="O2" s="33"/>
-      <c r="P2" s="126"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="94"/>
-      <c r="S2" s="94"/>
-      <c r="T2" s="94"/>
-      <c r="U2" s="94"/>
-      <c r="V2" s="27"/>
-      <c r="W2" s="27"/>
-      <c r="X2" s="27"/>
-      <c r="Y2" s="35"/>
-      <c r="Z2" s="96"/>
-      <c r="AA2" s="96"/>
-      <c r="AB2" s="178"/>
-      <c r="AC2" s="36"/>
-      <c r="AD2" s="115"/>
-      <c r="AE2" s="116"/>
-      <c r="AF2" s="37"/>
-      <c r="AG2" s="140"/>
-      <c r="AH2" s="140"/>
+      <c r="K2" s="137"/>
+      <c r="L2" s="31"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="32"/>
+      <c r="O2" s="32"/>
+      <c r="P2" s="101"/>
+      <c r="Q2" s="33"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="79"/>
+      <c r="T2" s="79"/>
+      <c r="U2" s="79"/>
+      <c r="V2" s="26"/>
+      <c r="W2" s="26"/>
+      <c r="X2" s="26"/>
+      <c r="Y2" s="34"/>
+      <c r="Z2" s="80"/>
+      <c r="AA2" s="80"/>
+      <c r="AB2" s="146"/>
+      <c r="AC2" s="35"/>
+      <c r="AD2" s="94"/>
+      <c r="AE2" s="95"/>
+      <c r="AF2" s="36"/>
+      <c r="AG2" s="113"/>
+      <c r="AH2" s="113"/>
     </row>
     <row r="3" customHeight="1" spans="1:34">
       <c r="A3" s="6"/>
@@ -4053,42 +3920,42 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
-      <c r="K3" s="166"/>
-      <c r="L3" s="24" t="s">
+      <c r="K3" s="137"/>
+      <c r="L3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="M3" s="25"/>
-      <c r="N3" s="25"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="125"/>
-      <c r="Q3" s="26" t="s">
+      <c r="M3" s="24"/>
+      <c r="N3" s="24"/>
+      <c r="O3" s="24"/>
+      <c r="P3" s="100"/>
+      <c r="Q3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="93"/>
-      <c r="S3" s="93"/>
-      <c r="T3" s="93"/>
-      <c r="U3" s="93"/>
-      <c r="V3" s="27" t="s">
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="78"/>
+      <c r="U3" s="78"/>
+      <c r="V3" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="W3" s="27"/>
-      <c r="X3" s="27"/>
-      <c r="Y3" s="28" t="s">
+      <c r="W3" s="26"/>
+      <c r="X3" s="26"/>
+      <c r="Y3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="Z3" s="95"/>
-      <c r="AA3" s="95"/>
-      <c r="AB3" s="175"/>
-      <c r="AC3" s="27" t="s">
+      <c r="Z3" s="16"/>
+      <c r="AA3" s="16"/>
+      <c r="AB3" s="17"/>
+      <c r="AC3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="AD3" s="27"/>
-      <c r="AE3" s="27"/>
-      <c r="AF3" s="186" t="s">
+      <c r="AD3" s="26"/>
+      <c r="AE3" s="26"/>
+      <c r="AF3" s="154" t="s">
         <v>18</v>
       </c>
-      <c r="AG3" s="139"/>
-      <c r="AH3" s="139"/>
+      <c r="AG3" s="112"/>
+      <c r="AH3" s="112"/>
     </row>
     <row r="4" customHeight="1" spans="1:34">
       <c r="A4" s="8"/>
@@ -4101,601 +3968,601 @@
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
-      <c r="K4" s="167"/>
-      <c r="L4" s="32"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="33"/>
-      <c r="O4" s="33"/>
-      <c r="P4" s="126"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="94"/>
-      <c r="S4" s="94"/>
-      <c r="T4" s="94"/>
-      <c r="U4" s="94"/>
-      <c r="V4" s="27"/>
-      <c r="W4" s="27"/>
-      <c r="X4" s="27"/>
-      <c r="Y4" s="35"/>
-      <c r="Z4" s="96"/>
-      <c r="AA4" s="96"/>
-      <c r="AB4" s="178"/>
-      <c r="AC4" s="27"/>
-      <c r="AD4" s="27"/>
-      <c r="AE4" s="27"/>
-      <c r="AF4" s="37"/>
-      <c r="AG4" s="140"/>
-      <c r="AH4" s="140"/>
+      <c r="K4" s="138"/>
+      <c r="L4" s="31"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="32"/>
+      <c r="O4" s="32"/>
+      <c r="P4" s="101"/>
+      <c r="Q4" s="33"/>
+      <c r="R4" s="79"/>
+      <c r="S4" s="79"/>
+      <c r="T4" s="79"/>
+      <c r="U4" s="79"/>
+      <c r="V4" s="26"/>
+      <c r="W4" s="26"/>
+      <c r="X4" s="26"/>
+      <c r="Y4" s="34"/>
+      <c r="Z4" s="80"/>
+      <c r="AA4" s="80"/>
+      <c r="AB4" s="146"/>
+      <c r="AC4" s="26"/>
+      <c r="AD4" s="26"/>
+      <c r="AE4" s="26"/>
+      <c r="AF4" s="36"/>
+      <c r="AG4" s="113"/>
+      <c r="AH4" s="113"/>
     </row>
     <row r="5" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A5" s="144" t="s">
+      <c r="A5" s="117" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="145"/>
-      <c r="C5" s="145"/>
-      <c r="D5" s="145"/>
-      <c r="E5" s="145"/>
-      <c r="F5" s="145"/>
-      <c r="G5" s="146"/>
-      <c r="H5" s="147" t="s">
+      <c r="B5" s="118"/>
+      <c r="C5" s="118"/>
+      <c r="D5" s="118"/>
+      <c r="E5" s="118"/>
+      <c r="F5" s="118"/>
+      <c r="G5" s="119"/>
+      <c r="H5" s="120" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="168"/>
-      <c r="J5" s="168"/>
-      <c r="K5" s="168"/>
-      <c r="L5" s="168"/>
-      <c r="M5" s="168"/>
-      <c r="N5" s="168"/>
-      <c r="O5" s="168"/>
-      <c r="P5" s="168"/>
-      <c r="Q5" s="168"/>
-      <c r="R5" s="168"/>
-      <c r="S5" s="168"/>
-      <c r="T5" s="168"/>
-      <c r="U5" s="168"/>
-      <c r="V5" s="168"/>
-      <c r="W5" s="168"/>
-      <c r="X5" s="168"/>
-      <c r="Y5" s="168"/>
-      <c r="Z5" s="168"/>
-      <c r="AA5" s="168"/>
-      <c r="AB5" s="168"/>
-      <c r="AC5" s="168"/>
-      <c r="AD5" s="168"/>
-      <c r="AE5" s="168"/>
-      <c r="AF5" s="168"/>
-      <c r="AG5" s="168"/>
-      <c r="AH5" s="168"/>
+      <c r="I5" s="139"/>
+      <c r="J5" s="139"/>
+      <c r="K5" s="139"/>
+      <c r="L5" s="139"/>
+      <c r="M5" s="139"/>
+      <c r="N5" s="139"/>
+      <c r="O5" s="139"/>
+      <c r="P5" s="139"/>
+      <c r="Q5" s="139"/>
+      <c r="R5" s="139"/>
+      <c r="S5" s="139"/>
+      <c r="T5" s="139"/>
+      <c r="U5" s="139"/>
+      <c r="V5" s="139"/>
+      <c r="W5" s="139"/>
+      <c r="X5" s="139"/>
+      <c r="Y5" s="139"/>
+      <c r="Z5" s="139"/>
+      <c r="AA5" s="139"/>
+      <c r="AB5" s="139"/>
+      <c r="AC5" s="139"/>
+      <c r="AD5" s="139"/>
+      <c r="AE5" s="139"/>
+      <c r="AF5" s="139"/>
+      <c r="AG5" s="139"/>
+      <c r="AH5" s="139"/>
     </row>
     <row r="6" customFormat="1" ht="63.75" customHeight="1" spans="1:34">
-      <c r="A6" s="144" t="s">
+      <c r="A6" s="117" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="145"/>
-      <c r="C6" s="145"/>
-      <c r="D6" s="145"/>
-      <c r="E6" s="145"/>
-      <c r="F6" s="145"/>
-      <c r="G6" s="146"/>
-      <c r="H6" s="148" t="s">
+      <c r="B6" s="118"/>
+      <c r="C6" s="118"/>
+      <c r="D6" s="118"/>
+      <c r="E6" s="118"/>
+      <c r="F6" s="118"/>
+      <c r="G6" s="119"/>
+      <c r="H6" s="121" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="168"/>
-      <c r="J6" s="168"/>
-      <c r="K6" s="168"/>
-      <c r="L6" s="168"/>
-      <c r="M6" s="168"/>
-      <c r="N6" s="168"/>
-      <c r="O6" s="168"/>
-      <c r="P6" s="168"/>
-      <c r="Q6" s="168"/>
-      <c r="R6" s="168"/>
-      <c r="S6" s="168"/>
-      <c r="T6" s="168"/>
-      <c r="U6" s="168"/>
-      <c r="V6" s="168"/>
-      <c r="W6" s="168"/>
-      <c r="X6" s="168"/>
-      <c r="Y6" s="168"/>
-      <c r="Z6" s="168"/>
-      <c r="AA6" s="168"/>
-      <c r="AB6" s="168"/>
-      <c r="AC6" s="168"/>
-      <c r="AD6" s="168"/>
-      <c r="AE6" s="168"/>
-      <c r="AF6" s="168"/>
-      <c r="AG6" s="168"/>
-      <c r="AH6" s="168"/>
+      <c r="I6" s="139"/>
+      <c r="J6" s="139"/>
+      <c r="K6" s="139"/>
+      <c r="L6" s="139"/>
+      <c r="M6" s="139"/>
+      <c r="N6" s="139"/>
+      <c r="O6" s="139"/>
+      <c r="P6" s="139"/>
+      <c r="Q6" s="139"/>
+      <c r="R6" s="139"/>
+      <c r="S6" s="139"/>
+      <c r="T6" s="139"/>
+      <c r="U6" s="139"/>
+      <c r="V6" s="139"/>
+      <c r="W6" s="139"/>
+      <c r="X6" s="139"/>
+      <c r="Y6" s="139"/>
+      <c r="Z6" s="139"/>
+      <c r="AA6" s="139"/>
+      <c r="AB6" s="139"/>
+      <c r="AC6" s="139"/>
+      <c r="AD6" s="139"/>
+      <c r="AE6" s="139"/>
+      <c r="AF6" s="139"/>
+      <c r="AG6" s="139"/>
+      <c r="AH6" s="139"/>
     </row>
     <row r="7" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A7" s="144" t="s">
+      <c r="A7" s="117" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="145"/>
-      <c r="C7" s="145"/>
-      <c r="D7" s="145"/>
-      <c r="E7" s="145"/>
-      <c r="F7" s="145"/>
-      <c r="G7" s="146"/>
-      <c r="H7" s="147" t="s">
+      <c r="B7" s="118"/>
+      <c r="C7" s="118"/>
+      <c r="D7" s="118"/>
+      <c r="E7" s="118"/>
+      <c r="F7" s="118"/>
+      <c r="G7" s="119"/>
+      <c r="H7" s="120" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="168"/>
-      <c r="J7" s="168"/>
-      <c r="K7" s="168"/>
-      <c r="L7" s="168"/>
-      <c r="M7" s="168"/>
-      <c r="N7" s="168"/>
-      <c r="O7" s="168"/>
-      <c r="P7" s="168"/>
-      <c r="Q7" s="168"/>
-      <c r="R7" s="168"/>
-      <c r="S7" s="168"/>
-      <c r="T7" s="168"/>
-      <c r="U7" s="168"/>
-      <c r="V7" s="168"/>
-      <c r="W7" s="168"/>
-      <c r="X7" s="168"/>
-      <c r="Y7" s="168"/>
-      <c r="Z7" s="168"/>
-      <c r="AA7" s="168"/>
-      <c r="AB7" s="168"/>
-      <c r="AC7" s="168"/>
-      <c r="AD7" s="168"/>
-      <c r="AE7" s="168"/>
-      <c r="AF7" s="168"/>
-      <c r="AG7" s="168"/>
-      <c r="AH7" s="168"/>
+      <c r="I7" s="139"/>
+      <c r="J7" s="139"/>
+      <c r="K7" s="139"/>
+      <c r="L7" s="139"/>
+      <c r="M7" s="139"/>
+      <c r="N7" s="139"/>
+      <c r="O7" s="139"/>
+      <c r="P7" s="139"/>
+      <c r="Q7" s="139"/>
+      <c r="R7" s="139"/>
+      <c r="S7" s="139"/>
+      <c r="T7" s="139"/>
+      <c r="U7" s="139"/>
+      <c r="V7" s="139"/>
+      <c r="W7" s="139"/>
+      <c r="X7" s="139"/>
+      <c r="Y7" s="139"/>
+      <c r="Z7" s="139"/>
+      <c r="AA7" s="139"/>
+      <c r="AB7" s="139"/>
+      <c r="AC7" s="139"/>
+      <c r="AD7" s="139"/>
+      <c r="AE7" s="139"/>
+      <c r="AF7" s="139"/>
+      <c r="AG7" s="139"/>
+      <c r="AH7" s="139"/>
     </row>
     <row r="8" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A8" s="144" t="s">
+      <c r="A8" s="117" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="145"/>
-      <c r="C8" s="145"/>
-      <c r="D8" s="145"/>
-      <c r="E8" s="145"/>
-      <c r="F8" s="145"/>
-      <c r="G8" s="146"/>
-      <c r="H8" s="147" t="s">
+      <c r="B8" s="118"/>
+      <c r="C8" s="118"/>
+      <c r="D8" s="118"/>
+      <c r="E8" s="118"/>
+      <c r="F8" s="118"/>
+      <c r="G8" s="119"/>
+      <c r="H8" s="120" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="168"/>
-      <c r="J8" s="168"/>
-      <c r="K8" s="168"/>
-      <c r="L8" s="168"/>
-      <c r="M8" s="168"/>
-      <c r="N8" s="168"/>
-      <c r="O8" s="168"/>
-      <c r="P8" s="168"/>
-      <c r="Q8" s="168"/>
-      <c r="R8" s="168"/>
-      <c r="S8" s="168"/>
-      <c r="T8" s="168"/>
-      <c r="U8" s="168"/>
-      <c r="V8" s="168"/>
-      <c r="W8" s="168"/>
-      <c r="X8" s="168"/>
-      <c r="Y8" s="168"/>
-      <c r="Z8" s="168"/>
-      <c r="AA8" s="168"/>
-      <c r="AB8" s="168"/>
-      <c r="AC8" s="168"/>
-      <c r="AD8" s="168"/>
-      <c r="AE8" s="168"/>
-      <c r="AF8" s="168"/>
-      <c r="AG8" s="168"/>
-      <c r="AH8" s="168"/>
+      <c r="I8" s="139"/>
+      <c r="J8" s="139"/>
+      <c r="K8" s="139"/>
+      <c r="L8" s="139"/>
+      <c r="M8" s="139"/>
+      <c r="N8" s="139"/>
+      <c r="O8" s="139"/>
+      <c r="P8" s="139"/>
+      <c r="Q8" s="139"/>
+      <c r="R8" s="139"/>
+      <c r="S8" s="139"/>
+      <c r="T8" s="139"/>
+      <c r="U8" s="139"/>
+      <c r="V8" s="139"/>
+      <c r="W8" s="139"/>
+      <c r="X8" s="139"/>
+      <c r="Y8" s="139"/>
+      <c r="Z8" s="139"/>
+      <c r="AA8" s="139"/>
+      <c r="AB8" s="139"/>
+      <c r="AC8" s="139"/>
+      <c r="AD8" s="139"/>
+      <c r="AE8" s="139"/>
+      <c r="AF8" s="139"/>
+      <c r="AG8" s="139"/>
+      <c r="AH8" s="139"/>
     </row>
     <row r="9" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A9" s="144" t="s">
+      <c r="A9" s="117" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="145"/>
-      <c r="C9" s="145"/>
-      <c r="D9" s="145"/>
-      <c r="E9" s="145"/>
-      <c r="F9" s="145"/>
-      <c r="G9" s="146"/>
-      <c r="H9" s="147" t="s">
+      <c r="B9" s="118"/>
+      <c r="C9" s="118"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="118"/>
+      <c r="F9" s="118"/>
+      <c r="G9" s="119"/>
+      <c r="H9" s="120" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="168"/>
-      <c r="J9" s="168"/>
-      <c r="K9" s="168"/>
-      <c r="L9" s="168"/>
-      <c r="M9" s="168"/>
-      <c r="N9" s="168"/>
-      <c r="O9" s="168"/>
-      <c r="P9" s="168"/>
-      <c r="Q9" s="168"/>
-      <c r="R9" s="168"/>
-      <c r="S9" s="168"/>
-      <c r="T9" s="168"/>
-      <c r="U9" s="168"/>
-      <c r="V9" s="168"/>
-      <c r="W9" s="168"/>
-      <c r="X9" s="168"/>
-      <c r="Y9" s="168"/>
-      <c r="Z9" s="168"/>
-      <c r="AA9" s="168"/>
-      <c r="AB9" s="168"/>
-      <c r="AC9" s="168"/>
-      <c r="AD9" s="168"/>
-      <c r="AE9" s="168"/>
-      <c r="AF9" s="168"/>
-      <c r="AG9" s="168"/>
-      <c r="AH9" s="168"/>
+      <c r="I9" s="139"/>
+      <c r="J9" s="139"/>
+      <c r="K9" s="139"/>
+      <c r="L9" s="139"/>
+      <c r="M9" s="139"/>
+      <c r="N9" s="139"/>
+      <c r="O9" s="139"/>
+      <c r="P9" s="139"/>
+      <c r="Q9" s="139"/>
+      <c r="R9" s="139"/>
+      <c r="S9" s="139"/>
+      <c r="T9" s="139"/>
+      <c r="U9" s="139"/>
+      <c r="V9" s="139"/>
+      <c r="W9" s="139"/>
+      <c r="X9" s="139"/>
+      <c r="Y9" s="139"/>
+      <c r="Z9" s="139"/>
+      <c r="AA9" s="139"/>
+      <c r="AB9" s="139"/>
+      <c r="AC9" s="139"/>
+      <c r="AD9" s="139"/>
+      <c r="AE9" s="139"/>
+      <c r="AF9" s="139"/>
+      <c r="AG9" s="139"/>
+      <c r="AH9" s="139"/>
     </row>
     <row r="10" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A10" s="149" t="s">
+      <c r="A10" s="122" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="150"/>
-      <c r="C10" s="150"/>
-      <c r="D10" s="150"/>
-      <c r="E10" s="150"/>
-      <c r="F10" s="150"/>
-      <c r="G10" s="151"/>
-      <c r="H10" s="152" t="s">
+      <c r="B10" s="123"/>
+      <c r="C10" s="123"/>
+      <c r="D10" s="123"/>
+      <c r="E10" s="123"/>
+      <c r="F10" s="123"/>
+      <c r="G10" s="124"/>
+      <c r="H10" s="125" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="169"/>
-      <c r="J10" s="169"/>
-      <c r="K10" s="169"/>
-      <c r="L10" s="169"/>
-      <c r="M10" s="169"/>
-      <c r="N10" s="169"/>
-      <c r="O10" s="169"/>
-      <c r="P10" s="169"/>
-      <c r="Q10" s="169"/>
-      <c r="R10" s="169"/>
-      <c r="S10" s="169"/>
-      <c r="T10" s="169"/>
-      <c r="U10" s="169"/>
-      <c r="V10" s="169"/>
-      <c r="W10" s="169"/>
-      <c r="X10" s="169"/>
-      <c r="Y10" s="169"/>
-      <c r="Z10" s="169"/>
-      <c r="AA10" s="169"/>
-      <c r="AB10" s="169"/>
-      <c r="AC10" s="169"/>
-      <c r="AD10" s="169"/>
-      <c r="AE10" s="169"/>
-      <c r="AF10" s="169"/>
-      <c r="AG10" s="169"/>
-      <c r="AH10" s="169"/>
+      <c r="I10" s="140"/>
+      <c r="J10" s="140"/>
+      <c r="K10" s="140"/>
+      <c r="L10" s="140"/>
+      <c r="M10" s="140"/>
+      <c r="N10" s="140"/>
+      <c r="O10" s="140"/>
+      <c r="P10" s="140"/>
+      <c r="Q10" s="140"/>
+      <c r="R10" s="140"/>
+      <c r="S10" s="140"/>
+      <c r="T10" s="140"/>
+      <c r="U10" s="140"/>
+      <c r="V10" s="140"/>
+      <c r="W10" s="140"/>
+      <c r="X10" s="140"/>
+      <c r="Y10" s="140"/>
+      <c r="Z10" s="140"/>
+      <c r="AA10" s="140"/>
+      <c r="AB10" s="140"/>
+      <c r="AC10" s="140"/>
+      <c r="AD10" s="140"/>
+      <c r="AE10" s="140"/>
+      <c r="AF10" s="140"/>
+      <c r="AG10" s="140"/>
+      <c r="AH10" s="140"/>
     </row>
     <row r="11" s="3" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A11" s="153" t="s">
+      <c r="A11" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="B11" s="154"/>
-      <c r="C11" s="154"/>
-      <c r="D11" s="154"/>
-      <c r="E11" s="154"/>
-      <c r="F11" s="154"/>
-      <c r="G11" s="154"/>
-      <c r="H11" s="154"/>
-      <c r="I11" s="154"/>
-      <c r="J11" s="154"/>
-      <c r="K11" s="154"/>
-      <c r="L11" s="154"/>
-      <c r="M11" s="154"/>
-      <c r="N11" s="154"/>
-      <c r="O11" s="154"/>
-      <c r="P11" s="154"/>
-      <c r="Q11" s="154"/>
-      <c r="R11" s="154"/>
-      <c r="S11" s="154"/>
-      <c r="T11" s="154"/>
-      <c r="U11" s="154"/>
-      <c r="V11" s="154"/>
-      <c r="W11" s="154"/>
-      <c r="X11" s="154"/>
-      <c r="Y11" s="154"/>
-      <c r="Z11" s="154"/>
-      <c r="AA11" s="154"/>
-      <c r="AB11" s="154"/>
-      <c r="AC11" s="154"/>
-      <c r="AD11" s="154"/>
-      <c r="AE11" s="154"/>
-      <c r="AF11" s="154"/>
-      <c r="AG11" s="154"/>
-      <c r="AH11" s="154"/>
+      <c r="B11" s="13"/>
+      <c r="C11" s="13"/>
+      <c r="D11" s="13"/>
+      <c r="E11" s="13"/>
+      <c r="F11" s="13"/>
+      <c r="G11" s="13"/>
+      <c r="H11" s="13"/>
+      <c r="I11" s="13"/>
+      <c r="J11" s="13"/>
+      <c r="K11" s="13"/>
+      <c r="L11" s="13"/>
+      <c r="M11" s="13"/>
+      <c r="N11" s="13"/>
+      <c r="O11" s="13"/>
+      <c r="P11" s="13"/>
+      <c r="Q11" s="13"/>
+      <c r="R11" s="13"/>
+      <c r="S11" s="13"/>
+      <c r="T11" s="13"/>
+      <c r="U11" s="13"/>
+      <c r="V11" s="13"/>
+      <c r="W11" s="13"/>
+      <c r="X11" s="13"/>
+      <c r="Y11" s="13"/>
+      <c r="Z11" s="13"/>
+      <c r="AA11" s="13"/>
+      <c r="AB11" s="13"/>
+      <c r="AC11" s="13"/>
+      <c r="AD11" s="13"/>
+      <c r="AE11" s="13"/>
+      <c r="AF11" s="13"/>
+      <c r="AG11" s="13"/>
+      <c r="AH11" s="13"/>
     </row>
     <row r="12" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A12" s="155"/>
+      <c r="A12" s="126"/>
     </row>
     <row r="13" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A13" s="155"/>
+      <c r="A13" s="126"/>
     </row>
     <row r="14" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A14" s="155"/>
+      <c r="A14" s="126"/>
     </row>
     <row r="15" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A15" s="155"/>
+      <c r="A15" s="126"/>
     </row>
     <row r="16" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A16" s="155"/>
+      <c r="A16" s="126"/>
     </row>
     <row r="17" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A17" s="155"/>
+      <c r="A17" s="126"/>
     </row>
     <row r="18" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A18" s="155"/>
+      <c r="A18" s="126"/>
     </row>
     <row r="19" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A19" s="155"/>
+      <c r="A19" s="126"/>
     </row>
     <row r="20" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A20" s="155"/>
+      <c r="A20" s="126"/>
     </row>
     <row r="21" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A21" s="155"/>
+      <c r="A21" s="126"/>
     </row>
     <row r="22" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A22" s="155"/>
+      <c r="A22" s="126"/>
     </row>
     <row r="23" s="3" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A23" s="156"/>
-      <c r="B23" s="157"/>
-      <c r="C23" s="157"/>
-      <c r="D23" s="157"/>
-      <c r="E23" s="157"/>
-      <c r="F23" s="157"/>
-      <c r="G23" s="157"/>
-      <c r="H23" s="157"/>
-      <c r="I23" s="157"/>
-      <c r="J23" s="157"/>
-      <c r="K23" s="157"/>
-      <c r="L23" s="157"/>
-      <c r="M23" s="157"/>
-      <c r="N23" s="157"/>
-      <c r="O23" s="157"/>
-      <c r="P23" s="157"/>
-      <c r="Q23" s="157"/>
-      <c r="R23" s="157"/>
-      <c r="S23" s="157"/>
-      <c r="T23" s="157"/>
-      <c r="U23" s="157"/>
-      <c r="V23" s="157"/>
-      <c r="W23" s="157"/>
-      <c r="X23" s="157"/>
-      <c r="Y23" s="157"/>
-      <c r="Z23" s="157"/>
-      <c r="AA23" s="157"/>
-      <c r="AB23" s="157"/>
-      <c r="AC23" s="157"/>
-      <c r="AD23" s="157"/>
-      <c r="AE23" s="157"/>
-      <c r="AF23" s="157"/>
-      <c r="AG23" s="157"/>
-      <c r="AH23" s="157"/>
+      <c r="A23" s="127"/>
+      <c r="B23" s="128"/>
+      <c r="C23" s="128"/>
+      <c r="D23" s="128"/>
+      <c r="E23" s="128"/>
+      <c r="F23" s="128"/>
+      <c r="G23" s="128"/>
+      <c r="H23" s="128"/>
+      <c r="I23" s="128"/>
+      <c r="J23" s="128"/>
+      <c r="K23" s="128"/>
+      <c r="L23" s="128"/>
+      <c r="M23" s="128"/>
+      <c r="N23" s="128"/>
+      <c r="O23" s="128"/>
+      <c r="P23" s="128"/>
+      <c r="Q23" s="128"/>
+      <c r="R23" s="128"/>
+      <c r="S23" s="128"/>
+      <c r="T23" s="128"/>
+      <c r="U23" s="128"/>
+      <c r="V23" s="128"/>
+      <c r="W23" s="128"/>
+      <c r="X23" s="128"/>
+      <c r="Y23" s="128"/>
+      <c r="Z23" s="128"/>
+      <c r="AA23" s="128"/>
+      <c r="AB23" s="128"/>
+      <c r="AC23" s="128"/>
+      <c r="AD23" s="128"/>
+      <c r="AE23" s="128"/>
+      <c r="AF23" s="128"/>
+      <c r="AG23" s="128"/>
+      <c r="AH23" s="128"/>
     </row>
     <row r="24" customHeight="1" spans="1:34">
-      <c r="A24" s="158" t="s">
+      <c r="A24" s="129" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="159"/>
-      <c r="C24" s="158" t="s">
+      <c r="B24" s="130"/>
+      <c r="C24" s="129" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="160"/>
-      <c r="E24" s="160"/>
-      <c r="F24" s="160"/>
-      <c r="G24" s="160"/>
-      <c r="H24" s="160"/>
-      <c r="I24" s="160"/>
-      <c r="J24" s="159"/>
-      <c r="K24" s="170" t="s">
+      <c r="D24" s="131"/>
+      <c r="E24" s="131"/>
+      <c r="F24" s="131"/>
+      <c r="G24" s="131"/>
+      <c r="H24" s="131"/>
+      <c r="I24" s="131"/>
+      <c r="J24" s="130"/>
+      <c r="K24" s="141" t="s">
         <v>33</v>
       </c>
-      <c r="L24" s="170" t="s">
+      <c r="L24" s="141" t="s">
         <v>34</v>
       </c>
-      <c r="M24" s="170" t="s">
+      <c r="M24" s="141" t="s">
         <v>35</v>
       </c>
-      <c r="N24" s="158" t="s">
+      <c r="N24" s="129" t="s">
         <v>36</v>
       </c>
-      <c r="O24" s="171" t="s">
+      <c r="O24" s="142" t="s">
         <v>37</v>
       </c>
-      <c r="P24" s="171"/>
-      <c r="Q24" s="171"/>
-      <c r="R24" s="171"/>
-      <c r="S24" s="171"/>
-      <c r="T24" s="171"/>
-      <c r="U24" s="171"/>
-      <c r="V24" s="171"/>
-      <c r="W24" s="171"/>
-      <c r="X24" s="171"/>
-      <c r="Y24" s="171"/>
-      <c r="Z24" s="171"/>
-      <c r="AA24" s="171"/>
-      <c r="AB24" s="171"/>
-      <c r="AC24" s="171"/>
-      <c r="AD24" s="171"/>
-      <c r="AE24" s="171"/>
-      <c r="AF24" s="171"/>
-      <c r="AG24" s="171"/>
-      <c r="AH24" s="171"/>
+      <c r="P24" s="142"/>
+      <c r="Q24" s="142"/>
+      <c r="R24" s="142"/>
+      <c r="S24" s="142"/>
+      <c r="T24" s="142"/>
+      <c r="U24" s="142"/>
+      <c r="V24" s="142"/>
+      <c r="W24" s="142"/>
+      <c r="X24" s="142"/>
+      <c r="Y24" s="142"/>
+      <c r="Z24" s="142"/>
+      <c r="AA24" s="142"/>
+      <c r="AB24" s="142"/>
+      <c r="AC24" s="142"/>
+      <c r="AD24" s="142"/>
+      <c r="AE24" s="142"/>
+      <c r="AF24" s="142"/>
+      <c r="AG24" s="142"/>
+      <c r="AH24" s="142"/>
     </row>
     <row r="25" customHeight="1" spans="1:34">
-      <c r="A25" s="161">
+      <c r="A25" s="132">
         <v>1</v>
       </c>
-      <c r="B25" s="162"/>
-      <c r="C25" s="163" t="s">
+      <c r="B25" s="133"/>
+      <c r="C25" s="134" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="164"/>
-      <c r="E25" s="164"/>
-      <c r="F25" s="164"/>
-      <c r="G25" s="164"/>
-      <c r="H25" s="164"/>
-      <c r="I25" s="164"/>
-      <c r="J25" s="164"/>
-      <c r="K25" s="172" t="s">
+      <c r="D25" s="135"/>
+      <c r="E25" s="135"/>
+      <c r="F25" s="135"/>
+      <c r="G25" s="135"/>
+      <c r="H25" s="135"/>
+      <c r="I25" s="135"/>
+      <c r="J25" s="135"/>
+      <c r="K25" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="L25" s="172" t="s">
+      <c r="L25" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="M25" s="172" t="s">
+      <c r="M25" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="N25" s="173"/>
-      <c r="O25" s="172"/>
-      <c r="P25" s="172"/>
-      <c r="Q25" s="172"/>
-      <c r="R25" s="172"/>
-      <c r="S25" s="172"/>
-      <c r="T25" s="172"/>
-      <c r="U25" s="172"/>
-      <c r="V25" s="172"/>
-      <c r="W25" s="172"/>
-      <c r="X25" s="172"/>
-      <c r="Y25" s="172"/>
-      <c r="Z25" s="172"/>
-      <c r="AA25" s="172"/>
-      <c r="AB25" s="172"/>
-      <c r="AC25" s="172"/>
-      <c r="AD25" s="172"/>
-      <c r="AE25" s="172"/>
-      <c r="AF25" s="172"/>
-      <c r="AG25" s="172"/>
-      <c r="AH25" s="172"/>
+      <c r="N25" s="134"/>
+      <c r="O25" s="143"/>
+      <c r="P25" s="143"/>
+      <c r="Q25" s="143"/>
+      <c r="R25" s="143"/>
+      <c r="S25" s="143"/>
+      <c r="T25" s="143"/>
+      <c r="U25" s="143"/>
+      <c r="V25" s="143"/>
+      <c r="W25" s="143"/>
+      <c r="X25" s="143"/>
+      <c r="Y25" s="143"/>
+      <c r="Z25" s="143"/>
+      <c r="AA25" s="143"/>
+      <c r="AB25" s="143"/>
+      <c r="AC25" s="143"/>
+      <c r="AD25" s="143"/>
+      <c r="AE25" s="143"/>
+      <c r="AF25" s="143"/>
+      <c r="AG25" s="143"/>
+      <c r="AH25" s="143"/>
     </row>
     <row r="26" customHeight="1" spans="1:34">
-      <c r="A26" s="161">
+      <c r="A26" s="132">
         <v>2</v>
       </c>
-      <c r="B26" s="162"/>
-      <c r="C26" s="187" t="s">
+      <c r="B26" s="133"/>
+      <c r="C26" s="155" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="164"/>
-      <c r="E26" s="164"/>
-      <c r="F26" s="164"/>
-      <c r="G26" s="164"/>
-      <c r="H26" s="164"/>
-      <c r="I26" s="164"/>
-      <c r="J26" s="164"/>
-      <c r="K26" s="174" t="s">
+      <c r="D26" s="135"/>
+      <c r="E26" s="135"/>
+      <c r="F26" s="135"/>
+      <c r="G26" s="135"/>
+      <c r="H26" s="135"/>
+      <c r="I26" s="135"/>
+      <c r="J26" s="135"/>
+      <c r="K26" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="L26" s="172" t="s">
+      <c r="L26" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="M26" s="172"/>
-      <c r="N26" s="173"/>
-      <c r="O26" s="172"/>
-      <c r="P26" s="172"/>
-      <c r="Q26" s="172"/>
-      <c r="R26" s="172"/>
-      <c r="S26" s="172"/>
-      <c r="T26" s="172"/>
-      <c r="U26" s="172"/>
-      <c r="V26" s="172"/>
-      <c r="W26" s="172"/>
-      <c r="X26" s="172"/>
-      <c r="Y26" s="172"/>
-      <c r="Z26" s="172"/>
-      <c r="AA26" s="172"/>
-      <c r="AB26" s="172"/>
-      <c r="AC26" s="172"/>
-      <c r="AD26" s="172"/>
-      <c r="AE26" s="172"/>
-      <c r="AF26" s="172"/>
-      <c r="AG26" s="172"/>
-      <c r="AH26" s="172"/>
+      <c r="M26" s="143"/>
+      <c r="N26" s="134"/>
+      <c r="O26" s="143"/>
+      <c r="P26" s="143"/>
+      <c r="Q26" s="143"/>
+      <c r="R26" s="143"/>
+      <c r="S26" s="143"/>
+      <c r="T26" s="143"/>
+      <c r="U26" s="143"/>
+      <c r="V26" s="143"/>
+      <c r="W26" s="143"/>
+      <c r="X26" s="143"/>
+      <c r="Y26" s="143"/>
+      <c r="Z26" s="143"/>
+      <c r="AA26" s="143"/>
+      <c r="AB26" s="143"/>
+      <c r="AC26" s="143"/>
+      <c r="AD26" s="143"/>
+      <c r="AE26" s="143"/>
+      <c r="AF26" s="143"/>
+      <c r="AG26" s="143"/>
+      <c r="AH26" s="143"/>
     </row>
     <row r="27" customHeight="1" spans="1:34">
-      <c r="A27" s="161">
+      <c r="A27" s="132">
         <v>3</v>
       </c>
-      <c r="B27" s="162"/>
-      <c r="C27" s="163" t="s">
+      <c r="B27" s="133"/>
+      <c r="C27" s="134" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="164"/>
-      <c r="E27" s="164"/>
-      <c r="F27" s="164"/>
-      <c r="G27" s="164"/>
-      <c r="H27" s="164"/>
-      <c r="I27" s="164"/>
-      <c r="J27" s="164"/>
-      <c r="K27" s="172" t="s">
+      <c r="D27" s="135"/>
+      <c r="E27" s="135"/>
+      <c r="F27" s="135"/>
+      <c r="G27" s="135"/>
+      <c r="H27" s="135"/>
+      <c r="I27" s="135"/>
+      <c r="J27" s="135"/>
+      <c r="K27" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="L27" s="172"/>
-      <c r="M27" s="172"/>
-      <c r="N27" s="173"/>
-      <c r="O27" s="172"/>
-      <c r="P27" s="172"/>
-      <c r="Q27" s="172"/>
-      <c r="R27" s="172"/>
-      <c r="S27" s="172"/>
-      <c r="T27" s="172"/>
-      <c r="U27" s="172"/>
-      <c r="V27" s="172"/>
-      <c r="W27" s="172"/>
-      <c r="X27" s="172"/>
-      <c r="Y27" s="172"/>
-      <c r="Z27" s="172"/>
-      <c r="AA27" s="172"/>
-      <c r="AB27" s="172"/>
-      <c r="AC27" s="172"/>
-      <c r="AD27" s="172"/>
-      <c r="AE27" s="172"/>
-      <c r="AF27" s="172"/>
-      <c r="AG27" s="172"/>
-      <c r="AH27" s="172"/>
+      <c r="L27" s="143"/>
+      <c r="M27" s="143"/>
+      <c r="N27" s="134"/>
+      <c r="O27" s="143"/>
+      <c r="P27" s="143"/>
+      <c r="Q27" s="143"/>
+      <c r="R27" s="143"/>
+      <c r="S27" s="143"/>
+      <c r="T27" s="143"/>
+      <c r="U27" s="143"/>
+      <c r="V27" s="143"/>
+      <c r="W27" s="143"/>
+      <c r="X27" s="143"/>
+      <c r="Y27" s="143"/>
+      <c r="Z27" s="143"/>
+      <c r="AA27" s="143"/>
+      <c r="AB27" s="143"/>
+      <c r="AC27" s="143"/>
+      <c r="AD27" s="143"/>
+      <c r="AE27" s="143"/>
+      <c r="AF27" s="143"/>
+      <c r="AG27" s="143"/>
+      <c r="AH27" s="143"/>
     </row>
     <row r="28" customHeight="1" spans="1:34">
-      <c r="A28" s="161">
+      <c r="A28" s="132">
         <v>4</v>
       </c>
-      <c r="B28" s="162"/>
-      <c r="C28" s="187" t="s">
+      <c r="B28" s="133"/>
+      <c r="C28" s="155" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="164"/>
-      <c r="E28" s="164"/>
-      <c r="F28" s="164"/>
-      <c r="G28" s="164"/>
-      <c r="H28" s="164"/>
-      <c r="I28" s="164"/>
-      <c r="J28" s="164"/>
-      <c r="K28" s="172" t="s">
+      <c r="D28" s="135"/>
+      <c r="E28" s="135"/>
+      <c r="F28" s="135"/>
+      <c r="G28" s="135"/>
+      <c r="H28" s="135"/>
+      <c r="I28" s="135"/>
+      <c r="J28" s="135"/>
+      <c r="K28" s="143" t="s">
         <v>39</v>
       </c>
-      <c r="L28" s="172"/>
-      <c r="M28" s="172"/>
-      <c r="N28" s="173"/>
-      <c r="O28" s="172"/>
-      <c r="P28" s="172"/>
-      <c r="Q28" s="172"/>
-      <c r="R28" s="172"/>
-      <c r="S28" s="172"/>
-      <c r="T28" s="172"/>
-      <c r="U28" s="172"/>
-      <c r="V28" s="172"/>
-      <c r="W28" s="172"/>
-      <c r="X28" s="172"/>
-      <c r="Y28" s="172"/>
-      <c r="Z28" s="172"/>
-      <c r="AA28" s="172"/>
-      <c r="AB28" s="172"/>
-      <c r="AC28" s="172"/>
-      <c r="AD28" s="172"/>
-      <c r="AE28" s="172"/>
-      <c r="AF28" s="172"/>
-      <c r="AG28" s="172"/>
-      <c r="AH28" s="172"/>
+      <c r="L28" s="143"/>
+      <c r="M28" s="143"/>
+      <c r="N28" s="134"/>
+      <c r="O28" s="143"/>
+      <c r="P28" s="143"/>
+      <c r="Q28" s="143"/>
+      <c r="R28" s="143"/>
+      <c r="S28" s="143"/>
+      <c r="T28" s="143"/>
+      <c r="U28" s="143"/>
+      <c r="V28" s="143"/>
+      <c r="W28" s="143"/>
+      <c r="X28" s="143"/>
+      <c r="Y28" s="143"/>
+      <c r="Z28" s="143"/>
+      <c r="AA28" s="143"/>
+      <c r="AB28" s="143"/>
+      <c r="AC28" s="143"/>
+      <c r="AD28" s="143"/>
+      <c r="AE28" s="143"/>
+      <c r="AF28" s="143"/>
+      <c r="AG28" s="143"/>
+      <c r="AH28" s="143"/>
     </row>
   </sheetData>
   <mergeCells count="37">
@@ -4779,34 +4646,34 @@
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
-      <c r="J1" s="24" t="s">
+      <c r="J1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="25"/>
-      <c r="N1" s="125"/>
-      <c r="O1" s="26" t="s">
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="24"/>
+      <c r="N1" s="100"/>
+      <c r="O1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="93"/>
-      <c r="Q1" s="93"/>
-      <c r="R1" s="93"/>
-      <c r="S1" s="93"/>
-      <c r="T1" s="27" t="s">
+      <c r="P1" s="78"/>
+      <c r="Q1" s="78"/>
+      <c r="R1" s="78"/>
+      <c r="S1" s="78"/>
+      <c r="T1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="U1" s="28" t="s">
+      <c r="U1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="V1" s="95"/>
-      <c r="W1" s="29" t="s">
+      <c r="V1" s="16"/>
+      <c r="W1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="186" t="s">
+      <c r="X1" s="154" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="139"/>
+      <c r="Y1" s="112"/>
     </row>
     <row r="2" customHeight="1" spans="1:25">
       <c r="A2" s="6"/>
@@ -4818,22 +4685,22 @@
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
-      <c r="J2" s="32"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="33"/>
-      <c r="N2" s="126"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="94"/>
-      <c r="Q2" s="94"/>
-      <c r="R2" s="94"/>
-      <c r="S2" s="94"/>
-      <c r="T2" s="27"/>
-      <c r="U2" s="35"/>
-      <c r="V2" s="96"/>
-      <c r="W2" s="36"/>
-      <c r="X2" s="37"/>
-      <c r="Y2" s="140"/>
+      <c r="J2" s="31"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="32"/>
+      <c r="N2" s="101"/>
+      <c r="O2" s="33"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="79"/>
+      <c r="R2" s="79"/>
+      <c r="S2" s="79"/>
+      <c r="T2" s="26"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="80"/>
+      <c r="W2" s="35"/>
+      <c r="X2" s="36"/>
+      <c r="Y2" s="113"/>
     </row>
     <row r="3" customHeight="1" spans="1:25">
       <c r="A3" s="6"/>
@@ -4845,34 +4712,34 @@
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
-      <c r="J3" s="24" t="s">
+      <c r="J3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="25"/>
-      <c r="N3" s="125"/>
-      <c r="O3" s="127" t="s">
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="24"/>
+      <c r="N3" s="100"/>
+      <c r="O3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="93"/>
-      <c r="Q3" s="93"/>
-      <c r="R3" s="93"/>
-      <c r="S3" s="93"/>
-      <c r="T3" s="27" t="s">
+      <c r="P3" s="78"/>
+      <c r="Q3" s="78"/>
+      <c r="R3" s="78"/>
+      <c r="S3" s="78"/>
+      <c r="T3" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="U3" s="28" t="s">
+      <c r="U3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="V3" s="95"/>
-      <c r="W3" s="27" t="s">
+      <c r="V3" s="16"/>
+      <c r="W3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="X3" s="186" t="s">
+      <c r="X3" s="154" t="s">
         <v>18</v>
       </c>
-      <c r="Y3" s="139"/>
+      <c r="Y3" s="112"/>
     </row>
     <row r="4" customHeight="1" spans="1:25">
       <c r="A4" s="8"/>
@@ -4884,22 +4751,22 @@
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
-      <c r="J4" s="32"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="33"/>
-      <c r="N4" s="126"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="94"/>
-      <c r="Q4" s="94"/>
-      <c r="R4" s="94"/>
-      <c r="S4" s="94"/>
-      <c r="T4" s="27"/>
-      <c r="U4" s="35"/>
-      <c r="V4" s="96"/>
-      <c r="W4" s="27"/>
-      <c r="X4" s="37"/>
-      <c r="Y4" s="140"/>
+      <c r="J4" s="31"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="32"/>
+      <c r="N4" s="101"/>
+      <c r="O4" s="33"/>
+      <c r="P4" s="79"/>
+      <c r="Q4" s="79"/>
+      <c r="R4" s="79"/>
+      <c r="S4" s="79"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="34"/>
+      <c r="V4" s="80"/>
+      <c r="W4" s="26"/>
+      <c r="X4" s="36"/>
+      <c r="Y4" s="113"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A5" s="10" t="s">
@@ -4909,7 +4776,7 @@
       <c r="C5" s="10"/>
       <c r="D5" s="10"/>
       <c r="E5" s="10"/>
-      <c r="F5" s="118" t="s">
+      <c r="F5" s="11" t="s">
         <v>25</v>
       </c>
       <c r="G5" s="11"/>
@@ -4941,748 +4808,748 @@
       <c r="Y5" s="11"/>
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A6" s="92" t="s">
+      <c r="A6" s="77" t="s">
         <v>47</v>
       </c>
     </row>
     <row r="7" s="2" customFormat="1" ht="23.1" customHeight="1" spans="1:25">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="C7" s="27"/>
-      <c r="D7" s="27"/>
-      <c r="E7" s="27"/>
-      <c r="F7" s="27"/>
-      <c r="G7" s="27"/>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="128" t="s">
+      <c r="C7" s="26"/>
+      <c r="D7" s="26"/>
+      <c r="E7" s="26"/>
+      <c r="F7" s="26"/>
+      <c r="G7" s="26"/>
+      <c r="H7" s="26"/>
+      <c r="I7" s="26"/>
+      <c r="J7" s="102" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="129" t="s">
+      <c r="K7" s="103" t="s">
         <v>50</v>
       </c>
-      <c r="L7" s="130"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="131"/>
-      <c r="O7" s="27" t="s">
+      <c r="L7" s="104"/>
+      <c r="M7" s="104"/>
+      <c r="N7" s="105"/>
+      <c r="O7" s="26" t="s">
         <v>51</v>
       </c>
-      <c r="P7" s="27"/>
-      <c r="Q7" s="27"/>
-      <c r="R7" s="27"/>
-      <c r="S7" s="27" t="s">
+      <c r="P7" s="26"/>
+      <c r="Q7" s="26"/>
+      <c r="R7" s="26"/>
+      <c r="S7" s="26" t="s">
         <v>52</v>
       </c>
-      <c r="T7" s="27"/>
-      <c r="U7" s="129" t="s">
+      <c r="T7" s="26"/>
+      <c r="U7" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="V7" s="130"/>
-      <c r="W7" s="130"/>
-      <c r="X7" s="130"/>
-      <c r="Y7" s="130"/>
+      <c r="V7" s="104"/>
+      <c r="W7" s="104"/>
+      <c r="X7" s="104"/>
+      <c r="Y7" s="104"/>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A8" s="101">
+      <c r="A8" s="66">
         <v>1</v>
       </c>
-      <c r="B8" s="119" t="s">
+      <c r="B8" s="97" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="119"/>
-      <c r="D8" s="119"/>
-      <c r="E8" s="119"/>
-      <c r="F8" s="119"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="119"/>
-      <c r="I8" s="119"/>
-      <c r="J8" s="119" t="s">
+      <c r="C8" s="97"/>
+      <c r="D8" s="97"/>
+      <c r="E8" s="97"/>
+      <c r="F8" s="97"/>
+      <c r="G8" s="97"/>
+      <c r="H8" s="97"/>
+      <c r="I8" s="97"/>
+      <c r="J8" s="97" t="s">
         <v>55</v>
       </c>
-      <c r="K8" s="109" t="s">
+      <c r="K8" s="67" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="110"/>
-      <c r="M8" s="110"/>
-      <c r="N8" s="111"/>
-      <c r="O8" s="101">
+      <c r="L8" s="91"/>
+      <c r="M8" s="91"/>
+      <c r="N8" s="70"/>
+      <c r="O8" s="66">
         <v>4000</v>
       </c>
-      <c r="P8" s="101"/>
-      <c r="Q8" s="101"/>
-      <c r="R8" s="101"/>
-      <c r="S8" s="101" t="s">
+      <c r="P8" s="66"/>
+      <c r="Q8" s="66"/>
+      <c r="R8" s="66"/>
+      <c r="S8" s="66" t="s">
         <v>57</v>
       </c>
-      <c r="T8" s="101"/>
-      <c r="U8" s="109" t="s">
+      <c r="T8" s="66"/>
+      <c r="U8" s="67" t="s">
         <v>58</v>
       </c>
-      <c r="V8" s="110"/>
-      <c r="W8" s="110"/>
-      <c r="X8" s="110"/>
-      <c r="Y8" s="110"/>
+      <c r="V8" s="91"/>
+      <c r="W8" s="91"/>
+      <c r="X8" s="91"/>
+      <c r="Y8" s="91"/>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A9" s="92"/>
+      <c r="A9" s="77"/>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="77" t="s">
         <v>59</v>
       </c>
     </row>
     <row r="11" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="C11" s="27"/>
-      <c r="D11" s="27"/>
-      <c r="E11" s="27"/>
-      <c r="F11" s="27" t="s">
+      <c r="C11" s="26"/>
+      <c r="D11" s="26"/>
+      <c r="E11" s="26"/>
+      <c r="F11" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="G11" s="27"/>
-      <c r="H11" s="27"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="27"/>
-      <c r="K11" s="27" t="s">
+      <c r="G11" s="26"/>
+      <c r="H11" s="26"/>
+      <c r="I11" s="26"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="L11" s="27"/>
-      <c r="M11" s="27"/>
-      <c r="N11" s="27"/>
-      <c r="O11" s="27" t="s">
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
+      <c r="N11" s="26"/>
+      <c r="O11" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="P11" s="27"/>
-      <c r="Q11" s="128" t="s">
+      <c r="P11" s="26"/>
+      <c r="Q11" s="102" t="s">
         <v>52</v>
       </c>
-      <c r="R11" s="128"/>
-      <c r="S11" s="128"/>
-      <c r="T11" s="128"/>
-      <c r="U11" s="27" t="s">
+      <c r="R11" s="102"/>
+      <c r="S11" s="102"/>
+      <c r="T11" s="102"/>
+      <c r="U11" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="V11" s="27"/>
-      <c r="W11" s="27"/>
-      <c r="X11" s="129" t="s">
+      <c r="V11" s="26"/>
+      <c r="W11" s="26"/>
+      <c r="X11" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="Y11" s="130"/>
+      <c r="Y11" s="104"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A12" s="101">
+      <c r="A12" s="66">
         <v>1</v>
       </c>
-      <c r="B12" s="113" t="s">
+      <c r="B12" s="66" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="101"/>
-      <c r="D12" s="101"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="113" t="s">
+      <c r="C12" s="66"/>
+      <c r="D12" s="66"/>
+      <c r="E12" s="66"/>
+      <c r="F12" s="66" t="s">
         <v>65</v>
       </c>
-      <c r="G12" s="101"/>
-      <c r="H12" s="101"/>
-      <c r="I12" s="101"/>
-      <c r="J12" s="101"/>
-      <c r="K12" s="132" t="s">
+      <c r="G12" s="66"/>
+      <c r="H12" s="66"/>
+      <c r="I12" s="66"/>
+      <c r="J12" s="66"/>
+      <c r="K12" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="L12" s="110"/>
-      <c r="M12" s="110"/>
-      <c r="N12" s="111"/>
-      <c r="O12" s="133" t="s">
+      <c r="L12" s="91"/>
+      <c r="M12" s="91"/>
+      <c r="N12" s="70"/>
+      <c r="O12" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="P12" s="134"/>
-      <c r="Q12" s="101" t="s">
+      <c r="P12" s="107"/>
+      <c r="Q12" s="66" t="s">
         <v>64</v>
       </c>
-      <c r="R12" s="101"/>
-      <c r="S12" s="101"/>
-      <c r="T12" s="101"/>
-      <c r="U12" s="135" t="s">
+      <c r="R12" s="66"/>
+      <c r="S12" s="66"/>
+      <c r="T12" s="66"/>
+      <c r="U12" s="108" t="s">
         <v>67</v>
       </c>
-      <c r="V12" s="101"/>
-      <c r="W12" s="101"/>
-      <c r="X12" s="101" t="s">
+      <c r="V12" s="66"/>
+      <c r="W12" s="66"/>
+      <c r="X12" s="66" t="s">
         <v>68</v>
       </c>
-      <c r="Y12" s="101"/>
+      <c r="Y12" s="66"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A13" s="101">
+      <c r="A13" s="66">
         <v>2</v>
       </c>
-      <c r="B13" s="113" t="s">
+      <c r="B13" s="66" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="101"/>
-      <c r="D13" s="101"/>
-      <c r="E13" s="101"/>
-      <c r="F13" s="121" t="s">
+      <c r="C13" s="66"/>
+      <c r="D13" s="66"/>
+      <c r="E13" s="66"/>
+      <c r="F13" s="98" t="s">
         <v>70</v>
       </c>
-      <c r="G13" s="122"/>
-      <c r="H13" s="122"/>
-      <c r="I13" s="122"/>
-      <c r="J13" s="122"/>
-      <c r="K13" s="109" t="s">
+      <c r="G13" s="98"/>
+      <c r="H13" s="98"/>
+      <c r="I13" s="98"/>
+      <c r="J13" s="98"/>
+      <c r="K13" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="L13" s="110"/>
-      <c r="M13" s="110"/>
-      <c r="N13" s="111"/>
-      <c r="O13" s="133" t="s">
+      <c r="L13" s="91"/>
+      <c r="M13" s="91"/>
+      <c r="N13" s="70"/>
+      <c r="O13" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="P13" s="134"/>
-      <c r="Q13" s="188" t="s">
+      <c r="P13" s="107"/>
+      <c r="Q13" s="156" t="s">
         <v>71</v>
       </c>
-      <c r="R13" s="101"/>
-      <c r="S13" s="101"/>
-      <c r="T13" s="101"/>
-      <c r="U13" s="135" t="s">
+      <c r="R13" s="66"/>
+      <c r="S13" s="66"/>
+      <c r="T13" s="66"/>
+      <c r="U13" s="108" t="s">
         <v>72</v>
       </c>
-      <c r="V13" s="101"/>
-      <c r="W13" s="101"/>
-      <c r="X13" s="113" t="s">
+      <c r="V13" s="66"/>
+      <c r="W13" s="66"/>
+      <c r="X13" s="66" t="s">
         <v>73</v>
       </c>
-      <c r="Y13" s="101"/>
+      <c r="Y13" s="66"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A14" s="101">
+      <c r="A14" s="66">
         <v>3</v>
       </c>
-      <c r="B14" s="189" t="s">
+      <c r="B14" s="156" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="101"/>
-      <c r="D14" s="101"/>
-      <c r="E14" s="101"/>
-      <c r="F14" s="113" t="s">
+      <c r="C14" s="66"/>
+      <c r="D14" s="66"/>
+      <c r="E14" s="66"/>
+      <c r="F14" s="66" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="101"/>
-      <c r="H14" s="101"/>
-      <c r="I14" s="101"/>
-      <c r="J14" s="101"/>
-      <c r="K14" s="109" t="s">
+      <c r="G14" s="66"/>
+      <c r="H14" s="66"/>
+      <c r="I14" s="66"/>
+      <c r="J14" s="66"/>
+      <c r="K14" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="L14" s="110"/>
-      <c r="M14" s="110"/>
-      <c r="N14" s="111"/>
-      <c r="O14" s="133" t="s">
+      <c r="L14" s="91"/>
+      <c r="M14" s="91"/>
+      <c r="N14" s="70"/>
+      <c r="O14" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="P14" s="134"/>
-      <c r="Q14" s="101" t="s">
+      <c r="P14" s="107"/>
+      <c r="Q14" s="66" t="s">
         <v>76</v>
       </c>
-      <c r="R14" s="101"/>
-      <c r="S14" s="101"/>
-      <c r="T14" s="101"/>
-      <c r="U14" s="135"/>
-      <c r="V14" s="101"/>
-      <c r="W14" s="101"/>
-      <c r="X14" s="136" t="s">
+      <c r="R14" s="66"/>
+      <c r="S14" s="66"/>
+      <c r="T14" s="66"/>
+      <c r="U14" s="108"/>
+      <c r="V14" s="66"/>
+      <c r="W14" s="66"/>
+      <c r="X14" s="109" t="s">
         <v>77</v>
       </c>
-      <c r="Y14" s="141"/>
+      <c r="Y14" s="114"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A15" s="101">
+      <c r="A15" s="66">
         <v>4</v>
       </c>
-      <c r="B15" s="113" t="s">
+      <c r="B15" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="101"/>
-      <c r="D15" s="101"/>
-      <c r="E15" s="101"/>
-      <c r="F15" s="113" t="s">
+      <c r="C15" s="66"/>
+      <c r="D15" s="66"/>
+      <c r="E15" s="66"/>
+      <c r="F15" s="66" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="101"/>
-      <c r="H15" s="101"/>
-      <c r="I15" s="101"/>
-      <c r="J15" s="101"/>
-      <c r="K15" s="109" t="s">
+      <c r="G15" s="66"/>
+      <c r="H15" s="66"/>
+      <c r="I15" s="66"/>
+      <c r="J15" s="66"/>
+      <c r="K15" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="L15" s="110"/>
-      <c r="M15" s="110"/>
-      <c r="N15" s="111"/>
-      <c r="O15" s="133" t="s">
+      <c r="L15" s="91"/>
+      <c r="M15" s="91"/>
+      <c r="N15" s="70"/>
+      <c r="O15" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="P15" s="134"/>
-      <c r="Q15" s="101" t="s">
+      <c r="P15" s="107"/>
+      <c r="Q15" s="66" t="s">
         <v>78</v>
       </c>
-      <c r="R15" s="101"/>
-      <c r="S15" s="101"/>
-      <c r="T15" s="101"/>
-      <c r="U15" s="101"/>
-      <c r="V15" s="101"/>
-      <c r="W15" s="101"/>
-      <c r="X15" s="109" t="s">
+      <c r="R15" s="66"/>
+      <c r="S15" s="66"/>
+      <c r="T15" s="66"/>
+      <c r="U15" s="66"/>
+      <c r="V15" s="66"/>
+      <c r="W15" s="66"/>
+      <c r="X15" s="67" t="s">
         <v>80</v>
       </c>
-      <c r="Y15" s="111"/>
+      <c r="Y15" s="70"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A16" s="101">
+      <c r="A16" s="66">
         <v>5</v>
       </c>
-      <c r="B16" s="113" t="s">
+      <c r="B16" s="66" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="101"/>
-      <c r="D16" s="101"/>
-      <c r="E16" s="101"/>
-      <c r="F16" s="113" t="s">
+      <c r="C16" s="66"/>
+      <c r="D16" s="66"/>
+      <c r="E16" s="66"/>
+      <c r="F16" s="66" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="101"/>
-      <c r="H16" s="101"/>
-      <c r="I16" s="101"/>
-      <c r="J16" s="101"/>
-      <c r="K16" s="109" t="s">
+      <c r="G16" s="66"/>
+      <c r="H16" s="66"/>
+      <c r="I16" s="66"/>
+      <c r="J16" s="66"/>
+      <c r="K16" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="L16" s="110"/>
-      <c r="M16" s="110"/>
-      <c r="N16" s="111"/>
-      <c r="O16" s="133" t="s">
+      <c r="L16" s="91"/>
+      <c r="M16" s="91"/>
+      <c r="N16" s="70"/>
+      <c r="O16" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="P16" s="134"/>
-      <c r="Q16" s="101" t="s">
+      <c r="P16" s="107"/>
+      <c r="Q16" s="66" t="s">
         <v>83</v>
       </c>
-      <c r="R16" s="101"/>
-      <c r="S16" s="101"/>
-      <c r="T16" s="101"/>
-      <c r="U16" s="101"/>
-      <c r="V16" s="101"/>
-      <c r="W16" s="101"/>
-      <c r="X16" s="109" t="s">
+      <c r="R16" s="66"/>
+      <c r="S16" s="66"/>
+      <c r="T16" s="66"/>
+      <c r="U16" s="66"/>
+      <c r="V16" s="66"/>
+      <c r="W16" s="66"/>
+      <c r="X16" s="67" t="s">
         <v>84</v>
       </c>
-      <c r="Y16" s="111"/>
+      <c r="Y16" s="70"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A17" s="101">
+      <c r="A17" s="66">
         <v>6</v>
       </c>
-      <c r="B17" s="113" t="s">
+      <c r="B17" s="66" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="101"/>
-      <c r="D17" s="101"/>
-      <c r="E17" s="101"/>
-      <c r="F17" s="113" t="s">
+      <c r="C17" s="66"/>
+      <c r="D17" s="66"/>
+      <c r="E17" s="66"/>
+      <c r="F17" s="66" t="s">
         <v>86</v>
       </c>
-      <c r="G17" s="101"/>
-      <c r="H17" s="101"/>
-      <c r="I17" s="101"/>
-      <c r="J17" s="101"/>
-      <c r="K17" s="109" t="s">
+      <c r="G17" s="66"/>
+      <c r="H17" s="66"/>
+      <c r="I17" s="66"/>
+      <c r="J17" s="66"/>
+      <c r="K17" s="67" t="s">
         <v>87</v>
       </c>
-      <c r="L17" s="110"/>
-      <c r="M17" s="110"/>
-      <c r="N17" s="111"/>
-      <c r="O17" s="133" t="s">
+      <c r="L17" s="91"/>
+      <c r="M17" s="91"/>
+      <c r="N17" s="70"/>
+      <c r="O17" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="P17" s="134"/>
-      <c r="Q17" s="137" t="s">
+      <c r="P17" s="107"/>
+      <c r="Q17" s="110" t="s">
         <v>88</v>
       </c>
-      <c r="R17" s="110"/>
-      <c r="S17" s="110"/>
-      <c r="T17" s="110"/>
-      <c r="U17" s="110"/>
-      <c r="V17" s="110"/>
-      <c r="W17" s="111"/>
-      <c r="X17" s="109" t="s">
+      <c r="R17" s="91"/>
+      <c r="S17" s="91"/>
+      <c r="T17" s="91"/>
+      <c r="U17" s="91"/>
+      <c r="V17" s="91"/>
+      <c r="W17" s="70"/>
+      <c r="X17" s="67" t="s">
         <v>89</v>
       </c>
-      <c r="Y17" s="111"/>
+      <c r="Y17" s="70"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A18" s="123"/>
-      <c r="B18" s="82"/>
-      <c r="C18" s="82"/>
-      <c r="D18" s="82"/>
-      <c r="E18" s="82"/>
-      <c r="F18" s="82"/>
-      <c r="G18" s="82"/>
-      <c r="H18" s="82"/>
-      <c r="I18" s="82"/>
-      <c r="J18" s="82"/>
-      <c r="K18" s="82"/>
-      <c r="L18" s="82"/>
-      <c r="M18" s="82"/>
-      <c r="N18" s="82"/>
+      <c r="A18" s="99"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="63"/>
+      <c r="D18" s="63"/>
+      <c r="E18" s="63"/>
+      <c r="F18" s="63"/>
+      <c r="G18" s="63"/>
+      <c r="H18" s="63"/>
+      <c r="I18" s="63"/>
+      <c r="J18" s="63"/>
+      <c r="K18" s="63"/>
+      <c r="L18" s="63"/>
+      <c r="M18" s="63"/>
+      <c r="N18" s="63"/>
       <c r="O18" s="18"/>
       <c r="P18" s="18"/>
-      <c r="Q18" s="82"/>
-      <c r="R18" s="82"/>
-      <c r="S18" s="82"/>
-      <c r="T18" s="82"/>
-      <c r="U18" s="82"/>
-      <c r="V18" s="82"/>
-      <c r="W18" s="82"/>
-      <c r="X18" s="82"/>
-      <c r="Y18" s="82"/>
+      <c r="Q18" s="63"/>
+      <c r="R18" s="63"/>
+      <c r="S18" s="63"/>
+      <c r="T18" s="63"/>
+      <c r="U18" s="63"/>
+      <c r="V18" s="63"/>
+      <c r="W18" s="63"/>
+      <c r="X18" s="63"/>
+      <c r="Y18" s="63"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A19" s="124" t="s">
+      <c r="A19" s="99" t="s">
         <v>90</v>
       </c>
-      <c r="B19" s="82"/>
-      <c r="C19" s="82"/>
-      <c r="D19" s="82"/>
-      <c r="E19" s="82"/>
-      <c r="F19" s="82"/>
-      <c r="G19" s="82"/>
-      <c r="H19" s="82"/>
-      <c r="I19" s="82"/>
-      <c r="J19" s="82"/>
-      <c r="K19" s="82"/>
-      <c r="L19" s="82"/>
-      <c r="M19" s="82"/>
-      <c r="N19" s="82"/>
+      <c r="B19" s="63"/>
+      <c r="C19" s="63"/>
+      <c r="D19" s="63"/>
+      <c r="E19" s="63"/>
+      <c r="F19" s="63"/>
+      <c r="G19" s="63"/>
+      <c r="H19" s="63"/>
+      <c r="I19" s="63"/>
+      <c r="J19" s="63"/>
+      <c r="K19" s="63"/>
+      <c r="L19" s="63"/>
+      <c r="M19" s="63"/>
+      <c r="N19" s="63"/>
       <c r="O19" s="18"/>
       <c r="P19" s="18"/>
-      <c r="Q19" s="82"/>
-      <c r="R19" s="82"/>
-      <c r="S19" s="82"/>
-      <c r="T19" s="82"/>
-      <c r="U19" s="82"/>
-      <c r="V19" s="82"/>
-      <c r="W19" s="82"/>
-      <c r="X19" s="82"/>
-      <c r="Y19" s="82"/>
+      <c r="Q19" s="63"/>
+      <c r="R19" s="63"/>
+      <c r="S19" s="63"/>
+      <c r="T19" s="63"/>
+      <c r="U19" s="63"/>
+      <c r="V19" s="63"/>
+      <c r="W19" s="63"/>
+      <c r="X19" s="63"/>
+      <c r="Y19" s="63"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="26" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="26" t="s">
         <v>60</v>
       </c>
-      <c r="C20" s="27"/>
-      <c r="D20" s="27"/>
-      <c r="E20" s="27"/>
-      <c r="F20" s="27" t="s">
+      <c r="C20" s="26"/>
+      <c r="D20" s="26"/>
+      <c r="E20" s="26"/>
+      <c r="F20" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="G20" s="27"/>
-      <c r="H20" s="27"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="27"/>
-      <c r="K20" s="27" t="s">
+      <c r="G20" s="26"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="26"/>
+      <c r="K20" s="26" t="s">
         <v>61</v>
       </c>
-      <c r="L20" s="27"/>
-      <c r="M20" s="27"/>
-      <c r="N20" s="27"/>
-      <c r="O20" s="27" t="s">
+      <c r="L20" s="26"/>
+      <c r="M20" s="26"/>
+      <c r="N20" s="26"/>
+      <c r="O20" s="26" t="s">
         <v>49</v>
       </c>
-      <c r="P20" s="27"/>
-      <c r="Q20" s="128" t="s">
+      <c r="P20" s="26"/>
+      <c r="Q20" s="102" t="s">
         <v>52</v>
       </c>
-      <c r="R20" s="128"/>
-      <c r="S20" s="128"/>
-      <c r="T20" s="128"/>
-      <c r="U20" s="27" t="s">
+      <c r="R20" s="102"/>
+      <c r="S20" s="102"/>
+      <c r="T20" s="102"/>
+      <c r="U20" s="26" t="s">
         <v>62</v>
       </c>
-      <c r="V20" s="27"/>
-      <c r="W20" s="27"/>
-      <c r="X20" s="129" t="s">
+      <c r="V20" s="26"/>
+      <c r="W20" s="26"/>
+      <c r="X20" s="103" t="s">
         <v>63</v>
       </c>
-      <c r="Y20" s="130"/>
+      <c r="Y20" s="104"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A21" s="101">
+      <c r="A21" s="66">
         <v>1</v>
       </c>
-      <c r="B21" s="113" t="s">
+      <c r="B21" s="66" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="101"/>
-      <c r="D21" s="101"/>
-      <c r="E21" s="101"/>
-      <c r="F21" s="121" t="s">
+      <c r="C21" s="66"/>
+      <c r="D21" s="66"/>
+      <c r="E21" s="66"/>
+      <c r="F21" s="98" t="s">
         <v>92</v>
       </c>
-      <c r="G21" s="122"/>
-      <c r="H21" s="122"/>
-      <c r="I21" s="122"/>
-      <c r="J21" s="122"/>
-      <c r="K21" s="109" t="s">
+      <c r="G21" s="98"/>
+      <c r="H21" s="98"/>
+      <c r="I21" s="98"/>
+      <c r="J21" s="98"/>
+      <c r="K21" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="L21" s="110"/>
-      <c r="M21" s="110"/>
-      <c r="N21" s="111"/>
-      <c r="O21" s="133"/>
-      <c r="P21" s="134"/>
-      <c r="Q21" s="101" t="s">
+      <c r="L21" s="91"/>
+      <c r="M21" s="91"/>
+      <c r="N21" s="70"/>
+      <c r="O21" s="106"/>
+      <c r="P21" s="107"/>
+      <c r="Q21" s="66" t="s">
         <v>94</v>
       </c>
-      <c r="R21" s="101"/>
-      <c r="S21" s="101"/>
-      <c r="T21" s="101"/>
-      <c r="U21" s="101" t="s">
+      <c r="R21" s="66"/>
+      <c r="S21" s="66"/>
+      <c r="T21" s="66"/>
+      <c r="U21" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="V21" s="101"/>
-      <c r="W21" s="101"/>
-      <c r="X21" s="138">
+      <c r="V21" s="66"/>
+      <c r="W21" s="66"/>
+      <c r="X21" s="111">
         <v>5</v>
       </c>
-      <c r="Y21" s="142"/>
+      <c r="Y21" s="115"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A22" s="101">
+      <c r="A22" s="66">
         <v>2</v>
       </c>
-      <c r="B22" s="113" t="s">
+      <c r="B22" s="66" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="101"/>
-      <c r="D22" s="101"/>
-      <c r="E22" s="101"/>
-      <c r="F22" s="113" t="s">
+      <c r="C22" s="66"/>
+      <c r="D22" s="66"/>
+      <c r="E22" s="66"/>
+      <c r="F22" s="66" t="s">
         <v>96</v>
       </c>
-      <c r="G22" s="101"/>
-      <c r="H22" s="101"/>
-      <c r="I22" s="101"/>
-      <c r="J22" s="101"/>
-      <c r="K22" s="109" t="s">
+      <c r="G22" s="66"/>
+      <c r="H22" s="66"/>
+      <c r="I22" s="66"/>
+      <c r="J22" s="66"/>
+      <c r="K22" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="L22" s="110"/>
-      <c r="M22" s="110"/>
-      <c r="N22" s="111"/>
-      <c r="O22" s="133" t="s">
+      <c r="L22" s="91"/>
+      <c r="M22" s="91"/>
+      <c r="N22" s="70"/>
+      <c r="O22" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="P22" s="134"/>
-      <c r="Q22" s="188" t="s">
+      <c r="P22" s="107"/>
+      <c r="Q22" s="156" t="s">
         <v>97</v>
       </c>
-      <c r="R22" s="101"/>
-      <c r="S22" s="101"/>
-      <c r="T22" s="101"/>
-      <c r="U22" s="101" t="s">
+      <c r="R22" s="66"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="66"/>
+      <c r="U22" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="V22" s="101"/>
-      <c r="W22" s="101"/>
-      <c r="X22" s="101">
+      <c r="V22" s="66"/>
+      <c r="W22" s="66"/>
+      <c r="X22" s="66">
         <v>2</v>
       </c>
-      <c r="Y22" s="101"/>
+      <c r="Y22" s="66"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A23" s="101">
+      <c r="A23" s="66">
         <v>3</v>
       </c>
-      <c r="B23" s="113" t="s">
+      <c r="B23" s="66" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="101"/>
-      <c r="D23" s="101"/>
-      <c r="E23" s="101"/>
-      <c r="F23" s="113" t="s">
+      <c r="C23" s="66"/>
+      <c r="D23" s="66"/>
+      <c r="E23" s="66"/>
+      <c r="F23" s="66" t="s">
         <v>99</v>
       </c>
-      <c r="G23" s="101"/>
-      <c r="H23" s="101"/>
-      <c r="I23" s="101"/>
-      <c r="J23" s="101"/>
-      <c r="K23" s="109" t="s">
+      <c r="G23" s="66"/>
+      <c r="H23" s="66"/>
+      <c r="I23" s="66"/>
+      <c r="J23" s="66"/>
+      <c r="K23" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="L23" s="110"/>
-      <c r="M23" s="110"/>
-      <c r="N23" s="111"/>
-      <c r="O23" s="133" t="s">
+      <c r="L23" s="91"/>
+      <c r="M23" s="91"/>
+      <c r="N23" s="70"/>
+      <c r="O23" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="P23" s="134"/>
-      <c r="Q23" s="188" t="s">
+      <c r="P23" s="107"/>
+      <c r="Q23" s="156" t="s">
         <v>97</v>
       </c>
-      <c r="R23" s="101"/>
-      <c r="S23" s="101"/>
-      <c r="T23" s="101"/>
-      <c r="U23" s="101" t="s">
+      <c r="R23" s="66"/>
+      <c r="S23" s="66"/>
+      <c r="T23" s="66"/>
+      <c r="U23" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="V23" s="101"/>
-      <c r="W23" s="101"/>
-      <c r="X23" s="138">
+      <c r="V23" s="66"/>
+      <c r="W23" s="66"/>
+      <c r="X23" s="111">
         <v>1</v>
       </c>
-      <c r="Y23" s="142"/>
+      <c r="Y23" s="115"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A24" s="101">
+      <c r="A24" s="66">
         <v>4</v>
       </c>
-      <c r="B24" s="113" t="s">
+      <c r="B24" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="C24" s="101"/>
-      <c r="D24" s="101"/>
-      <c r="E24" s="101"/>
-      <c r="F24" s="121" t="s">
+      <c r="C24" s="66"/>
+      <c r="D24" s="66"/>
+      <c r="E24" s="66"/>
+      <c r="F24" s="98" t="s">
         <v>101</v>
       </c>
-      <c r="G24" s="122"/>
-      <c r="H24" s="122"/>
-      <c r="I24" s="122"/>
-      <c r="J24" s="122"/>
-      <c r="K24" s="109" t="s">
+      <c r="G24" s="98"/>
+      <c r="H24" s="98"/>
+      <c r="I24" s="98"/>
+      <c r="J24" s="98"/>
+      <c r="K24" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="L24" s="110"/>
-      <c r="M24" s="110"/>
-      <c r="N24" s="111"/>
-      <c r="O24" s="133" t="s">
+      <c r="L24" s="91"/>
+      <c r="M24" s="91"/>
+      <c r="N24" s="70"/>
+      <c r="O24" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="P24" s="134"/>
-      <c r="Q24" s="101" t="s">
+      <c r="P24" s="107"/>
+      <c r="Q24" s="66" t="s">
         <v>100</v>
       </c>
-      <c r="R24" s="101"/>
-      <c r="S24" s="101"/>
-      <c r="T24" s="101"/>
-      <c r="U24" s="101" t="s">
+      <c r="R24" s="66"/>
+      <c r="S24" s="66"/>
+      <c r="T24" s="66"/>
+      <c r="U24" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="V24" s="101"/>
-      <c r="W24" s="101"/>
-      <c r="X24" s="101" t="s">
+      <c r="V24" s="66"/>
+      <c r="W24" s="66"/>
+      <c r="X24" s="66" t="s">
         <v>102</v>
       </c>
-      <c r="Y24" s="101"/>
+      <c r="Y24" s="66"/>
     </row>
     <row r="25" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A25" s="101">
+      <c r="A25" s="66">
         <v>5</v>
       </c>
-      <c r="B25" s="113" t="s">
+      <c r="B25" s="66" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="101"/>
-      <c r="D25" s="101"/>
-      <c r="E25" s="101"/>
-      <c r="F25" s="113" t="s">
+      <c r="C25" s="66"/>
+      <c r="D25" s="66"/>
+      <c r="E25" s="66"/>
+      <c r="F25" s="66" t="s">
         <v>104</v>
       </c>
-      <c r="G25" s="101"/>
-      <c r="H25" s="101"/>
-      <c r="I25" s="101"/>
-      <c r="J25" s="101"/>
-      <c r="K25" s="109" t="s">
+      <c r="G25" s="66"/>
+      <c r="H25" s="66"/>
+      <c r="I25" s="66"/>
+      <c r="J25" s="66"/>
+      <c r="K25" s="67" t="s">
         <v>93</v>
       </c>
-      <c r="L25" s="110"/>
-      <c r="M25" s="110"/>
-      <c r="N25" s="111"/>
-      <c r="O25" s="133" t="s">
+      <c r="L25" s="91"/>
+      <c r="M25" s="91"/>
+      <c r="N25" s="70"/>
+      <c r="O25" s="106" t="s">
         <v>55</v>
       </c>
-      <c r="P25" s="134"/>
-      <c r="Q25" s="101"/>
-      <c r="R25" s="101"/>
-      <c r="S25" s="101"/>
-      <c r="T25" s="101"/>
-      <c r="U25" s="101" t="s">
+      <c r="P25" s="107"/>
+      <c r="Q25" s="66"/>
+      <c r="R25" s="66"/>
+      <c r="S25" s="66"/>
+      <c r="T25" s="66"/>
+      <c r="U25" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="V25" s="101"/>
-      <c r="W25" s="101"/>
-      <c r="X25" s="136">
+      <c r="V25" s="66"/>
+      <c r="W25" s="66"/>
+      <c r="X25" s="109">
         <v>20</v>
       </c>
-      <c r="Y25" s="141"/>
+      <c r="Y25" s="114"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A26" s="101">
+      <c r="A26" s="66">
         <v>6</v>
       </c>
-      <c r="B26" s="113" t="s">
+      <c r="B26" s="66" t="s">
         <v>105</v>
       </c>
-      <c r="C26" s="101"/>
-      <c r="D26" s="101"/>
-      <c r="E26" s="101"/>
-      <c r="F26" s="113" t="s">
+      <c r="C26" s="66"/>
+      <c r="D26" s="66"/>
+      <c r="E26" s="66"/>
+      <c r="F26" s="66" t="s">
         <v>106</v>
       </c>
-      <c r="G26" s="101"/>
-      <c r="H26" s="101"/>
-      <c r="I26" s="101"/>
-      <c r="J26" s="101"/>
-      <c r="K26" s="109" t="s">
+      <c r="G26" s="66"/>
+      <c r="H26" s="66"/>
+      <c r="I26" s="66"/>
+      <c r="J26" s="66"/>
+      <c r="K26" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="L26" s="110"/>
-      <c r="M26" s="110"/>
-      <c r="N26" s="111"/>
-      <c r="O26" s="133"/>
-      <c r="P26" s="134"/>
-      <c r="Q26" s="101" t="s">
+      <c r="L26" s="91"/>
+      <c r="M26" s="91"/>
+      <c r="N26" s="70"/>
+      <c r="O26" s="106"/>
+      <c r="P26" s="107"/>
+      <c r="Q26" s="66" t="s">
         <v>107</v>
       </c>
-      <c r="R26" s="101"/>
-      <c r="S26" s="101"/>
-      <c r="T26" s="101"/>
-      <c r="U26" s="101" t="s">
+      <c r="R26" s="66"/>
+      <c r="S26" s="66"/>
+      <c r="T26" s="66"/>
+      <c r="U26" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="V26" s="101"/>
-      <c r="W26" s="101"/>
-      <c r="X26" s="109" t="s">
+      <c r="V26" s="66"/>
+      <c r="W26" s="66"/>
+      <c r="X26" s="67" t="s">
         <v>108</v>
       </c>
-      <c r="Y26" s="111"/>
+      <c r="Y26" s="70"/>
     </row>
     <row r="27" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A27" s="123"/>
-      <c r="X27" s="82"/>
-      <c r="Y27" s="82"/>
+      <c r="A27" s="99"/>
+      <c r="X27" s="63"/>
+      <c r="Y27" s="63"/>
     </row>
   </sheetData>
   <mergeCells count="125">
@@ -5852,32 +5719,32 @@
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="26" t="s">
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="93"/>
-      <c r="O1" s="93"/>
-      <c r="P1" s="93"/>
-      <c r="Q1" s="27" t="s">
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="28" t="s">
+      <c r="R1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="95"/>
-      <c r="T1" s="29" t="s">
+      <c r="S1" s="16"/>
+      <c r="T1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="186" t="s">
+      <c r="U1" s="154" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="31"/>
+      <c r="V1" s="30"/>
     </row>
     <row r="2" customHeight="1" spans="1:22">
       <c r="A2" s="6"/>
@@ -5888,20 +5755,20 @@
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="94"/>
-      <c r="O2" s="94"/>
-      <c r="P2" s="94"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="96"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="38"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="79"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="37"/>
     </row>
     <row r="3" customHeight="1" spans="1:22">
       <c r="A3" s="6"/>
@@ -5912,32 +5779,32 @@
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
-      <c r="I3" s="24" t="s">
+      <c r="I3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="26" t="s">
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="93"/>
-      <c r="O3" s="93"/>
-      <c r="P3" s="93"/>
-      <c r="Q3" s="27" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="28" t="s">
+      <c r="R3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="95"/>
-      <c r="T3" s="27" t="s">
+      <c r="S3" s="16"/>
+      <c r="T3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="186" t="s">
+      <c r="U3" s="154" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="31"/>
+      <c r="V3" s="30"/>
     </row>
     <row r="4" customHeight="1" spans="1:22">
       <c r="A4" s="8"/>
@@ -5948,20 +5815,20 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="94"/>
-      <c r="O4" s="94"/>
-      <c r="P4" s="94"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="96"/>
-      <c r="T4" s="27"/>
-      <c r="U4" s="37"/>
-      <c r="V4" s="38"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="79"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="79"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="37"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A5" s="10" t="s">
@@ -6000,7 +5867,7 @@
       <c r="V5" s="11"/>
     </row>
     <row r="6" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A6" s="91"/>
+      <c r="A6" s="76"/>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -6024,177 +5891,177 @@
       <c r="V6" s="18"/>
     </row>
     <row r="7" s="2" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A7" s="98" t="s">
+      <c r="A7" s="82" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="99"/>
-      <c r="C7" s="99"/>
-      <c r="D7" s="99"/>
-      <c r="E7" s="99"/>
-      <c r="F7" s="99"/>
-      <c r="G7" s="99"/>
-      <c r="H7" s="99"/>
-      <c r="I7" s="99"/>
-      <c r="J7" s="99"/>
-      <c r="K7" s="99"/>
-      <c r="L7" s="99"/>
-      <c r="M7" s="99"/>
-      <c r="N7" s="99"/>
-      <c r="O7" s="99"/>
-      <c r="P7" s="99"/>
-      <c r="Q7" s="99"/>
-      <c r="R7" s="99"/>
-      <c r="S7" s="99"/>
-      <c r="T7" s="99"/>
-      <c r="U7" s="99"/>
-      <c r="V7" s="114"/>
+      <c r="B7" s="83"/>
+      <c r="C7" s="83"/>
+      <c r="D7" s="83"/>
+      <c r="E7" s="83"/>
+      <c r="F7" s="83"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="83"/>
+      <c r="I7" s="83"/>
+      <c r="J7" s="83"/>
+      <c r="K7" s="83"/>
+      <c r="L7" s="83"/>
+      <c r="M7" s="83"/>
+      <c r="N7" s="83"/>
+      <c r="O7" s="83"/>
+      <c r="P7" s="83"/>
+      <c r="Q7" s="83"/>
+      <c r="R7" s="83"/>
+      <c r="S7" s="83"/>
+      <c r="T7" s="83"/>
+      <c r="U7" s="83"/>
+      <c r="V7" s="93"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A8" s="100" t="s">
+      <c r="A8" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="100" t="s">
+      <c r="B8" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="100"/>
-      <c r="D8" s="100"/>
-      <c r="E8" s="100"/>
-      <c r="F8" s="100"/>
-      <c r="G8" s="100"/>
-      <c r="H8" s="100"/>
-      <c r="I8" s="100" t="s">
+      <c r="C8" s="84"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="84"/>
+      <c r="H8" s="84"/>
+      <c r="I8" s="84" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="100"/>
-      <c r="K8" s="100"/>
-      <c r="L8" s="100"/>
-      <c r="M8" s="100" t="s">
+      <c r="J8" s="84"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="84"/>
+      <c r="M8" s="84" t="s">
         <v>49</v>
       </c>
-      <c r="N8" s="100"/>
-      <c r="O8" s="100"/>
-      <c r="P8" s="112" t="s">
+      <c r="N8" s="84"/>
+      <c r="O8" s="84"/>
+      <c r="P8" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="Q8" s="112"/>
-      <c r="R8" s="112"/>
-      <c r="S8" s="112"/>
-      <c r="T8" s="36" t="s">
+      <c r="Q8" s="92"/>
+      <c r="R8" s="92"/>
+      <c r="S8" s="92"/>
+      <c r="T8" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="U8" s="115"/>
-      <c r="V8" s="116"/>
+      <c r="U8" s="94"/>
+      <c r="V8" s="95"/>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A9" s="101">
+      <c r="A9" s="66">
         <v>1</v>
       </c>
-      <c r="B9" s="102" t="s">
+      <c r="B9" s="85" t="s">
         <v>112</v>
       </c>
-      <c r="C9" s="103"/>
-      <c r="D9" s="103"/>
-      <c r="E9" s="103"/>
-      <c r="F9" s="103"/>
-      <c r="G9" s="103"/>
-      <c r="H9" s="103"/>
-      <c r="I9" s="109" t="s">
+      <c r="C9" s="86"/>
+      <c r="D9" s="86"/>
+      <c r="E9" s="86"/>
+      <c r="F9" s="86"/>
+      <c r="G9" s="86"/>
+      <c r="H9" s="86"/>
+      <c r="I9" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="J9" s="110"/>
-      <c r="K9" s="110"/>
-      <c r="L9" s="111"/>
-      <c r="M9" s="188" t="s">
+      <c r="J9" s="91"/>
+      <c r="K9" s="91"/>
+      <c r="L9" s="70"/>
+      <c r="M9" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="N9" s="101"/>
-      <c r="O9" s="101"/>
-      <c r="P9" s="188" t="s">
+      <c r="N9" s="66"/>
+      <c r="O9" s="66"/>
+      <c r="P9" s="156" t="s">
         <v>113</v>
       </c>
-      <c r="Q9" s="101"/>
-      <c r="R9" s="101"/>
-      <c r="S9" s="101"/>
-      <c r="T9" s="101" t="s">
+      <c r="Q9" s="66"/>
+      <c r="R9" s="66"/>
+      <c r="S9" s="66"/>
+      <c r="T9" s="66" t="s">
         <v>114</v>
       </c>
-      <c r="U9" s="101"/>
-      <c r="V9" s="101"/>
+      <c r="U9" s="66"/>
+      <c r="V9" s="66"/>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A10" s="101">
+      <c r="A10" s="66">
         <v>2</v>
       </c>
-      <c r="B10" s="104" t="s">
+      <c r="B10" s="87" t="s">
         <v>115</v>
       </c>
-      <c r="C10" s="103"/>
-      <c r="D10" s="103"/>
-      <c r="E10" s="103"/>
-      <c r="F10" s="103"/>
-      <c r="G10" s="103"/>
-      <c r="H10" s="103"/>
-      <c r="I10" s="109" t="s">
+      <c r="C10" s="86"/>
+      <c r="D10" s="86"/>
+      <c r="E10" s="86"/>
+      <c r="F10" s="86"/>
+      <c r="G10" s="86"/>
+      <c r="H10" s="86"/>
+      <c r="I10" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="J10" s="110"/>
-      <c r="K10" s="110"/>
-      <c r="L10" s="111"/>
-      <c r="M10" s="188" t="s">
+      <c r="J10" s="91"/>
+      <c r="K10" s="91"/>
+      <c r="L10" s="70"/>
+      <c r="M10" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="101"/>
-      <c r="O10" s="101"/>
-      <c r="P10" s="188" t="s">
+      <c r="N10" s="66"/>
+      <c r="O10" s="66"/>
+      <c r="P10" s="156" t="s">
         <v>116</v>
       </c>
-      <c r="Q10" s="101"/>
-      <c r="R10" s="101"/>
-      <c r="S10" s="101"/>
-      <c r="T10" s="113" t="s">
+      <c r="Q10" s="66"/>
+      <c r="R10" s="66"/>
+      <c r="S10" s="66"/>
+      <c r="T10" s="66" t="s">
         <v>117</v>
       </c>
-      <c r="U10" s="101"/>
-      <c r="V10" s="101"/>
-    </row>
-    <row r="11" s="97" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A11" s="101">
+      <c r="U10" s="66"/>
+      <c r="V10" s="66"/>
+    </row>
+    <row r="11" s="81" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A11" s="66">
         <v>3</v>
       </c>
-      <c r="B11" s="104" t="s">
+      <c r="B11" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="103"/>
-      <c r="D11" s="103"/>
-      <c r="E11" s="103"/>
-      <c r="F11" s="103"/>
-      <c r="G11" s="103"/>
-      <c r="H11" s="105"/>
-      <c r="I11" s="109" t="s">
+      <c r="C11" s="86"/>
+      <c r="D11" s="86"/>
+      <c r="E11" s="86"/>
+      <c r="F11" s="86"/>
+      <c r="G11" s="86"/>
+      <c r="H11" s="88"/>
+      <c r="I11" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="J11" s="110"/>
-      <c r="K11" s="110"/>
-      <c r="L11" s="111"/>
-      <c r="M11" s="188" t="s">
+      <c r="J11" s="91"/>
+      <c r="K11" s="91"/>
+      <c r="L11" s="70"/>
+      <c r="M11" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="N11" s="101"/>
-      <c r="O11" s="101"/>
-      <c r="P11" s="113" t="s">
+      <c r="N11" s="66"/>
+      <c r="O11" s="66"/>
+      <c r="P11" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="Q11" s="101"/>
-      <c r="R11" s="101"/>
-      <c r="S11" s="101"/>
-      <c r="T11" s="101" t="s">
+      <c r="Q11" s="66"/>
+      <c r="R11" s="66"/>
+      <c r="S11" s="66"/>
+      <c r="T11" s="66" t="s">
         <v>119</v>
       </c>
-      <c r="U11" s="101"/>
-      <c r="V11" s="101"/>
+      <c r="U11" s="66"/>
+      <c r="V11" s="66"/>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A12" s="91"/>
+      <c r="A12" s="76"/>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
@@ -6218,416 +6085,416 @@
       <c r="V12" s="18"/>
     </row>
     <row r="13" customHeight="1" spans="1:22">
-      <c r="A13" s="106" t="s">
+      <c r="A13" s="89" t="s">
         <v>120</v>
       </c>
-      <c r="B13" s="107"/>
-      <c r="C13" s="107"/>
-      <c r="D13" s="107"/>
-      <c r="E13" s="107"/>
-      <c r="F13" s="107"/>
-      <c r="G13" s="107"/>
-      <c r="H13" s="107"/>
-      <c r="I13" s="107"/>
-      <c r="J13" s="107"/>
-      <c r="K13" s="107"/>
-      <c r="L13" s="107"/>
-      <c r="M13" s="107"/>
-      <c r="N13" s="107"/>
-      <c r="O13" s="107"/>
-      <c r="P13" s="107"/>
-      <c r="Q13" s="107"/>
-      <c r="R13" s="107"/>
-      <c r="S13" s="107"/>
-      <c r="T13" s="107"/>
-      <c r="U13" s="107"/>
-      <c r="V13" s="117"/>
+      <c r="B13" s="90"/>
+      <c r="C13" s="90"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="90"/>
+      <c r="F13" s="90"/>
+      <c r="G13" s="90"/>
+      <c r="H13" s="90"/>
+      <c r="I13" s="90"/>
+      <c r="J13" s="90"/>
+      <c r="K13" s="90"/>
+      <c r="L13" s="90"/>
+      <c r="M13" s="90"/>
+      <c r="N13" s="90"/>
+      <c r="O13" s="90"/>
+      <c r="P13" s="90"/>
+      <c r="Q13" s="90"/>
+      <c r="R13" s="90"/>
+      <c r="S13" s="90"/>
+      <c r="T13" s="90"/>
+      <c r="U13" s="90"/>
+      <c r="V13" s="96"/>
     </row>
     <row r="14" customHeight="1" spans="1:22">
-      <c r="A14" s="100" t="s">
+      <c r="A14" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="100" t="s">
+      <c r="B14" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="100"/>
-      <c r="D14" s="100"/>
-      <c r="E14" s="100"/>
-      <c r="F14" s="100"/>
-      <c r="G14" s="100"/>
-      <c r="H14" s="100"/>
-      <c r="I14" s="100" t="s">
+      <c r="C14" s="84"/>
+      <c r="D14" s="84"/>
+      <c r="E14" s="84"/>
+      <c r="F14" s="84"/>
+      <c r="G14" s="84"/>
+      <c r="H14" s="84"/>
+      <c r="I14" s="84" t="s">
         <v>61</v>
       </c>
-      <c r="J14" s="100"/>
-      <c r="K14" s="100"/>
-      <c r="L14" s="100"/>
-      <c r="M14" s="100" t="s">
+      <c r="J14" s="84"/>
+      <c r="K14" s="84"/>
+      <c r="L14" s="84"/>
+      <c r="M14" s="84" t="s">
         <v>49</v>
       </c>
-      <c r="N14" s="100"/>
-      <c r="O14" s="100"/>
-      <c r="P14" s="112" t="s">
+      <c r="N14" s="84"/>
+      <c r="O14" s="84"/>
+      <c r="P14" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="Q14" s="112"/>
-      <c r="R14" s="112"/>
-      <c r="S14" s="112"/>
-      <c r="T14" s="36" t="s">
+      <c r="Q14" s="92"/>
+      <c r="R14" s="92"/>
+      <c r="S14" s="92"/>
+      <c r="T14" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="U14" s="115"/>
-      <c r="V14" s="116"/>
-    </row>
-    <row r="15" s="97" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A15" s="101">
+      <c r="U14" s="94"/>
+      <c r="V14" s="95"/>
+    </row>
+    <row r="15" s="81" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A15" s="66">
         <v>1</v>
       </c>
-      <c r="B15" s="102" t="s">
+      <c r="B15" s="85" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="103"/>
-      <c r="D15" s="103"/>
-      <c r="E15" s="103"/>
-      <c r="F15" s="103"/>
-      <c r="G15" s="103"/>
-      <c r="H15" s="103"/>
-      <c r="I15" s="109" t="s">
+      <c r="C15" s="86"/>
+      <c r="D15" s="86"/>
+      <c r="E15" s="86"/>
+      <c r="F15" s="86"/>
+      <c r="G15" s="86"/>
+      <c r="H15" s="86"/>
+      <c r="I15" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="J15" s="110"/>
-      <c r="K15" s="110"/>
-      <c r="L15" s="111"/>
-      <c r="M15" s="188" t="s">
+      <c r="J15" s="91"/>
+      <c r="K15" s="91"/>
+      <c r="L15" s="70"/>
+      <c r="M15" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="N15" s="101"/>
-      <c r="O15" s="101"/>
-      <c r="P15" s="188" t="s">
+      <c r="N15" s="66"/>
+      <c r="O15" s="66"/>
+      <c r="P15" s="156" t="s">
         <v>113</v>
       </c>
-      <c r="Q15" s="101"/>
-      <c r="R15" s="101"/>
-      <c r="S15" s="101"/>
-      <c r="T15" s="101" t="s">
+      <c r="Q15" s="66"/>
+      <c r="R15" s="66"/>
+      <c r="S15" s="66"/>
+      <c r="T15" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="U15" s="101"/>
-      <c r="V15" s="101"/>
-    </row>
-    <row r="16" s="97" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A16" s="101">
+      <c r="U15" s="66"/>
+      <c r="V15" s="66"/>
+    </row>
+    <row r="16" s="81" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A16" s="66">
         <v>2</v>
       </c>
-      <c r="B16" s="102" t="s">
+      <c r="B16" s="85" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="103"/>
-      <c r="D16" s="103"/>
-      <c r="E16" s="103"/>
-      <c r="F16" s="103"/>
-      <c r="G16" s="103"/>
-      <c r="H16" s="103"/>
-      <c r="I16" s="109" t="s">
+      <c r="C16" s="86"/>
+      <c r="D16" s="86"/>
+      <c r="E16" s="86"/>
+      <c r="F16" s="86"/>
+      <c r="G16" s="86"/>
+      <c r="H16" s="86"/>
+      <c r="I16" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="J16" s="110"/>
-      <c r="K16" s="110"/>
-      <c r="L16" s="111"/>
-      <c r="M16" s="188" t="s">
+      <c r="J16" s="91"/>
+      <c r="K16" s="91"/>
+      <c r="L16" s="70"/>
+      <c r="M16" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="N16" s="101"/>
-      <c r="O16" s="101"/>
-      <c r="P16" s="188" t="s">
+      <c r="N16" s="66"/>
+      <c r="O16" s="66"/>
+      <c r="P16" s="156" t="s">
         <v>122</v>
       </c>
-      <c r="Q16" s="101"/>
-      <c r="R16" s="101"/>
-      <c r="S16" s="101"/>
-      <c r="T16" s="101" t="s">
+      <c r="Q16" s="66"/>
+      <c r="R16" s="66"/>
+      <c r="S16" s="66"/>
+      <c r="T16" s="66" t="s">
         <v>123</v>
       </c>
-      <c r="U16" s="101"/>
-      <c r="V16" s="101"/>
-    </row>
-    <row r="17" s="97" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A17" s="101">
+      <c r="U16" s="66"/>
+      <c r="V16" s="66"/>
+    </row>
+    <row r="17" s="81" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A17" s="66">
         <v>3</v>
       </c>
-      <c r="B17" s="104" t="s">
+      <c r="B17" s="87" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="103"/>
-      <c r="D17" s="103"/>
-      <c r="E17" s="103"/>
-      <c r="F17" s="103"/>
-      <c r="G17" s="103"/>
-      <c r="H17" s="105"/>
-      <c r="I17" s="109" t="s">
+      <c r="C17" s="86"/>
+      <c r="D17" s="86"/>
+      <c r="E17" s="86"/>
+      <c r="F17" s="86"/>
+      <c r="G17" s="86"/>
+      <c r="H17" s="88"/>
+      <c r="I17" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="J17" s="110"/>
-      <c r="K17" s="110"/>
-      <c r="L17" s="111"/>
-      <c r="M17" s="188" t="s">
+      <c r="J17" s="91"/>
+      <c r="K17" s="91"/>
+      <c r="L17" s="70"/>
+      <c r="M17" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="N17" s="101"/>
-      <c r="O17" s="101"/>
-      <c r="P17" s="113" t="s">
+      <c r="N17" s="66"/>
+      <c r="O17" s="66"/>
+      <c r="P17" s="66" t="s">
         <v>89</v>
       </c>
-      <c r="Q17" s="101"/>
-      <c r="R17" s="101"/>
-      <c r="S17" s="101"/>
-      <c r="T17" s="101" t="s">
+      <c r="Q17" s="66"/>
+      <c r="R17" s="66"/>
+      <c r="S17" s="66"/>
+      <c r="T17" s="66" t="s">
         <v>119</v>
       </c>
-      <c r="U17" s="101"/>
-      <c r="V17" s="101"/>
+      <c r="U17" s="66"/>
+      <c r="V17" s="66"/>
     </row>
     <row r="19" customHeight="1" spans="1:22">
-      <c r="A19" s="106" t="s">
+      <c r="A19" s="89" t="s">
         <v>124</v>
       </c>
-      <c r="B19" s="107"/>
-      <c r="C19" s="107"/>
-      <c r="D19" s="107"/>
-      <c r="E19" s="107"/>
-      <c r="F19" s="107"/>
-      <c r="G19" s="107"/>
-      <c r="H19" s="107"/>
-      <c r="I19" s="107"/>
-      <c r="J19" s="107"/>
-      <c r="K19" s="107"/>
-      <c r="L19" s="107"/>
-      <c r="M19" s="107"/>
-      <c r="N19" s="107"/>
-      <c r="O19" s="107"/>
-      <c r="P19" s="107"/>
-      <c r="Q19" s="107"/>
-      <c r="R19" s="107"/>
-      <c r="S19" s="107"/>
-      <c r="T19" s="107"/>
-      <c r="U19" s="107"/>
-      <c r="V19" s="117"/>
+      <c r="B19" s="90"/>
+      <c r="C19" s="90"/>
+      <c r="D19" s="90"/>
+      <c r="E19" s="90"/>
+      <c r="F19" s="90"/>
+      <c r="G19" s="90"/>
+      <c r="H19" s="90"/>
+      <c r="I19" s="90"/>
+      <c r="J19" s="90"/>
+      <c r="K19" s="90"/>
+      <c r="L19" s="90"/>
+      <c r="M19" s="90"/>
+      <c r="N19" s="90"/>
+      <c r="O19" s="90"/>
+      <c r="P19" s="90"/>
+      <c r="Q19" s="90"/>
+      <c r="R19" s="90"/>
+      <c r="S19" s="90"/>
+      <c r="T19" s="90"/>
+      <c r="U19" s="90"/>
+      <c r="V19" s="96"/>
     </row>
     <row r="20" customHeight="1" spans="1:22">
-      <c r="A20" s="100" t="s">
+      <c r="A20" s="84" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="100" t="s">
+      <c r="B20" s="84" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="100"/>
-      <c r="D20" s="100"/>
-      <c r="E20" s="100"/>
-      <c r="F20" s="100"/>
-      <c r="G20" s="100"/>
-      <c r="H20" s="100"/>
-      <c r="I20" s="100" t="s">
+      <c r="C20" s="84"/>
+      <c r="D20" s="84"/>
+      <c r="E20" s="84"/>
+      <c r="F20" s="84"/>
+      <c r="G20" s="84"/>
+      <c r="H20" s="84"/>
+      <c r="I20" s="84" t="s">
         <v>61</v>
       </c>
-      <c r="J20" s="100"/>
-      <c r="K20" s="100"/>
-      <c r="L20" s="100"/>
-      <c r="M20" s="100" t="s">
+      <c r="J20" s="84"/>
+      <c r="K20" s="84"/>
+      <c r="L20" s="84"/>
+      <c r="M20" s="84" t="s">
         <v>49</v>
       </c>
-      <c r="N20" s="100"/>
-      <c r="O20" s="100"/>
-      <c r="P20" s="112" t="s">
+      <c r="N20" s="84"/>
+      <c r="O20" s="84"/>
+      <c r="P20" s="92" t="s">
         <v>52</v>
       </c>
-      <c r="Q20" s="112"/>
-      <c r="R20" s="112"/>
-      <c r="S20" s="112"/>
-      <c r="T20" s="36" t="s">
+      <c r="Q20" s="92"/>
+      <c r="R20" s="92"/>
+      <c r="S20" s="92"/>
+      <c r="T20" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="U20" s="115"/>
-      <c r="V20" s="116"/>
-    </row>
-    <row r="21" s="97" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A21" s="101">
+      <c r="U20" s="94"/>
+      <c r="V20" s="95"/>
+    </row>
+    <row r="21" s="81" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A21" s="66">
         <v>1</v>
       </c>
-      <c r="B21" s="102" t="s">
+      <c r="B21" s="85" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="103"/>
-      <c r="D21" s="103"/>
-      <c r="E21" s="103"/>
-      <c r="F21" s="103"/>
-      <c r="G21" s="103"/>
-      <c r="H21" s="103"/>
-      <c r="I21" s="109" t="s">
+      <c r="C21" s="86"/>
+      <c r="D21" s="86"/>
+      <c r="E21" s="86"/>
+      <c r="F21" s="86"/>
+      <c r="G21" s="86"/>
+      <c r="H21" s="86"/>
+      <c r="I21" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="J21" s="110"/>
-      <c r="K21" s="110"/>
-      <c r="L21" s="111"/>
-      <c r="M21" s="188" t="s">
+      <c r="J21" s="91"/>
+      <c r="K21" s="91"/>
+      <c r="L21" s="70"/>
+      <c r="M21" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="N21" s="101"/>
-      <c r="O21" s="101"/>
-      <c r="P21" s="188" t="s">
+      <c r="N21" s="66"/>
+      <c r="O21" s="66"/>
+      <c r="P21" s="156" t="s">
         <v>113</v>
       </c>
-      <c r="Q21" s="101"/>
-      <c r="R21" s="101"/>
-      <c r="S21" s="101"/>
-      <c r="T21" s="101" t="s">
+      <c r="Q21" s="66"/>
+      <c r="R21" s="66"/>
+      <c r="S21" s="66"/>
+      <c r="T21" s="66" t="s">
         <v>121</v>
       </c>
-      <c r="U21" s="101"/>
-      <c r="V21" s="101"/>
-    </row>
-    <row r="22" s="97" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A22" s="101">
+      <c r="U21" s="66"/>
+      <c r="V21" s="66"/>
+    </row>
+    <row r="22" s="81" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A22" s="66">
         <v>2</v>
       </c>
-      <c r="B22" s="102" t="s">
+      <c r="B22" s="85" t="s">
         <v>115</v>
       </c>
-      <c r="C22" s="108"/>
-      <c r="D22" s="108"/>
-      <c r="E22" s="108"/>
-      <c r="F22" s="108"/>
-      <c r="G22" s="108"/>
-      <c r="H22" s="108"/>
-      <c r="I22" s="109" t="s">
+      <c r="C22" s="52"/>
+      <c r="D22" s="52"/>
+      <c r="E22" s="52"/>
+      <c r="F22" s="52"/>
+      <c r="G22" s="52"/>
+      <c r="H22" s="52"/>
+      <c r="I22" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="J22" s="110"/>
-      <c r="K22" s="110"/>
-      <c r="L22" s="111"/>
-      <c r="M22" s="188" t="s">
+      <c r="J22" s="91"/>
+      <c r="K22" s="91"/>
+      <c r="L22" s="70"/>
+      <c r="M22" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="N22" s="101"/>
-      <c r="O22" s="101"/>
-      <c r="P22" s="188" t="s">
+      <c r="N22" s="66"/>
+      <c r="O22" s="66"/>
+      <c r="P22" s="156" t="s">
         <v>122</v>
       </c>
-      <c r="Q22" s="101"/>
-      <c r="R22" s="101"/>
-      <c r="S22" s="101"/>
-      <c r="T22" s="101" t="s">
+      <c r="Q22" s="66"/>
+      <c r="R22" s="66"/>
+      <c r="S22" s="66"/>
+      <c r="T22" s="66" t="s">
         <v>125</v>
       </c>
-      <c r="U22" s="101"/>
-      <c r="V22" s="101"/>
-    </row>
-    <row r="23" s="97" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A23" s="101">
+      <c r="U22" s="66"/>
+      <c r="V22" s="66"/>
+    </row>
+    <row r="23" s="81" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A23" s="66">
         <v>3</v>
       </c>
-      <c r="B23" s="109" t="s">
+      <c r="B23" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="C23" s="110"/>
-      <c r="D23" s="110"/>
-      <c r="E23" s="110"/>
-      <c r="F23" s="110"/>
-      <c r="G23" s="110"/>
-      <c r="H23" s="111"/>
-      <c r="I23" s="109" t="s">
+      <c r="C23" s="91"/>
+      <c r="D23" s="91"/>
+      <c r="E23" s="91"/>
+      <c r="F23" s="91"/>
+      <c r="G23" s="91"/>
+      <c r="H23" s="70"/>
+      <c r="I23" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="J23" s="110"/>
-      <c r="K23" s="110"/>
-      <c r="L23" s="111"/>
-      <c r="M23" s="188" t="s">
+      <c r="J23" s="91"/>
+      <c r="K23" s="91"/>
+      <c r="L23" s="70"/>
+      <c r="M23" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="N23" s="101"/>
-      <c r="O23" s="101"/>
-      <c r="P23" s="101" t="s">
+      <c r="N23" s="66"/>
+      <c r="O23" s="66"/>
+      <c r="P23" s="66" t="s">
         <v>127</v>
       </c>
-      <c r="Q23" s="101"/>
-      <c r="R23" s="101"/>
-      <c r="S23" s="101"/>
-      <c r="T23" s="188" t="s">
+      <c r="Q23" s="66"/>
+      <c r="R23" s="66"/>
+      <c r="S23" s="66"/>
+      <c r="T23" s="156" t="s">
         <v>128</v>
       </c>
-      <c r="U23" s="101"/>
-      <c r="V23" s="101"/>
-    </row>
-    <row r="24" s="97" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A24" s="101">
+      <c r="U23" s="66"/>
+      <c r="V23" s="66"/>
+    </row>
+    <row r="24" s="81" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A24" s="66">
         <v>4</v>
       </c>
-      <c r="B24" s="109" t="s">
+      <c r="B24" s="67" t="s">
         <v>129</v>
       </c>
-      <c r="C24" s="110"/>
-      <c r="D24" s="110"/>
-      <c r="E24" s="110"/>
-      <c r="F24" s="110"/>
-      <c r="G24" s="110"/>
-      <c r="H24" s="111"/>
-      <c r="I24" s="109" t="s">
+      <c r="C24" s="91"/>
+      <c r="D24" s="91"/>
+      <c r="E24" s="91"/>
+      <c r="F24" s="91"/>
+      <c r="G24" s="91"/>
+      <c r="H24" s="70"/>
+      <c r="I24" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="J24" s="110"/>
-      <c r="K24" s="110"/>
-      <c r="L24" s="111"/>
-      <c r="M24" s="188" t="s">
+      <c r="J24" s="91"/>
+      <c r="K24" s="91"/>
+      <c r="L24" s="70"/>
+      <c r="M24" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="N24" s="101"/>
-      <c r="O24" s="101"/>
-      <c r="P24" s="101" t="s">
+      <c r="N24" s="66"/>
+      <c r="O24" s="66"/>
+      <c r="P24" s="66" t="s">
         <v>130</v>
       </c>
-      <c r="Q24" s="101"/>
-      <c r="R24" s="101"/>
-      <c r="S24" s="101"/>
-      <c r="T24" s="101" t="s">
+      <c r="Q24" s="66"/>
+      <c r="R24" s="66"/>
+      <c r="S24" s="66"/>
+      <c r="T24" s="66" t="s">
         <v>131</v>
       </c>
-      <c r="U24" s="101"/>
-      <c r="V24" s="101"/>
-    </row>
-    <row r="25" s="97" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A25" s="101">
+      <c r="U24" s="66"/>
+      <c r="V24" s="66"/>
+    </row>
+    <row r="25" s="81" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A25" s="66">
         <v>5</v>
       </c>
-      <c r="B25" s="109" t="s">
+      <c r="B25" s="67" t="s">
         <v>132</v>
       </c>
-      <c r="C25" s="110"/>
-      <c r="D25" s="110"/>
-      <c r="E25" s="110"/>
-      <c r="F25" s="110"/>
-      <c r="G25" s="110"/>
-      <c r="H25" s="111"/>
-      <c r="I25" s="109" t="s">
+      <c r="C25" s="91"/>
+      <c r="D25" s="91"/>
+      <c r="E25" s="91"/>
+      <c r="F25" s="91"/>
+      <c r="G25" s="91"/>
+      <c r="H25" s="70"/>
+      <c r="I25" s="67" t="s">
         <v>66</v>
       </c>
-      <c r="J25" s="110"/>
-      <c r="K25" s="110"/>
-      <c r="L25" s="111"/>
-      <c r="M25" s="188" t="s">
+      <c r="J25" s="91"/>
+      <c r="K25" s="91"/>
+      <c r="L25" s="70"/>
+      <c r="M25" s="156" t="s">
         <v>55</v>
       </c>
-      <c r="N25" s="101"/>
-      <c r="O25" s="101"/>
-      <c r="P25" s="101" t="s">
+      <c r="N25" s="66"/>
+      <c r="O25" s="66"/>
+      <c r="P25" s="66" t="s">
         <v>133</v>
       </c>
-      <c r="Q25" s="101"/>
-      <c r="R25" s="101"/>
-      <c r="S25" s="101"/>
-      <c r="T25" s="101" t="s">
+      <c r="Q25" s="66"/>
+      <c r="R25" s="66"/>
+      <c r="S25" s="66"/>
+      <c r="T25" s="66" t="s">
         <v>134</v>
       </c>
-      <c r="U25" s="101"/>
-      <c r="V25" s="101"/>
+      <c r="U25" s="66"/>
+      <c r="V25" s="66"/>
     </row>
   </sheetData>
   <mergeCells count="83">
@@ -6755,32 +6622,32 @@
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
-      <c r="M1" s="26" t="s">
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
+      <c r="M1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="93"/>
-      <c r="O1" s="93"/>
-      <c r="P1" s="93"/>
-      <c r="Q1" s="27" t="s">
+      <c r="N1" s="78"/>
+      <c r="O1" s="78"/>
+      <c r="P1" s="78"/>
+      <c r="Q1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="R1" s="28" t="s">
+      <c r="R1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="S1" s="95"/>
-      <c r="T1" s="29" t="s">
+      <c r="S1" s="16"/>
+      <c r="T1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="186" t="s">
+      <c r="U1" s="154" t="s">
         <v>12</v>
       </c>
-      <c r="V1" s="31"/>
+      <c r="V1" s="30"/>
     </row>
     <row r="2" customHeight="1" spans="1:22">
       <c r="A2" s="6"/>
@@ -6791,20 +6658,20 @@
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="33"/>
-      <c r="L2" s="33"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="94"/>
-      <c r="O2" s="94"/>
-      <c r="P2" s="94"/>
-      <c r="Q2" s="27"/>
-      <c r="R2" s="35"/>
-      <c r="S2" s="96"/>
-      <c r="T2" s="36"/>
-      <c r="U2" s="37"/>
-      <c r="V2" s="38"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="32"/>
+      <c r="L2" s="32"/>
+      <c r="M2" s="33"/>
+      <c r="N2" s="79"/>
+      <c r="O2" s="79"/>
+      <c r="P2" s="79"/>
+      <c r="Q2" s="26"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="36"/>
+      <c r="V2" s="37"/>
     </row>
     <row r="3" customHeight="1" spans="1:22">
       <c r="A3" s="6"/>
@@ -6815,32 +6682,32 @@
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
-      <c r="I3" s="24" t="s">
+      <c r="I3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="25"/>
-      <c r="K3" s="25"/>
-      <c r="L3" s="25"/>
-      <c r="M3" s="26" t="s">
+      <c r="J3" s="24"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="24"/>
+      <c r="M3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="93"/>
-      <c r="O3" s="93"/>
-      <c r="P3" s="93"/>
-      <c r="Q3" s="27" t="s">
+      <c r="N3" s="78"/>
+      <c r="O3" s="78"/>
+      <c r="P3" s="78"/>
+      <c r="Q3" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="R3" s="28" t="s">
+      <c r="R3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="S3" s="95"/>
-      <c r="T3" s="27" t="s">
+      <c r="S3" s="16"/>
+      <c r="T3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="186" t="s">
+      <c r="U3" s="154" t="s">
         <v>18</v>
       </c>
-      <c r="V3" s="31"/>
+      <c r="V3" s="30"/>
     </row>
     <row r="4" customHeight="1" spans="1:22">
       <c r="A4" s="8"/>
@@ -6851,20 +6718,20 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="33"/>
-      <c r="L4" s="33"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="94"/>
-      <c r="O4" s="94"/>
-      <c r="P4" s="94"/>
-      <c r="Q4" s="27"/>
-      <c r="R4" s="35"/>
-      <c r="S4" s="96"/>
-      <c r="T4" s="27"/>
-      <c r="U4" s="37"/>
-      <c r="V4" s="38"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="32"/>
+      <c r="L4" s="32"/>
+      <c r="M4" s="33"/>
+      <c r="N4" s="79"/>
+      <c r="O4" s="79"/>
+      <c r="P4" s="79"/>
+      <c r="Q4" s="26"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="26"/>
+      <c r="U4" s="36"/>
+      <c r="V4" s="37"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:22">
       <c r="A5" s="10" t="s">
@@ -6903,7 +6770,7 @@
       <c r="V5" s="11"/>
     </row>
     <row r="6" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A6" s="91"/>
+      <c r="A6" s="76"/>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -6927,7 +6794,7 @@
       <c r="V6" s="18"/>
     </row>
     <row r="7" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A7" s="91"/>
+      <c r="A7" s="76"/>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -6951,7 +6818,7 @@
       <c r="V7" s="18"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A8" s="92" t="s">
+      <c r="A8" s="77" t="s">
         <v>136</v>
       </c>
       <c r="B8" s="18"/>
@@ -6977,7 +6844,7 @@
       <c r="V8" s="18"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A9" s="91"/>
+      <c r="A9" s="76"/>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
@@ -7001,7 +6868,7 @@
       <c r="V9" s="18"/>
     </row>
     <row r="10" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A10" s="91"/>
+      <c r="A10" s="76"/>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
@@ -7025,7 +6892,7 @@
       <c r="V10" s="18"/>
     </row>
     <row r="11" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A11" s="91"/>
+      <c r="A11" s="76"/>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
@@ -7049,7 +6916,7 @@
       <c r="V11" s="18"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A12" s="91"/>
+      <c r="A12" s="76"/>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
@@ -7073,7 +6940,7 @@
       <c r="V12" s="18"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A13" s="91"/>
+      <c r="A13" s="76"/>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -7097,7 +6964,7 @@
       <c r="V13" s="18"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A14" s="91"/>
+      <c r="A14" s="76"/>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -7121,7 +6988,7 @@
       <c r="V14" s="18"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A15" s="91"/>
+      <c r="A15" s="76"/>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -7145,7 +7012,7 @@
       <c r="V15" s="18"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A16" s="91"/>
+      <c r="A16" s="76"/>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -7169,7 +7036,7 @@
       <c r="V16" s="18"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A17" s="91"/>
+      <c r="A17" s="76"/>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
@@ -7193,7 +7060,7 @@
       <c r="V17" s="18"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A18" s="91"/>
+      <c r="A18" s="76"/>
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
@@ -7217,7 +7084,7 @@
       <c r="V18" s="18"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A19" s="91"/>
+      <c r="A19" s="76"/>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
@@ -7241,7 +7108,7 @@
       <c r="V19" s="18"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A20" s="91"/>
+      <c r="A20" s="76"/>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
@@ -7265,7 +7132,7 @@
       <c r="V20" s="18"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A21" s="91"/>
+      <c r="A21" s="76"/>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
       <c r="D21" s="18"/>
@@ -7289,7 +7156,7 @@
       <c r="V21" s="18"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A22" s="91"/>
+      <c r="A22" s="76"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
       <c r="D22" s="18"/>
@@ -7313,7 +7180,7 @@
       <c r="V22" s="18"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A23" s="91"/>
+      <c r="A23" s="76"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
       <c r="D23" s="18"/>
@@ -7337,7 +7204,7 @@
       <c r="V23" s="18"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A24" s="91"/>
+      <c r="A24" s="76"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
@@ -7361,7 +7228,7 @@
       <c r="V24" s="18"/>
     </row>
     <row r="25" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A25" s="91"/>
+      <c r="A25" s="76"/>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
@@ -7385,7 +7252,7 @@
       <c r="V25" s="18"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A26" s="91"/>
+      <c r="A26" s="76"/>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
@@ -7409,7 +7276,7 @@
       <c r="V26" s="18"/>
     </row>
     <row r="27" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A27" s="91"/>
+      <c r="A27" s="76"/>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
@@ -7433,7 +7300,7 @@
       <c r="V27" s="18"/>
     </row>
     <row r="28" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A28" s="91"/>
+      <c r="A28" s="76"/>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
@@ -7457,7 +7324,7 @@
       <c r="V28" s="18"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A29" s="91"/>
+      <c r="A29" s="76"/>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
@@ -7481,7 +7348,7 @@
       <c r="V29" s="18"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A30" s="91"/>
+      <c r="A30" s="76"/>
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
@@ -7505,7 +7372,7 @@
       <c r="V30" s="18"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A31" s="91"/>
+      <c r="A31" s="76"/>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
       <c r="D31" s="18"/>
@@ -7529,7 +7396,7 @@
       <c r="V31" s="18"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A32" s="91"/>
+      <c r="A32" s="76"/>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
       <c r="D32" s="18"/>
@@ -7553,7 +7420,7 @@
       <c r="V32" s="18"/>
     </row>
     <row r="33" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A33" s="91"/>
+      <c r="A33" s="76"/>
       <c r="B33" s="18"/>
       <c r="C33" s="18"/>
       <c r="D33" s="18"/>
@@ -7577,7 +7444,7 @@
       <c r="V33" s="18"/>
     </row>
     <row r="34" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A34" s="91"/>
+      <c r="A34" s="76"/>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
       <c r="D34" s="18"/>
@@ -7601,7 +7468,7 @@
       <c r="V34" s="18"/>
     </row>
     <row r="35" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A35" s="91"/>
+      <c r="A35" s="76"/>
       <c r="B35" s="18"/>
       <c r="C35" s="18"/>
       <c r="D35" s="18"/>
@@ -7625,7 +7492,7 @@
       <c r="V35" s="18"/>
     </row>
     <row r="36" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A36" s="91"/>
+      <c r="A36" s="76"/>
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
@@ -7649,7 +7516,7 @@
       <c r="V36" s="18"/>
     </row>
     <row r="37" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A37" s="91"/>
+      <c r="A37" s="76"/>
       <c r="B37" s="18"/>
       <c r="C37" s="18"/>
       <c r="D37" s="18"/>
@@ -7703,7 +7570,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P137"/>
+  <dimension ref="A1:P134"/>
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.44444444444444" style="3" customWidth="1"/>
@@ -7732,26 +7599,26 @@
       <c r="F1" s="5"/>
       <c r="G1" s="5"/>
       <c r="H1" s="5"/>
-      <c r="I1" s="24" t="s">
+      <c r="I1" s="23" t="s">
         <v>9</v>
       </c>
-      <c r="J1" s="25"/>
-      <c r="K1" s="26" t="s">
+      <c r="J1" s="24"/>
+      <c r="K1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="27" t="s">
+      <c r="L1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="M1" s="28" t="s">
+      <c r="M1" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="N1" s="29" t="s">
+      <c r="N1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="186" t="s">
+      <c r="O1" s="154" t="s">
         <v>12</v>
       </c>
-      <c r="P1" s="31"/>
+      <c r="P1" s="30"/>
     </row>
     <row r="2" customHeight="1" spans="1:16">
       <c r="A2" s="6"/>
@@ -7762,14 +7629,14 @@
       <c r="F2" s="7"/>
       <c r="G2" s="7"/>
       <c r="H2" s="7"/>
-      <c r="I2" s="32"/>
-      <c r="J2" s="33"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="27"/>
-      <c r="M2" s="35"/>
-      <c r="N2" s="36"/>
-      <c r="O2" s="37"/>
-      <c r="P2" s="38"/>
+      <c r="I2" s="31"/>
+      <c r="J2" s="32"/>
+      <c r="K2" s="33"/>
+      <c r="L2" s="26"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="36"/>
+      <c r="P2" s="37"/>
     </row>
     <row r="3" customHeight="1" spans="1:16">
       <c r="A3" s="6"/>
@@ -7780,26 +7647,26 @@
       <c r="F3" s="7"/>
       <c r="G3" s="7"/>
       <c r="H3" s="7"/>
-      <c r="I3" s="24" t="s">
+      <c r="I3" s="23" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="25"/>
-      <c r="K3" s="26" t="s">
+      <c r="J3" s="24"/>
+      <c r="K3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="28" t="s">
+      <c r="M3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="N3" s="27" t="s">
+      <c r="N3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="186" t="s">
+      <c r="O3" s="154" t="s">
         <v>18</v>
       </c>
-      <c r="P3" s="31"/>
+      <c r="P3" s="30"/>
     </row>
     <row r="4" customHeight="1" spans="1:16">
       <c r="A4" s="8"/>
@@ -7810,14 +7677,14 @@
       <c r="F4" s="9"/>
       <c r="G4" s="9"/>
       <c r="H4" s="9"/>
-      <c r="I4" s="32"/>
-      <c r="J4" s="33"/>
-      <c r="K4" s="34"/>
-      <c r="L4" s="27"/>
-      <c r="M4" s="35"/>
-      <c r="N4" s="27"/>
-      <c r="O4" s="37"/>
-      <c r="P4" s="38"/>
+      <c r="I4" s="31"/>
+      <c r="J4" s="32"/>
+      <c r="K4" s="33"/>
+      <c r="L4" s="26"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="26"/>
+      <c r="O4" s="36"/>
+      <c r="P4" s="37"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:16">
       <c r="A5" s="10" t="s">
@@ -7890,7 +7757,7 @@
       <c r="L7" s="18"/>
       <c r="M7" s="18"/>
       <c r="N7" s="18"/>
-      <c r="O7" s="39"/>
+      <c r="O7" s="27"/>
       <c r="P7" s="17"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -7904,10 +7771,10 @@
       <c r="F8" s="18"/>
       <c r="G8" s="20"/>
       <c r="H8" s="18"/>
-      <c r="I8" s="40" t="s">
+      <c r="I8" s="38" t="s">
         <v>143</v>
       </c>
-      <c r="J8" s="41"/>
+      <c r="J8" s="39"/>
       <c r="K8" s="18"/>
       <c r="L8" s="18"/>
       <c r="M8" s="18"/>
@@ -7928,8 +7795,8 @@
       <c r="F9" s="18"/>
       <c r="G9" s="20"/>
       <c r="H9" s="18"/>
-      <c r="I9" s="40"/>
-      <c r="J9" s="41" t="s">
+      <c r="I9" s="38"/>
+      <c r="J9" s="39" t="s">
         <v>146</v>
       </c>
       <c r="K9" s="18"/>
@@ -7953,18 +7820,18 @@
       <c r="G10" s="20"/>
       <c r="H10" s="18"/>
       <c r="I10" s="18"/>
-      <c r="J10" s="42" t="s">
+      <c r="J10" s="40" t="s">
         <v>149</v>
       </c>
-      <c r="K10" s="43" t="s">
+      <c r="K10" s="41" t="s">
         <v>150</v>
       </c>
-      <c r="L10" s="43" t="s">
+      <c r="L10" s="41" t="s">
         <v>53</v>
       </c>
       <c r="M10" s="18"/>
       <c r="N10" s="18"/>
-      <c r="O10" s="44"/>
+      <c r="O10" s="42"/>
       <c r="P10" s="20"/>
     </row>
     <row r="11" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -7979,18 +7846,18 @@
       <c r="G11" s="20"/>
       <c r="H11" s="18"/>
       <c r="I11" s="18"/>
-      <c r="J11" s="45" t="s">
+      <c r="J11" s="43" t="s">
         <v>65</v>
       </c>
-      <c r="K11" s="46" t="s">
+      <c r="K11" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="L11" s="46" t="s">
+      <c r="L11" s="44" t="s">
         <v>64</v>
       </c>
       <c r="M11" s="18"/>
       <c r="N11" s="18"/>
-      <c r="O11" s="44"/>
+      <c r="O11" s="42"/>
       <c r="P11" s="20"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8005,18 +7872,18 @@
       <c r="G12" s="20"/>
       <c r="H12" s="18"/>
       <c r="I12" s="18"/>
-      <c r="J12" s="45" t="s">
+      <c r="J12" s="43" t="s">
         <v>70</v>
       </c>
-      <c r="K12" s="46" t="s">
+      <c r="K12" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="L12" s="46" t="s">
+      <c r="L12" s="44" t="s">
         <v>154</v>
       </c>
       <c r="M12" s="18"/>
       <c r="N12" s="18"/>
-      <c r="O12" s="44"/>
+      <c r="O12" s="42"/>
       <c r="P12" s="20"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8031,18 +7898,18 @@
       <c r="G13" s="20"/>
       <c r="H13" s="18"/>
       <c r="I13" s="18"/>
-      <c r="J13" s="45" t="s">
+      <c r="J13" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="K13" s="46" t="s">
+      <c r="K13" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="L13" s="46" t="s">
+      <c r="L13" s="44" t="s">
         <v>156</v>
       </c>
       <c r="M13" s="18"/>
       <c r="N13" s="18"/>
-      <c r="O13" s="44"/>
+      <c r="O13" s="42"/>
       <c r="P13" s="20"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8057,18 +7924,18 @@
       <c r="G14" s="20"/>
       <c r="H14" s="18"/>
       <c r="I14" s="18"/>
-      <c r="J14" s="45" t="s">
+      <c r="J14" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="K14" s="46" t="s">
+      <c r="K14" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="L14" s="46" t="s">
+      <c r="L14" s="44" t="s">
         <v>78</v>
       </c>
       <c r="M14" s="18"/>
       <c r="N14" s="18"/>
-      <c r="O14" s="44"/>
+      <c r="O14" s="42"/>
       <c r="P14" s="20"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8083,18 +7950,18 @@
       <c r="G15" s="20"/>
       <c r="H15" s="18"/>
       <c r="I15" s="18"/>
-      <c r="J15" s="45" t="s">
+      <c r="J15" s="43" t="s">
         <v>82</v>
       </c>
-      <c r="K15" s="46" t="s">
+      <c r="K15" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="L15" s="46" t="s">
+      <c r="L15" s="44" t="s">
         <v>81</v>
       </c>
       <c r="M15" s="18"/>
       <c r="N15" s="18"/>
-      <c r="O15" s="44"/>
+      <c r="O15" s="42"/>
       <c r="P15" s="20"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8109,18 +7976,18 @@
       <c r="G16" s="20"/>
       <c r="H16" s="18"/>
       <c r="I16" s="18"/>
-      <c r="J16" s="45" t="s">
+      <c r="J16" s="43" t="s">
         <v>86</v>
       </c>
-      <c r="K16" s="46" t="s">
+      <c r="K16" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="L16" s="46" t="s">
+      <c r="L16" s="44" t="s">
         <v>85</v>
       </c>
       <c r="M16" s="18"/>
       <c r="N16" s="18"/>
-      <c r="O16" s="44"/>
+      <c r="O16" s="42"/>
       <c r="P16" s="20"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8135,12 +8002,10 @@
       <c r="G17" s="20"/>
       <c r="H17" s="18"/>
       <c r="I17" s="18"/>
-      <c r="J17" s="2"/>
-      <c r="K17" s="2"/>
       <c r="L17" s="18"/>
       <c r="M17" s="18"/>
       <c r="N17" s="18"/>
-      <c r="O17" s="44"/>
+      <c r="O17" s="42"/>
       <c r="P17" s="20"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8155,18 +8020,18 @@
       <c r="G18" s="20"/>
       <c r="H18" s="18"/>
       <c r="I18" s="18"/>
-      <c r="J18" s="42" t="s">
+      <c r="J18" s="40" t="s">
         <v>85</v>
       </c>
-      <c r="K18" s="43" t="s">
+      <c r="K18" s="41" t="s">
         <v>162</v>
       </c>
-      <c r="L18" s="43" t="s">
+      <c r="L18" s="41" t="s">
         <v>53</v>
       </c>
       <c r="M18" s="18"/>
       <c r="N18" s="18"/>
-      <c r="O18" s="44"/>
+      <c r="O18" s="42"/>
       <c r="P18" s="20"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8181,18 +8046,18 @@
       <c r="G19" s="20"/>
       <c r="H19" s="18"/>
       <c r="I19" s="18"/>
-      <c r="J19" s="45" t="s">
+      <c r="J19" s="43" t="s">
         <v>92</v>
       </c>
-      <c r="K19" s="46" t="s">
+      <c r="K19" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="L19" s="46" t="s">
+      <c r="L19" s="44" t="s">
         <v>164</v>
       </c>
       <c r="M19" s="18"/>
       <c r="N19" s="18"/>
-      <c r="O19" s="44"/>
+      <c r="O19" s="42"/>
       <c r="P19" s="20"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8207,18 +8072,18 @@
       <c r="G20" s="20"/>
       <c r="H20" s="18"/>
       <c r="I20" s="18"/>
-      <c r="J20" s="45" t="s">
+      <c r="J20" s="43" t="s">
         <v>96</v>
       </c>
-      <c r="K20" s="46" t="s">
+      <c r="K20" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="L20" s="46" t="s">
+      <c r="L20" s="44" t="s">
         <v>166</v>
       </c>
       <c r="M20" s="18"/>
       <c r="N20" s="18"/>
-      <c r="O20" s="44"/>
+      <c r="O20" s="42"/>
       <c r="P20" s="20"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8233,18 +8098,18 @@
       <c r="G21" s="20"/>
       <c r="H21" s="18"/>
       <c r="I21" s="18"/>
-      <c r="J21" s="45" t="s">
+      <c r="J21" s="43" t="s">
         <v>99</v>
       </c>
-      <c r="K21" s="46" t="s">
+      <c r="K21" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="L21" s="46" t="s">
+      <c r="L21" s="44" t="s">
         <v>97</v>
       </c>
       <c r="M21" s="18"/>
       <c r="N21" s="18"/>
-      <c r="O21" s="44"/>
+      <c r="O21" s="42"/>
       <c r="P21" s="20"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8259,18 +8124,18 @@
       <c r="G22" s="20"/>
       <c r="H22" s="18"/>
       <c r="I22" s="18"/>
-      <c r="J22" s="45" t="s">
+      <c r="J22" s="43" t="s">
         <v>101</v>
       </c>
-      <c r="K22" s="46" t="s">
+      <c r="K22" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="L22" s="46" t="s">
+      <c r="L22" s="44" t="s">
         <v>100</v>
       </c>
       <c r="M22" s="18"/>
       <c r="N22" s="18"/>
-      <c r="O22" s="44"/>
+      <c r="O22" s="42"/>
       <c r="P22" s="20"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8283,18 +8148,18 @@
       <c r="G23" s="20"/>
       <c r="H23" s="18"/>
       <c r="I23" s="18"/>
-      <c r="J23" s="45" t="s">
+      <c r="J23" s="43" t="s">
         <v>104</v>
       </c>
-      <c r="K23" s="46" t="s">
+      <c r="K23" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="L23" s="46" t="s">
+      <c r="L23" s="44" t="s">
         <v>103</v>
       </c>
       <c r="M23" s="18"/>
       <c r="N23" s="18"/>
-      <c r="O23" s="44"/>
+      <c r="O23" s="42"/>
       <c r="P23" s="20"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8307,18 +8172,18 @@
       <c r="G24" s="20"/>
       <c r="H24" s="18"/>
       <c r="I24" s="18"/>
-      <c r="J24" s="45" t="s">
+      <c r="J24" s="43" t="s">
         <v>106</v>
       </c>
-      <c r="K24" s="46" t="s">
+      <c r="K24" s="44" t="s">
         <v>152</v>
       </c>
-      <c r="L24" s="46" t="s">
+      <c r="L24" s="44" t="s">
         <v>105</v>
       </c>
       <c r="M24" s="18"/>
       <c r="N24" s="18"/>
-      <c r="O24" s="44"/>
+      <c r="O24" s="42"/>
       <c r="P24" s="20"/>
     </row>
     <row r="25" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8336,7 +8201,7 @@
       <c r="L25" s="18"/>
       <c r="M25" s="18"/>
       <c r="N25" s="18"/>
-      <c r="O25" s="44"/>
+      <c r="O25" s="42"/>
       <c r="P25" s="20"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8348,15 +8213,15 @@
       <c r="F26" s="18"/>
       <c r="G26" s="20"/>
       <c r="H26" s="18"/>
-      <c r="I26" s="41" t="s">
+      <c r="I26" s="39" t="s">
         <v>169</v>
       </c>
-      <c r="J26" s="41"/>
+      <c r="J26" s="39"/>
       <c r="K26" s="18"/>
       <c r="L26" s="18"/>
       <c r="M26" s="18"/>
       <c r="N26" s="18"/>
-      <c r="O26" s="44"/>
+      <c r="O26" s="42"/>
       <c r="P26" s="20"/>
     </row>
     <row r="27" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8368,15 +8233,15 @@
       <c r="F27" s="18"/>
       <c r="G27" s="20"/>
       <c r="H27" s="18"/>
-      <c r="I27" s="41"/>
-      <c r="J27" s="41" t="s">
+      <c r="I27" s="39"/>
+      <c r="J27" s="39" t="s">
         <v>170</v>
       </c>
       <c r="K27" s="18"/>
       <c r="L27" s="18"/>
       <c r="M27" s="18"/>
       <c r="N27" s="18"/>
-      <c r="O27" s="44"/>
+      <c r="O27" s="42"/>
       <c r="P27" s="20"/>
     </row>
     <row r="28" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8388,13 +8253,13 @@
       <c r="F28" s="18"/>
       <c r="G28" s="20"/>
       <c r="H28" s="18"/>
-      <c r="I28" s="41"/>
-      <c r="J28" s="41"/>
+      <c r="I28" s="39"/>
+      <c r="J28" s="39"/>
       <c r="K28" s="18"/>
       <c r="L28" s="18"/>
       <c r="M28" s="18"/>
       <c r="N28" s="18"/>
-      <c r="O28" s="44"/>
+      <c r="O28" s="42"/>
       <c r="P28" s="20"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8406,15 +8271,15 @@
       <c r="F29" s="18"/>
       <c r="G29" s="20"/>
       <c r="H29" s="18"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41" t="s">
+      <c r="I29" s="39"/>
+      <c r="J29" s="39" t="s">
         <v>144</v>
       </c>
       <c r="K29" s="18"/>
       <c r="L29" s="18"/>
       <c r="M29" s="18"/>
       <c r="N29" s="18"/>
-      <c r="O29" s="44"/>
+      <c r="O29" s="42"/>
       <c r="P29" s="20"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8426,19 +8291,19 @@
       <c r="F30" s="18"/>
       <c r="G30" s="20"/>
       <c r="H30" s="18"/>
-      <c r="I30" s="41"/>
-      <c r="J30" s="47" t="s">
+      <c r="I30" s="39"/>
+      <c r="J30" s="45" t="s">
         <v>171</v>
       </c>
-      <c r="K30" s="47" t="s">
+      <c r="K30" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="L30" s="48" t="s">
+      <c r="L30" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="M30" s="48"/>
+      <c r="M30" s="45"/>
       <c r="N30" s="18"/>
-      <c r="O30" s="44"/>
+      <c r="O30" s="42"/>
       <c r="P30" s="20"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8450,19 +8315,19 @@
       <c r="F31" s="18"/>
       <c r="G31" s="20"/>
       <c r="H31" s="18"/>
-      <c r="I31" s="41"/>
-      <c r="J31" s="49" t="s">
+      <c r="I31" s="39"/>
+      <c r="J31" s="46" t="s">
         <v>65</v>
       </c>
-      <c r="K31" s="50" t="s">
+      <c r="K31" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="L31" s="51" t="s">
+      <c r="L31" s="48" t="s">
         <v>174</v>
       </c>
-      <c r="M31" s="51"/>
+      <c r="M31" s="48"/>
       <c r="N31" s="18"/>
-      <c r="O31" s="44"/>
+      <c r="O31" s="42"/>
       <c r="P31" s="20"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8474,19 +8339,19 @@
       <c r="F32" s="18"/>
       <c r="G32" s="20"/>
       <c r="H32" s="18"/>
-      <c r="I32" s="41"/>
-      <c r="J32" s="52" t="s">
+      <c r="I32" s="39"/>
+      <c r="J32" s="49" t="s">
         <v>70</v>
       </c>
-      <c r="K32" s="53" t="s">
+      <c r="K32" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="L32" s="51" t="s">
+      <c r="L32" s="48" t="s">
         <v>176</v>
       </c>
-      <c r="M32" s="51"/>
+      <c r="M32" s="48"/>
       <c r="N32" s="18"/>
-      <c r="O32" s="44"/>
+      <c r="O32" s="42"/>
       <c r="P32" s="20"/>
     </row>
     <row r="33" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8498,19 +8363,19 @@
       <c r="F33" s="18"/>
       <c r="G33" s="20"/>
       <c r="H33" s="18"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="54" t="s">
+      <c r="I33" s="39"/>
+      <c r="J33" s="46" t="s">
         <v>75</v>
       </c>
-      <c r="K33" s="53" t="s">
+      <c r="K33" s="48" t="s">
         <v>177</v>
       </c>
-      <c r="L33" s="51" t="s">
+      <c r="L33" s="48" t="s">
         <v>178</v>
       </c>
-      <c r="M33" s="51"/>
+      <c r="M33" s="48"/>
       <c r="N33" s="18"/>
-      <c r="O33" s="44"/>
+      <c r="O33" s="42"/>
       <c r="P33" s="20"/>
     </row>
     <row r="34" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8522,19 +8387,19 @@
       <c r="F34" s="18"/>
       <c r="G34" s="20"/>
       <c r="H34" s="18"/>
-      <c r="I34" s="41"/>
-      <c r="J34" s="54" t="s">
+      <c r="I34" s="39"/>
+      <c r="J34" s="46" t="s">
         <v>79</v>
       </c>
-      <c r="K34" s="55" t="s">
+      <c r="K34" s="48" t="s">
         <v>179</v>
       </c>
-      <c r="L34" s="51" t="s">
+      <c r="L34" s="48" t="s">
         <v>180</v>
       </c>
-      <c r="M34" s="51"/>
+      <c r="M34" s="48"/>
       <c r="N34" s="18"/>
-      <c r="O34" s="44"/>
+      <c r="O34" s="42"/>
       <c r="P34" s="20"/>
     </row>
     <row r="35" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8546,19 +8411,19 @@
       <c r="F35" s="18"/>
       <c r="G35" s="20"/>
       <c r="H35" s="18"/>
-      <c r="I35" s="41"/>
-      <c r="J35" s="54" t="s">
+      <c r="I35" s="39"/>
+      <c r="J35" s="46" t="s">
         <v>82</v>
       </c>
-      <c r="K35" s="55" t="s">
+      <c r="K35" s="48" t="s">
         <v>181</v>
       </c>
-      <c r="L35" s="51" t="s">
+      <c r="L35" s="48" t="s">
         <v>182</v>
       </c>
-      <c r="M35" s="51"/>
+      <c r="M35" s="48"/>
       <c r="N35" s="18"/>
-      <c r="O35" s="44"/>
+      <c r="O35" s="42"/>
       <c r="P35" s="20"/>
     </row>
     <row r="36" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8570,19 +8435,19 @@
       <c r="F36" s="18"/>
       <c r="G36" s="20"/>
       <c r="H36" s="18"/>
-      <c r="I36" s="41"/>
-      <c r="J36" s="56" t="s">
+      <c r="I36" s="39"/>
+      <c r="J36" s="50" t="s">
         <v>86</v>
       </c>
-      <c r="K36" s="57" t="s">
+      <c r="K36" s="51" t="s">
         <v>183</v>
       </c>
-      <c r="L36" s="51" t="s">
+      <c r="L36" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="M36" s="51"/>
+      <c r="M36" s="48"/>
       <c r="N36" s="18"/>
-      <c r="O36" s="44"/>
+      <c r="O36" s="42"/>
       <c r="P36" s="20"/>
     </row>
     <row r="37" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8594,13 +8459,13 @@
       <c r="F37" s="18"/>
       <c r="G37" s="20"/>
       <c r="H37" s="18"/>
-      <c r="I37" s="41"/>
-      <c r="J37" s="58"/>
-      <c r="K37" s="59"/>
-      <c r="L37" s="60"/>
-      <c r="M37" s="61"/>
+      <c r="I37" s="39"/>
+      <c r="J37" s="52"/>
+      <c r="K37" s="53"/>
+      <c r="L37" s="54"/>
+      <c r="M37" s="55"/>
       <c r="N37" s="18"/>
-      <c r="O37" s="44"/>
+      <c r="O37" s="42"/>
       <c r="P37" s="20"/>
     </row>
     <row r="38" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8612,15 +8477,15 @@
       <c r="F38" s="18"/>
       <c r="G38" s="20"/>
       <c r="H38" s="18"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="62" t="s">
+      <c r="I38" s="39"/>
+      <c r="J38" s="56" t="s">
         <v>147</v>
       </c>
-      <c r="K38" s="63"/>
-      <c r="L38" s="60"/>
-      <c r="M38" s="61"/>
+      <c r="K38" s="57"/>
+      <c r="L38" s="54"/>
+      <c r="M38" s="55"/>
       <c r="N38" s="18"/>
-      <c r="O38" s="44"/>
+      <c r="O38" s="42"/>
       <c r="P38" s="20"/>
     </row>
     <row r="39" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8632,19 +8497,19 @@
       <c r="F39" s="18"/>
       <c r="G39" s="20"/>
       <c r="H39" s="18"/>
-      <c r="I39" s="41"/>
-      <c r="J39" s="47" t="s">
+      <c r="I39" s="39"/>
+      <c r="J39" s="45" t="s">
         <v>171</v>
       </c>
-      <c r="K39" s="47" t="s">
+      <c r="K39" s="45" t="s">
         <v>172</v>
       </c>
-      <c r="L39" s="48" t="s">
+      <c r="L39" s="45" t="s">
         <v>122</v>
       </c>
-      <c r="M39" s="48"/>
+      <c r="M39" s="45"/>
       <c r="N39" s="18"/>
-      <c r="O39" s="44"/>
+      <c r="O39" s="42"/>
       <c r="P39" s="20"/>
     </row>
     <row r="40" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8656,19 +8521,19 @@
       <c r="F40" s="18"/>
       <c r="G40" s="20"/>
       <c r="H40" s="18"/>
-      <c r="I40" s="41"/>
-      <c r="J40" s="64" t="s">
+      <c r="I40" s="39"/>
+      <c r="J40" s="58" t="s">
         <v>96</v>
       </c>
-      <c r="K40" s="64" t="s">
+      <c r="K40" s="58" t="s">
         <v>185</v>
       </c>
-      <c r="L40" s="51" t="s">
+      <c r="L40" s="48" t="s">
         <v>186</v>
       </c>
-      <c r="M40" s="51"/>
+      <c r="M40" s="48"/>
       <c r="N40" s="18"/>
-      <c r="O40" s="44"/>
+      <c r="O40" s="42"/>
       <c r="P40" s="20"/>
     </row>
     <row r="41" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8680,19 +8545,19 @@
       <c r="F41" s="18"/>
       <c r="G41" s="20"/>
       <c r="H41" s="18"/>
-      <c r="I41" s="41"/>
-      <c r="J41" s="54" t="s">
+      <c r="I41" s="39"/>
+      <c r="J41" s="46" t="s">
         <v>96</v>
       </c>
-      <c r="K41" s="54" t="s">
+      <c r="K41" s="46" t="s">
         <v>187</v>
       </c>
-      <c r="L41" s="51" t="s">
+      <c r="L41" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="M41" s="51"/>
+      <c r="M41" s="48"/>
       <c r="N41" s="18"/>
-      <c r="O41" s="44"/>
+      <c r="O41" s="42"/>
       <c r="P41" s="20"/>
     </row>
     <row r="42" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8704,19 +8569,19 @@
       <c r="F42" s="18"/>
       <c r="G42" s="20"/>
       <c r="H42" s="18"/>
-      <c r="I42" s="41"/>
-      <c r="J42" s="54" t="s">
+      <c r="I42" s="39"/>
+      <c r="J42" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="K42" s="54" t="s">
+      <c r="K42" s="46" t="s">
         <v>189</v>
       </c>
-      <c r="L42" s="51" t="s">
+      <c r="L42" s="48" t="s">
         <v>190</v>
       </c>
-      <c r="M42" s="51"/>
+      <c r="M42" s="48"/>
       <c r="N42" s="18"/>
-      <c r="O42" s="44"/>
+      <c r="O42" s="42"/>
       <c r="P42" s="20"/>
     </row>
     <row r="43" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8728,19 +8593,19 @@
       <c r="F43" s="18"/>
       <c r="G43" s="20"/>
       <c r="H43" s="18"/>
-      <c r="I43" s="41"/>
-      <c r="J43" s="54" t="s">
+      <c r="I43" s="39"/>
+      <c r="J43" s="46" t="s">
         <v>99</v>
       </c>
-      <c r="K43" s="54" t="s">
+      <c r="K43" s="46" t="s">
         <v>187</v>
       </c>
-      <c r="L43" s="51" t="s">
+      <c r="L43" s="48" t="s">
         <v>191</v>
       </c>
-      <c r="M43" s="51"/>
+      <c r="M43" s="48"/>
       <c r="N43" s="18"/>
-      <c r="O43" s="44"/>
+      <c r="O43" s="42"/>
       <c r="P43" s="20"/>
     </row>
     <row r="44" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8752,19 +8617,19 @@
       <c r="F44" s="18"/>
       <c r="G44" s="20"/>
       <c r="H44" s="18"/>
-      <c r="I44" s="41"/>
-      <c r="J44" s="54" t="s">
+      <c r="I44" s="39"/>
+      <c r="J44" s="46" t="s">
         <v>101</v>
       </c>
-      <c r="K44" s="54" t="s">
+      <c r="K44" s="46" t="s">
         <v>192</v>
       </c>
-      <c r="L44" s="51" t="s">
+      <c r="L44" s="48" t="s">
         <v>193</v>
       </c>
-      <c r="M44" s="51"/>
+      <c r="M44" s="48"/>
       <c r="N44" s="18"/>
-      <c r="O44" s="44"/>
+      <c r="O44" s="42"/>
       <c r="P44" s="20"/>
     </row>
     <row r="45" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8776,19 +8641,19 @@
       <c r="F45" s="18"/>
       <c r="G45" s="20"/>
       <c r="H45" s="18"/>
-      <c r="I45" s="41"/>
-      <c r="J45" s="54" t="s">
+      <c r="I45" s="39"/>
+      <c r="J45" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="K45" s="54" t="s">
+      <c r="K45" s="46" t="s">
         <v>194</v>
       </c>
-      <c r="L45" s="51" t="s">
+      <c r="L45" s="48" t="s">
         <v>195</v>
       </c>
-      <c r="M45" s="51"/>
+      <c r="M45" s="48"/>
       <c r="N45" s="18"/>
-      <c r="O45" s="44"/>
+      <c r="O45" s="42"/>
       <c r="P45" s="20"/>
     </row>
     <row r="46" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8800,19 +8665,19 @@
       <c r="F46" s="18"/>
       <c r="G46" s="20"/>
       <c r="H46" s="18"/>
-      <c r="I46" s="41"/>
-      <c r="J46" s="54" t="s">
+      <c r="I46" s="39"/>
+      <c r="J46" s="46" t="s">
         <v>104</v>
       </c>
-      <c r="K46" s="54" t="s">
+      <c r="K46" s="46" t="s">
         <v>196</v>
       </c>
-      <c r="L46" s="51" t="s">
+      <c r="L46" s="48" t="s">
         <v>197</v>
       </c>
-      <c r="M46" s="51"/>
+      <c r="M46" s="48"/>
       <c r="N46" s="18"/>
-      <c r="O46" s="44"/>
+      <c r="O46" s="42"/>
       <c r="P46" s="20"/>
     </row>
     <row r="47" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8824,13 +8689,13 @@
       <c r="F47" s="18"/>
       <c r="G47" s="20"/>
       <c r="H47" s="18"/>
-      <c r="I47" s="41"/>
-      <c r="J47" s="41"/>
+      <c r="I47" s="39"/>
+      <c r="J47" s="39"/>
       <c r="K47" s="18"/>
       <c r="L47" s="18"/>
       <c r="M47" s="18"/>
       <c r="N47" s="18"/>
-      <c r="O47" s="44"/>
+      <c r="O47" s="42"/>
       <c r="P47" s="20"/>
     </row>
     <row r="48" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8844,15 +8709,15 @@
       <c r="F48" s="18"/>
       <c r="G48" s="20"/>
       <c r="H48" s="18"/>
-      <c r="I48" s="40" t="s">
+      <c r="I48" s="38" t="s">
         <v>198</v>
       </c>
-      <c r="J48" s="41"/>
+      <c r="J48" s="39"/>
       <c r="K48" s="18"/>
       <c r="L48" s="18"/>
       <c r="M48" s="18"/>
       <c r="N48" s="18"/>
-      <c r="O48" s="44"/>
+      <c r="O48" s="42"/>
       <c r="P48" s="20"/>
     </row>
     <row r="49" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -8866,7 +8731,7 @@
       <c r="F49" s="18"/>
       <c r="G49" s="20"/>
       <c r="H49" s="18"/>
-      <c r="I49" s="40"/>
+      <c r="I49" s="38"/>
       <c r="J49" s="2" t="s">
         <v>200</v>
       </c>
@@ -8874,11 +8739,11 @@
       <c r="L49" s="18"/>
       <c r="M49" s="18"/>
       <c r="N49" s="18"/>
-      <c r="O49" s="44"/>
+      <c r="O49" s="42"/>
       <c r="P49" s="20"/>
     </row>
     <row r="50" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A50" s="23"/>
+      <c r="A50" s="19"/>
       <c r="B50" s="18"/>
       <c r="C50" s="18"/>
       <c r="D50" s="18"/>
@@ -8886,19 +8751,19 @@
       <c r="F50" s="18"/>
       <c r="G50" s="20"/>
       <c r="H50" s="18"/>
-      <c r="I50" s="40"/>
-      <c r="J50" s="65" t="s">
+      <c r="I50" s="38"/>
+      <c r="J50" s="38" t="s">
         <v>201</v>
       </c>
       <c r="K50" s="18"/>
       <c r="L50" s="18"/>
       <c r="M50" s="18"/>
       <c r="N50" s="18"/>
-      <c r="O50" s="44"/>
+      <c r="O50" s="42"/>
       <c r="P50" s="20"/>
     </row>
     <row r="51" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A51" s="23"/>
+      <c r="A51" s="19"/>
       <c r="B51" s="18"/>
       <c r="C51" s="18"/>
       <c r="D51" s="18"/>
@@ -8906,17 +8771,17 @@
       <c r="F51" s="18"/>
       <c r="G51" s="20"/>
       <c r="H51" s="18"/>
-      <c r="I51" s="40"/>
-      <c r="J51" s="65"/>
+      <c r="I51" s="38"/>
+      <c r="J51" s="38"/>
       <c r="K51" s="18"/>
       <c r="L51" s="18"/>
       <c r="M51" s="18"/>
       <c r="N51" s="18"/>
-      <c r="O51" s="44"/>
+      <c r="O51" s="42"/>
       <c r="P51" s="20"/>
     </row>
     <row r="52" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A52" s="23"/>
+      <c r="A52" s="19"/>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
       <c r="D52" s="18"/>
@@ -8924,19 +8789,19 @@
       <c r="F52" s="18"/>
       <c r="G52" s="20"/>
       <c r="H52" s="18"/>
-      <c r="I52" s="40"/>
-      <c r="J52" s="66" t="s">
+      <c r="I52" s="38"/>
+      <c r="J52" s="39" t="s">
         <v>202</v>
       </c>
       <c r="K52" s="18"/>
       <c r="L52" s="18"/>
       <c r="M52" s="18"/>
       <c r="N52" s="18"/>
-      <c r="O52" s="44"/>
+      <c r="O52" s="42"/>
       <c r="P52" s="20"/>
     </row>
     <row r="53" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A53" s="23"/>
+      <c r="A53" s="19"/>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
       <c r="D53" s="18"/>
@@ -8944,19 +8809,19 @@
       <c r="F53" s="18"/>
       <c r="G53" s="20"/>
       <c r="H53" s="18"/>
-      <c r="I53" s="40"/>
-      <c r="J53" s="65" t="s">
+      <c r="I53" s="38"/>
+      <c r="J53" s="38" t="s">
         <v>203</v>
       </c>
       <c r="K53" s="18"/>
       <c r="L53" s="18"/>
       <c r="M53" s="18"/>
       <c r="N53" s="18"/>
-      <c r="O53" s="44"/>
+      <c r="O53" s="42"/>
       <c r="P53" s="20"/>
     </row>
     <row r="54" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A54" s="23"/>
+      <c r="A54" s="19"/>
       <c r="B54" s="18"/>
       <c r="C54" s="18"/>
       <c r="D54" s="18"/>
@@ -8964,19 +8829,16 @@
       <c r="F54" s="18"/>
       <c r="G54" s="20"/>
       <c r="H54" s="18"/>
-      <c r="I54" s="40"/>
-      <c r="J54" s="2" t="s">
-        <v>204</v>
-      </c>
+      <c r="I54" s="38"/>
       <c r="K54" s="18"/>
       <c r="L54" s="18"/>
       <c r="M54" s="18"/>
       <c r="N54" s="18"/>
-      <c r="O54" s="44"/>
+      <c r="O54" s="42"/>
       <c r="P54" s="20"/>
     </row>
     <row r="55" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A55" s="23"/>
+      <c r="A55" s="21"/>
       <c r="B55" s="18"/>
       <c r="C55" s="18"/>
       <c r="D55" s="18"/>
@@ -8984,13 +8846,15 @@
       <c r="F55" s="18"/>
       <c r="G55" s="20"/>
       <c r="H55" s="18"/>
-      <c r="I55" s="40"/>
-      <c r="J55" s="2"/>
-      <c r="K55" s="18"/>
-      <c r="L55" s="18"/>
-      <c r="M55" s="18"/>
+      <c r="I55" s="39"/>
+      <c r="J55" s="39" t="s">
+        <v>204</v>
+      </c>
+      <c r="K55" s="59"/>
+      <c r="L55" s="59"/>
+      <c r="M55" s="59"/>
       <c r="N55" s="18"/>
-      <c r="O55" s="44"/>
+      <c r="O55" s="42"/>
       <c r="P55" s="20"/>
     </row>
     <row r="56" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9002,15 +8866,19 @@
       <c r="F56" s="18"/>
       <c r="G56" s="20"/>
       <c r="H56" s="18"/>
-      <c r="I56" s="41"/>
-      <c r="J56" s="41" t="s">
+      <c r="I56" s="39"/>
+      <c r="J56" s="40" t="s">
         <v>205</v>
       </c>
-      <c r="K56" s="67"/>
-      <c r="L56" s="67"/>
-      <c r="M56" s="67"/>
+      <c r="K56" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="L56" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="M56" s="60"/>
       <c r="N56" s="18"/>
-      <c r="O56" s="44"/>
+      <c r="O56" s="42"/>
       <c r="P56" s="20"/>
     </row>
     <row r="57" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9022,19 +8890,19 @@
       <c r="F57" s="18"/>
       <c r="G57" s="20"/>
       <c r="H57" s="18"/>
-      <c r="I57" s="41"/>
-      <c r="J57" s="68" t="s">
+      <c r="I57" s="39"/>
+      <c r="J57" s="61" t="s">
         <v>206</v>
       </c>
-      <c r="K57" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="L57" s="69" t="s">
-        <v>53</v>
-      </c>
-      <c r="M57" s="69"/>
+      <c r="K57" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="L57" s="62" t="s">
+        <v>208</v>
+      </c>
+      <c r="M57" s="62"/>
       <c r="N57" s="18"/>
-      <c r="O57" s="44"/>
+      <c r="O57" s="42"/>
       <c r="P57" s="20"/>
     </row>
     <row r="58" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9046,23 +8914,19 @@
       <c r="F58" s="18"/>
       <c r="G58" s="20"/>
       <c r="H58" s="18"/>
-      <c r="I58" s="41"/>
-      <c r="J58" s="70" t="s">
-        <v>207</v>
-      </c>
-      <c r="K58" s="71" t="s">
-        <v>208</v>
-      </c>
-      <c r="L58" s="72" t="s">
-        <v>209</v>
-      </c>
-      <c r="M58" s="72"/>
+      <c r="I58" s="39"/>
+      <c r="J58" s="39"/>
+      <c r="K58" s="18"/>
+      <c r="L58" s="18"/>
+      <c r="M58" s="18"/>
       <c r="N58" s="18"/>
-      <c r="O58" s="44"/>
+      <c r="O58" s="42"/>
       <c r="P58" s="20"/>
     </row>
     <row r="59" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A59" s="21"/>
+      <c r="A59" s="19" t="s">
+        <v>147</v>
+      </c>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
       <c r="D59" s="18"/>
@@ -9070,19 +8934,19 @@
       <c r="F59" s="18"/>
       <c r="G59" s="20"/>
       <c r="H59" s="18"/>
-      <c r="I59" s="41"/>
-      <c r="J59" s="41"/>
+      <c r="I59" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="J59" s="39"/>
       <c r="K59" s="18"/>
       <c r="L59" s="18"/>
       <c r="M59" s="18"/>
       <c r="N59" s="18"/>
-      <c r="O59" s="44"/>
+      <c r="O59" s="42"/>
       <c r="P59" s="20"/>
     </row>
     <row r="60" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A60" s="19" t="s">
-        <v>147</v>
-      </c>
+      <c r="A60" s="19"/>
       <c r="B60" s="18"/>
       <c r="C60" s="18"/>
       <c r="D60" s="18"/>
@@ -9090,15 +8954,15 @@
       <c r="F60" s="18"/>
       <c r="G60" s="20"/>
       <c r="H60" s="18"/>
-      <c r="I60" s="40" t="s">
-        <v>210</v>
-      </c>
-      <c r="J60" s="41"/>
+      <c r="I60" s="38"/>
+      <c r="J60" s="2" t="s">
+        <v>200</v>
+      </c>
       <c r="K60" s="18"/>
       <c r="L60" s="18"/>
       <c r="M60" s="18"/>
       <c r="N60" s="18"/>
-      <c r="O60" s="44"/>
+      <c r="O60" s="42"/>
       <c r="P60" s="20"/>
     </row>
     <row r="61" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9110,15 +8974,15 @@
       <c r="F61" s="18"/>
       <c r="G61" s="20"/>
       <c r="H61" s="18"/>
-      <c r="I61" s="40"/>
-      <c r="J61" s="2" t="s">
-        <v>200</v>
+      <c r="I61" s="38"/>
+      <c r="J61" s="38" t="s">
+        <v>210</v>
       </c>
       <c r="K61" s="18"/>
       <c r="L61" s="18"/>
       <c r="M61" s="18"/>
       <c r="N61" s="18"/>
-      <c r="O61" s="44"/>
+      <c r="O61" s="42"/>
       <c r="P61" s="20"/>
     </row>
     <row r="62" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9130,15 +8994,13 @@
       <c r="F62" s="18"/>
       <c r="G62" s="20"/>
       <c r="H62" s="18"/>
-      <c r="I62" s="40"/>
-      <c r="J62" s="65" t="s">
-        <v>211</v>
-      </c>
+      <c r="I62" s="38"/>
+      <c r="J62" s="38"/>
       <c r="K62" s="18"/>
       <c r="L62" s="18"/>
       <c r="M62" s="18"/>
       <c r="N62" s="18"/>
-      <c r="O62" s="44"/>
+      <c r="O62" s="42"/>
       <c r="P62" s="20"/>
     </row>
     <row r="63" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9150,13 +9012,15 @@
       <c r="F63" s="18"/>
       <c r="G63" s="20"/>
       <c r="H63" s="18"/>
-      <c r="I63" s="40"/>
-      <c r="J63" s="65"/>
+      <c r="I63" s="38"/>
+      <c r="J63" s="38" t="s">
+        <v>211</v>
+      </c>
       <c r="K63" s="18"/>
       <c r="L63" s="18"/>
       <c r="M63" s="18"/>
       <c r="N63" s="18"/>
-      <c r="O63" s="44"/>
+      <c r="O63" s="42"/>
       <c r="P63" s="20"/>
     </row>
     <row r="64" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9168,15 +9032,15 @@
       <c r="F64" s="18"/>
       <c r="G64" s="20"/>
       <c r="H64" s="18"/>
-      <c r="I64" s="40"/>
-      <c r="J64" s="65" t="s">
+      <c r="I64" s="38"/>
+      <c r="J64" s="38" t="s">
         <v>212</v>
       </c>
       <c r="K64" s="18"/>
       <c r="L64" s="18"/>
       <c r="M64" s="18"/>
       <c r="N64" s="18"/>
-      <c r="O64" s="44"/>
+      <c r="O64" s="42"/>
       <c r="P64" s="20"/>
     </row>
     <row r="65" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9188,15 +9052,13 @@
       <c r="F65" s="18"/>
       <c r="G65" s="20"/>
       <c r="H65" s="18"/>
-      <c r="I65" s="40"/>
-      <c r="J65" s="65" t="s">
-        <v>202</v>
-      </c>
+      <c r="I65" s="38"/>
+      <c r="J65" s="38"/>
       <c r="K65" s="18"/>
       <c r="L65" s="18"/>
       <c r="M65" s="18"/>
       <c r="N65" s="18"/>
-      <c r="O65" s="44"/>
+      <c r="O65" s="42"/>
       <c r="P65" s="20"/>
     </row>
     <row r="66" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9208,15 +9070,15 @@
       <c r="F66" s="18"/>
       <c r="G66" s="20"/>
       <c r="H66" s="18"/>
-      <c r="I66" s="40"/>
-      <c r="J66" s="65" t="s">
-        <v>203</v>
+      <c r="I66" s="38"/>
+      <c r="J66" s="38" t="s">
+        <v>213</v>
       </c>
       <c r="K66" s="18"/>
       <c r="L66" s="18"/>
       <c r="M66" s="18"/>
       <c r="N66" s="18"/>
-      <c r="O66" s="44"/>
+      <c r="O66" s="42"/>
       <c r="P66" s="20"/>
     </row>
     <row r="67" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9228,13 +9090,17 @@
       <c r="F67" s="18"/>
       <c r="G67" s="20"/>
       <c r="H67" s="18"/>
-      <c r="I67" s="40"/>
-      <c r="J67" s="65"/>
-      <c r="K67" s="18"/>
+      <c r="I67" s="38"/>
+      <c r="J67" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="K67" s="63" t="s">
+        <v>215</v>
+      </c>
       <c r="L67" s="18"/>
       <c r="M67" s="18"/>
       <c r="N67" s="18"/>
-      <c r="O67" s="44"/>
+      <c r="O67" s="42"/>
       <c r="P67" s="20"/>
     </row>
     <row r="68" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9246,15 +9112,17 @@
       <c r="F68" s="18"/>
       <c r="G68" s="20"/>
       <c r="H68" s="18"/>
-      <c r="I68" s="40"/>
-      <c r="J68" s="65" t="s">
-        <v>213</v>
-      </c>
-      <c r="K68" s="18"/>
+      <c r="I68" s="38"/>
+      <c r="J68" s="38" t="s">
+        <v>216</v>
+      </c>
+      <c r="K68" s="63" t="s">
+        <v>217</v>
+      </c>
       <c r="L68" s="18"/>
       <c r="M68" s="18"/>
       <c r="N68" s="18"/>
-      <c r="O68" s="44"/>
+      <c r="O68" s="42"/>
       <c r="P68" s="20"/>
     </row>
     <row r="69" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9266,15 +9134,13 @@
       <c r="F69" s="18"/>
       <c r="G69" s="20"/>
       <c r="H69" s="18"/>
-      <c r="I69" s="40"/>
-      <c r="J69" s="65" t="s">
-        <v>214</v>
-      </c>
+      <c r="I69" s="38"/>
+      <c r="J69" s="38"/>
       <c r="K69" s="18"/>
       <c r="L69" s="18"/>
       <c r="M69" s="18"/>
       <c r="N69" s="18"/>
-      <c r="O69" s="44"/>
+      <c r="O69" s="42"/>
       <c r="P69" s="20"/>
     </row>
     <row r="70" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9286,13 +9152,15 @@
       <c r="F70" s="18"/>
       <c r="G70" s="20"/>
       <c r="H70" s="18"/>
-      <c r="I70" s="40"/>
-      <c r="J70" s="65"/>
+      <c r="I70" s="39"/>
+      <c r="J70" s="38" t="s">
+        <v>218</v>
+      </c>
       <c r="K70" s="18"/>
       <c r="L70" s="18"/>
       <c r="M70" s="18"/>
       <c r="N70" s="18"/>
-      <c r="O70" s="44"/>
+      <c r="O70" s="42"/>
       <c r="P70" s="20"/>
     </row>
     <row r="71" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9304,15 +9172,15 @@
       <c r="F71" s="18"/>
       <c r="G71" s="20"/>
       <c r="H71" s="18"/>
-      <c r="I71" s="41"/>
-      <c r="J71" s="65" t="s">
-        <v>215</v>
+      <c r="I71" s="39"/>
+      <c r="J71" s="38" t="s">
+        <v>219</v>
       </c>
       <c r="K71" s="18"/>
       <c r="L71" s="18"/>
       <c r="M71" s="18"/>
       <c r="N71" s="18"/>
-      <c r="O71" s="44"/>
+      <c r="O71" s="42"/>
       <c r="P71" s="20"/>
     </row>
     <row r="72" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9324,15 +9192,19 @@
       <c r="F72" s="18"/>
       <c r="G72" s="20"/>
       <c r="H72" s="18"/>
-      <c r="I72" s="41"/>
-      <c r="J72" s="65" t="s">
-        <v>216</v>
-      </c>
-      <c r="K72" s="18"/>
-      <c r="L72" s="18"/>
-      <c r="M72" s="18"/>
+      <c r="I72" s="39"/>
+      <c r="J72" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="K72" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="L72" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="M72" s="64"/>
       <c r="N72" s="18"/>
-      <c r="O72" s="44"/>
+      <c r="O72" s="42"/>
       <c r="P72" s="20"/>
     </row>
     <row r="73" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9344,19 +9216,19 @@
       <c r="F73" s="18"/>
       <c r="G73" s="20"/>
       <c r="H73" s="18"/>
-      <c r="I73" s="41"/>
-      <c r="J73" s="43" t="s">
-        <v>206</v>
-      </c>
-      <c r="K73" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="L73" s="73" t="s">
-        <v>217</v>
-      </c>
-      <c r="M73" s="74"/>
+      <c r="I73" s="39"/>
+      <c r="J73" s="65" t="s">
+        <v>38</v>
+      </c>
+      <c r="K73" s="66" t="s">
+        <v>221</v>
+      </c>
+      <c r="L73" s="67" t="s">
+        <v>222</v>
+      </c>
+      <c r="M73" s="68"/>
       <c r="N73" s="18"/>
-      <c r="O73" s="44"/>
+      <c r="O73" s="42"/>
       <c r="P73" s="20"/>
     </row>
     <row r="74" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9368,19 +9240,17 @@
       <c r="F74" s="18"/>
       <c r="G74" s="20"/>
       <c r="H74" s="18"/>
-      <c r="I74" s="41"/>
-      <c r="J74" s="75" t="s">
-        <v>38</v>
-      </c>
-      <c r="K74" s="76" t="s">
-        <v>218</v>
-      </c>
-      <c r="L74" s="77" t="s">
-        <v>219</v>
-      </c>
-      <c r="M74" s="78"/>
+      <c r="I74" s="39"/>
+      <c r="J74" s="69"/>
+      <c r="K74" s="66" t="s">
+        <v>223</v>
+      </c>
+      <c r="L74" s="67" t="s">
+        <v>224</v>
+      </c>
+      <c r="M74" s="70"/>
       <c r="N74" s="18"/>
-      <c r="O74" s="44"/>
+      <c r="O74" s="42"/>
       <c r="P74" s="20"/>
     </row>
     <row r="75" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9392,17 +9262,17 @@
       <c r="F75" s="18"/>
       <c r="G75" s="20"/>
       <c r="H75" s="18"/>
-      <c r="I75" s="41"/>
-      <c r="J75" s="79"/>
-      <c r="K75" s="76" t="s">
-        <v>220</v>
-      </c>
-      <c r="L75" s="77" t="s">
-        <v>221</v>
-      </c>
-      <c r="M75" s="80"/>
+      <c r="I75" s="39"/>
+      <c r="J75" s="69"/>
+      <c r="K75" s="66" t="s">
+        <v>225</v>
+      </c>
+      <c r="L75" s="67" t="s">
+        <v>226</v>
+      </c>
+      <c r="M75" s="70"/>
       <c r="N75" s="18"/>
-      <c r="O75" s="44"/>
+      <c r="O75" s="42"/>
       <c r="P75" s="20"/>
     </row>
     <row r="76" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9414,21 +9284,21 @@
       <c r="F76" s="18"/>
       <c r="G76" s="20"/>
       <c r="H76" s="18"/>
-      <c r="I76" s="41"/>
-      <c r="J76" s="79"/>
-      <c r="K76" s="76" t="s">
-        <v>222</v>
-      </c>
-      <c r="L76" s="77" t="s">
-        <v>223</v>
-      </c>
-      <c r="M76" s="80"/>
+      <c r="I76" s="39"/>
+      <c r="J76" s="69"/>
+      <c r="K76" s="66" t="s">
+        <v>227</v>
+      </c>
+      <c r="L76" s="67" t="s">
+        <v>228</v>
+      </c>
+      <c r="M76" s="70"/>
       <c r="N76" s="18"/>
-      <c r="O76" s="44"/>
+      <c r="O76" s="42"/>
       <c r="P76" s="20"/>
     </row>
     <row r="77" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A77" s="23"/>
+      <c r="A77" s="19"/>
       <c r="B77" s="18"/>
       <c r="C77" s="18"/>
       <c r="D77" s="18"/>
@@ -9436,21 +9306,21 @@
       <c r="F77" s="18"/>
       <c r="G77" s="20"/>
       <c r="H77" s="18"/>
-      <c r="I77" s="41"/>
-      <c r="J77" s="79"/>
-      <c r="K77" s="76" t="s">
-        <v>224</v>
-      </c>
-      <c r="L77" s="77" t="s">
-        <v>225</v>
-      </c>
-      <c r="M77" s="80"/>
+      <c r="I77" s="39"/>
+      <c r="J77" s="69"/>
+      <c r="K77" s="66" t="s">
+        <v>229</v>
+      </c>
+      <c r="L77" s="67" t="s">
+        <v>230</v>
+      </c>
+      <c r="M77" s="70"/>
       <c r="N77" s="18"/>
-      <c r="O77" s="44"/>
+      <c r="O77" s="42"/>
       <c r="P77" s="20"/>
     </row>
     <row r="78" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A78" s="23"/>
+      <c r="A78" s="19"/>
       <c r="B78" s="18"/>
       <c r="C78" s="18"/>
       <c r="D78" s="18"/>
@@ -9458,21 +9328,21 @@
       <c r="F78" s="18"/>
       <c r="G78" s="20"/>
       <c r="H78" s="18"/>
-      <c r="I78" s="41"/>
-      <c r="J78" s="79"/>
-      <c r="K78" s="76" t="s">
-        <v>226</v>
-      </c>
-      <c r="L78" s="77" t="s">
-        <v>227</v>
-      </c>
-      <c r="M78" s="80"/>
+      <c r="I78" s="39"/>
+      <c r="J78" s="69"/>
+      <c r="K78" s="66" t="s">
+        <v>231</v>
+      </c>
+      <c r="L78" s="67" t="s">
+        <v>232</v>
+      </c>
+      <c r="M78" s="70"/>
       <c r="N78" s="18"/>
-      <c r="O78" s="44"/>
+      <c r="O78" s="42"/>
       <c r="P78" s="20"/>
     </row>
     <row r="79" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A79" s="23"/>
+      <c r="A79" s="19"/>
       <c r="B79" s="18"/>
       <c r="C79" s="18"/>
       <c r="D79" s="18"/>
@@ -9480,21 +9350,21 @@
       <c r="F79" s="18"/>
       <c r="G79" s="20"/>
       <c r="H79" s="18"/>
-      <c r="I79" s="41"/>
-      <c r="J79" s="79"/>
-      <c r="K79" s="76" t="s">
-        <v>228</v>
-      </c>
-      <c r="L79" s="77" t="s">
-        <v>229</v>
-      </c>
-      <c r="M79" s="80"/>
+      <c r="I79" s="39"/>
+      <c r="J79" s="69"/>
+      <c r="K79" s="66" t="s">
+        <v>233</v>
+      </c>
+      <c r="L79" s="67" t="s">
+        <v>234</v>
+      </c>
+      <c r="M79" s="68"/>
       <c r="N79" s="18"/>
-      <c r="O79" s="44"/>
+      <c r="O79" s="42"/>
       <c r="P79" s="20"/>
     </row>
     <row r="80" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A80" s="23"/>
+      <c r="A80" s="19"/>
       <c r="B80" s="18"/>
       <c r="C80" s="18"/>
       <c r="D80" s="18"/>
@@ -9502,21 +9372,21 @@
       <c r="F80" s="18"/>
       <c r="G80" s="20"/>
       <c r="H80" s="18"/>
-      <c r="I80" s="41"/>
-      <c r="J80" s="79"/>
-      <c r="K80" s="76" t="s">
-        <v>230</v>
-      </c>
-      <c r="L80" s="77" t="s">
-        <v>231</v>
-      </c>
-      <c r="M80" s="78"/>
+      <c r="I80" s="39"/>
+      <c r="J80" s="69"/>
+      <c r="K80" s="66" t="s">
+        <v>235</v>
+      </c>
+      <c r="L80" s="67" t="s">
+        <v>236</v>
+      </c>
+      <c r="M80" s="68"/>
       <c r="N80" s="18"/>
-      <c r="O80" s="44"/>
+      <c r="O80" s="42"/>
       <c r="P80" s="20"/>
     </row>
     <row r="81" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A81" s="23"/>
+      <c r="A81" s="21"/>
       <c r="B81" s="18"/>
       <c r="C81" s="18"/>
       <c r="D81" s="18"/>
@@ -9524,17 +9394,17 @@
       <c r="F81" s="18"/>
       <c r="G81" s="20"/>
       <c r="H81" s="18"/>
-      <c r="I81" s="41"/>
-      <c r="J81" s="79"/>
-      <c r="K81" s="76" t="s">
-        <v>232</v>
-      </c>
-      <c r="L81" s="77" t="s">
-        <v>233</v>
-      </c>
-      <c r="M81" s="78"/>
+      <c r="I81" s="39"/>
+      <c r="J81" s="71"/>
+      <c r="K81" s="66" t="s">
+        <v>237</v>
+      </c>
+      <c r="L81" s="67" t="s">
+        <v>236</v>
+      </c>
+      <c r="M81" s="70"/>
       <c r="N81" s="18"/>
-      <c r="O81" s="44"/>
+      <c r="O81" s="42"/>
       <c r="P81" s="20"/>
     </row>
     <row r="82" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9546,17 +9416,13 @@
       <c r="F82" s="18"/>
       <c r="G82" s="20"/>
       <c r="H82" s="18"/>
-      <c r="I82" s="41"/>
-      <c r="J82" s="81"/>
-      <c r="K82" s="76" t="s">
-        <v>234</v>
-      </c>
-      <c r="L82" s="77" t="s">
-        <v>233</v>
-      </c>
-      <c r="M82" s="80"/>
+      <c r="I82" s="39"/>
+      <c r="J82" s="39"/>
+      <c r="K82" s="18"/>
+      <c r="L82" s="18"/>
+      <c r="M82" s="18"/>
       <c r="N82" s="18"/>
-      <c r="O82" s="44"/>
+      <c r="O82" s="42"/>
       <c r="P82" s="20"/>
     </row>
     <row r="83" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9568,13 +9434,15 @@
       <c r="F83" s="18"/>
       <c r="G83" s="20"/>
       <c r="H83" s="18"/>
-      <c r="I83" s="41"/>
-      <c r="J83" s="41"/>
+      <c r="I83" s="39"/>
+      <c r="J83" s="39" t="s">
+        <v>238</v>
+      </c>
       <c r="K83" s="18"/>
       <c r="L83" s="18"/>
       <c r="M83" s="18"/>
       <c r="N83" s="18"/>
-      <c r="O83" s="44"/>
+      <c r="O83" s="42"/>
       <c r="P83" s="20"/>
     </row>
     <row r="84" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9586,15 +9454,19 @@
       <c r="F84" s="18"/>
       <c r="G84" s="20"/>
       <c r="H84" s="18"/>
-      <c r="I84" s="41"/>
+      <c r="I84" s="39"/>
       <c r="J84" s="41" t="s">
-        <v>235</v>
-      </c>
-      <c r="K84" s="18"/>
-      <c r="L84" s="18"/>
-      <c r="M84" s="18"/>
+        <v>205</v>
+      </c>
+      <c r="K84" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="L84" s="40" t="s">
+        <v>220</v>
+      </c>
+      <c r="M84" s="64"/>
       <c r="N84" s="18"/>
-      <c r="O84" s="44"/>
+      <c r="O84" s="42"/>
       <c r="P84" s="20"/>
     </row>
     <row r="85" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9606,19 +9478,19 @@
       <c r="F85" s="18"/>
       <c r="G85" s="20"/>
       <c r="H85" s="18"/>
-      <c r="I85" s="41"/>
-      <c r="J85" s="43" t="s">
-        <v>206</v>
-      </c>
-      <c r="K85" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="L85" s="73" t="s">
-        <v>217</v>
-      </c>
-      <c r="M85" s="74"/>
+      <c r="I85" s="39"/>
+      <c r="J85" s="66" t="s">
+        <v>38</v>
+      </c>
+      <c r="K85" s="66" t="s">
+        <v>231</v>
+      </c>
+      <c r="L85" s="67" t="s">
+        <v>239</v>
+      </c>
+      <c r="M85" s="70"/>
       <c r="N85" s="18"/>
-      <c r="O85" s="44"/>
+      <c r="O85" s="42"/>
       <c r="P85" s="20"/>
     </row>
     <row r="86" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9630,19 +9502,17 @@
       <c r="F86" s="18"/>
       <c r="G86" s="20"/>
       <c r="H86" s="18"/>
-      <c r="I86" s="41"/>
-      <c r="J86" s="76" t="s">
-        <v>38</v>
-      </c>
-      <c r="K86" s="76" t="s">
-        <v>228</v>
-      </c>
-      <c r="L86" s="77" t="s">
+      <c r="I86" s="39"/>
+      <c r="J86" s="66"/>
+      <c r="K86" s="66" t="s">
+        <v>237</v>
+      </c>
+      <c r="L86" s="67" t="s">
         <v>236</v>
       </c>
-      <c r="M86" s="80"/>
+      <c r="M86" s="70"/>
       <c r="N86" s="18"/>
-      <c r="O86" s="44"/>
+      <c r="O86" s="42"/>
       <c r="P86" s="20"/>
     </row>
     <row r="87" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9654,17 +9524,13 @@
       <c r="F87" s="18"/>
       <c r="G87" s="20"/>
       <c r="H87" s="18"/>
-      <c r="I87" s="41"/>
-      <c r="J87" s="76"/>
-      <c r="K87" s="76" t="s">
-        <v>234</v>
-      </c>
-      <c r="L87" s="77" t="s">
-        <v>233</v>
-      </c>
-      <c r="M87" s="80"/>
+      <c r="I87" s="39"/>
+      <c r="J87" s="63"/>
+      <c r="K87" s="63"/>
+      <c r="L87" s="63"/>
+      <c r="M87" s="63"/>
       <c r="N87" s="18"/>
-      <c r="O87" s="44"/>
+      <c r="O87" s="42"/>
       <c r="P87" s="20"/>
     </row>
     <row r="88" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9676,13 +9542,15 @@
       <c r="F88" s="18"/>
       <c r="G88" s="20"/>
       <c r="H88" s="18"/>
-      <c r="I88" s="41"/>
-      <c r="J88" s="82"/>
-      <c r="K88" s="82"/>
-      <c r="L88" s="82"/>
-      <c r="M88" s="82"/>
+      <c r="I88" s="39"/>
+      <c r="J88" s="63" t="s">
+        <v>240</v>
+      </c>
+      <c r="K88" s="63"/>
+      <c r="L88" s="63"/>
+      <c r="M88" s="63"/>
       <c r="N88" s="18"/>
-      <c r="O88" s="44"/>
+      <c r="O88" s="42"/>
       <c r="P88" s="20"/>
     </row>
     <row r="89" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9694,15 +9562,13 @@
       <c r="F89" s="18"/>
       <c r="G89" s="20"/>
       <c r="H89" s="18"/>
-      <c r="I89" s="41"/>
-      <c r="J89" s="82" t="s">
-        <v>237</v>
-      </c>
-      <c r="K89" s="82"/>
-      <c r="L89" s="82"/>
-      <c r="M89" s="82"/>
+      <c r="I89" s="39"/>
+      <c r="J89" s="63"/>
+      <c r="K89" s="63"/>
+      <c r="L89" s="63"/>
+      <c r="M89" s="63"/>
       <c r="N89" s="18"/>
-      <c r="O89" s="44"/>
+      <c r="O89" s="42"/>
       <c r="P89" s="20"/>
     </row>
     <row r="90" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9714,13 +9580,15 @@
       <c r="F90" s="18"/>
       <c r="G90" s="20"/>
       <c r="H90" s="18"/>
-      <c r="I90" s="41"/>
-      <c r="J90" s="82"/>
-      <c r="K90" s="82"/>
-      <c r="L90" s="82"/>
-      <c r="M90" s="82"/>
+      <c r="I90" s="39"/>
+      <c r="J90" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="K90" s="63"/>
+      <c r="L90" s="63"/>
+      <c r="M90" s="63"/>
       <c r="N90" s="18"/>
-      <c r="O90" s="44"/>
+      <c r="O90" s="42"/>
       <c r="P90" s="20"/>
     </row>
     <row r="91" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9732,15 +9600,15 @@
       <c r="F91" s="18"/>
       <c r="G91" s="20"/>
       <c r="H91" s="18"/>
-      <c r="I91" s="41"/>
+      <c r="I91" s="39"/>
       <c r="J91" s="2" t="s">
-        <v>238</v>
-      </c>
-      <c r="K91" s="82"/>
-      <c r="L91" s="82"/>
-      <c r="M91" s="82"/>
+        <v>242</v>
+      </c>
+      <c r="K91" s="63"/>
+      <c r="L91" s="63"/>
+      <c r="M91" s="63"/>
       <c r="N91" s="18"/>
-      <c r="O91" s="44"/>
+      <c r="O91" s="42"/>
       <c r="P91" s="20"/>
     </row>
     <row r="92" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9752,15 +9620,15 @@
       <c r="F92" s="18"/>
       <c r="G92" s="20"/>
       <c r="H92" s="18"/>
-      <c r="I92" s="41"/>
+      <c r="I92" s="39"/>
       <c r="J92" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K92" s="82"/>
-      <c r="L92" s="82"/>
-      <c r="M92" s="82"/>
+        <v>243</v>
+      </c>
+      <c r="K92" s="63"/>
+      <c r="L92" s="63"/>
+      <c r="M92" s="63"/>
       <c r="N92" s="18"/>
-      <c r="O92" s="44"/>
+      <c r="O92" s="42"/>
       <c r="P92" s="20"/>
     </row>
     <row r="93" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9772,15 +9640,12 @@
       <c r="F93" s="18"/>
       <c r="G93" s="20"/>
       <c r="H93" s="18"/>
-      <c r="I93" s="41"/>
-      <c r="J93" s="2" t="s">
-        <v>240</v>
-      </c>
-      <c r="K93" s="82"/>
-      <c r="L93" s="82"/>
-      <c r="M93" s="82"/>
+      <c r="I93" s="39"/>
+      <c r="K93" s="63"/>
+      <c r="L93" s="63"/>
+      <c r="M93" s="63"/>
       <c r="N93" s="18"/>
-      <c r="O93" s="44"/>
+      <c r="O93" s="42"/>
       <c r="P93" s="20"/>
     </row>
     <row r="94" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9792,13 +9657,15 @@
       <c r="F94" s="18"/>
       <c r="G94" s="20"/>
       <c r="H94" s="18"/>
-      <c r="I94" s="41"/>
-      <c r="J94" s="2"/>
-      <c r="K94" s="82"/>
-      <c r="L94" s="82"/>
-      <c r="M94" s="82"/>
+      <c r="I94" s="39"/>
+      <c r="J94" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="K94" s="63"/>
+      <c r="L94" s="63"/>
+      <c r="M94" s="63"/>
       <c r="N94" s="18"/>
-      <c r="O94" s="44"/>
+      <c r="O94" s="42"/>
       <c r="P94" s="20"/>
     </row>
     <row r="95" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9810,15 +9677,15 @@
       <c r="F95" s="18"/>
       <c r="G95" s="20"/>
       <c r="H95" s="18"/>
-      <c r="I95" s="41"/>
+      <c r="I95" s="39"/>
       <c r="J95" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="K95" s="82"/>
-      <c r="L95" s="82"/>
-      <c r="M95" s="82"/>
+        <v>245</v>
+      </c>
+      <c r="K95" s="18"/>
+      <c r="L95" s="18"/>
+      <c r="M95" s="18"/>
       <c r="N95" s="18"/>
-      <c r="O95" s="44"/>
+      <c r="O95" s="42"/>
       <c r="P95" s="20"/>
     </row>
     <row r="96" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9830,19 +9697,19 @@
       <c r="F96" s="18"/>
       <c r="G96" s="20"/>
       <c r="H96" s="18"/>
-      <c r="I96" s="41"/>
-      <c r="J96" s="2" t="s">
-        <v>242</v>
-      </c>
+      <c r="I96" s="18"/>
+      <c r="J96" s="18"/>
       <c r="K96" s="18"/>
       <c r="L96" s="18"/>
       <c r="M96" s="18"/>
       <c r="N96" s="18"/>
-      <c r="O96" s="44"/>
+      <c r="O96" s="42"/>
       <c r="P96" s="20"/>
     </row>
     <row r="97" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A97" s="21"/>
+      <c r="A97" s="19" t="s">
+        <v>144</v>
+      </c>
       <c r="B97" s="18"/>
       <c r="C97" s="18"/>
       <c r="D97" s="18"/>
@@ -9850,18 +9717,19 @@
       <c r="F97" s="18"/>
       <c r="G97" s="20"/>
       <c r="H97" s="18"/>
-      <c r="I97" s="18"/>
-      <c r="J97" s="18"/>
-      <c r="K97" s="18"/>
+      <c r="I97" s="38" t="s">
+        <v>246</v>
+      </c>
+      <c r="K97" s="39"/>
       <c r="L97" s="18"/>
       <c r="M97" s="18"/>
       <c r="N97" s="18"/>
-      <c r="O97" s="44"/>
+      <c r="O97" s="42"/>
       <c r="P97" s="20"/>
     </row>
     <row r="98" s="2" customFormat="1" ht="16.5" spans="1:16">
       <c r="A98" s="19" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="B98" s="18"/>
       <c r="C98" s="18"/>
@@ -9870,21 +9738,19 @@
       <c r="F98" s="18"/>
       <c r="G98" s="20"/>
       <c r="H98" s="18"/>
-      <c r="I98" s="40" t="s">
-        <v>243</v>
-      </c>
-      <c r="J98" s="2"/>
-      <c r="K98" s="41"/>
+      <c r="I98" s="38"/>
+      <c r="J98" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="K98" s="39"/>
       <c r="L98" s="18"/>
       <c r="M98" s="18"/>
       <c r="N98" s="18"/>
-      <c r="O98" s="44"/>
+      <c r="O98" s="42"/>
       <c r="P98" s="20"/>
     </row>
     <row r="99" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A99" s="19" t="s">
-        <v>147</v>
-      </c>
+      <c r="A99" s="19"/>
       <c r="B99" s="18"/>
       <c r="C99" s="18"/>
       <c r="D99" s="18"/>
@@ -9892,15 +9758,15 @@
       <c r="F99" s="18"/>
       <c r="G99" s="20"/>
       <c r="H99" s="18"/>
-      <c r="I99" s="40"/>
+      <c r="I99" s="38"/>
       <c r="J99" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="K99" s="41"/>
+        <v>247</v>
+      </c>
+      <c r="K99" s="39"/>
       <c r="L99" s="18"/>
       <c r="M99" s="18"/>
       <c r="N99" s="18"/>
-      <c r="O99" s="44"/>
+      <c r="O99" s="42"/>
       <c r="P99" s="20"/>
     </row>
     <row r="100" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9912,19 +9778,15 @@
       <c r="F100" s="18"/>
       <c r="G100" s="20"/>
       <c r="H100" s="18"/>
-      <c r="I100" s="40"/>
-      <c r="J100" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="K100" s="41"/>
+      <c r="I100" s="38"/>
+      <c r="K100" s="39"/>
       <c r="L100" s="18"/>
       <c r="M100" s="18"/>
       <c r="N100" s="18"/>
-      <c r="O100" s="44"/>
+      <c r="O100" s="42"/>
       <c r="P100" s="20"/>
     </row>
-    <row r="101" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A101" s="19"/>
+    <row r="101" s="2" customFormat="1" ht="16.5" spans="2:16">
       <c r="B101" s="18"/>
       <c r="C101" s="18"/>
       <c r="D101" s="18"/>
@@ -9932,16 +9794,19 @@
       <c r="F101" s="18"/>
       <c r="G101" s="20"/>
       <c r="H101" s="18"/>
-      <c r="I101" s="40"/>
-      <c r="J101" s="2"/>
-      <c r="K101" s="41"/>
+      <c r="I101" s="38"/>
+      <c r="J101" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="K101" s="39"/>
       <c r="L101" s="18"/>
       <c r="M101" s="18"/>
       <c r="N101" s="18"/>
-      <c r="O101" s="44"/>
+      <c r="O101" s="42"/>
       <c r="P101" s="20"/>
     </row>
-    <row r="102" s="2" customFormat="1" ht="16.5" spans="2:16">
+    <row r="102" s="2" customFormat="1" ht="16.5" spans="1:16">
+      <c r="A102" s="19"/>
       <c r="B102" s="18"/>
       <c r="C102" s="18"/>
       <c r="D102" s="18"/>
@@ -9949,15 +9814,15 @@
       <c r="F102" s="18"/>
       <c r="G102" s="20"/>
       <c r="H102" s="18"/>
-      <c r="I102" s="40"/>
+      <c r="I102" s="38"/>
       <c r="J102" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="K102" s="41"/>
+        <v>249</v>
+      </c>
+      <c r="K102" s="39"/>
       <c r="L102" s="18"/>
       <c r="M102" s="18"/>
       <c r="N102" s="18"/>
-      <c r="O102" s="44"/>
+      <c r="O102" s="42"/>
       <c r="P102" s="20"/>
     </row>
     <row r="103" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9969,15 +9834,15 @@
       <c r="F103" s="18"/>
       <c r="G103" s="20"/>
       <c r="H103" s="18"/>
-      <c r="I103" s="40"/>
+      <c r="I103" s="38"/>
       <c r="J103" s="2" t="s">
-        <v>246</v>
-      </c>
-      <c r="K103" s="41"/>
+        <v>250</v>
+      </c>
+      <c r="K103" s="39"/>
       <c r="L103" s="18"/>
       <c r="M103" s="18"/>
       <c r="N103" s="18"/>
-      <c r="O103" s="44"/>
+      <c r="O103" s="42"/>
       <c r="P103" s="20"/>
     </row>
     <row r="104" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -9989,17 +9854,15 @@
       <c r="F104" s="18"/>
       <c r="G104" s="20"/>
       <c r="H104" s="18"/>
-      <c r="I104" s="40"/>
-      <c r="J104" s="2"/>
-      <c r="K104" s="41"/>
+      <c r="I104" s="38"/>
+      <c r="K104" s="39"/>
       <c r="L104" s="18"/>
       <c r="M104" s="18"/>
       <c r="N104" s="18"/>
-      <c r="O104" s="44"/>
+      <c r="O104" s="42"/>
       <c r="P104" s="20"/>
     </row>
-    <row r="105" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A105" s="19"/>
+    <row r="105" s="2" customFormat="1" ht="16.5" spans="2:16">
       <c r="B105" s="18"/>
       <c r="C105" s="18"/>
       <c r="D105" s="18"/>
@@ -10007,19 +9870,18 @@
       <c r="F105" s="18"/>
       <c r="G105" s="20"/>
       <c r="H105" s="18"/>
-      <c r="I105" s="40"/>
-      <c r="J105" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="K105" s="41"/>
+      <c r="I105" s="18"/>
+      <c r="J105" s="38" t="s">
+        <v>251</v>
+      </c>
       <c r="L105" s="18"/>
       <c r="M105" s="18"/>
       <c r="N105" s="18"/>
-      <c r="O105" s="44"/>
+      <c r="O105" s="42"/>
       <c r="P105" s="20"/>
     </row>
     <row r="106" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A106" s="19"/>
+      <c r="A106" s="21"/>
       <c r="B106" s="18"/>
       <c r="C106" s="18"/>
       <c r="D106" s="18"/>
@@ -10027,19 +9889,23 @@
       <c r="F106" s="18"/>
       <c r="G106" s="20"/>
       <c r="H106" s="18"/>
-      <c r="I106" s="40"/>
-      <c r="J106" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="K106" s="41"/>
-      <c r="L106" s="18"/>
-      <c r="M106" s="18"/>
+      <c r="I106" s="18"/>
+      <c r="J106" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="K106" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="L106" s="41" t="s">
+        <v>220</v>
+      </c>
+      <c r="M106" s="41"/>
       <c r="N106" s="18"/>
-      <c r="O106" s="44"/>
+      <c r="O106" s="42"/>
       <c r="P106" s="20"/>
     </row>
     <row r="107" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A107" s="19"/>
+      <c r="A107" s="21"/>
       <c r="B107" s="18"/>
       <c r="C107" s="18"/>
       <c r="D107" s="18"/>
@@ -10047,16 +9913,23 @@
       <c r="F107" s="18"/>
       <c r="G107" s="20"/>
       <c r="H107" s="18"/>
-      <c r="I107" s="40"/>
-      <c r="J107" s="2"/>
-      <c r="K107" s="41"/>
-      <c r="L107" s="18"/>
-      <c r="M107" s="18"/>
+      <c r="I107" s="18"/>
+      <c r="J107" s="65" t="s">
+        <v>252</v>
+      </c>
+      <c r="K107" s="66" t="s">
+        <v>253</v>
+      </c>
+      <c r="L107" s="66" t="s">
+        <v>222</v>
+      </c>
+      <c r="M107" s="66"/>
       <c r="N107" s="18"/>
-      <c r="O107" s="44"/>
+      <c r="O107" s="42"/>
       <c r="P107" s="20"/>
     </row>
-    <row r="108" s="2" customFormat="1" ht="16.5" spans="2:16">
+    <row r="108" s="2" customFormat="1" ht="16.5" spans="1:16">
+      <c r="A108" s="21"/>
       <c r="B108" s="18"/>
       <c r="C108" s="18"/>
       <c r="D108" s="18"/>
@@ -10065,14 +9938,16 @@
       <c r="G108" s="20"/>
       <c r="H108" s="18"/>
       <c r="I108" s="18"/>
-      <c r="J108" s="65" t="s">
-        <v>249</v>
-      </c>
-      <c r="K108" s="2"/>
-      <c r="L108" s="18"/>
-      <c r="M108" s="18"/>
+      <c r="J108" s="69"/>
+      <c r="K108" s="66" t="s">
+        <v>221</v>
+      </c>
+      <c r="L108" s="66" t="s">
+        <v>254</v>
+      </c>
+      <c r="M108" s="66"/>
       <c r="N108" s="18"/>
-      <c r="O108" s="44"/>
+      <c r="O108" s="42"/>
       <c r="P108" s="20"/>
     </row>
     <row r="109" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10085,18 +9960,16 @@
       <c r="G109" s="20"/>
       <c r="H109" s="18"/>
       <c r="I109" s="18"/>
-      <c r="J109" s="43" t="s">
-        <v>206</v>
-      </c>
-      <c r="K109" s="43" t="s">
-        <v>60</v>
-      </c>
-      <c r="L109" s="83" t="s">
-        <v>217</v>
-      </c>
-      <c r="M109" s="83"/>
+      <c r="J109" s="69"/>
+      <c r="K109" s="66" t="s">
+        <v>255</v>
+      </c>
+      <c r="L109" s="66" t="s">
+        <v>256</v>
+      </c>
+      <c r="M109" s="66"/>
       <c r="N109" s="18"/>
-      <c r="O109" s="44"/>
+      <c r="O109" s="42"/>
       <c r="P109" s="20"/>
     </row>
     <row r="110" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10109,18 +9982,16 @@
       <c r="G110" s="20"/>
       <c r="H110" s="18"/>
       <c r="I110" s="18"/>
-      <c r="J110" s="75" t="s">
-        <v>250</v>
-      </c>
-      <c r="K110" s="76" t="s">
-        <v>251</v>
-      </c>
-      <c r="L110" s="76" t="s">
-        <v>219</v>
-      </c>
-      <c r="M110" s="76"/>
+      <c r="J110" s="69"/>
+      <c r="K110" s="66" t="s">
+        <v>257</v>
+      </c>
+      <c r="L110" s="66" t="s">
+        <v>258</v>
+      </c>
+      <c r="M110" s="66"/>
       <c r="N110" s="18"/>
-      <c r="O110" s="44"/>
+      <c r="O110" s="42"/>
       <c r="P110" s="20"/>
     </row>
     <row r="111" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10133,16 +10004,16 @@
       <c r="G111" s="20"/>
       <c r="H111" s="18"/>
       <c r="I111" s="18"/>
-      <c r="J111" s="79"/>
-      <c r="K111" s="76" t="s">
-        <v>218</v>
-      </c>
-      <c r="L111" s="76" t="s">
-        <v>252</v>
-      </c>
-      <c r="M111" s="76"/>
+      <c r="J111" s="69"/>
+      <c r="K111" s="66" t="s">
+        <v>259</v>
+      </c>
+      <c r="L111" s="66" t="s">
+        <v>260</v>
+      </c>
+      <c r="M111" s="66"/>
       <c r="N111" s="18"/>
-      <c r="O111" s="44"/>
+      <c r="O111" s="42"/>
       <c r="P111" s="20"/>
     </row>
     <row r="112" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10155,16 +10026,16 @@
       <c r="G112" s="20"/>
       <c r="H112" s="18"/>
       <c r="I112" s="18"/>
-      <c r="J112" s="79"/>
-      <c r="K112" s="76" t="s">
-        <v>253</v>
-      </c>
-      <c r="L112" s="76" t="s">
-        <v>254</v>
-      </c>
-      <c r="M112" s="76"/>
+      <c r="J112" s="69"/>
+      <c r="K112" s="66" t="s">
+        <v>261</v>
+      </c>
+      <c r="L112" s="66" t="s">
+        <v>232</v>
+      </c>
+      <c r="M112" s="66"/>
       <c r="N112" s="18"/>
-      <c r="O112" s="44"/>
+      <c r="O112" s="42"/>
       <c r="P112" s="20"/>
     </row>
     <row r="113" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10177,16 +10048,16 @@
       <c r="G113" s="20"/>
       <c r="H113" s="18"/>
       <c r="I113" s="18"/>
-      <c r="J113" s="79"/>
-      <c r="K113" s="76" t="s">
-        <v>255</v>
-      </c>
-      <c r="L113" s="76" t="s">
-        <v>256</v>
-      </c>
-      <c r="M113" s="76"/>
+      <c r="J113" s="69"/>
+      <c r="K113" s="66" t="s">
+        <v>262</v>
+      </c>
+      <c r="L113" s="66" t="s">
+        <v>263</v>
+      </c>
+      <c r="M113" s="66"/>
       <c r="N113" s="18"/>
-      <c r="O113" s="44"/>
+      <c r="O113" s="42"/>
       <c r="P113" s="20"/>
     </row>
     <row r="114" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10199,16 +10070,16 @@
       <c r="G114" s="20"/>
       <c r="H114" s="18"/>
       <c r="I114" s="18"/>
-      <c r="J114" s="79"/>
-      <c r="K114" s="76" t="s">
-        <v>257</v>
-      </c>
-      <c r="L114" s="76" t="s">
-        <v>258</v>
-      </c>
-      <c r="M114" s="76"/>
+      <c r="J114" s="69"/>
+      <c r="K114" s="66" t="s">
+        <v>264</v>
+      </c>
+      <c r="L114" s="66" t="s">
+        <v>265</v>
+      </c>
+      <c r="M114" s="66"/>
       <c r="N114" s="18"/>
-      <c r="O114" s="44"/>
+      <c r="O114" s="42"/>
       <c r="P114" s="20"/>
     </row>
     <row r="115" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10221,16 +10092,16 @@
       <c r="G115" s="20"/>
       <c r="H115" s="18"/>
       <c r="I115" s="18"/>
-      <c r="J115" s="79"/>
-      <c r="K115" s="76" t="s">
-        <v>259</v>
-      </c>
-      <c r="L115" s="76" t="s">
-        <v>229</v>
-      </c>
-      <c r="M115" s="76"/>
+      <c r="J115" s="69"/>
+      <c r="K115" s="66" t="s">
+        <v>266</v>
+      </c>
+      <c r="L115" s="66" t="s">
+        <v>267</v>
+      </c>
+      <c r="M115" s="66"/>
       <c r="N115" s="18"/>
-      <c r="O115" s="44"/>
+      <c r="O115" s="42"/>
       <c r="P115" s="20"/>
     </row>
     <row r="116" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10243,16 +10114,16 @@
       <c r="G116" s="20"/>
       <c r="H116" s="18"/>
       <c r="I116" s="18"/>
-      <c r="J116" s="79"/>
-      <c r="K116" s="76" t="s">
-        <v>260</v>
-      </c>
-      <c r="L116" s="76" t="s">
-        <v>261</v>
-      </c>
-      <c r="M116" s="76"/>
+      <c r="J116" s="69"/>
+      <c r="K116" s="66" t="s">
+        <v>268</v>
+      </c>
+      <c r="L116" s="66" t="s">
+        <v>269</v>
+      </c>
+      <c r="M116" s="66"/>
       <c r="N116" s="18"/>
-      <c r="O116" s="44"/>
+      <c r="O116" s="42"/>
       <c r="P116" s="20"/>
     </row>
     <row r="117" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10265,16 +10136,16 @@
       <c r="G117" s="20"/>
       <c r="H117" s="18"/>
       <c r="I117" s="18"/>
-      <c r="J117" s="79"/>
-      <c r="K117" s="76" t="s">
-        <v>262</v>
-      </c>
-      <c r="L117" s="76" t="s">
-        <v>263</v>
-      </c>
-      <c r="M117" s="76"/>
+      <c r="J117" s="69"/>
+      <c r="K117" s="66" t="s">
+        <v>233</v>
+      </c>
+      <c r="L117" s="66" t="s">
+        <v>234</v>
+      </c>
+      <c r="M117" s="66"/>
       <c r="N117" s="18"/>
-      <c r="O117" s="44"/>
+      <c r="O117" s="42"/>
       <c r="P117" s="20"/>
     </row>
     <row r="118" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10287,16 +10158,16 @@
       <c r="G118" s="20"/>
       <c r="H118" s="18"/>
       <c r="I118" s="18"/>
-      <c r="J118" s="79"/>
-      <c r="K118" s="76" t="s">
-        <v>264</v>
-      </c>
-      <c r="L118" s="76" t="s">
-        <v>265</v>
-      </c>
-      <c r="M118" s="76"/>
+      <c r="J118" s="69"/>
+      <c r="K118" s="66" t="s">
+        <v>235</v>
+      </c>
+      <c r="L118" s="66" t="s">
+        <v>236</v>
+      </c>
+      <c r="M118" s="66"/>
       <c r="N118" s="18"/>
-      <c r="O118" s="44"/>
+      <c r="O118" s="42"/>
       <c r="P118" s="20"/>
     </row>
     <row r="119" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10309,16 +10180,16 @@
       <c r="G119" s="20"/>
       <c r="H119" s="18"/>
       <c r="I119" s="18"/>
-      <c r="J119" s="79"/>
-      <c r="K119" s="76" t="s">
-        <v>266</v>
-      </c>
-      <c r="L119" s="76" t="s">
-        <v>267</v>
-      </c>
-      <c r="M119" s="76"/>
+      <c r="J119" s="71"/>
+      <c r="K119" s="66" t="s">
+        <v>237</v>
+      </c>
+      <c r="L119" s="66" t="s">
+        <v>236</v>
+      </c>
+      <c r="M119" s="66"/>
       <c r="N119" s="18"/>
-      <c r="O119" s="44"/>
+      <c r="O119" s="42"/>
       <c r="P119" s="20"/>
     </row>
     <row r="120" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10331,16 +10202,12 @@
       <c r="G120" s="20"/>
       <c r="H120" s="18"/>
       <c r="I120" s="18"/>
-      <c r="J120" s="79"/>
-      <c r="K120" s="76" t="s">
-        <v>230</v>
-      </c>
-      <c r="L120" s="76" t="s">
-        <v>231</v>
-      </c>
-      <c r="M120" s="76"/>
+      <c r="J120" s="18"/>
+      <c r="K120" s="18"/>
+      <c r="L120" s="18"/>
+      <c r="M120" s="18"/>
       <c r="N120" s="18"/>
-      <c r="O120" s="44"/>
+      <c r="O120" s="42"/>
       <c r="P120" s="20"/>
     </row>
     <row r="121" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10352,17 +10219,12 @@
       <c r="F121" s="18"/>
       <c r="G121" s="20"/>
       <c r="H121" s="18"/>
-      <c r="I121" s="18"/>
-      <c r="J121" s="79"/>
-      <c r="K121" s="76" t="s">
-        <v>232</v>
-      </c>
-      <c r="L121" s="76" t="s">
-        <v>233</v>
-      </c>
-      <c r="M121" s="76"/>
+      <c r="J121" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="M121" s="18"/>
       <c r="N121" s="18"/>
-      <c r="O121" s="44"/>
+      <c r="O121" s="42"/>
       <c r="P121" s="20"/>
     </row>
     <row r="122" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10374,17 +10236,12 @@
       <c r="F122" s="18"/>
       <c r="G122" s="20"/>
       <c r="H122" s="18"/>
-      <c r="I122" s="18"/>
-      <c r="J122" s="81"/>
-      <c r="K122" s="76" t="s">
-        <v>234</v>
-      </c>
-      <c r="L122" s="76" t="s">
-        <v>233</v>
-      </c>
-      <c r="M122" s="76"/>
+      <c r="J122" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="M122" s="18"/>
       <c r="N122" s="18"/>
-      <c r="O122" s="44"/>
+      <c r="O122" s="42"/>
       <c r="P122" s="20"/>
     </row>
     <row r="123" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10396,13 +10253,12 @@
       <c r="F123" s="18"/>
       <c r="G123" s="20"/>
       <c r="H123" s="18"/>
-      <c r="I123" s="18"/>
-      <c r="J123" s="18"/>
-      <c r="K123" s="18"/>
-      <c r="L123" s="18"/>
+      <c r="J123" s="2" t="s">
+        <v>271</v>
+      </c>
       <c r="M123" s="18"/>
       <c r="N123" s="18"/>
-      <c r="O123" s="44"/>
+      <c r="O123" s="42"/>
       <c r="P123" s="20"/>
     </row>
     <row r="124" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10414,15 +10270,9 @@
       <c r="F124" s="18"/>
       <c r="G124" s="20"/>
       <c r="H124" s="18"/>
-      <c r="I124" s="2"/>
-      <c r="J124" s="2" t="s">
-        <v>268</v>
-      </c>
-      <c r="K124" s="2"/>
-      <c r="L124" s="2"/>
       <c r="M124" s="18"/>
       <c r="N124" s="18"/>
-      <c r="O124" s="44"/>
+      <c r="O124" s="42"/>
       <c r="P124" s="20"/>
     </row>
     <row r="125" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10434,15 +10284,12 @@
       <c r="F125" s="18"/>
       <c r="G125" s="20"/>
       <c r="H125" s="18"/>
-      <c r="I125" s="2"/>
       <c r="J125" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="K125" s="2"/>
-      <c r="L125" s="2"/>
+        <v>244</v>
+      </c>
       <c r="M125" s="18"/>
       <c r="N125" s="18"/>
-      <c r="O125" s="44"/>
+      <c r="O125" s="42"/>
       <c r="P125" s="20"/>
     </row>
     <row r="126" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10454,15 +10301,12 @@
       <c r="F126" s="18"/>
       <c r="G126" s="20"/>
       <c r="H126" s="18"/>
-      <c r="I126" s="2"/>
       <c r="J126" s="2" t="s">
-        <v>269</v>
-      </c>
-      <c r="K126" s="2"/>
-      <c r="L126" s="2"/>
+        <v>272</v>
+      </c>
       <c r="M126" s="18"/>
       <c r="N126" s="18"/>
-      <c r="O126" s="44"/>
+      <c r="O126" s="42"/>
       <c r="P126" s="20"/>
     </row>
     <row r="127" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10474,13 +10318,13 @@
       <c r="F127" s="18"/>
       <c r="G127" s="20"/>
       <c r="H127" s="18"/>
-      <c r="I127" s="2"/>
-      <c r="J127" s="2"/>
-      <c r="K127" s="2"/>
-      <c r="L127" s="2"/>
+      <c r="I127" s="18"/>
+      <c r="J127" s="72"/>
+      <c r="K127" s="18"/>
+      <c r="L127" s="18"/>
       <c r="M127" s="18"/>
       <c r="N127" s="18"/>
-      <c r="O127" s="44"/>
+      <c r="O127" s="42"/>
       <c r="P127" s="20"/>
     </row>
     <row r="128" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10492,15 +10336,17 @@
       <c r="F128" s="18"/>
       <c r="G128" s="20"/>
       <c r="H128" s="18"/>
-      <c r="I128" s="2"/>
-      <c r="J128" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="K128" s="2"/>
-      <c r="L128" s="2"/>
+      <c r="I128" s="63" t="s">
+        <v>273</v>
+      </c>
+      <c r="J128" s="18"/>
+      <c r="K128" s="18"/>
+      <c r="L128" s="18"/>
       <c r="M128" s="18"/>
       <c r="N128" s="18"/>
-      <c r="O128" s="44"/>
+      <c r="O128" s="19" t="s">
+        <v>274</v>
+      </c>
       <c r="P128" s="20"/>
     </row>
     <row r="129" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10512,15 +10358,15 @@
       <c r="F129" s="18"/>
       <c r="G129" s="20"/>
       <c r="H129" s="18"/>
-      <c r="I129" s="2"/>
-      <c r="J129" s="2" t="s">
-        <v>270</v>
-      </c>
-      <c r="K129" s="2"/>
-      <c r="L129" s="2"/>
+      <c r="I129" s="18"/>
+      <c r="J129" s="39" t="s">
+        <v>275</v>
+      </c>
+      <c r="K129" s="18"/>
+      <c r="L129" s="18"/>
       <c r="M129" s="18"/>
       <c r="N129" s="18"/>
-      <c r="O129" s="44"/>
+      <c r="O129" s="42"/>
       <c r="P129" s="20"/>
     </row>
     <row r="130" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10533,12 +10379,16 @@
       <c r="G130" s="20"/>
       <c r="H130" s="18"/>
       <c r="I130" s="18"/>
-      <c r="J130" s="85"/>
-      <c r="K130" s="18"/>
-      <c r="L130" s="18"/>
+      <c r="J130" s="40" t="s">
+        <v>276</v>
+      </c>
+      <c r="K130" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="L130" s="64"/>
       <c r="M130" s="18"/>
       <c r="N130" s="18"/>
-      <c r="O130" s="44"/>
+      <c r="O130" s="42"/>
       <c r="P130" s="20"/>
     </row>
     <row r="131" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10550,17 +10400,17 @@
       <c r="F131" s="18"/>
       <c r="G131" s="20"/>
       <c r="H131" s="18"/>
-      <c r="I131" s="82" t="s">
-        <v>271</v>
-      </c>
-      <c r="J131" s="18"/>
-      <c r="K131" s="18"/>
-      <c r="L131" s="18"/>
+      <c r="I131" s="18"/>
+      <c r="J131" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="K131" s="74" t="s">
+        <v>114</v>
+      </c>
+      <c r="L131" s="75"/>
       <c r="M131" s="18"/>
       <c r="N131" s="18"/>
-      <c r="O131" s="19" t="s">
-        <v>272</v>
-      </c>
+      <c r="O131" s="42"/>
       <c r="P131" s="20"/>
     </row>
     <row r="132" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10573,14 +10423,16 @@
       <c r="G132" s="20"/>
       <c r="H132" s="18"/>
       <c r="I132" s="18"/>
-      <c r="J132" s="66" t="s">
-        <v>273</v>
-      </c>
-      <c r="K132" s="18"/>
-      <c r="L132" s="18"/>
+      <c r="J132" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="K132" s="74" t="s">
+        <v>117</v>
+      </c>
+      <c r="L132" s="75"/>
       <c r="M132" s="18"/>
       <c r="N132" s="18"/>
-      <c r="O132" s="44"/>
+      <c r="O132" s="42"/>
       <c r="P132" s="20"/>
     </row>
     <row r="133" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10593,20 +10445,20 @@
       <c r="G133" s="20"/>
       <c r="H133" s="18"/>
       <c r="I133" s="18"/>
-      <c r="J133" s="42" t="s">
-        <v>274</v>
-      </c>
-      <c r="K133" s="86" t="s">
-        <v>53</v>
-      </c>
-      <c r="L133" s="87"/>
+      <c r="J133" s="62" t="s">
+        <v>277</v>
+      </c>
+      <c r="K133" s="74" t="s">
+        <v>119</v>
+      </c>
+      <c r="L133" s="75"/>
       <c r="M133" s="18"/>
       <c r="N133" s="18"/>
-      <c r="O133" s="44"/>
+      <c r="O133" s="42"/>
       <c r="P133" s="20"/>
     </row>
-    <row r="134" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A134" s="21"/>
+    <row r="134" s="2" customFormat="1" ht="19.5" spans="1:16">
+      <c r="A134" s="73"/>
       <c r="B134" s="18"/>
       <c r="C134" s="18"/>
       <c r="D134" s="18"/>
@@ -10615,79 +10467,13 @@
       <c r="G134" s="20"/>
       <c r="H134" s="18"/>
       <c r="I134" s="18"/>
-      <c r="J134" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="K134" s="88" t="s">
-        <v>114</v>
-      </c>
-      <c r="L134" s="89"/>
+      <c r="J134" s="39"/>
+      <c r="K134" s="18"/>
+      <c r="L134" s="18"/>
       <c r="M134" s="18"/>
       <c r="N134" s="18"/>
-      <c r="O134" s="44"/>
+      <c r="O134" s="42"/>
       <c r="P134" s="20"/>
-    </row>
-    <row r="135" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A135" s="21"/>
-      <c r="B135" s="18"/>
-      <c r="C135" s="18"/>
-      <c r="D135" s="18"/>
-      <c r="E135" s="18"/>
-      <c r="F135" s="18"/>
-      <c r="G135" s="20"/>
-      <c r="H135" s="18"/>
-      <c r="I135" s="18"/>
-      <c r="J135" s="45" t="s">
-        <v>115</v>
-      </c>
-      <c r="K135" s="88" t="s">
-        <v>117</v>
-      </c>
-      <c r="L135" s="89"/>
-      <c r="M135" s="18"/>
-      <c r="N135" s="18"/>
-      <c r="O135" s="44"/>
-      <c r="P135" s="20"/>
-    </row>
-    <row r="136" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A136" s="21"/>
-      <c r="B136" s="18"/>
-      <c r="C136" s="18"/>
-      <c r="D136" s="18"/>
-      <c r="E136" s="18"/>
-      <c r="F136" s="18"/>
-      <c r="G136" s="20"/>
-      <c r="H136" s="18"/>
-      <c r="I136" s="18"/>
-      <c r="J136" s="90" t="s">
-        <v>275</v>
-      </c>
-      <c r="K136" s="88" t="s">
-        <v>119</v>
-      </c>
-      <c r="L136" s="89"/>
-      <c r="M136" s="18"/>
-      <c r="N136" s="18"/>
-      <c r="O136" s="44"/>
-      <c r="P136" s="20"/>
-    </row>
-    <row r="137" s="2" customFormat="1" ht="19.5" spans="1:16">
-      <c r="A137" s="84"/>
-      <c r="B137" s="18"/>
-      <c r="C137" s="18"/>
-      <c r="D137" s="18"/>
-      <c r="E137" s="18"/>
-      <c r="F137" s="18"/>
-      <c r="G137" s="20"/>
-      <c r="H137" s="18"/>
-      <c r="I137" s="18"/>
-      <c r="J137" s="41"/>
-      <c r="K137" s="18"/>
-      <c r="L137" s="18"/>
-      <c r="M137" s="18"/>
-      <c r="N137" s="18"/>
-      <c r="O137" s="44"/>
-      <c r="P137" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="71">
@@ -10713,8 +10499,9 @@
     <mergeCell ref="L44:M44"/>
     <mergeCell ref="L45:M45"/>
     <mergeCell ref="L46:M46"/>
+    <mergeCell ref="L56:M56"/>
     <mergeCell ref="L57:M57"/>
-    <mergeCell ref="L58:M58"/>
+    <mergeCell ref="L72:M72"/>
     <mergeCell ref="L73:M73"/>
     <mergeCell ref="L74:M74"/>
     <mergeCell ref="L75:M75"/>
@@ -10724,10 +10511,12 @@
     <mergeCell ref="L79:M79"/>
     <mergeCell ref="L80:M80"/>
     <mergeCell ref="L81:M81"/>
-    <mergeCell ref="L82:M82"/>
+    <mergeCell ref="L84:M84"/>
     <mergeCell ref="L85:M85"/>
     <mergeCell ref="L86:M86"/>
-    <mergeCell ref="L87:M87"/>
+    <mergeCell ref="L106:M106"/>
+    <mergeCell ref="L107:M107"/>
+    <mergeCell ref="L108:M108"/>
     <mergeCell ref="L109:M109"/>
     <mergeCell ref="L110:M110"/>
     <mergeCell ref="L111:M111"/>
@@ -10739,16 +10528,13 @@
     <mergeCell ref="L117:M117"/>
     <mergeCell ref="L118:M118"/>
     <mergeCell ref="L119:M119"/>
-    <mergeCell ref="L120:M120"/>
-    <mergeCell ref="L121:M121"/>
-    <mergeCell ref="L122:M122"/>
+    <mergeCell ref="K130:L130"/>
+    <mergeCell ref="K131:L131"/>
+    <mergeCell ref="K132:L132"/>
     <mergeCell ref="K133:L133"/>
-    <mergeCell ref="K134:L134"/>
-    <mergeCell ref="K135:L135"/>
-    <mergeCell ref="K136:L136"/>
-    <mergeCell ref="J74:J82"/>
-    <mergeCell ref="J86:J87"/>
-    <mergeCell ref="J110:J122"/>
+    <mergeCell ref="J73:J81"/>
+    <mergeCell ref="J85:J86"/>
+    <mergeCell ref="J107:J119"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L1:L2"/>

--- a/docs/設計/部品在庫管理/機能仕様書_部品入荷API.xlsx
+++ b/docs/設計/部品在庫管理/機能仕様書_部品入荷API.xlsx
@@ -19,14 +19,14 @@
     <definedName name="_xlnm.Print_Area" localSheetId="3">レスポンス!$A$1:$V$27</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">機能概要!$A$1:$AH$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">シーケンス!$A$1:$V$39</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">処理詳細!$A$1:$P$134</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">処理詳細!$A$1:$P$127</definedName>
   </definedNames>
   <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="542" uniqueCount="278">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="276">
   <si>
     <t>改訂履歴</t>
   </si>
@@ -543,6 +543,9 @@
     <t>@Valid を付与し、ReceiveRequestDTO、ReceiveItemDTO のDTOアノテーションを検証</t>
   </si>
   <si>
+    <t>＜ReceiveRequestDTO＞</t>
+  </si>
+  <si>
     <t>対象項目名</t>
   </si>
   <si>
@@ -585,6 +588,9 @@
     <t>入荷部品リストは必須です</t>
   </si>
   <si>
+    <t>＜ReceiveItemDTO＞</t>
+  </si>
+  <si>
     <t>center_id = NULL</t>
   </si>
   <si>
@@ -630,16 +636,10 @@
     <t>　在庫ID</t>
   </si>
   <si>
-    <t>＜メソッド＞</t>
-  </si>
-  <si>
-    <t>PartsStockReceiveService.findExistingStockAmount()</t>
-  </si>
-  <si>
     <t>＜取得条件＞</t>
   </si>
   <si>
-    <t>入荷部品リスト.stock_id　＝　部品在庫テーブル.stock_id</t>
+    <t>入荷部品リスト.stock_id　＝　部品在庫テーブル.stock_id（部品在庫テーブルから、入荷部品リストの在庫IDと一致するレコードの数量を取得）</t>
   </si>
   <si>
     <t>＜取得項目＞</t>
@@ -660,13 +660,10 @@
     <t>4. 部品在庫　登録・更新</t>
   </si>
   <si>
-    <t>PartsStockReceiveService.saveOrUpdatePartsStock()</t>
-  </si>
-  <si>
     <t>4.1 UPSERT処理実行</t>
   </si>
   <si>
-    <t>部品在庫テーブルに対して、在庫IDをキーとした挿入・更新処理を実行する。</t>
+    <t>部品在庫テーブルに対して、在庫IDをキーとした挿入・更新処理を実行</t>
   </si>
   <si>
     <t>＜実行内容＞</t>
@@ -747,7 +744,7 @@
     <t>＜更新＞（stock_id = 既存ID）</t>
   </si>
   <si>
-    <t>3.で取得した既存数量　＋　入荷部品リスト.入荷数量</t>
+    <t>取得した既存数量　＋　入荷部品リスト.入荷数量</t>
   </si>
   <si>
     <t>4.3 LAST_INSERT_ID関数により実際の stock_id（新規または既存）を取得（新規挿入の場合は自動採番されたID、更新の場合は既存のIDを取得）</t>
@@ -771,9 +768,6 @@
     <t>5. 部品在庫履歴　登録</t>
   </si>
   <si>
-    <t>PartsStockReceiveService.insertPartsStockHistory()</t>
-  </si>
-  <si>
     <t>5.1 「入荷日時」を文字列形式（yyyy-MM-dd）を日時オブジェクト（yyyy-MM-dd 00:00:00）に変換</t>
   </si>
   <si>
@@ -792,7 +786,7 @@
     <t>履歴ID（history_id）</t>
   </si>
   <si>
-    <t>4.3で取得したstock_id</t>
+    <t>取得した実際の stock_id</t>
   </si>
   <si>
     <t>取引種別（transaction_type）</t>
@@ -804,13 +798,13 @@
     <t>処理日時（transaction_date）</t>
   </si>
   <si>
-    <t>5.1で変換した日時</t>
+    <t>変換した日時（yyyy-MM-dd 00:00:00）</t>
   </si>
   <si>
     <t>処理前数量（amount_before）</t>
   </si>
   <si>
-    <t>3.1で取得した更新前数量</t>
+    <t>取得した既存数量</t>
   </si>
   <si>
     <t>変動数量（amount_change）</t>
@@ -869,10 +863,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
-    <numFmt numFmtId="176" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="177" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="_-&quot;\&quot;* #,##0_-\ ;\-&quot;\&quot;* #,##0_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
+    <numFmt numFmtId="177" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="178" formatCode="_-&quot;\&quot;* #,##0.00_-\ ;\-&quot;\&quot;* #,##0.00_-\ ;_-&quot;\&quot;* &quot;-&quot;??_-\ ;_-@_-"/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -920,56 +914,12 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="0"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -983,25 +933,30 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color theme="1"/>
+      <color rgb="FF006100"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
-      <sz val="15"/>
+      <sz val="11"/>
       <color theme="3"/>
       <name val="游ゴシック"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF3F3F76"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1015,40 +970,9 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <u/>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="游ゴシック"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="游ゴシック"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1065,6 +989,76 @@
       <color rgb="FF9C6500"/>
       <name val="游ゴシック"/>
       <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="游ゴシック"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="游ゴシック"/>
+      <charset val="134"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -1095,7 +1089,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1107,19 +1137,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFEB9C"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1131,19 +1167,49 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1155,13 +1221,25 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1173,91 +1251,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1440,30 +1434,6 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
@@ -1481,20 +1451,24 @@
     <border>
       <left/>
       <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1531,9 +1505,29 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+        <color theme="4"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1542,155 +1536,155 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="177" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="178" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="176" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="11" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="17" borderId="20" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="22" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="22" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="16" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="6" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="17" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="16" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="19" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="21" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="8" borderId="18" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="20" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="17" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="154">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1880,9 +1874,18 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="9" xfId="49" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1906,12 +1909,6 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="49" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -3368,7 +3365,7 @@
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="16.5" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="3.66666666666667" style="38"/>
-    <col min="2" max="2" width="5.11111111111111" style="147" customWidth="1"/>
+    <col min="2" max="2" width="5.11111111111111" style="148" customWidth="1"/>
     <col min="3" max="3" width="12.3333333333333" style="38" customWidth="1"/>
     <col min="4" max="4" width="10.3333333333333" style="38" customWidth="1"/>
     <col min="5" max="5" width="66.1111111111111" style="38" customWidth="1"/>
@@ -3381,428 +3378,428 @@
       </c>
     </row>
     <row r="2" spans="2:5">
-      <c r="B2" s="148" t="s">
+      <c r="B2" s="149" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="149" t="s">
+      <c r="C2" s="150" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="149" t="s">
+      <c r="D2" s="150" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="149" t="s">
+      <c r="E2" s="150" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="2:5">
-      <c r="B3" s="150" t="s">
+      <c r="B3" s="151" t="s">
         <v>5</v>
       </c>
-      <c r="C3" s="151">
+      <c r="C3" s="152">
         <v>45636</v>
       </c>
-      <c r="D3" s="152" t="s">
+      <c r="D3" s="153" t="s">
         <v>6</v>
       </c>
-      <c r="E3" s="152" t="s">
+      <c r="E3" s="153" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" spans="2:5">
-      <c r="B4" s="150"/>
-      <c r="C4" s="151"/>
-      <c r="D4" s="152"/>
-      <c r="E4" s="153"/>
+      <c r="B4" s="151"/>
+      <c r="C4" s="152"/>
+      <c r="D4" s="153"/>
+      <c r="E4" s="154"/>
     </row>
     <row r="5" spans="2:5">
-      <c r="B5" s="150"/>
-      <c r="C5" s="151"/>
-      <c r="D5" s="152"/>
-      <c r="E5" s="153"/>
+      <c r="B5" s="151"/>
+      <c r="C5" s="152"/>
+      <c r="D5" s="153"/>
+      <c r="E5" s="154"/>
     </row>
     <row r="6" spans="2:5">
-      <c r="B6" s="150"/>
-      <c r="C6" s="152"/>
-      <c r="D6" s="152"/>
-      <c r="E6" s="152"/>
+      <c r="B6" s="151"/>
+      <c r="C6" s="153"/>
+      <c r="D6" s="153"/>
+      <c r="E6" s="153"/>
     </row>
     <row r="7" spans="2:5">
-      <c r="B7" s="150"/>
-      <c r="C7" s="152"/>
-      <c r="D7" s="152"/>
-      <c r="E7" s="152"/>
+      <c r="B7" s="151"/>
+      <c r="C7" s="153"/>
+      <c r="D7" s="153"/>
+      <c r="E7" s="153"/>
     </row>
     <row r="8" spans="2:5">
-      <c r="B8" s="150"/>
-      <c r="C8" s="152"/>
-      <c r="D8" s="152"/>
-      <c r="E8" s="152"/>
+      <c r="B8" s="151"/>
+      <c r="C8" s="153"/>
+      <c r="D8" s="153"/>
+      <c r="E8" s="153"/>
     </row>
     <row r="9" spans="2:5">
-      <c r="B9" s="150"/>
-      <c r="C9" s="152"/>
-      <c r="D9" s="152"/>
-      <c r="E9" s="152"/>
+      <c r="B9" s="151"/>
+      <c r="C9" s="153"/>
+      <c r="D9" s="153"/>
+      <c r="E9" s="153"/>
     </row>
     <row r="10" spans="2:5">
-      <c r="B10" s="150"/>
-      <c r="C10" s="152"/>
-      <c r="D10" s="152"/>
-      <c r="E10" s="152"/>
+      <c r="B10" s="151"/>
+      <c r="C10" s="153"/>
+      <c r="D10" s="153"/>
+      <c r="E10" s="153"/>
     </row>
     <row r="11" spans="2:5">
-      <c r="B11" s="150"/>
-      <c r="C11" s="152"/>
-      <c r="D11" s="152"/>
-      <c r="E11" s="152"/>
+      <c r="B11" s="151"/>
+      <c r="C11" s="153"/>
+      <c r="D11" s="153"/>
+      <c r="E11" s="153"/>
     </row>
     <row r="12" spans="2:5">
-      <c r="B12" s="150"/>
-      <c r="C12" s="152"/>
-      <c r="D12" s="152"/>
-      <c r="E12" s="152"/>
+      <c r="B12" s="151"/>
+      <c r="C12" s="153"/>
+      <c r="D12" s="153"/>
+      <c r="E12" s="153"/>
     </row>
     <row r="13" spans="2:5">
-      <c r="B13" s="150"/>
-      <c r="C13" s="152"/>
-      <c r="D13" s="152"/>
-      <c r="E13" s="152"/>
+      <c r="B13" s="151"/>
+      <c r="C13" s="153"/>
+      <c r="D13" s="153"/>
+      <c r="E13" s="153"/>
     </row>
     <row r="14" spans="2:5">
-      <c r="B14" s="150"/>
-      <c r="C14" s="152"/>
-      <c r="D14" s="152"/>
-      <c r="E14" s="152"/>
+      <c r="B14" s="151"/>
+      <c r="C14" s="153"/>
+      <c r="D14" s="153"/>
+      <c r="E14" s="153"/>
     </row>
     <row r="15" spans="2:5">
-      <c r="B15" s="150"/>
-      <c r="C15" s="152"/>
-      <c r="D15" s="152"/>
-      <c r="E15" s="152"/>
+      <c r="B15" s="151"/>
+      <c r="C15" s="153"/>
+      <c r="D15" s="153"/>
+      <c r="E15" s="153"/>
     </row>
     <row r="16" spans="2:5">
-      <c r="B16" s="150"/>
-      <c r="C16" s="152"/>
-      <c r="D16" s="152"/>
-      <c r="E16" s="152"/>
+      <c r="B16" s="151"/>
+      <c r="C16" s="153"/>
+      <c r="D16" s="153"/>
+      <c r="E16" s="153"/>
     </row>
     <row r="17" spans="2:5">
-      <c r="B17" s="150"/>
-      <c r="C17" s="152"/>
-      <c r="D17" s="152"/>
-      <c r="E17" s="152"/>
+      <c r="B17" s="151"/>
+      <c r="C17" s="153"/>
+      <c r="D17" s="153"/>
+      <c r="E17" s="153"/>
     </row>
     <row r="18" spans="2:5">
-      <c r="B18" s="150"/>
-      <c r="C18" s="152"/>
-      <c r="D18" s="152"/>
-      <c r="E18" s="152"/>
+      <c r="B18" s="151"/>
+      <c r="C18" s="153"/>
+      <c r="D18" s="153"/>
+      <c r="E18" s="153"/>
     </row>
     <row r="19" spans="2:5">
-      <c r="B19" s="150"/>
-      <c r="C19" s="152"/>
-      <c r="D19" s="152"/>
-      <c r="E19" s="152"/>
+      <c r="B19" s="151"/>
+      <c r="C19" s="153"/>
+      <c r="D19" s="153"/>
+      <c r="E19" s="153"/>
     </row>
     <row r="20" spans="2:5">
-      <c r="B20" s="150"/>
-      <c r="C20" s="152"/>
-      <c r="D20" s="152"/>
-      <c r="E20" s="152"/>
+      <c r="B20" s="151"/>
+      <c r="C20" s="153"/>
+      <c r="D20" s="153"/>
+      <c r="E20" s="153"/>
     </row>
     <row r="21" spans="2:5">
-      <c r="B21" s="150"/>
-      <c r="C21" s="152"/>
-      <c r="D21" s="152"/>
-      <c r="E21" s="152"/>
+      <c r="B21" s="151"/>
+      <c r="C21" s="153"/>
+      <c r="D21" s="153"/>
+      <c r="E21" s="153"/>
     </row>
     <row r="22" spans="2:5">
-      <c r="B22" s="150"/>
-      <c r="C22" s="152"/>
-      <c r="D22" s="152"/>
-      <c r="E22" s="152"/>
+      <c r="B22" s="151"/>
+      <c r="C22" s="153"/>
+      <c r="D22" s="153"/>
+      <c r="E22" s="153"/>
     </row>
     <row r="23" spans="2:5">
-      <c r="B23" s="150"/>
-      <c r="C23" s="152"/>
-      <c r="D23" s="152"/>
-      <c r="E23" s="152"/>
+      <c r="B23" s="151"/>
+      <c r="C23" s="153"/>
+      <c r="D23" s="153"/>
+      <c r="E23" s="153"/>
     </row>
     <row r="24" spans="2:5">
-      <c r="B24" s="150"/>
-      <c r="C24" s="152"/>
-      <c r="D24" s="152"/>
-      <c r="E24" s="152"/>
+      <c r="B24" s="151"/>
+      <c r="C24" s="153"/>
+      <c r="D24" s="153"/>
+      <c r="E24" s="153"/>
     </row>
     <row r="25" spans="2:5">
-      <c r="B25" s="150"/>
-      <c r="C25" s="152"/>
-      <c r="D25" s="152"/>
-      <c r="E25" s="152"/>
+      <c r="B25" s="151"/>
+      <c r="C25" s="153"/>
+      <c r="D25" s="153"/>
+      <c r="E25" s="153"/>
     </row>
     <row r="26" spans="2:5">
-      <c r="B26" s="150"/>
-      <c r="C26" s="152"/>
-      <c r="D26" s="152"/>
-      <c r="E26" s="152"/>
+      <c r="B26" s="151"/>
+      <c r="C26" s="153"/>
+      <c r="D26" s="153"/>
+      <c r="E26" s="153"/>
     </row>
     <row r="27" spans="2:5">
-      <c r="B27" s="150"/>
-      <c r="C27" s="152"/>
-      <c r="D27" s="152"/>
-      <c r="E27" s="152"/>
+      <c r="B27" s="151"/>
+      <c r="C27" s="153"/>
+      <c r="D27" s="153"/>
+      <c r="E27" s="153"/>
     </row>
     <row r="28" spans="2:5">
-      <c r="B28" s="150"/>
-      <c r="C28" s="152"/>
-      <c r="D28" s="152"/>
-      <c r="E28" s="152"/>
+      <c r="B28" s="151"/>
+      <c r="C28" s="153"/>
+      <c r="D28" s="153"/>
+      <c r="E28" s="153"/>
     </row>
     <row r="29" spans="2:5">
-      <c r="B29" s="150"/>
-      <c r="C29" s="152"/>
-      <c r="D29" s="152"/>
-      <c r="E29" s="152"/>
+      <c r="B29" s="151"/>
+      <c r="C29" s="153"/>
+      <c r="D29" s="153"/>
+      <c r="E29" s="153"/>
     </row>
     <row r="30" spans="2:5">
-      <c r="B30" s="150"/>
-      <c r="C30" s="152"/>
-      <c r="D30" s="152"/>
-      <c r="E30" s="152"/>
+      <c r="B30" s="151"/>
+      <c r="C30" s="153"/>
+      <c r="D30" s="153"/>
+      <c r="E30" s="153"/>
     </row>
     <row r="31" spans="2:5">
-      <c r="B31" s="150"/>
-      <c r="C31" s="152"/>
-      <c r="D31" s="152"/>
-      <c r="E31" s="152"/>
+      <c r="B31" s="151"/>
+      <c r="C31" s="153"/>
+      <c r="D31" s="153"/>
+      <c r="E31" s="153"/>
     </row>
     <row r="32" spans="2:5">
-      <c r="B32" s="150"/>
-      <c r="C32" s="152"/>
-      <c r="D32" s="152"/>
-      <c r="E32" s="152"/>
+      <c r="B32" s="151"/>
+      <c r="C32" s="153"/>
+      <c r="D32" s="153"/>
+      <c r="E32" s="153"/>
     </row>
     <row r="33" spans="2:5">
-      <c r="B33" s="150"/>
-      <c r="C33" s="152"/>
-      <c r="D33" s="152"/>
-      <c r="E33" s="152"/>
+      <c r="B33" s="151"/>
+      <c r="C33" s="153"/>
+      <c r="D33" s="153"/>
+      <c r="E33" s="153"/>
     </row>
     <row r="34" spans="2:5">
-      <c r="B34" s="150"/>
-      <c r="C34" s="152"/>
-      <c r="D34" s="152"/>
-      <c r="E34" s="152"/>
+      <c r="B34" s="151"/>
+      <c r="C34" s="153"/>
+      <c r="D34" s="153"/>
+      <c r="E34" s="153"/>
     </row>
     <row r="35" spans="2:5">
-      <c r="B35" s="150"/>
-      <c r="C35" s="152"/>
-      <c r="D35" s="152"/>
-      <c r="E35" s="152"/>
+      <c r="B35" s="151"/>
+      <c r="C35" s="153"/>
+      <c r="D35" s="153"/>
+      <c r="E35" s="153"/>
     </row>
     <row r="36" spans="2:5">
-      <c r="B36" s="150"/>
-      <c r="C36" s="152"/>
-      <c r="D36" s="152"/>
-      <c r="E36" s="152"/>
+      <c r="B36" s="151"/>
+      <c r="C36" s="153"/>
+      <c r="D36" s="153"/>
+      <c r="E36" s="153"/>
     </row>
     <row r="37" spans="2:5">
-      <c r="B37" s="150"/>
-      <c r="C37" s="152"/>
-      <c r="D37" s="152"/>
-      <c r="E37" s="152"/>
+      <c r="B37" s="151"/>
+      <c r="C37" s="153"/>
+      <c r="D37" s="153"/>
+      <c r="E37" s="153"/>
     </row>
     <row r="38" spans="2:5">
-      <c r="B38" s="150"/>
-      <c r="C38" s="152"/>
-      <c r="D38" s="152"/>
-      <c r="E38" s="152"/>
+      <c r="B38" s="151"/>
+      <c r="C38" s="153"/>
+      <c r="D38" s="153"/>
+      <c r="E38" s="153"/>
     </row>
     <row r="39" spans="2:5">
-      <c r="B39" s="150"/>
-      <c r="C39" s="152"/>
-      <c r="D39" s="152"/>
-      <c r="E39" s="152"/>
+      <c r="B39" s="151"/>
+      <c r="C39" s="153"/>
+      <c r="D39" s="153"/>
+      <c r="E39" s="153"/>
     </row>
     <row r="40" spans="2:5">
-      <c r="B40" s="150"/>
-      <c r="C40" s="152"/>
-      <c r="D40" s="152"/>
-      <c r="E40" s="152"/>
+      <c r="B40" s="151"/>
+      <c r="C40" s="153"/>
+      <c r="D40" s="153"/>
+      <c r="E40" s="153"/>
     </row>
     <row r="41" spans="2:5">
-      <c r="B41" s="150"/>
-      <c r="C41" s="152"/>
-      <c r="D41" s="152"/>
-      <c r="E41" s="152"/>
+      <c r="B41" s="151"/>
+      <c r="C41" s="153"/>
+      <c r="D41" s="153"/>
+      <c r="E41" s="153"/>
     </row>
     <row r="42" spans="2:5">
-      <c r="B42" s="150"/>
-      <c r="C42" s="152"/>
-      <c r="D42" s="152"/>
-      <c r="E42" s="152"/>
+      <c r="B42" s="151"/>
+      <c r="C42" s="153"/>
+      <c r="D42" s="153"/>
+      <c r="E42" s="153"/>
     </row>
     <row r="43" spans="2:5">
-      <c r="B43" s="150"/>
-      <c r="C43" s="152"/>
-      <c r="D43" s="152"/>
-      <c r="E43" s="152"/>
+      <c r="B43" s="151"/>
+      <c r="C43" s="153"/>
+      <c r="D43" s="153"/>
+      <c r="E43" s="153"/>
     </row>
     <row r="44" spans="2:5">
-      <c r="B44" s="150"/>
-      <c r="C44" s="152"/>
-      <c r="D44" s="152"/>
-      <c r="E44" s="152"/>
+      <c r="B44" s="151"/>
+      <c r="C44" s="153"/>
+      <c r="D44" s="153"/>
+      <c r="E44" s="153"/>
     </row>
     <row r="45" spans="2:5">
-      <c r="B45" s="150"/>
-      <c r="C45" s="152"/>
-      <c r="D45" s="152"/>
-      <c r="E45" s="152"/>
+      <c r="B45" s="151"/>
+      <c r="C45" s="153"/>
+      <c r="D45" s="153"/>
+      <c r="E45" s="153"/>
     </row>
     <row r="46" spans="2:5">
-      <c r="B46" s="150"/>
-      <c r="C46" s="152"/>
-      <c r="D46" s="152"/>
-      <c r="E46" s="152"/>
+      <c r="B46" s="151"/>
+      <c r="C46" s="153"/>
+      <c r="D46" s="153"/>
+      <c r="E46" s="153"/>
     </row>
     <row r="47" spans="2:5">
-      <c r="B47" s="150"/>
-      <c r="C47" s="152"/>
-      <c r="D47" s="152"/>
-      <c r="E47" s="152"/>
+      <c r="B47" s="151"/>
+      <c r="C47" s="153"/>
+      <c r="D47" s="153"/>
+      <c r="E47" s="153"/>
     </row>
     <row r="48" spans="2:5">
-      <c r="B48" s="150"/>
-      <c r="C48" s="152"/>
-      <c r="D48" s="152"/>
-      <c r="E48" s="152"/>
+      <c r="B48" s="151"/>
+      <c r="C48" s="153"/>
+      <c r="D48" s="153"/>
+      <c r="E48" s="153"/>
     </row>
     <row r="49" spans="2:5">
-      <c r="B49" s="150"/>
-      <c r="C49" s="152"/>
-      <c r="D49" s="152"/>
-      <c r="E49" s="152"/>
+      <c r="B49" s="151"/>
+      <c r="C49" s="153"/>
+      <c r="D49" s="153"/>
+      <c r="E49" s="153"/>
     </row>
     <row r="50" spans="2:5">
-      <c r="B50" s="150"/>
-      <c r="C50" s="152"/>
-      <c r="D50" s="152"/>
-      <c r="E50" s="152"/>
+      <c r="B50" s="151"/>
+      <c r="C50" s="153"/>
+      <c r="D50" s="153"/>
+      <c r="E50" s="153"/>
     </row>
     <row r="51" spans="2:5">
-      <c r="B51" s="150"/>
-      <c r="C51" s="152"/>
-      <c r="D51" s="152"/>
-      <c r="E51" s="152"/>
+      <c r="B51" s="151"/>
+      <c r="C51" s="153"/>
+      <c r="D51" s="153"/>
+      <c r="E51" s="153"/>
     </row>
     <row r="52" spans="2:5">
-      <c r="B52" s="150"/>
-      <c r="C52" s="152"/>
-      <c r="D52" s="152"/>
-      <c r="E52" s="152"/>
+      <c r="B52" s="151"/>
+      <c r="C52" s="153"/>
+      <c r="D52" s="153"/>
+      <c r="E52" s="153"/>
     </row>
     <row r="53" spans="2:5">
-      <c r="B53" s="150"/>
-      <c r="C53" s="152"/>
-      <c r="D53" s="152"/>
-      <c r="E53" s="152"/>
+      <c r="B53" s="151"/>
+      <c r="C53" s="153"/>
+      <c r="D53" s="153"/>
+      <c r="E53" s="153"/>
     </row>
     <row r="54" spans="2:5">
-      <c r="B54" s="150"/>
-      <c r="C54" s="152"/>
-      <c r="D54" s="152"/>
-      <c r="E54" s="152"/>
+      <c r="B54" s="151"/>
+      <c r="C54" s="153"/>
+      <c r="D54" s="153"/>
+      <c r="E54" s="153"/>
     </row>
     <row r="55" spans="2:5">
-      <c r="B55" s="150"/>
-      <c r="C55" s="152"/>
-      <c r="D55" s="152"/>
-      <c r="E55" s="152"/>
+      <c r="B55" s="151"/>
+      <c r="C55" s="153"/>
+      <c r="D55" s="153"/>
+      <c r="E55" s="153"/>
     </row>
     <row r="56" spans="2:5">
-      <c r="B56" s="150"/>
-      <c r="C56" s="152"/>
-      <c r="D56" s="152"/>
-      <c r="E56" s="152"/>
+      <c r="B56" s="151"/>
+      <c r="C56" s="153"/>
+      <c r="D56" s="153"/>
+      <c r="E56" s="153"/>
     </row>
     <row r="57" spans="2:5">
-      <c r="B57" s="150"/>
-      <c r="C57" s="152"/>
-      <c r="D57" s="152"/>
-      <c r="E57" s="152"/>
+      <c r="B57" s="151"/>
+      <c r="C57" s="153"/>
+      <c r="D57" s="153"/>
+      <c r="E57" s="153"/>
     </row>
     <row r="58" spans="2:5">
-      <c r="B58" s="150"/>
-      <c r="C58" s="152"/>
-      <c r="D58" s="152"/>
-      <c r="E58" s="152"/>
+      <c r="B58" s="151"/>
+      <c r="C58" s="153"/>
+      <c r="D58" s="153"/>
+      <c r="E58" s="153"/>
     </row>
     <row r="59" spans="2:5">
-      <c r="B59" s="150"/>
-      <c r="C59" s="152"/>
-      <c r="D59" s="152"/>
-      <c r="E59" s="152"/>
+      <c r="B59" s="151"/>
+      <c r="C59" s="153"/>
+      <c r="D59" s="153"/>
+      <c r="E59" s="153"/>
     </row>
     <row r="60" spans="2:5">
-      <c r="B60" s="150"/>
-      <c r="C60" s="152"/>
-      <c r="D60" s="152"/>
-      <c r="E60" s="152"/>
+      <c r="B60" s="151"/>
+      <c r="C60" s="153"/>
+      <c r="D60" s="153"/>
+      <c r="E60" s="153"/>
     </row>
     <row r="61" spans="2:5">
-      <c r="B61" s="150"/>
-      <c r="C61" s="152"/>
-      <c r="D61" s="152"/>
-      <c r="E61" s="152"/>
+      <c r="B61" s="151"/>
+      <c r="C61" s="153"/>
+      <c r="D61" s="153"/>
+      <c r="E61" s="153"/>
     </row>
     <row r="62" spans="2:5">
-      <c r="B62" s="150"/>
-      <c r="C62" s="152"/>
-      <c r="D62" s="152"/>
-      <c r="E62" s="152"/>
+      <c r="B62" s="151"/>
+      <c r="C62" s="153"/>
+      <c r="D62" s="153"/>
+      <c r="E62" s="153"/>
     </row>
     <row r="63" spans="2:5">
-      <c r="B63" s="150"/>
-      <c r="C63" s="152"/>
-      <c r="D63" s="152"/>
-      <c r="E63" s="152"/>
+      <c r="B63" s="151"/>
+      <c r="C63" s="153"/>
+      <c r="D63" s="153"/>
+      <c r="E63" s="153"/>
     </row>
     <row r="64" spans="2:5">
-      <c r="B64" s="150"/>
-      <c r="C64" s="152"/>
-      <c r="D64" s="152"/>
-      <c r="E64" s="152"/>
+      <c r="B64" s="151"/>
+      <c r="C64" s="153"/>
+      <c r="D64" s="153"/>
+      <c r="E64" s="153"/>
     </row>
     <row r="65" spans="2:5">
-      <c r="B65" s="150"/>
-      <c r="C65" s="152"/>
-      <c r="D65" s="152"/>
-      <c r="E65" s="152"/>
+      <c r="B65" s="151"/>
+      <c r="C65" s="153"/>
+      <c r="D65" s="153"/>
+      <c r="E65" s="153"/>
     </row>
     <row r="66" spans="2:5">
-      <c r="B66" s="150"/>
-      <c r="C66" s="152"/>
-      <c r="D66" s="152"/>
-      <c r="E66" s="152"/>
+      <c r="B66" s="151"/>
+      <c r="C66" s="153"/>
+      <c r="D66" s="153"/>
+      <c r="E66" s="153"/>
     </row>
     <row r="67" spans="2:5">
-      <c r="B67" s="150"/>
-      <c r="C67" s="152"/>
-      <c r="D67" s="152"/>
-      <c r="E67" s="152"/>
+      <c r="B67" s="151"/>
+      <c r="C67" s="153"/>
+      <c r="D67" s="153"/>
+      <c r="E67" s="153"/>
     </row>
     <row r="68" spans="2:5">
-      <c r="B68" s="150"/>
-      <c r="C68" s="152"/>
-      <c r="D68" s="152"/>
-      <c r="E68" s="152"/>
+      <c r="B68" s="151"/>
+      <c r="C68" s="153"/>
+      <c r="D68" s="153"/>
+      <c r="E68" s="153"/>
     </row>
     <row r="69" spans="2:5">
-      <c r="B69" s="150"/>
-      <c r="C69" s="152"/>
-      <c r="D69" s="152"/>
-      <c r="E69" s="152"/>
+      <c r="B69" s="151"/>
+      <c r="C69" s="153"/>
+      <c r="D69" s="153"/>
+      <c r="E69" s="153"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3816,11 +3813,11 @@
   <dimension ref="A1:AH28"/>
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
-    <col min="1" max="20" width="3.66666666666667" style="116"/>
-    <col min="21" max="21" width="5.88888888888889" style="116" customWidth="1"/>
-    <col min="22" max="33" width="3.66666666666667" style="116"/>
-    <col min="34" max="34" width="13" style="116" customWidth="1"/>
-    <col min="35" max="16384" width="3.66666666666667" style="116"/>
+    <col min="1" max="20" width="3.66666666666667" style="117"/>
+    <col min="21" max="21" width="5.88888888888889" style="117" customWidth="1"/>
+    <col min="22" max="33" width="3.66666666666667" style="117"/>
+    <col min="34" max="34" width="13" style="117" customWidth="1"/>
+    <col min="35" max="16384" width="3.66666666666667" style="117"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:34">
@@ -3836,21 +3833,21 @@
       <c r="H1" s="5"/>
       <c r="I1" s="5"/>
       <c r="J1" s="5"/>
-      <c r="K1" s="136"/>
+      <c r="K1" s="137"/>
       <c r="L1" s="23" t="s">
         <v>9</v>
       </c>
       <c r="M1" s="24"/>
       <c r="N1" s="24"/>
       <c r="O1" s="24"/>
-      <c r="P1" s="100"/>
+      <c r="P1" s="101"/>
       <c r="Q1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
-      <c r="T1" s="78"/>
-      <c r="U1" s="78"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
+      <c r="T1" s="79"/>
+      <c r="U1" s="79"/>
       <c r="V1" s="26" t="s">
         <v>3</v>
       </c>
@@ -3865,13 +3862,13 @@
       <c r="AC1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="AD1" s="144"/>
-      <c r="AE1" s="145"/>
-      <c r="AF1" s="154" t="s">
+      <c r="AD1" s="145"/>
+      <c r="AE1" s="146"/>
+      <c r="AF1" s="155" t="s">
         <v>12</v>
       </c>
-      <c r="AG1" s="112"/>
-      <c r="AH1" s="112"/>
+      <c r="AG1" s="113"/>
+      <c r="AH1" s="113"/>
     </row>
     <row r="2" customHeight="1" spans="1:34">
       <c r="A2" s="6"/>
@@ -3884,30 +3881,30 @@
       <c r="H2" s="7"/>
       <c r="I2" s="7"/>
       <c r="J2" s="7"/>
-      <c r="K2" s="137"/>
+      <c r="K2" s="138"/>
       <c r="L2" s="31"/>
       <c r="M2" s="32"/>
       <c r="N2" s="32"/>
       <c r="O2" s="32"/>
-      <c r="P2" s="101"/>
+      <c r="P2" s="102"/>
       <c r="Q2" s="33"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="79"/>
-      <c r="T2" s="79"/>
-      <c r="U2" s="79"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
+      <c r="T2" s="80"/>
+      <c r="U2" s="80"/>
       <c r="V2" s="26"/>
       <c r="W2" s="26"/>
       <c r="X2" s="26"/>
       <c r="Y2" s="34"/>
-      <c r="Z2" s="80"/>
-      <c r="AA2" s="80"/>
-      <c r="AB2" s="146"/>
+      <c r="Z2" s="81"/>
+      <c r="AA2" s="81"/>
+      <c r="AB2" s="147"/>
       <c r="AC2" s="35"/>
-      <c r="AD2" s="94"/>
-      <c r="AE2" s="95"/>
+      <c r="AD2" s="95"/>
+      <c r="AE2" s="96"/>
       <c r="AF2" s="36"/>
-      <c r="AG2" s="113"/>
-      <c r="AH2" s="113"/>
+      <c r="AG2" s="114"/>
+      <c r="AH2" s="114"/>
     </row>
     <row r="3" customHeight="1" spans="1:34">
       <c r="A3" s="6"/>
@@ -3920,21 +3917,21 @@
       <c r="H3" s="7"/>
       <c r="I3" s="7"/>
       <c r="J3" s="7"/>
-      <c r="K3" s="137"/>
+      <c r="K3" s="138"/>
       <c r="L3" s="23" t="s">
         <v>13</v>
       </c>
       <c r="M3" s="24"/>
       <c r="N3" s="24"/>
       <c r="O3" s="24"/>
-      <c r="P3" s="100"/>
+      <c r="P3" s="101"/>
       <c r="Q3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="R3" s="78"/>
-      <c r="S3" s="78"/>
-      <c r="T3" s="78"/>
-      <c r="U3" s="78"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="79"/>
+      <c r="T3" s="79"/>
+      <c r="U3" s="79"/>
       <c r="V3" s="26" t="s">
         <v>15</v>
       </c>
@@ -3951,11 +3948,11 @@
       </c>
       <c r="AD3" s="26"/>
       <c r="AE3" s="26"/>
-      <c r="AF3" s="154" t="s">
+      <c r="AF3" s="155" t="s">
         <v>18</v>
       </c>
-      <c r="AG3" s="112"/>
-      <c r="AH3" s="112"/>
+      <c r="AG3" s="113"/>
+      <c r="AH3" s="113"/>
     </row>
     <row r="4" customHeight="1" spans="1:34">
       <c r="A4" s="8"/>
@@ -3968,270 +3965,270 @@
       <c r="H4" s="9"/>
       <c r="I4" s="9"/>
       <c r="J4" s="9"/>
-      <c r="K4" s="138"/>
+      <c r="K4" s="139"/>
       <c r="L4" s="31"/>
       <c r="M4" s="32"/>
       <c r="N4" s="32"/>
       <c r="O4" s="32"/>
-      <c r="P4" s="101"/>
+      <c r="P4" s="102"/>
       <c r="Q4" s="33"/>
-      <c r="R4" s="79"/>
-      <c r="S4" s="79"/>
-      <c r="T4" s="79"/>
-      <c r="U4" s="79"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="80"/>
+      <c r="T4" s="80"/>
+      <c r="U4" s="80"/>
       <c r="V4" s="26"/>
       <c r="W4" s="26"/>
       <c r="X4" s="26"/>
       <c r="Y4" s="34"/>
-      <c r="Z4" s="80"/>
-      <c r="AA4" s="80"/>
-      <c r="AB4" s="146"/>
+      <c r="Z4" s="81"/>
+      <c r="AA4" s="81"/>
+      <c r="AB4" s="147"/>
       <c r="AC4" s="26"/>
       <c r="AD4" s="26"/>
       <c r="AE4" s="26"/>
       <c r="AF4" s="36"/>
-      <c r="AG4" s="113"/>
-      <c r="AH4" s="113"/>
+      <c r="AG4" s="114"/>
+      <c r="AH4" s="114"/>
     </row>
     <row r="5" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A5" s="117" t="s">
+      <c r="A5" s="118" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="118"/>
-      <c r="C5" s="118"/>
-      <c r="D5" s="118"/>
-      <c r="E5" s="118"/>
-      <c r="F5" s="118"/>
-      <c r="G5" s="119"/>
-      <c r="H5" s="120" t="s">
+      <c r="B5" s="119"/>
+      <c r="C5" s="119"/>
+      <c r="D5" s="119"/>
+      <c r="E5" s="119"/>
+      <c r="F5" s="119"/>
+      <c r="G5" s="120"/>
+      <c r="H5" s="121" t="s">
         <v>19</v>
       </c>
-      <c r="I5" s="139"/>
-      <c r="J5" s="139"/>
-      <c r="K5" s="139"/>
-      <c r="L5" s="139"/>
-      <c r="M5" s="139"/>
-      <c r="N5" s="139"/>
-      <c r="O5" s="139"/>
-      <c r="P5" s="139"/>
-      <c r="Q5" s="139"/>
-      <c r="R5" s="139"/>
-      <c r="S5" s="139"/>
-      <c r="T5" s="139"/>
-      <c r="U5" s="139"/>
-      <c r="V5" s="139"/>
-      <c r="W5" s="139"/>
-      <c r="X5" s="139"/>
-      <c r="Y5" s="139"/>
-      <c r="Z5" s="139"/>
-      <c r="AA5" s="139"/>
-      <c r="AB5" s="139"/>
-      <c r="AC5" s="139"/>
-      <c r="AD5" s="139"/>
-      <c r="AE5" s="139"/>
-      <c r="AF5" s="139"/>
-      <c r="AG5" s="139"/>
-      <c r="AH5" s="139"/>
+      <c r="I5" s="140"/>
+      <c r="J5" s="140"/>
+      <c r="K5" s="140"/>
+      <c r="L5" s="140"/>
+      <c r="M5" s="140"/>
+      <c r="N5" s="140"/>
+      <c r="O5" s="140"/>
+      <c r="P5" s="140"/>
+      <c r="Q5" s="140"/>
+      <c r="R5" s="140"/>
+      <c r="S5" s="140"/>
+      <c r="T5" s="140"/>
+      <c r="U5" s="140"/>
+      <c r="V5" s="140"/>
+      <c r="W5" s="140"/>
+      <c r="X5" s="140"/>
+      <c r="Y5" s="140"/>
+      <c r="Z5" s="140"/>
+      <c r="AA5" s="140"/>
+      <c r="AB5" s="140"/>
+      <c r="AC5" s="140"/>
+      <c r="AD5" s="140"/>
+      <c r="AE5" s="140"/>
+      <c r="AF5" s="140"/>
+      <c r="AG5" s="140"/>
+      <c r="AH5" s="140"/>
     </row>
     <row r="6" customFormat="1" ht="63.75" customHeight="1" spans="1:34">
-      <c r="A6" s="117" t="s">
+      <c r="A6" s="118" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="118"/>
-      <c r="C6" s="118"/>
-      <c r="D6" s="118"/>
-      <c r="E6" s="118"/>
-      <c r="F6" s="118"/>
-      <c r="G6" s="119"/>
-      <c r="H6" s="121" t="s">
+      <c r="B6" s="119"/>
+      <c r="C6" s="119"/>
+      <c r="D6" s="119"/>
+      <c r="E6" s="119"/>
+      <c r="F6" s="119"/>
+      <c r="G6" s="120"/>
+      <c r="H6" s="122" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="139"/>
-      <c r="J6" s="139"/>
-      <c r="K6" s="139"/>
-      <c r="L6" s="139"/>
-      <c r="M6" s="139"/>
-      <c r="N6" s="139"/>
-      <c r="O6" s="139"/>
-      <c r="P6" s="139"/>
-      <c r="Q6" s="139"/>
-      <c r="R6" s="139"/>
-      <c r="S6" s="139"/>
-      <c r="T6" s="139"/>
-      <c r="U6" s="139"/>
-      <c r="V6" s="139"/>
-      <c r="W6" s="139"/>
-      <c r="X6" s="139"/>
-      <c r="Y6" s="139"/>
-      <c r="Z6" s="139"/>
-      <c r="AA6" s="139"/>
-      <c r="AB6" s="139"/>
-      <c r="AC6" s="139"/>
-      <c r="AD6" s="139"/>
-      <c r="AE6" s="139"/>
-      <c r="AF6" s="139"/>
-      <c r="AG6" s="139"/>
-      <c r="AH6" s="139"/>
+      <c r="I6" s="140"/>
+      <c r="J6" s="140"/>
+      <c r="K6" s="140"/>
+      <c r="L6" s="140"/>
+      <c r="M6" s="140"/>
+      <c r="N6" s="140"/>
+      <c r="O6" s="140"/>
+      <c r="P6" s="140"/>
+      <c r="Q6" s="140"/>
+      <c r="R6" s="140"/>
+      <c r="S6" s="140"/>
+      <c r="T6" s="140"/>
+      <c r="U6" s="140"/>
+      <c r="V6" s="140"/>
+      <c r="W6" s="140"/>
+      <c r="X6" s="140"/>
+      <c r="Y6" s="140"/>
+      <c r="Z6" s="140"/>
+      <c r="AA6" s="140"/>
+      <c r="AB6" s="140"/>
+      <c r="AC6" s="140"/>
+      <c r="AD6" s="140"/>
+      <c r="AE6" s="140"/>
+      <c r="AF6" s="140"/>
+      <c r="AG6" s="140"/>
+      <c r="AH6" s="140"/>
     </row>
     <row r="7" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A7" s="117" t="s">
+      <c r="A7" s="118" t="s">
         <v>22</v>
       </c>
-      <c r="B7" s="118"/>
-      <c r="C7" s="118"/>
-      <c r="D7" s="118"/>
-      <c r="E7" s="118"/>
-      <c r="F7" s="118"/>
-      <c r="G7" s="119"/>
-      <c r="H7" s="120" t="s">
+      <c r="B7" s="119"/>
+      <c r="C7" s="119"/>
+      <c r="D7" s="119"/>
+      <c r="E7" s="119"/>
+      <c r="F7" s="119"/>
+      <c r="G7" s="120"/>
+      <c r="H7" s="121" t="s">
         <v>23</v>
       </c>
-      <c r="I7" s="139"/>
-      <c r="J7" s="139"/>
-      <c r="K7" s="139"/>
-      <c r="L7" s="139"/>
-      <c r="M7" s="139"/>
-      <c r="N7" s="139"/>
-      <c r="O7" s="139"/>
-      <c r="P7" s="139"/>
-      <c r="Q7" s="139"/>
-      <c r="R7" s="139"/>
-      <c r="S7" s="139"/>
-      <c r="T7" s="139"/>
-      <c r="U7" s="139"/>
-      <c r="V7" s="139"/>
-      <c r="W7" s="139"/>
-      <c r="X7" s="139"/>
-      <c r="Y7" s="139"/>
-      <c r="Z7" s="139"/>
-      <c r="AA7" s="139"/>
-      <c r="AB7" s="139"/>
-      <c r="AC7" s="139"/>
-      <c r="AD7" s="139"/>
-      <c r="AE7" s="139"/>
-      <c r="AF7" s="139"/>
-      <c r="AG7" s="139"/>
-      <c r="AH7" s="139"/>
+      <c r="I7" s="140"/>
+      <c r="J7" s="140"/>
+      <c r="K7" s="140"/>
+      <c r="L7" s="140"/>
+      <c r="M7" s="140"/>
+      <c r="N7" s="140"/>
+      <c r="O7" s="140"/>
+      <c r="P7" s="140"/>
+      <c r="Q7" s="140"/>
+      <c r="R7" s="140"/>
+      <c r="S7" s="140"/>
+      <c r="T7" s="140"/>
+      <c r="U7" s="140"/>
+      <c r="V7" s="140"/>
+      <c r="W7" s="140"/>
+      <c r="X7" s="140"/>
+      <c r="Y7" s="140"/>
+      <c r="Z7" s="140"/>
+      <c r="AA7" s="140"/>
+      <c r="AB7" s="140"/>
+      <c r="AC7" s="140"/>
+      <c r="AD7" s="140"/>
+      <c r="AE7" s="140"/>
+      <c r="AF7" s="140"/>
+      <c r="AG7" s="140"/>
+      <c r="AH7" s="140"/>
     </row>
     <row r="8" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A8" s="117" t="s">
+      <c r="A8" s="118" t="s">
         <v>24</v>
       </c>
-      <c r="B8" s="118"/>
-      <c r="C8" s="118"/>
-      <c r="D8" s="118"/>
-      <c r="E8" s="118"/>
-      <c r="F8" s="118"/>
-      <c r="G8" s="119"/>
-      <c r="H8" s="120" t="s">
+      <c r="B8" s="119"/>
+      <c r="C8" s="119"/>
+      <c r="D8" s="119"/>
+      <c r="E8" s="119"/>
+      <c r="F8" s="119"/>
+      <c r="G8" s="120"/>
+      <c r="H8" s="121" t="s">
         <v>25</v>
       </c>
-      <c r="I8" s="139"/>
-      <c r="J8" s="139"/>
-      <c r="K8" s="139"/>
-      <c r="L8" s="139"/>
-      <c r="M8" s="139"/>
-      <c r="N8" s="139"/>
-      <c r="O8" s="139"/>
-      <c r="P8" s="139"/>
-      <c r="Q8" s="139"/>
-      <c r="R8" s="139"/>
-      <c r="S8" s="139"/>
-      <c r="T8" s="139"/>
-      <c r="U8" s="139"/>
-      <c r="V8" s="139"/>
-      <c r="W8" s="139"/>
-      <c r="X8" s="139"/>
-      <c r="Y8" s="139"/>
-      <c r="Z8" s="139"/>
-      <c r="AA8" s="139"/>
-      <c r="AB8" s="139"/>
-      <c r="AC8" s="139"/>
-      <c r="AD8" s="139"/>
-      <c r="AE8" s="139"/>
-      <c r="AF8" s="139"/>
-      <c r="AG8" s="139"/>
-      <c r="AH8" s="139"/>
+      <c r="I8" s="140"/>
+      <c r="J8" s="140"/>
+      <c r="K8" s="140"/>
+      <c r="L8" s="140"/>
+      <c r="M8" s="140"/>
+      <c r="N8" s="140"/>
+      <c r="O8" s="140"/>
+      <c r="P8" s="140"/>
+      <c r="Q8" s="140"/>
+      <c r="R8" s="140"/>
+      <c r="S8" s="140"/>
+      <c r="T8" s="140"/>
+      <c r="U8" s="140"/>
+      <c r="V8" s="140"/>
+      <c r="W8" s="140"/>
+      <c r="X8" s="140"/>
+      <c r="Y8" s="140"/>
+      <c r="Z8" s="140"/>
+      <c r="AA8" s="140"/>
+      <c r="AB8" s="140"/>
+      <c r="AC8" s="140"/>
+      <c r="AD8" s="140"/>
+      <c r="AE8" s="140"/>
+      <c r="AF8" s="140"/>
+      <c r="AG8" s="140"/>
+      <c r="AH8" s="140"/>
     </row>
     <row r="9" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A9" s="117" t="s">
+      <c r="A9" s="118" t="s">
         <v>26</v>
       </c>
-      <c r="B9" s="118"/>
-      <c r="C9" s="118"/>
-      <c r="D9" s="118"/>
-      <c r="E9" s="118"/>
-      <c r="F9" s="118"/>
-      <c r="G9" s="119"/>
-      <c r="H9" s="120" t="s">
+      <c r="B9" s="119"/>
+      <c r="C9" s="119"/>
+      <c r="D9" s="119"/>
+      <c r="E9" s="119"/>
+      <c r="F9" s="119"/>
+      <c r="G9" s="120"/>
+      <c r="H9" s="121" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="139"/>
-      <c r="J9" s="139"/>
-      <c r="K9" s="139"/>
-      <c r="L9" s="139"/>
-      <c r="M9" s="139"/>
-      <c r="N9" s="139"/>
-      <c r="O9" s="139"/>
-      <c r="P9" s="139"/>
-      <c r="Q9" s="139"/>
-      <c r="R9" s="139"/>
-      <c r="S9" s="139"/>
-      <c r="T9" s="139"/>
-      <c r="U9" s="139"/>
-      <c r="V9" s="139"/>
-      <c r="W9" s="139"/>
-      <c r="X9" s="139"/>
-      <c r="Y9" s="139"/>
-      <c r="Z9" s="139"/>
-      <c r="AA9" s="139"/>
-      <c r="AB9" s="139"/>
-      <c r="AC9" s="139"/>
-      <c r="AD9" s="139"/>
-      <c r="AE9" s="139"/>
-      <c r="AF9" s="139"/>
-      <c r="AG9" s="139"/>
-      <c r="AH9" s="139"/>
+      <c r="I9" s="140"/>
+      <c r="J9" s="140"/>
+      <c r="K9" s="140"/>
+      <c r="L9" s="140"/>
+      <c r="M9" s="140"/>
+      <c r="N9" s="140"/>
+      <c r="O9" s="140"/>
+      <c r="P9" s="140"/>
+      <c r="Q9" s="140"/>
+      <c r="R9" s="140"/>
+      <c r="S9" s="140"/>
+      <c r="T9" s="140"/>
+      <c r="U9" s="140"/>
+      <c r="V9" s="140"/>
+      <c r="W9" s="140"/>
+      <c r="X9" s="140"/>
+      <c r="Y9" s="140"/>
+      <c r="Z9" s="140"/>
+      <c r="AA9" s="140"/>
+      <c r="AB9" s="140"/>
+      <c r="AC9" s="140"/>
+      <c r="AD9" s="140"/>
+      <c r="AE9" s="140"/>
+      <c r="AF9" s="140"/>
+      <c r="AG9" s="140"/>
+      <c r="AH9" s="140"/>
     </row>
     <row r="10" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A10" s="122" t="s">
+      <c r="A10" s="123" t="s">
         <v>28</v>
       </c>
-      <c r="B10" s="123"/>
-      <c r="C10" s="123"/>
-      <c r="D10" s="123"/>
-      <c r="E10" s="123"/>
-      <c r="F10" s="123"/>
-      <c r="G10" s="124"/>
-      <c r="H10" s="125" t="s">
+      <c r="B10" s="124"/>
+      <c r="C10" s="124"/>
+      <c r="D10" s="124"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="124"/>
+      <c r="G10" s="125"/>
+      <c r="H10" s="126" t="s">
         <v>29</v>
       </c>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="140"/>
-      <c r="M10" s="140"/>
-      <c r="N10" s="140"/>
-      <c r="O10" s="140"/>
-      <c r="P10" s="140"/>
-      <c r="Q10" s="140"/>
-      <c r="R10" s="140"/>
-      <c r="S10" s="140"/>
-      <c r="T10" s="140"/>
-      <c r="U10" s="140"/>
-      <c r="V10" s="140"/>
-      <c r="W10" s="140"/>
-      <c r="X10" s="140"/>
-      <c r="Y10" s="140"/>
-      <c r="Z10" s="140"/>
-      <c r="AA10" s="140"/>
-      <c r="AB10" s="140"/>
-      <c r="AC10" s="140"/>
-      <c r="AD10" s="140"/>
-      <c r="AE10" s="140"/>
-      <c r="AF10" s="140"/>
-      <c r="AG10" s="140"/>
-      <c r="AH10" s="140"/>
+      <c r="I10" s="141"/>
+      <c r="J10" s="141"/>
+      <c r="K10" s="141"/>
+      <c r="L10" s="141"/>
+      <c r="M10" s="141"/>
+      <c r="N10" s="141"/>
+      <c r="O10" s="141"/>
+      <c r="P10" s="141"/>
+      <c r="Q10" s="141"/>
+      <c r="R10" s="141"/>
+      <c r="S10" s="141"/>
+      <c r="T10" s="141"/>
+      <c r="U10" s="141"/>
+      <c r="V10" s="141"/>
+      <c r="W10" s="141"/>
+      <c r="X10" s="141"/>
+      <c r="Y10" s="141"/>
+      <c r="Z10" s="141"/>
+      <c r="AA10" s="141"/>
+      <c r="AB10" s="141"/>
+      <c r="AC10" s="141"/>
+      <c r="AD10" s="141"/>
+      <c r="AE10" s="141"/>
+      <c r="AF10" s="141"/>
+      <c r="AG10" s="141"/>
+      <c r="AH10" s="141"/>
     </row>
     <row r="11" s="3" customFormat="1" customHeight="1" spans="1:34">
       <c r="A11" s="12" t="s">
@@ -4272,297 +4269,297 @@
       <c r="AH11" s="13"/>
     </row>
     <row r="12" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A12" s="126"/>
+      <c r="A12" s="127"/>
     </row>
     <row r="13" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A13" s="126"/>
+      <c r="A13" s="127"/>
     </row>
     <row r="14" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A14" s="126"/>
+      <c r="A14" s="127"/>
     </row>
     <row r="15" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A15" s="126"/>
+      <c r="A15" s="127"/>
     </row>
     <row r="16" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A16" s="126"/>
+      <c r="A16" s="127"/>
     </row>
     <row r="17" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A17" s="126"/>
+      <c r="A17" s="127"/>
     </row>
     <row r="18" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A18" s="126"/>
+      <c r="A18" s="127"/>
     </row>
     <row r="19" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A19" s="126"/>
+      <c r="A19" s="127"/>
     </row>
     <row r="20" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A20" s="126"/>
+      <c r="A20" s="127"/>
     </row>
     <row r="21" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A21" s="126"/>
+      <c r="A21" s="127"/>
     </row>
     <row r="22" s="3" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A22" s="126"/>
+      <c r="A22" s="127"/>
     </row>
     <row r="23" s="3" customFormat="1" customHeight="1" spans="1:34">
-      <c r="A23" s="127"/>
-      <c r="B23" s="128"/>
-      <c r="C23" s="128"/>
-      <c r="D23" s="128"/>
-      <c r="E23" s="128"/>
-      <c r="F23" s="128"/>
-      <c r="G23" s="128"/>
-      <c r="H23" s="128"/>
-      <c r="I23" s="128"/>
-      <c r="J23" s="128"/>
-      <c r="K23" s="128"/>
-      <c r="L23" s="128"/>
-      <c r="M23" s="128"/>
-      <c r="N23" s="128"/>
-      <c r="O23" s="128"/>
-      <c r="P23" s="128"/>
-      <c r="Q23" s="128"/>
-      <c r="R23" s="128"/>
-      <c r="S23" s="128"/>
-      <c r="T23" s="128"/>
-      <c r="U23" s="128"/>
-      <c r="V23" s="128"/>
-      <c r="W23" s="128"/>
-      <c r="X23" s="128"/>
-      <c r="Y23" s="128"/>
-      <c r="Z23" s="128"/>
-      <c r="AA23" s="128"/>
-      <c r="AB23" s="128"/>
-      <c r="AC23" s="128"/>
-      <c r="AD23" s="128"/>
-      <c r="AE23" s="128"/>
-      <c r="AF23" s="128"/>
-      <c r="AG23" s="128"/>
-      <c r="AH23" s="128"/>
+      <c r="A23" s="128"/>
+      <c r="B23" s="129"/>
+      <c r="C23" s="129"/>
+      <c r="D23" s="129"/>
+      <c r="E23" s="129"/>
+      <c r="F23" s="129"/>
+      <c r="G23" s="129"/>
+      <c r="H23" s="129"/>
+      <c r="I23" s="129"/>
+      <c r="J23" s="129"/>
+      <c r="K23" s="129"/>
+      <c r="L23" s="129"/>
+      <c r="M23" s="129"/>
+      <c r="N23" s="129"/>
+      <c r="O23" s="129"/>
+      <c r="P23" s="129"/>
+      <c r="Q23" s="129"/>
+      <c r="R23" s="129"/>
+      <c r="S23" s="129"/>
+      <c r="T23" s="129"/>
+      <c r="U23" s="129"/>
+      <c r="V23" s="129"/>
+      <c r="W23" s="129"/>
+      <c r="X23" s="129"/>
+      <c r="Y23" s="129"/>
+      <c r="Z23" s="129"/>
+      <c r="AA23" s="129"/>
+      <c r="AB23" s="129"/>
+      <c r="AC23" s="129"/>
+      <c r="AD23" s="129"/>
+      <c r="AE23" s="129"/>
+      <c r="AF23" s="129"/>
+      <c r="AG23" s="129"/>
+      <c r="AH23" s="129"/>
     </row>
     <row r="24" customHeight="1" spans="1:34">
-      <c r="A24" s="129" t="s">
+      <c r="A24" s="130" t="s">
         <v>31</v>
       </c>
-      <c r="B24" s="130"/>
-      <c r="C24" s="129" t="s">
+      <c r="B24" s="131"/>
+      <c r="C24" s="130" t="s">
         <v>32</v>
       </c>
-      <c r="D24" s="131"/>
-      <c r="E24" s="131"/>
-      <c r="F24" s="131"/>
-      <c r="G24" s="131"/>
-      <c r="H24" s="131"/>
-      <c r="I24" s="131"/>
-      <c r="J24" s="130"/>
-      <c r="K24" s="141" t="s">
+      <c r="D24" s="132"/>
+      <c r="E24" s="132"/>
+      <c r="F24" s="132"/>
+      <c r="G24" s="132"/>
+      <c r="H24" s="132"/>
+      <c r="I24" s="132"/>
+      <c r="J24" s="131"/>
+      <c r="K24" s="142" t="s">
         <v>33</v>
       </c>
-      <c r="L24" s="141" t="s">
+      <c r="L24" s="142" t="s">
         <v>34</v>
       </c>
-      <c r="M24" s="141" t="s">
+      <c r="M24" s="142" t="s">
         <v>35</v>
       </c>
-      <c r="N24" s="129" t="s">
+      <c r="N24" s="130" t="s">
         <v>36</v>
       </c>
-      <c r="O24" s="142" t="s">
+      <c r="O24" s="143" t="s">
         <v>37</v>
       </c>
-      <c r="P24" s="142"/>
-      <c r="Q24" s="142"/>
-      <c r="R24" s="142"/>
-      <c r="S24" s="142"/>
-      <c r="T24" s="142"/>
-      <c r="U24" s="142"/>
-      <c r="V24" s="142"/>
-      <c r="W24" s="142"/>
-      <c r="X24" s="142"/>
-      <c r="Y24" s="142"/>
-      <c r="Z24" s="142"/>
-      <c r="AA24" s="142"/>
-      <c r="AB24" s="142"/>
-      <c r="AC24" s="142"/>
-      <c r="AD24" s="142"/>
-      <c r="AE24" s="142"/>
-      <c r="AF24" s="142"/>
-      <c r="AG24" s="142"/>
-      <c r="AH24" s="142"/>
+      <c r="P24" s="143"/>
+      <c r="Q24" s="143"/>
+      <c r="R24" s="143"/>
+      <c r="S24" s="143"/>
+      <c r="T24" s="143"/>
+      <c r="U24" s="143"/>
+      <c r="V24" s="143"/>
+      <c r="W24" s="143"/>
+      <c r="X24" s="143"/>
+      <c r="Y24" s="143"/>
+      <c r="Z24" s="143"/>
+      <c r="AA24" s="143"/>
+      <c r="AB24" s="143"/>
+      <c r="AC24" s="143"/>
+      <c r="AD24" s="143"/>
+      <c r="AE24" s="143"/>
+      <c r="AF24" s="143"/>
+      <c r="AG24" s="143"/>
+      <c r="AH24" s="143"/>
     </row>
     <row r="25" customHeight="1" spans="1:34">
-      <c r="A25" s="132">
+      <c r="A25" s="133">
         <v>1</v>
       </c>
-      <c r="B25" s="133"/>
-      <c r="C25" s="134" t="s">
+      <c r="B25" s="134"/>
+      <c r="C25" s="135" t="s">
         <v>38</v>
       </c>
-      <c r="D25" s="135"/>
-      <c r="E25" s="135"/>
-      <c r="F25" s="135"/>
-      <c r="G25" s="135"/>
-      <c r="H25" s="135"/>
-      <c r="I25" s="135"/>
-      <c r="J25" s="135"/>
-      <c r="K25" s="143" t="s">
+      <c r="D25" s="136"/>
+      <c r="E25" s="136"/>
+      <c r="F25" s="136"/>
+      <c r="G25" s="136"/>
+      <c r="H25" s="136"/>
+      <c r="I25" s="136"/>
+      <c r="J25" s="136"/>
+      <c r="K25" s="144" t="s">
         <v>39</v>
       </c>
-      <c r="L25" s="143" t="s">
+      <c r="L25" s="144" t="s">
         <v>39</v>
       </c>
-      <c r="M25" s="143" t="s">
+      <c r="M25" s="144" t="s">
         <v>39</v>
       </c>
-      <c r="N25" s="134"/>
-      <c r="O25" s="143"/>
-      <c r="P25" s="143"/>
-      <c r="Q25" s="143"/>
-      <c r="R25" s="143"/>
-      <c r="S25" s="143"/>
-      <c r="T25" s="143"/>
-      <c r="U25" s="143"/>
-      <c r="V25" s="143"/>
-      <c r="W25" s="143"/>
-      <c r="X25" s="143"/>
-      <c r="Y25" s="143"/>
-      <c r="Z25" s="143"/>
-      <c r="AA25" s="143"/>
-      <c r="AB25" s="143"/>
-      <c r="AC25" s="143"/>
-      <c r="AD25" s="143"/>
-      <c r="AE25" s="143"/>
-      <c r="AF25" s="143"/>
-      <c r="AG25" s="143"/>
-      <c r="AH25" s="143"/>
+      <c r="N25" s="135"/>
+      <c r="O25" s="144"/>
+      <c r="P25" s="144"/>
+      <c r="Q25" s="144"/>
+      <c r="R25" s="144"/>
+      <c r="S25" s="144"/>
+      <c r="T25" s="144"/>
+      <c r="U25" s="144"/>
+      <c r="V25" s="144"/>
+      <c r="W25" s="144"/>
+      <c r="X25" s="144"/>
+      <c r="Y25" s="144"/>
+      <c r="Z25" s="144"/>
+      <c r="AA25" s="144"/>
+      <c r="AB25" s="144"/>
+      <c r="AC25" s="144"/>
+      <c r="AD25" s="144"/>
+      <c r="AE25" s="144"/>
+      <c r="AF25" s="144"/>
+      <c r="AG25" s="144"/>
+      <c r="AH25" s="144"/>
     </row>
     <row r="26" customHeight="1" spans="1:34">
-      <c r="A26" s="132">
+      <c r="A26" s="133">
         <v>2</v>
       </c>
-      <c r="B26" s="133"/>
-      <c r="C26" s="155" t="s">
+      <c r="B26" s="134"/>
+      <c r="C26" s="156" t="s">
         <v>40</v>
       </c>
-      <c r="D26" s="135"/>
-      <c r="E26" s="135"/>
-      <c r="F26" s="135"/>
-      <c r="G26" s="135"/>
-      <c r="H26" s="135"/>
-      <c r="I26" s="135"/>
-      <c r="J26" s="135"/>
-      <c r="K26" s="143" t="s">
+      <c r="D26" s="136"/>
+      <c r="E26" s="136"/>
+      <c r="F26" s="136"/>
+      <c r="G26" s="136"/>
+      <c r="H26" s="136"/>
+      <c r="I26" s="136"/>
+      <c r="J26" s="136"/>
+      <c r="K26" s="144" t="s">
         <v>39</v>
       </c>
-      <c r="L26" s="143" t="s">
+      <c r="L26" s="144" t="s">
         <v>39</v>
       </c>
-      <c r="M26" s="143"/>
-      <c r="N26" s="134"/>
-      <c r="O26" s="143"/>
-      <c r="P26" s="143"/>
-      <c r="Q26" s="143"/>
-      <c r="R26" s="143"/>
-      <c r="S26" s="143"/>
-      <c r="T26" s="143"/>
-      <c r="U26" s="143"/>
-      <c r="V26" s="143"/>
-      <c r="W26" s="143"/>
-      <c r="X26" s="143"/>
-      <c r="Y26" s="143"/>
-      <c r="Z26" s="143"/>
-      <c r="AA26" s="143"/>
-      <c r="AB26" s="143"/>
-      <c r="AC26" s="143"/>
-      <c r="AD26" s="143"/>
-      <c r="AE26" s="143"/>
-      <c r="AF26" s="143"/>
-      <c r="AG26" s="143"/>
-      <c r="AH26" s="143"/>
+      <c r="M26" s="144"/>
+      <c r="N26" s="135"/>
+      <c r="O26" s="144"/>
+      <c r="P26" s="144"/>
+      <c r="Q26" s="144"/>
+      <c r="R26" s="144"/>
+      <c r="S26" s="144"/>
+      <c r="T26" s="144"/>
+      <c r="U26" s="144"/>
+      <c r="V26" s="144"/>
+      <c r="W26" s="144"/>
+      <c r="X26" s="144"/>
+      <c r="Y26" s="144"/>
+      <c r="Z26" s="144"/>
+      <c r="AA26" s="144"/>
+      <c r="AB26" s="144"/>
+      <c r="AC26" s="144"/>
+      <c r="AD26" s="144"/>
+      <c r="AE26" s="144"/>
+      <c r="AF26" s="144"/>
+      <c r="AG26" s="144"/>
+      <c r="AH26" s="144"/>
     </row>
     <row r="27" customHeight="1" spans="1:34">
-      <c r="A27" s="132">
+      <c r="A27" s="133">
         <v>3</v>
       </c>
-      <c r="B27" s="133"/>
-      <c r="C27" s="134" t="s">
+      <c r="B27" s="134"/>
+      <c r="C27" s="135" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="135"/>
-      <c r="E27" s="135"/>
-      <c r="F27" s="135"/>
-      <c r="G27" s="135"/>
-      <c r="H27" s="135"/>
-      <c r="I27" s="135"/>
-      <c r="J27" s="135"/>
-      <c r="K27" s="143" t="s">
+      <c r="D27" s="136"/>
+      <c r="E27" s="136"/>
+      <c r="F27" s="136"/>
+      <c r="G27" s="136"/>
+      <c r="H27" s="136"/>
+      <c r="I27" s="136"/>
+      <c r="J27" s="136"/>
+      <c r="K27" s="144" t="s">
         <v>39</v>
       </c>
-      <c r="L27" s="143"/>
-      <c r="M27" s="143"/>
-      <c r="N27" s="134"/>
-      <c r="O27" s="143"/>
-      <c r="P27" s="143"/>
-      <c r="Q27" s="143"/>
-      <c r="R27" s="143"/>
-      <c r="S27" s="143"/>
-      <c r="T27" s="143"/>
-      <c r="U27" s="143"/>
-      <c r="V27" s="143"/>
-      <c r="W27" s="143"/>
-      <c r="X27" s="143"/>
-      <c r="Y27" s="143"/>
-      <c r="Z27" s="143"/>
-      <c r="AA27" s="143"/>
-      <c r="AB27" s="143"/>
-      <c r="AC27" s="143"/>
-      <c r="AD27" s="143"/>
-      <c r="AE27" s="143"/>
-      <c r="AF27" s="143"/>
-      <c r="AG27" s="143"/>
-      <c r="AH27" s="143"/>
+      <c r="L27" s="144"/>
+      <c r="M27" s="144"/>
+      <c r="N27" s="135"/>
+      <c r="O27" s="144"/>
+      <c r="P27" s="144"/>
+      <c r="Q27" s="144"/>
+      <c r="R27" s="144"/>
+      <c r="S27" s="144"/>
+      <c r="T27" s="144"/>
+      <c r="U27" s="144"/>
+      <c r="V27" s="144"/>
+      <c r="W27" s="144"/>
+      <c r="X27" s="144"/>
+      <c r="Y27" s="144"/>
+      <c r="Z27" s="144"/>
+      <c r="AA27" s="144"/>
+      <c r="AB27" s="144"/>
+      <c r="AC27" s="144"/>
+      <c r="AD27" s="144"/>
+      <c r="AE27" s="144"/>
+      <c r="AF27" s="144"/>
+      <c r="AG27" s="144"/>
+      <c r="AH27" s="144"/>
     </row>
     <row r="28" customHeight="1" spans="1:34">
-      <c r="A28" s="132">
+      <c r="A28" s="133">
         <v>4</v>
       </c>
-      <c r="B28" s="133"/>
-      <c r="C28" s="155" t="s">
+      <c r="B28" s="134"/>
+      <c r="C28" s="156" t="s">
         <v>42</v>
       </c>
-      <c r="D28" s="135"/>
-      <c r="E28" s="135"/>
-      <c r="F28" s="135"/>
-      <c r="G28" s="135"/>
-      <c r="H28" s="135"/>
-      <c r="I28" s="135"/>
-      <c r="J28" s="135"/>
-      <c r="K28" s="143" t="s">
+      <c r="D28" s="136"/>
+      <c r="E28" s="136"/>
+      <c r="F28" s="136"/>
+      <c r="G28" s="136"/>
+      <c r="H28" s="136"/>
+      <c r="I28" s="136"/>
+      <c r="J28" s="136"/>
+      <c r="K28" s="144" t="s">
         <v>39</v>
       </c>
-      <c r="L28" s="143"/>
-      <c r="M28" s="143"/>
-      <c r="N28" s="134"/>
-      <c r="O28" s="143"/>
-      <c r="P28" s="143"/>
-      <c r="Q28" s="143"/>
-      <c r="R28" s="143"/>
-      <c r="S28" s="143"/>
-      <c r="T28" s="143"/>
-      <c r="U28" s="143"/>
-      <c r="V28" s="143"/>
-      <c r="W28" s="143"/>
-      <c r="X28" s="143"/>
-      <c r="Y28" s="143"/>
-      <c r="Z28" s="143"/>
-      <c r="AA28" s="143"/>
-      <c r="AB28" s="143"/>
-      <c r="AC28" s="143"/>
-      <c r="AD28" s="143"/>
-      <c r="AE28" s="143"/>
-      <c r="AF28" s="143"/>
-      <c r="AG28" s="143"/>
-      <c r="AH28" s="143"/>
+      <c r="L28" s="144"/>
+      <c r="M28" s="144"/>
+      <c r="N28" s="135"/>
+      <c r="O28" s="144"/>
+      <c r="P28" s="144"/>
+      <c r="Q28" s="144"/>
+      <c r="R28" s="144"/>
+      <c r="S28" s="144"/>
+      <c r="T28" s="144"/>
+      <c r="U28" s="144"/>
+      <c r="V28" s="144"/>
+      <c r="W28" s="144"/>
+      <c r="X28" s="144"/>
+      <c r="Y28" s="144"/>
+      <c r="Z28" s="144"/>
+      <c r="AA28" s="144"/>
+      <c r="AB28" s="144"/>
+      <c r="AC28" s="144"/>
+      <c r="AD28" s="144"/>
+      <c r="AE28" s="144"/>
+      <c r="AF28" s="144"/>
+      <c r="AG28" s="144"/>
+      <c r="AH28" s="144"/>
     </row>
   </sheetData>
   <mergeCells count="37">
@@ -4652,14 +4649,14 @@
       <c r="K1" s="24"/>
       <c r="L1" s="24"/>
       <c r="M1" s="24"/>
-      <c r="N1" s="100"/>
+      <c r="N1" s="101"/>
       <c r="O1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="P1" s="78"/>
-      <c r="Q1" s="78"/>
-      <c r="R1" s="78"/>
-      <c r="S1" s="78"/>
+      <c r="P1" s="79"/>
+      <c r="Q1" s="79"/>
+      <c r="R1" s="79"/>
+      <c r="S1" s="79"/>
       <c r="T1" s="26" t="s">
         <v>3</v>
       </c>
@@ -4670,10 +4667,10 @@
       <c r="W1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="X1" s="154" t="s">
+      <c r="X1" s="155" t="s">
         <v>12</v>
       </c>
-      <c r="Y1" s="112"/>
+      <c r="Y1" s="113"/>
     </row>
     <row r="2" customHeight="1" spans="1:25">
       <c r="A2" s="6"/>
@@ -4689,18 +4686,18 @@
       <c r="K2" s="32"/>
       <c r="L2" s="32"/>
       <c r="M2" s="32"/>
-      <c r="N2" s="101"/>
+      <c r="N2" s="102"/>
       <c r="O2" s="33"/>
-      <c r="P2" s="79"/>
-      <c r="Q2" s="79"/>
-      <c r="R2" s="79"/>
-      <c r="S2" s="79"/>
+      <c r="P2" s="80"/>
+      <c r="Q2" s="80"/>
+      <c r="R2" s="80"/>
+      <c r="S2" s="80"/>
       <c r="T2" s="26"/>
       <c r="U2" s="34"/>
-      <c r="V2" s="80"/>
+      <c r="V2" s="81"/>
       <c r="W2" s="35"/>
       <c r="X2" s="36"/>
-      <c r="Y2" s="113"/>
+      <c r="Y2" s="114"/>
     </row>
     <row r="3" customHeight="1" spans="1:25">
       <c r="A3" s="6"/>
@@ -4718,14 +4715,14 @@
       <c r="K3" s="24"/>
       <c r="L3" s="24"/>
       <c r="M3" s="24"/>
-      <c r="N3" s="100"/>
+      <c r="N3" s="101"/>
       <c r="O3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="P3" s="78"/>
-      <c r="Q3" s="78"/>
-      <c r="R3" s="78"/>
-      <c r="S3" s="78"/>
+      <c r="P3" s="79"/>
+      <c r="Q3" s="79"/>
+      <c r="R3" s="79"/>
+      <c r="S3" s="79"/>
       <c r="T3" s="26" t="s">
         <v>15</v>
       </c>
@@ -4736,10 +4733,10 @@
       <c r="W3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="X3" s="154" t="s">
+      <c r="X3" s="155" t="s">
         <v>18</v>
       </c>
-      <c r="Y3" s="112"/>
+      <c r="Y3" s="113"/>
     </row>
     <row r="4" customHeight="1" spans="1:25">
       <c r="A4" s="8"/>
@@ -4755,18 +4752,18 @@
       <c r="K4" s="32"/>
       <c r="L4" s="32"/>
       <c r="M4" s="32"/>
-      <c r="N4" s="101"/>
+      <c r="N4" s="102"/>
       <c r="O4" s="33"/>
-      <c r="P4" s="79"/>
-      <c r="Q4" s="79"/>
-      <c r="R4" s="79"/>
-      <c r="S4" s="79"/>
+      <c r="P4" s="80"/>
+      <c r="Q4" s="80"/>
+      <c r="R4" s="80"/>
+      <c r="S4" s="80"/>
       <c r="T4" s="26"/>
       <c r="U4" s="34"/>
-      <c r="V4" s="80"/>
+      <c r="V4" s="81"/>
       <c r="W4" s="26"/>
       <c r="X4" s="36"/>
-      <c r="Y4" s="113"/>
+      <c r="Y4" s="114"/>
     </row>
     <row r="5" s="1" customFormat="1" customHeight="1" spans="1:25">
       <c r="A5" s="10" t="s">
@@ -4808,7 +4805,7 @@
       <c r="Y5" s="11"/>
     </row>
     <row r="6" s="2" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A6" s="77" t="s">
+      <c r="A6" s="78" t="s">
         <v>47</v>
       </c>
     </row>
@@ -4826,15 +4823,15 @@
       <c r="G7" s="26"/>
       <c r="H7" s="26"/>
       <c r="I7" s="26"/>
-      <c r="J7" s="102" t="s">
+      <c r="J7" s="103" t="s">
         <v>49</v>
       </c>
-      <c r="K7" s="103" t="s">
+      <c r="K7" s="104" t="s">
         <v>50</v>
       </c>
-      <c r="L7" s="104"/>
-      <c r="M7" s="104"/>
-      <c r="N7" s="105"/>
+      <c r="L7" s="105"/>
+      <c r="M7" s="105"/>
+      <c r="N7" s="106"/>
       <c r="O7" s="26" t="s">
         <v>51</v>
       </c>
@@ -4845,60 +4842,60 @@
         <v>52</v>
       </c>
       <c r="T7" s="26"/>
-      <c r="U7" s="103" t="s">
+      <c r="U7" s="104" t="s">
         <v>53</v>
       </c>
-      <c r="V7" s="104"/>
-      <c r="W7" s="104"/>
-      <c r="X7" s="104"/>
-      <c r="Y7" s="104"/>
+      <c r="V7" s="105"/>
+      <c r="W7" s="105"/>
+      <c r="X7" s="105"/>
+      <c r="Y7" s="105"/>
     </row>
     <row r="8" s="2" customFormat="1" customHeight="1" spans="1:25">
-      <c r="A8" s="66">
+      <c r="A8" s="69">
         <v>1</v>
       </c>
-      <c r="B8" s="97" t="s">
+      <c r="B8" s="98" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="97"/>
-      <c r="D8" s="97"/>
-      <c r="E8" s="97"/>
-      <c r="F8" s="97"/>
-      <c r="G8" s="97"/>
-      <c r="H8" s="97"/>
-      <c r="I8" s="97"/>
-      <c r="J8" s="97" t="s">
+      <c r="C8" s="98"/>
+      <c r="D8" s="98"/>
+      <c r="E8" s="98"/>
+      <c r="F8" s="98"/>
+      <c r="G8" s="98"/>
+      <c r="H8" s="98"/>
+      <c r="I8" s="98"/>
+      <c r="J8" s="98" t="s">
         <v>55</v>
       </c>
-      <c r="K8" s="67" t="s">
+      <c r="K8" s="70" t="s">
         <v>56</v>
       </c>
-      <c r="L8" s="91"/>
-      <c r="M8" s="91"/>
-      <c r="N8" s="70"/>
-      <c r="O8" s="66">
+      <c r="L8" s="92"/>
+      <c r="M8" s="92"/>
+      <c r="N8" s="73"/>
+      <c r="O8" s="69">
         <v>4000</v>
       </c>
-      <c r="P8" s="66"/>
-      <c r="Q8" s="66"/>
-      <c r="R8" s="66"/>
-      <c r="S8" s="66" t="s">
+      <c r="P8" s="69"/>
+      <c r="Q8" s="69"/>
+      <c r="R8" s="69"/>
+      <c r="S8" s="69" t="s">
         <v>57</v>
       </c>
-      <c r="T8" s="66"/>
-      <c r="U8" s="67" t="s">
+      <c r="T8" s="69"/>
+      <c r="U8" s="70" t="s">
         <v>58</v>
       </c>
-      <c r="V8" s="91"/>
-      <c r="W8" s="91"/>
-      <c r="X8" s="91"/>
-      <c r="Y8" s="91"/>
+      <c r="V8" s="92"/>
+      <c r="W8" s="92"/>
+      <c r="X8" s="92"/>
+      <c r="Y8" s="92"/>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A9" s="77"/>
+      <c r="A9" s="78"/>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="1:1">
-      <c r="A10" s="77" t="s">
+      <c r="A10" s="78" t="s">
         <v>59</v>
       </c>
     </row>
@@ -4929,327 +4926,327 @@
         <v>49</v>
       </c>
       <c r="P11" s="26"/>
-      <c r="Q11" s="102" t="s">
+      <c r="Q11" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="R11" s="102"/>
-      <c r="S11" s="102"/>
-      <c r="T11" s="102"/>
+      <c r="R11" s="103"/>
+      <c r="S11" s="103"/>
+      <c r="T11" s="103"/>
       <c r="U11" s="26" t="s">
         <v>62</v>
       </c>
       <c r="V11" s="26"/>
       <c r="W11" s="26"/>
-      <c r="X11" s="103" t="s">
+      <c r="X11" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="Y11" s="104"/>
+      <c r="Y11" s="105"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A12" s="66">
+      <c r="A12" s="69">
         <v>1</v>
       </c>
-      <c r="B12" s="66" t="s">
+      <c r="B12" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="C12" s="66"/>
-      <c r="D12" s="66"/>
-      <c r="E12" s="66"/>
-      <c r="F12" s="66" t="s">
+      <c r="C12" s="69"/>
+      <c r="D12" s="69"/>
+      <c r="E12" s="69"/>
+      <c r="F12" s="69" t="s">
         <v>65</v>
       </c>
-      <c r="G12" s="66"/>
-      <c r="H12" s="66"/>
-      <c r="I12" s="66"/>
-      <c r="J12" s="66"/>
-      <c r="K12" s="67" t="s">
+      <c r="G12" s="69"/>
+      <c r="H12" s="69"/>
+      <c r="I12" s="69"/>
+      <c r="J12" s="69"/>
+      <c r="K12" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="L12" s="91"/>
-      <c r="M12" s="91"/>
-      <c r="N12" s="70"/>
-      <c r="O12" s="106" t="s">
+      <c r="L12" s="92"/>
+      <c r="M12" s="92"/>
+      <c r="N12" s="73"/>
+      <c r="O12" s="107" t="s">
         <v>55</v>
       </c>
-      <c r="P12" s="107"/>
-      <c r="Q12" s="66" t="s">
+      <c r="P12" s="108"/>
+      <c r="Q12" s="69" t="s">
         <v>64</v>
       </c>
-      <c r="R12" s="66"/>
-      <c r="S12" s="66"/>
-      <c r="T12" s="66"/>
-      <c r="U12" s="108" t="s">
+      <c r="R12" s="69"/>
+      <c r="S12" s="69"/>
+      <c r="T12" s="69"/>
+      <c r="U12" s="109" t="s">
         <v>67</v>
       </c>
-      <c r="V12" s="66"/>
-      <c r="W12" s="66"/>
-      <c r="X12" s="66" t="s">
+      <c r="V12" s="69"/>
+      <c r="W12" s="69"/>
+      <c r="X12" s="69" t="s">
         <v>68</v>
       </c>
-      <c r="Y12" s="66"/>
+      <c r="Y12" s="69"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A13" s="66">
+      <c r="A13" s="69">
         <v>2</v>
       </c>
-      <c r="B13" s="66" t="s">
+      <c r="B13" s="69" t="s">
         <v>69</v>
       </c>
-      <c r="C13" s="66"/>
-      <c r="D13" s="66"/>
-      <c r="E13" s="66"/>
-      <c r="F13" s="98" t="s">
+      <c r="C13" s="69"/>
+      <c r="D13" s="69"/>
+      <c r="E13" s="69"/>
+      <c r="F13" s="99" t="s">
         <v>70</v>
       </c>
-      <c r="G13" s="98"/>
-      <c r="H13" s="98"/>
-      <c r="I13" s="98"/>
-      <c r="J13" s="98"/>
-      <c r="K13" s="67" t="s">
+      <c r="G13" s="99"/>
+      <c r="H13" s="99"/>
+      <c r="I13" s="99"/>
+      <c r="J13" s="99"/>
+      <c r="K13" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="L13" s="91"/>
-      <c r="M13" s="91"/>
-      <c r="N13" s="70"/>
-      <c r="O13" s="106" t="s">
+      <c r="L13" s="92"/>
+      <c r="M13" s="92"/>
+      <c r="N13" s="73"/>
+      <c r="O13" s="107" t="s">
         <v>55</v>
       </c>
-      <c r="P13" s="107"/>
-      <c r="Q13" s="156" t="s">
+      <c r="P13" s="108"/>
+      <c r="Q13" s="157" t="s">
         <v>71</v>
       </c>
-      <c r="R13" s="66"/>
-      <c r="S13" s="66"/>
-      <c r="T13" s="66"/>
-      <c r="U13" s="108" t="s">
+      <c r="R13" s="69"/>
+      <c r="S13" s="69"/>
+      <c r="T13" s="69"/>
+      <c r="U13" s="109" t="s">
         <v>72</v>
       </c>
-      <c r="V13" s="66"/>
-      <c r="W13" s="66"/>
-      <c r="X13" s="66" t="s">
+      <c r="V13" s="69"/>
+      <c r="W13" s="69"/>
+      <c r="X13" s="69" t="s">
         <v>73</v>
       </c>
-      <c r="Y13" s="66"/>
+      <c r="Y13" s="69"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A14" s="66">
+      <c r="A14" s="69">
         <v>3</v>
       </c>
-      <c r="B14" s="156" t="s">
+      <c r="B14" s="157" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="66"/>
-      <c r="D14" s="66"/>
-      <c r="E14" s="66"/>
-      <c r="F14" s="66" t="s">
+      <c r="C14" s="69"/>
+      <c r="D14" s="69"/>
+      <c r="E14" s="69"/>
+      <c r="F14" s="69" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="66"/>
-      <c r="H14" s="66"/>
-      <c r="I14" s="66"/>
-      <c r="J14" s="66"/>
-      <c r="K14" s="67" t="s">
+      <c r="G14" s="69"/>
+      <c r="H14" s="69"/>
+      <c r="I14" s="69"/>
+      <c r="J14" s="69"/>
+      <c r="K14" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="L14" s="91"/>
-      <c r="M14" s="91"/>
-      <c r="N14" s="70"/>
-      <c r="O14" s="106" t="s">
+      <c r="L14" s="92"/>
+      <c r="M14" s="92"/>
+      <c r="N14" s="73"/>
+      <c r="O14" s="107" t="s">
         <v>55</v>
       </c>
-      <c r="P14" s="107"/>
-      <c r="Q14" s="66" t="s">
+      <c r="P14" s="108"/>
+      <c r="Q14" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="R14" s="66"/>
-      <c r="S14" s="66"/>
-      <c r="T14" s="66"/>
-      <c r="U14" s="108"/>
-      <c r="V14" s="66"/>
-      <c r="W14" s="66"/>
-      <c r="X14" s="109" t="s">
+      <c r="R14" s="69"/>
+      <c r="S14" s="69"/>
+      <c r="T14" s="69"/>
+      <c r="U14" s="109"/>
+      <c r="V14" s="69"/>
+      <c r="W14" s="69"/>
+      <c r="X14" s="110" t="s">
         <v>77</v>
       </c>
-      <c r="Y14" s="114"/>
+      <c r="Y14" s="115"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A15" s="66">
+      <c r="A15" s="69">
         <v>4</v>
       </c>
-      <c r="B15" s="66" t="s">
+      <c r="B15" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="C15" s="66"/>
-      <c r="D15" s="66"/>
-      <c r="E15" s="66"/>
-      <c r="F15" s="66" t="s">
+      <c r="C15" s="69"/>
+      <c r="D15" s="69"/>
+      <c r="E15" s="69"/>
+      <c r="F15" s="69" t="s">
         <v>79</v>
       </c>
-      <c r="G15" s="66"/>
-      <c r="H15" s="66"/>
-      <c r="I15" s="66"/>
-      <c r="J15" s="66"/>
-      <c r="K15" s="67" t="s">
+      <c r="G15" s="69"/>
+      <c r="H15" s="69"/>
+      <c r="I15" s="69"/>
+      <c r="J15" s="69"/>
+      <c r="K15" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="L15" s="91"/>
-      <c r="M15" s="91"/>
-      <c r="N15" s="70"/>
-      <c r="O15" s="106" t="s">
+      <c r="L15" s="92"/>
+      <c r="M15" s="92"/>
+      <c r="N15" s="73"/>
+      <c r="O15" s="107" t="s">
         <v>55</v>
       </c>
-      <c r="P15" s="107"/>
-      <c r="Q15" s="66" t="s">
+      <c r="P15" s="108"/>
+      <c r="Q15" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="R15" s="66"/>
-      <c r="S15" s="66"/>
-      <c r="T15" s="66"/>
-      <c r="U15" s="66"/>
-      <c r="V15" s="66"/>
-      <c r="W15" s="66"/>
-      <c r="X15" s="67" t="s">
+      <c r="R15" s="69"/>
+      <c r="S15" s="69"/>
+      <c r="T15" s="69"/>
+      <c r="U15" s="69"/>
+      <c r="V15" s="69"/>
+      <c r="W15" s="69"/>
+      <c r="X15" s="70" t="s">
         <v>80</v>
       </c>
-      <c r="Y15" s="70"/>
+      <c r="Y15" s="73"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A16" s="66">
+      <c r="A16" s="69">
         <v>5</v>
       </c>
-      <c r="B16" s="66" t="s">
+      <c r="B16" s="69" t="s">
         <v>81</v>
       </c>
-      <c r="C16" s="66"/>
-      <c r="D16" s="66"/>
-      <c r="E16" s="66"/>
-      <c r="F16" s="66" t="s">
+      <c r="C16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69" t="s">
         <v>82</v>
       </c>
-      <c r="G16" s="66"/>
-      <c r="H16" s="66"/>
-      <c r="I16" s="66"/>
-      <c r="J16" s="66"/>
-      <c r="K16" s="67" t="s">
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
+      <c r="I16" s="69"/>
+      <c r="J16" s="69"/>
+      <c r="K16" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="L16" s="91"/>
-      <c r="M16" s="91"/>
-      <c r="N16" s="70"/>
-      <c r="O16" s="106" t="s">
+      <c r="L16" s="92"/>
+      <c r="M16" s="92"/>
+      <c r="N16" s="73"/>
+      <c r="O16" s="107" t="s">
         <v>55</v>
       </c>
-      <c r="P16" s="107"/>
-      <c r="Q16" s="66" t="s">
+      <c r="P16" s="108"/>
+      <c r="Q16" s="69" t="s">
         <v>83</v>
       </c>
-      <c r="R16" s="66"/>
-      <c r="S16" s="66"/>
-      <c r="T16" s="66"/>
-      <c r="U16" s="66"/>
-      <c r="V16" s="66"/>
-      <c r="W16" s="66"/>
-      <c r="X16" s="67" t="s">
+      <c r="R16" s="69"/>
+      <c r="S16" s="69"/>
+      <c r="T16" s="69"/>
+      <c r="U16" s="69"/>
+      <c r="V16" s="69"/>
+      <c r="W16" s="69"/>
+      <c r="X16" s="70" t="s">
         <v>84</v>
       </c>
-      <c r="Y16" s="70"/>
+      <c r="Y16" s="73"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A17" s="66">
+      <c r="A17" s="69">
         <v>6</v>
       </c>
-      <c r="B17" s="66" t="s">
+      <c r="B17" s="69" t="s">
         <v>85</v>
       </c>
-      <c r="C17" s="66"/>
-      <c r="D17" s="66"/>
-      <c r="E17" s="66"/>
-      <c r="F17" s="66" t="s">
+      <c r="C17" s="69"/>
+      <c r="D17" s="69"/>
+      <c r="E17" s="69"/>
+      <c r="F17" s="69" t="s">
         <v>86</v>
       </c>
-      <c r="G17" s="66"/>
-      <c r="H17" s="66"/>
-      <c r="I17" s="66"/>
-      <c r="J17" s="66"/>
-      <c r="K17" s="67" t="s">
+      <c r="G17" s="69"/>
+      <c r="H17" s="69"/>
+      <c r="I17" s="69"/>
+      <c r="J17" s="69"/>
+      <c r="K17" s="70" t="s">
         <v>87</v>
       </c>
-      <c r="L17" s="91"/>
-      <c r="M17" s="91"/>
-      <c r="N17" s="70"/>
-      <c r="O17" s="106" t="s">
+      <c r="L17" s="92"/>
+      <c r="M17" s="92"/>
+      <c r="N17" s="73"/>
+      <c r="O17" s="107" t="s">
         <v>55</v>
       </c>
-      <c r="P17" s="107"/>
-      <c r="Q17" s="110" t="s">
+      <c r="P17" s="108"/>
+      <c r="Q17" s="111" t="s">
         <v>88</v>
       </c>
-      <c r="R17" s="91"/>
-      <c r="S17" s="91"/>
-      <c r="T17" s="91"/>
-      <c r="U17" s="91"/>
-      <c r="V17" s="91"/>
-      <c r="W17" s="70"/>
-      <c r="X17" s="67" t="s">
+      <c r="R17" s="92"/>
+      <c r="S17" s="92"/>
+      <c r="T17" s="92"/>
+      <c r="U17" s="92"/>
+      <c r="V17" s="92"/>
+      <c r="W17" s="73"/>
+      <c r="X17" s="70" t="s">
         <v>89</v>
       </c>
-      <c r="Y17" s="70"/>
+      <c r="Y17" s="73"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A18" s="99"/>
-      <c r="B18" s="63"/>
-      <c r="C18" s="63"/>
-      <c r="D18" s="63"/>
-      <c r="E18" s="63"/>
-      <c r="F18" s="63"/>
-      <c r="G18" s="63"/>
-      <c r="H18" s="63"/>
-      <c r="I18" s="63"/>
-      <c r="J18" s="63"/>
-      <c r="K18" s="63"/>
-      <c r="L18" s="63"/>
-      <c r="M18" s="63"/>
-      <c r="N18" s="63"/>
+      <c r="A18" s="100"/>
+      <c r="B18" s="65"/>
+      <c r="C18" s="65"/>
+      <c r="D18" s="65"/>
+      <c r="E18" s="65"/>
+      <c r="F18" s="65"/>
+      <c r="G18" s="65"/>
+      <c r="H18" s="65"/>
+      <c r="I18" s="65"/>
+      <c r="J18" s="65"/>
+      <c r="K18" s="65"/>
+      <c r="L18" s="65"/>
+      <c r="M18" s="65"/>
+      <c r="N18" s="65"/>
       <c r="O18" s="18"/>
       <c r="P18" s="18"/>
-      <c r="Q18" s="63"/>
-      <c r="R18" s="63"/>
-      <c r="S18" s="63"/>
-      <c r="T18" s="63"/>
-      <c r="U18" s="63"/>
-      <c r="V18" s="63"/>
-      <c r="W18" s="63"/>
-      <c r="X18" s="63"/>
-      <c r="Y18" s="63"/>
+      <c r="Q18" s="65"/>
+      <c r="R18" s="65"/>
+      <c r="S18" s="65"/>
+      <c r="T18" s="65"/>
+      <c r="U18" s="65"/>
+      <c r="V18" s="65"/>
+      <c r="W18" s="65"/>
+      <c r="X18" s="65"/>
+      <c r="Y18" s="65"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A19" s="99" t="s">
+      <c r="A19" s="100" t="s">
         <v>90</v>
       </c>
-      <c r="B19" s="63"/>
-      <c r="C19" s="63"/>
-      <c r="D19" s="63"/>
-      <c r="E19" s="63"/>
-      <c r="F19" s="63"/>
-      <c r="G19" s="63"/>
-      <c r="H19" s="63"/>
-      <c r="I19" s="63"/>
-      <c r="J19" s="63"/>
-      <c r="K19" s="63"/>
-      <c r="L19" s="63"/>
-      <c r="M19" s="63"/>
-      <c r="N19" s="63"/>
+      <c r="B19" s="65"/>
+      <c r="C19" s="65"/>
+      <c r="D19" s="65"/>
+      <c r="E19" s="65"/>
+      <c r="F19" s="65"/>
+      <c r="G19" s="65"/>
+      <c r="H19" s="65"/>
+      <c r="I19" s="65"/>
+      <c r="J19" s="65"/>
+      <c r="K19" s="65"/>
+      <c r="L19" s="65"/>
+      <c r="M19" s="65"/>
+      <c r="N19" s="65"/>
       <c r="O19" s="18"/>
       <c r="P19" s="18"/>
-      <c r="Q19" s="63"/>
-      <c r="R19" s="63"/>
-      <c r="S19" s="63"/>
-      <c r="T19" s="63"/>
-      <c r="U19" s="63"/>
-      <c r="V19" s="63"/>
-      <c r="W19" s="63"/>
-      <c r="X19" s="63"/>
-      <c r="Y19" s="63"/>
+      <c r="Q19" s="65"/>
+      <c r="R19" s="65"/>
+      <c r="S19" s="65"/>
+      <c r="T19" s="65"/>
+      <c r="U19" s="65"/>
+      <c r="V19" s="65"/>
+      <c r="W19" s="65"/>
+      <c r="X19" s="65"/>
+      <c r="Y19" s="65"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="16.5" spans="1:25">
       <c r="A20" s="26" t="s">
@@ -5278,278 +5275,278 @@
         <v>49</v>
       </c>
       <c r="P20" s="26"/>
-      <c r="Q20" s="102" t="s">
+      <c r="Q20" s="103" t="s">
         <v>52</v>
       </c>
-      <c r="R20" s="102"/>
-      <c r="S20" s="102"/>
-      <c r="T20" s="102"/>
+      <c r="R20" s="103"/>
+      <c r="S20" s="103"/>
+      <c r="T20" s="103"/>
       <c r="U20" s="26" t="s">
         <v>62</v>
       </c>
       <c r="V20" s="26"/>
       <c r="W20" s="26"/>
-      <c r="X20" s="103" t="s">
+      <c r="X20" s="104" t="s">
         <v>63</v>
       </c>
-      <c r="Y20" s="104"/>
+      <c r="Y20" s="105"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A21" s="66">
+      <c r="A21" s="69">
         <v>1</v>
       </c>
-      <c r="B21" s="66" t="s">
+      <c r="B21" s="69" t="s">
         <v>91</v>
       </c>
-      <c r="C21" s="66"/>
-      <c r="D21" s="66"/>
-      <c r="E21" s="66"/>
-      <c r="F21" s="98" t="s">
+      <c r="C21" s="69"/>
+      <c r="D21" s="69"/>
+      <c r="E21" s="69"/>
+      <c r="F21" s="99" t="s">
         <v>92</v>
       </c>
-      <c r="G21" s="98"/>
-      <c r="H21" s="98"/>
-      <c r="I21" s="98"/>
-      <c r="J21" s="98"/>
-      <c r="K21" s="67" t="s">
+      <c r="G21" s="99"/>
+      <c r="H21" s="99"/>
+      <c r="I21" s="99"/>
+      <c r="J21" s="99"/>
+      <c r="K21" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="L21" s="91"/>
-      <c r="M21" s="91"/>
-      <c r="N21" s="70"/>
-      <c r="O21" s="106"/>
-      <c r="P21" s="107"/>
-      <c r="Q21" s="66" t="s">
+      <c r="L21" s="92"/>
+      <c r="M21" s="92"/>
+      <c r="N21" s="73"/>
+      <c r="O21" s="107"/>
+      <c r="P21" s="108"/>
+      <c r="Q21" s="69" t="s">
         <v>94</v>
       </c>
-      <c r="R21" s="66"/>
-      <c r="S21" s="66"/>
-      <c r="T21" s="66"/>
-      <c r="U21" s="66" t="s">
+      <c r="R21" s="69"/>
+      <c r="S21" s="69"/>
+      <c r="T21" s="69"/>
+      <c r="U21" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="V21" s="66"/>
-      <c r="W21" s="66"/>
-      <c r="X21" s="111">
+      <c r="V21" s="69"/>
+      <c r="W21" s="69"/>
+      <c r="X21" s="112">
         <v>5</v>
       </c>
-      <c r="Y21" s="115"/>
+      <c r="Y21" s="116"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A22" s="66">
+      <c r="A22" s="69">
         <v>2</v>
       </c>
-      <c r="B22" s="66" t="s">
+      <c r="B22" s="69" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="66"/>
-      <c r="D22" s="66"/>
-      <c r="E22" s="66"/>
-      <c r="F22" s="66" t="s">
+      <c r="C22" s="69"/>
+      <c r="D22" s="69"/>
+      <c r="E22" s="69"/>
+      <c r="F22" s="69" t="s">
         <v>96</v>
       </c>
-      <c r="G22" s="66"/>
-      <c r="H22" s="66"/>
-      <c r="I22" s="66"/>
-      <c r="J22" s="66"/>
-      <c r="K22" s="67" t="s">
+      <c r="G22" s="69"/>
+      <c r="H22" s="69"/>
+      <c r="I22" s="69"/>
+      <c r="J22" s="69"/>
+      <c r="K22" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="L22" s="91"/>
-      <c r="M22" s="91"/>
-      <c r="N22" s="70"/>
-      <c r="O22" s="106" t="s">
+      <c r="L22" s="92"/>
+      <c r="M22" s="92"/>
+      <c r="N22" s="73"/>
+      <c r="O22" s="107" t="s">
         <v>55</v>
       </c>
-      <c r="P22" s="107"/>
-      <c r="Q22" s="156" t="s">
+      <c r="P22" s="108"/>
+      <c r="Q22" s="157" t="s">
         <v>97</v>
       </c>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66"/>
-      <c r="U22" s="66" t="s">
+      <c r="R22" s="69"/>
+      <c r="S22" s="69"/>
+      <c r="T22" s="69"/>
+      <c r="U22" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="V22" s="66"/>
-      <c r="W22" s="66"/>
-      <c r="X22" s="66">
+      <c r="V22" s="69"/>
+      <c r="W22" s="69"/>
+      <c r="X22" s="69">
         <v>2</v>
       </c>
-      <c r="Y22" s="66"/>
+      <c r="Y22" s="69"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A23" s="66">
+      <c r="A23" s="69">
         <v>3</v>
       </c>
-      <c r="B23" s="66" t="s">
+      <c r="B23" s="69" t="s">
         <v>98</v>
       </c>
-      <c r="C23" s="66"/>
-      <c r="D23" s="66"/>
-      <c r="E23" s="66"/>
-      <c r="F23" s="66" t="s">
+      <c r="C23" s="69"/>
+      <c r="D23" s="69"/>
+      <c r="E23" s="69"/>
+      <c r="F23" s="69" t="s">
         <v>99</v>
       </c>
-      <c r="G23" s="66"/>
-      <c r="H23" s="66"/>
-      <c r="I23" s="66"/>
-      <c r="J23" s="66"/>
-      <c r="K23" s="67" t="s">
+      <c r="G23" s="69"/>
+      <c r="H23" s="69"/>
+      <c r="I23" s="69"/>
+      <c r="J23" s="69"/>
+      <c r="K23" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="L23" s="91"/>
-      <c r="M23" s="91"/>
-      <c r="N23" s="70"/>
-      <c r="O23" s="106" t="s">
+      <c r="L23" s="92"/>
+      <c r="M23" s="92"/>
+      <c r="N23" s="73"/>
+      <c r="O23" s="107" t="s">
         <v>55</v>
       </c>
-      <c r="P23" s="107"/>
-      <c r="Q23" s="156" t="s">
+      <c r="P23" s="108"/>
+      <c r="Q23" s="157" t="s">
         <v>97</v>
       </c>
-      <c r="R23" s="66"/>
-      <c r="S23" s="66"/>
-      <c r="T23" s="66"/>
-      <c r="U23" s="66" t="s">
+      <c r="R23" s="69"/>
+      <c r="S23" s="69"/>
+      <c r="T23" s="69"/>
+      <c r="U23" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="V23" s="66"/>
-      <c r="W23" s="66"/>
-      <c r="X23" s="111">
+      <c r="V23" s="69"/>
+      <c r="W23" s="69"/>
+      <c r="X23" s="112">
         <v>1</v>
       </c>
-      <c r="Y23" s="115"/>
+      <c r="Y23" s="116"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A24" s="66">
+      <c r="A24" s="69">
         <v>4</v>
       </c>
-      <c r="B24" s="66" t="s">
+      <c r="B24" s="69" t="s">
         <v>100</v>
       </c>
-      <c r="C24" s="66"/>
-      <c r="D24" s="66"/>
-      <c r="E24" s="66"/>
-      <c r="F24" s="98" t="s">
+      <c r="C24" s="69"/>
+      <c r="D24" s="69"/>
+      <c r="E24" s="69"/>
+      <c r="F24" s="99" t="s">
         <v>101</v>
       </c>
-      <c r="G24" s="98"/>
-      <c r="H24" s="98"/>
-      <c r="I24" s="98"/>
-      <c r="J24" s="98"/>
-      <c r="K24" s="67" t="s">
+      <c r="G24" s="99"/>
+      <c r="H24" s="99"/>
+      <c r="I24" s="99"/>
+      <c r="J24" s="99"/>
+      <c r="K24" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="L24" s="91"/>
-      <c r="M24" s="91"/>
-      <c r="N24" s="70"/>
-      <c r="O24" s="106" t="s">
+      <c r="L24" s="92"/>
+      <c r="M24" s="92"/>
+      <c r="N24" s="73"/>
+      <c r="O24" s="107" t="s">
         <v>55</v>
       </c>
-      <c r="P24" s="107"/>
-      <c r="Q24" s="66" t="s">
+      <c r="P24" s="108"/>
+      <c r="Q24" s="69" t="s">
         <v>100</v>
       </c>
-      <c r="R24" s="66"/>
-      <c r="S24" s="66"/>
-      <c r="T24" s="66"/>
-      <c r="U24" s="66" t="s">
+      <c r="R24" s="69"/>
+      <c r="S24" s="69"/>
+      <c r="T24" s="69"/>
+      <c r="U24" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="V24" s="66"/>
-      <c r="W24" s="66"/>
-      <c r="X24" s="66" t="s">
+      <c r="V24" s="69"/>
+      <c r="W24" s="69"/>
+      <c r="X24" s="69" t="s">
         <v>102</v>
       </c>
-      <c r="Y24" s="66"/>
+      <c r="Y24" s="69"/>
     </row>
     <row r="25" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A25" s="66">
+      <c r="A25" s="69">
         <v>5</v>
       </c>
-      <c r="B25" s="66" t="s">
+      <c r="B25" s="69" t="s">
         <v>103</v>
       </c>
-      <c r="C25" s="66"/>
-      <c r="D25" s="66"/>
-      <c r="E25" s="66"/>
-      <c r="F25" s="66" t="s">
+      <c r="C25" s="69"/>
+      <c r="D25" s="69"/>
+      <c r="E25" s="69"/>
+      <c r="F25" s="69" t="s">
         <v>104</v>
       </c>
-      <c r="G25" s="66"/>
-      <c r="H25" s="66"/>
-      <c r="I25" s="66"/>
-      <c r="J25" s="66"/>
-      <c r="K25" s="67" t="s">
+      <c r="G25" s="69"/>
+      <c r="H25" s="69"/>
+      <c r="I25" s="69"/>
+      <c r="J25" s="69"/>
+      <c r="K25" s="70" t="s">
         <v>93</v>
       </c>
-      <c r="L25" s="91"/>
-      <c r="M25" s="91"/>
-      <c r="N25" s="70"/>
-      <c r="O25" s="106" t="s">
+      <c r="L25" s="92"/>
+      <c r="M25" s="92"/>
+      <c r="N25" s="73"/>
+      <c r="O25" s="107" t="s">
         <v>55</v>
       </c>
-      <c r="P25" s="107"/>
-      <c r="Q25" s="66"/>
-      <c r="R25" s="66"/>
-      <c r="S25" s="66"/>
-      <c r="T25" s="66"/>
-      <c r="U25" s="66" t="s">
+      <c r="P25" s="108"/>
+      <c r="Q25" s="69"/>
+      <c r="R25" s="69"/>
+      <c r="S25" s="69"/>
+      <c r="T25" s="69"/>
+      <c r="U25" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="V25" s="66"/>
-      <c r="W25" s="66"/>
-      <c r="X25" s="109">
+      <c r="V25" s="69"/>
+      <c r="W25" s="69"/>
+      <c r="X25" s="110">
         <v>20</v>
       </c>
-      <c r="Y25" s="114"/>
+      <c r="Y25" s="115"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A26" s="66">
+      <c r="A26" s="69">
         <v>6</v>
       </c>
-      <c r="B26" s="66" t="s">
+      <c r="B26" s="69" t="s">
         <v>105</v>
       </c>
-      <c r="C26" s="66"/>
-      <c r="D26" s="66"/>
-      <c r="E26" s="66"/>
-      <c r="F26" s="66" t="s">
+      <c r="C26" s="69"/>
+      <c r="D26" s="69"/>
+      <c r="E26" s="69"/>
+      <c r="F26" s="69" t="s">
         <v>106</v>
       </c>
-      <c r="G26" s="66"/>
-      <c r="H26" s="66"/>
-      <c r="I26" s="66"/>
-      <c r="J26" s="66"/>
-      <c r="K26" s="67" t="s">
+      <c r="G26" s="69"/>
+      <c r="H26" s="69"/>
+      <c r="I26" s="69"/>
+      <c r="J26" s="69"/>
+      <c r="K26" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="L26" s="91"/>
-      <c r="M26" s="91"/>
-      <c r="N26" s="70"/>
-      <c r="O26" s="106"/>
-      <c r="P26" s="107"/>
-      <c r="Q26" s="66" t="s">
+      <c r="L26" s="92"/>
+      <c r="M26" s="92"/>
+      <c r="N26" s="73"/>
+      <c r="O26" s="107"/>
+      <c r="P26" s="108"/>
+      <c r="Q26" s="69" t="s">
         <v>107</v>
       </c>
-      <c r="R26" s="66"/>
-      <c r="S26" s="66"/>
-      <c r="T26" s="66"/>
-      <c r="U26" s="66" t="s">
+      <c r="R26" s="69"/>
+      <c r="S26" s="69"/>
+      <c r="T26" s="69"/>
+      <c r="U26" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="V26" s="66"/>
-      <c r="W26" s="66"/>
-      <c r="X26" s="67" t="s">
+      <c r="V26" s="69"/>
+      <c r="W26" s="69"/>
+      <c r="X26" s="70" t="s">
         <v>108</v>
       </c>
-      <c r="Y26" s="70"/>
+      <c r="Y26" s="73"/>
     </row>
     <row r="27" s="2" customFormat="1" ht="16.5" spans="1:25">
-      <c r="A27" s="99"/>
-      <c r="X27" s="63"/>
-      <c r="Y27" s="63"/>
+      <c r="A27" s="100"/>
+      <c r="X27" s="65"/>
+      <c r="Y27" s="65"/>
     </row>
   </sheetData>
   <mergeCells count="125">
@@ -5728,9 +5725,9 @@
       <c r="M1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
       <c r="Q1" s="26" t="s">
         <v>3</v>
       </c>
@@ -5741,7 +5738,7 @@
       <c r="T1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="154" t="s">
+      <c r="U1" s="155" t="s">
         <v>12</v>
       </c>
       <c r="V1" s="30"/>
@@ -5760,12 +5757,12 @@
       <c r="K2" s="32"/>
       <c r="L2" s="32"/>
       <c r="M2" s="33"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
       <c r="Q2" s="26"/>
       <c r="R2" s="34"/>
-      <c r="S2" s="80"/>
+      <c r="S2" s="81"/>
       <c r="T2" s="35"/>
       <c r="U2" s="36"/>
       <c r="V2" s="37"/>
@@ -5788,9 +5785,9 @@
       <c r="M3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
+      <c r="N3" s="79"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
       <c r="Q3" s="26" t="s">
         <v>15</v>
       </c>
@@ -5801,7 +5798,7 @@
       <c r="T3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="154" t="s">
+      <c r="U3" s="155" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="30"/>
@@ -5820,12 +5817,12 @@
       <c r="K4" s="32"/>
       <c r="L4" s="32"/>
       <c r="M4" s="33"/>
-      <c r="N4" s="79"/>
-      <c r="O4" s="79"/>
-      <c r="P4" s="79"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="80"/>
       <c r="Q4" s="26"/>
       <c r="R4" s="34"/>
-      <c r="S4" s="80"/>
+      <c r="S4" s="81"/>
       <c r="T4" s="26"/>
       <c r="U4" s="36"/>
       <c r="V4" s="37"/>
@@ -5867,7 +5864,7 @@
       <c r="V5" s="11"/>
     </row>
     <row r="6" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A6" s="76"/>
+      <c r="A6" s="77"/>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -5891,177 +5888,177 @@
       <c r="V6" s="18"/>
     </row>
     <row r="7" s="2" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A7" s="82" t="s">
+      <c r="A7" s="83" t="s">
         <v>110</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
-      <c r="D7" s="83"/>
-      <c r="E7" s="83"/>
-      <c r="F7" s="83"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="83"/>
-      <c r="I7" s="83"/>
-      <c r="J7" s="83"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="83"/>
-      <c r="M7" s="83"/>
-      <c r="N7" s="83"/>
-      <c r="O7" s="83"/>
-      <c r="P7" s="83"/>
-      <c r="Q7" s="83"/>
-      <c r="R7" s="83"/>
-      <c r="S7" s="83"/>
-      <c r="T7" s="83"/>
-      <c r="U7" s="83"/>
-      <c r="V7" s="93"/>
+      <c r="B7" s="84"/>
+      <c r="C7" s="84"/>
+      <c r="D7" s="84"/>
+      <c r="E7" s="84"/>
+      <c r="F7" s="84"/>
+      <c r="G7" s="84"/>
+      <c r="H7" s="84"/>
+      <c r="I7" s="84"/>
+      <c r="J7" s="84"/>
+      <c r="K7" s="84"/>
+      <c r="L7" s="84"/>
+      <c r="M7" s="84"/>
+      <c r="N7" s="84"/>
+      <c r="O7" s="84"/>
+      <c r="P7" s="84"/>
+      <c r="Q7" s="84"/>
+      <c r="R7" s="84"/>
+      <c r="S7" s="84"/>
+      <c r="T7" s="84"/>
+      <c r="U7" s="84"/>
+      <c r="V7" s="94"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="B8" s="84" t="s">
+      <c r="B8" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="C8" s="84"/>
-      <c r="D8" s="84"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84"/>
-      <c r="H8" s="84"/>
-      <c r="I8" s="84" t="s">
+      <c r="C8" s="85"/>
+      <c r="D8" s="85"/>
+      <c r="E8" s="85"/>
+      <c r="F8" s="85"/>
+      <c r="G8" s="85"/>
+      <c r="H8" s="85"/>
+      <c r="I8" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="J8" s="84"/>
-      <c r="K8" s="84"/>
-      <c r="L8" s="84"/>
-      <c r="M8" s="84" t="s">
+      <c r="J8" s="85"/>
+      <c r="K8" s="85"/>
+      <c r="L8" s="85"/>
+      <c r="M8" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="N8" s="84"/>
-      <c r="O8" s="84"/>
-      <c r="P8" s="92" t="s">
+      <c r="N8" s="85"/>
+      <c r="O8" s="85"/>
+      <c r="P8" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="Q8" s="92"/>
-      <c r="R8" s="92"/>
-      <c r="S8" s="92"/>
+      <c r="Q8" s="93"/>
+      <c r="R8" s="93"/>
+      <c r="S8" s="93"/>
       <c r="T8" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="U8" s="94"/>
-      <c r="V8" s="95"/>
+      <c r="U8" s="95"/>
+      <c r="V8" s="96"/>
     </row>
     <row r="9" s="2" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A9" s="66">
+      <c r="A9" s="69">
         <v>1</v>
       </c>
-      <c r="B9" s="85" t="s">
+      <c r="B9" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="C9" s="86"/>
-      <c r="D9" s="86"/>
-      <c r="E9" s="86"/>
-      <c r="F9" s="86"/>
-      <c r="G9" s="86"/>
-      <c r="H9" s="86"/>
-      <c r="I9" s="67" t="s">
+      <c r="C9" s="87"/>
+      <c r="D9" s="87"/>
+      <c r="E9" s="87"/>
+      <c r="F9" s="87"/>
+      <c r="G9" s="87"/>
+      <c r="H9" s="87"/>
+      <c r="I9" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="J9" s="91"/>
-      <c r="K9" s="91"/>
-      <c r="L9" s="70"/>
-      <c r="M9" s="156" t="s">
+      <c r="J9" s="92"/>
+      <c r="K9" s="92"/>
+      <c r="L9" s="73"/>
+      <c r="M9" s="157" t="s">
         <v>55</v>
       </c>
-      <c r="N9" s="66"/>
-      <c r="O9" s="66"/>
-      <c r="P9" s="156" t="s">
+      <c r="N9" s="69"/>
+      <c r="O9" s="69"/>
+      <c r="P9" s="157" t="s">
         <v>113</v>
       </c>
-      <c r="Q9" s="66"/>
-      <c r="R9" s="66"/>
-      <c r="S9" s="66"/>
-      <c r="T9" s="66" t="s">
+      <c r="Q9" s="69"/>
+      <c r="R9" s="69"/>
+      <c r="S9" s="69"/>
+      <c r="T9" s="69" t="s">
         <v>114</v>
       </c>
-      <c r="U9" s="66"/>
-      <c r="V9" s="66"/>
+      <c r="U9" s="69"/>
+      <c r="V9" s="69"/>
     </row>
     <row r="10" s="2" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A10" s="66">
+      <c r="A10" s="69">
         <v>2</v>
       </c>
-      <c r="B10" s="87" t="s">
+      <c r="B10" s="88" t="s">
         <v>115</v>
       </c>
-      <c r="C10" s="86"/>
-      <c r="D10" s="86"/>
-      <c r="E10" s="86"/>
-      <c r="F10" s="86"/>
-      <c r="G10" s="86"/>
-      <c r="H10" s="86"/>
-      <c r="I10" s="67" t="s">
+      <c r="C10" s="87"/>
+      <c r="D10" s="87"/>
+      <c r="E10" s="87"/>
+      <c r="F10" s="87"/>
+      <c r="G10" s="87"/>
+      <c r="H10" s="87"/>
+      <c r="I10" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="J10" s="91"/>
-      <c r="K10" s="91"/>
-      <c r="L10" s="70"/>
-      <c r="M10" s="156" t="s">
+      <c r="J10" s="92"/>
+      <c r="K10" s="92"/>
+      <c r="L10" s="73"/>
+      <c r="M10" s="157" t="s">
         <v>55</v>
       </c>
-      <c r="N10" s="66"/>
-      <c r="O10" s="66"/>
-      <c r="P10" s="156" t="s">
+      <c r="N10" s="69"/>
+      <c r="O10" s="69"/>
+      <c r="P10" s="157" t="s">
         <v>116</v>
       </c>
-      <c r="Q10" s="66"/>
-      <c r="R10" s="66"/>
-      <c r="S10" s="66"/>
-      <c r="T10" s="66" t="s">
+      <c r="Q10" s="69"/>
+      <c r="R10" s="69"/>
+      <c r="S10" s="69"/>
+      <c r="T10" s="69" t="s">
         <v>117</v>
       </c>
-      <c r="U10" s="66"/>
-      <c r="V10" s="66"/>
-    </row>
-    <row r="11" s="81" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A11" s="66">
+      <c r="U10" s="69"/>
+      <c r="V10" s="69"/>
+    </row>
+    <row r="11" s="82" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A11" s="69">
         <v>3</v>
       </c>
-      <c r="B11" s="87" t="s">
+      <c r="B11" s="88" t="s">
         <v>118</v>
       </c>
-      <c r="C11" s="86"/>
-      <c r="D11" s="86"/>
-      <c r="E11" s="86"/>
-      <c r="F11" s="86"/>
-      <c r="G11" s="86"/>
-      <c r="H11" s="88"/>
-      <c r="I11" s="67" t="s">
+      <c r="C11" s="87"/>
+      <c r="D11" s="87"/>
+      <c r="E11" s="87"/>
+      <c r="F11" s="87"/>
+      <c r="G11" s="87"/>
+      <c r="H11" s="89"/>
+      <c r="I11" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="J11" s="91"/>
-      <c r="K11" s="91"/>
-      <c r="L11" s="70"/>
-      <c r="M11" s="156" t="s">
+      <c r="J11" s="92"/>
+      <c r="K11" s="92"/>
+      <c r="L11" s="73"/>
+      <c r="M11" s="157" t="s">
         <v>55</v>
       </c>
-      <c r="N11" s="66"/>
-      <c r="O11" s="66"/>
-      <c r="P11" s="66" t="s">
+      <c r="N11" s="69"/>
+      <c r="O11" s="69"/>
+      <c r="P11" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="Q11" s="66"/>
-      <c r="R11" s="66"/>
-      <c r="S11" s="66"/>
-      <c r="T11" s="66" t="s">
+      <c r="Q11" s="69"/>
+      <c r="R11" s="69"/>
+      <c r="S11" s="69"/>
+      <c r="T11" s="69" t="s">
         <v>119</v>
       </c>
-      <c r="U11" s="66"/>
-      <c r="V11" s="66"/>
+      <c r="U11" s="69"/>
+      <c r="V11" s="69"/>
     </row>
     <row r="12" s="2" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A12" s="76"/>
+      <c r="A12" s="77"/>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
@@ -6085,278 +6082,278 @@
       <c r="V12" s="18"/>
     </row>
     <row r="13" customHeight="1" spans="1:22">
-      <c r="A13" s="89" t="s">
+      <c r="A13" s="90" t="s">
         <v>120</v>
       </c>
-      <c r="B13" s="90"/>
-      <c r="C13" s="90"/>
-      <c r="D13" s="90"/>
-      <c r="E13" s="90"/>
-      <c r="F13" s="90"/>
-      <c r="G13" s="90"/>
-      <c r="H13" s="90"/>
-      <c r="I13" s="90"/>
-      <c r="J13" s="90"/>
-      <c r="K13" s="90"/>
-      <c r="L13" s="90"/>
-      <c r="M13" s="90"/>
-      <c r="N13" s="90"/>
-      <c r="O13" s="90"/>
-      <c r="P13" s="90"/>
-      <c r="Q13" s="90"/>
-      <c r="R13" s="90"/>
-      <c r="S13" s="90"/>
-      <c r="T13" s="90"/>
-      <c r="U13" s="90"/>
-      <c r="V13" s="96"/>
+      <c r="B13" s="91"/>
+      <c r="C13" s="91"/>
+      <c r="D13" s="91"/>
+      <c r="E13" s="91"/>
+      <c r="F13" s="91"/>
+      <c r="G13" s="91"/>
+      <c r="H13" s="91"/>
+      <c r="I13" s="91"/>
+      <c r="J13" s="91"/>
+      <c r="K13" s="91"/>
+      <c r="L13" s="91"/>
+      <c r="M13" s="91"/>
+      <c r="N13" s="91"/>
+      <c r="O13" s="91"/>
+      <c r="P13" s="91"/>
+      <c r="Q13" s="91"/>
+      <c r="R13" s="91"/>
+      <c r="S13" s="91"/>
+      <c r="T13" s="91"/>
+      <c r="U13" s="91"/>
+      <c r="V13" s="97"/>
     </row>
     <row r="14" customHeight="1" spans="1:22">
-      <c r="A14" s="84" t="s">
+      <c r="A14" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="B14" s="84" t="s">
+      <c r="B14" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="84"/>
-      <c r="D14" s="84"/>
-      <c r="E14" s="84"/>
-      <c r="F14" s="84"/>
-      <c r="G14" s="84"/>
-      <c r="H14" s="84"/>
-      <c r="I14" s="84" t="s">
+      <c r="C14" s="85"/>
+      <c r="D14" s="85"/>
+      <c r="E14" s="85"/>
+      <c r="F14" s="85"/>
+      <c r="G14" s="85"/>
+      <c r="H14" s="85"/>
+      <c r="I14" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="J14" s="84"/>
-      <c r="K14" s="84"/>
-      <c r="L14" s="84"/>
-      <c r="M14" s="84" t="s">
+      <c r="J14" s="85"/>
+      <c r="K14" s="85"/>
+      <c r="L14" s="85"/>
+      <c r="M14" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="N14" s="84"/>
-      <c r="O14" s="84"/>
-      <c r="P14" s="92" t="s">
+      <c r="N14" s="85"/>
+      <c r="O14" s="85"/>
+      <c r="P14" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="Q14" s="92"/>
-      <c r="R14" s="92"/>
-      <c r="S14" s="92"/>
+      <c r="Q14" s="93"/>
+      <c r="R14" s="93"/>
+      <c r="S14" s="93"/>
       <c r="T14" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="U14" s="94"/>
-      <c r="V14" s="95"/>
-    </row>
-    <row r="15" s="81" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A15" s="66">
+      <c r="U14" s="95"/>
+      <c r="V14" s="96"/>
+    </row>
+    <row r="15" s="82" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A15" s="69">
         <v>1</v>
       </c>
-      <c r="B15" s="85" t="s">
+      <c r="B15" s="86" t="s">
         <v>115</v>
       </c>
-      <c r="C15" s="86"/>
-      <c r="D15" s="86"/>
-      <c r="E15" s="86"/>
-      <c r="F15" s="86"/>
-      <c r="G15" s="86"/>
-      <c r="H15" s="86"/>
-      <c r="I15" s="67" t="s">
+      <c r="C15" s="87"/>
+      <c r="D15" s="87"/>
+      <c r="E15" s="87"/>
+      <c r="F15" s="87"/>
+      <c r="G15" s="87"/>
+      <c r="H15" s="87"/>
+      <c r="I15" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="J15" s="91"/>
-      <c r="K15" s="91"/>
-      <c r="L15" s="70"/>
-      <c r="M15" s="156" t="s">
+      <c r="J15" s="92"/>
+      <c r="K15" s="92"/>
+      <c r="L15" s="73"/>
+      <c r="M15" s="157" t="s">
         <v>55</v>
       </c>
-      <c r="N15" s="66"/>
-      <c r="O15" s="66"/>
-      <c r="P15" s="156" t="s">
+      <c r="N15" s="69"/>
+      <c r="O15" s="69"/>
+      <c r="P15" s="157" t="s">
         <v>113</v>
       </c>
-      <c r="Q15" s="66"/>
-      <c r="R15" s="66"/>
-      <c r="S15" s="66"/>
-      <c r="T15" s="66" t="s">
+      <c r="Q15" s="69"/>
+      <c r="R15" s="69"/>
+      <c r="S15" s="69"/>
+      <c r="T15" s="69" t="s">
         <v>121</v>
       </c>
-      <c r="U15" s="66"/>
-      <c r="V15" s="66"/>
-    </row>
-    <row r="16" s="81" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A16" s="66">
+      <c r="U15" s="69"/>
+      <c r="V15" s="69"/>
+    </row>
+    <row r="16" s="82" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A16" s="69">
         <v>2</v>
       </c>
-      <c r="B16" s="85" t="s">
+      <c r="B16" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="C16" s="86"/>
-      <c r="D16" s="86"/>
-      <c r="E16" s="86"/>
-      <c r="F16" s="86"/>
-      <c r="G16" s="86"/>
-      <c r="H16" s="86"/>
-      <c r="I16" s="67" t="s">
+      <c r="C16" s="87"/>
+      <c r="D16" s="87"/>
+      <c r="E16" s="87"/>
+      <c r="F16" s="87"/>
+      <c r="G16" s="87"/>
+      <c r="H16" s="87"/>
+      <c r="I16" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="J16" s="91"/>
-      <c r="K16" s="91"/>
-      <c r="L16" s="70"/>
-      <c r="M16" s="156" t="s">
+      <c r="J16" s="92"/>
+      <c r="K16" s="92"/>
+      <c r="L16" s="73"/>
+      <c r="M16" s="157" t="s">
         <v>55</v>
       </c>
-      <c r="N16" s="66"/>
-      <c r="O16" s="66"/>
-      <c r="P16" s="156" t="s">
+      <c r="N16" s="69"/>
+      <c r="O16" s="69"/>
+      <c r="P16" s="157" t="s">
         <v>122</v>
       </c>
-      <c r="Q16" s="66"/>
-      <c r="R16" s="66"/>
-      <c r="S16" s="66"/>
-      <c r="T16" s="66" t="s">
+      <c r="Q16" s="69"/>
+      <c r="R16" s="69"/>
+      <c r="S16" s="69"/>
+      <c r="T16" s="69" t="s">
         <v>123</v>
       </c>
-      <c r="U16" s="66"/>
-      <c r="V16" s="66"/>
-    </row>
-    <row r="17" s="81" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A17" s="66">
+      <c r="U16" s="69"/>
+      <c r="V16" s="69"/>
+    </row>
+    <row r="17" s="82" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A17" s="69">
         <v>3</v>
       </c>
-      <c r="B17" s="87" t="s">
+      <c r="B17" s="88" t="s">
         <v>118</v>
       </c>
-      <c r="C17" s="86"/>
-      <c r="D17" s="86"/>
-      <c r="E17" s="86"/>
-      <c r="F17" s="86"/>
-      <c r="G17" s="86"/>
-      <c r="H17" s="88"/>
-      <c r="I17" s="67" t="s">
+      <c r="C17" s="87"/>
+      <c r="D17" s="87"/>
+      <c r="E17" s="87"/>
+      <c r="F17" s="87"/>
+      <c r="G17" s="87"/>
+      <c r="H17" s="89"/>
+      <c r="I17" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="J17" s="91"/>
-      <c r="K17" s="91"/>
-      <c r="L17" s="70"/>
-      <c r="M17" s="156" t="s">
+      <c r="J17" s="92"/>
+      <c r="K17" s="92"/>
+      <c r="L17" s="73"/>
+      <c r="M17" s="157" t="s">
         <v>55</v>
       </c>
-      <c r="N17" s="66"/>
-      <c r="O17" s="66"/>
-      <c r="P17" s="66" t="s">
+      <c r="N17" s="69"/>
+      <c r="O17" s="69"/>
+      <c r="P17" s="69" t="s">
         <v>89</v>
       </c>
-      <c r="Q17" s="66"/>
-      <c r="R17" s="66"/>
-      <c r="S17" s="66"/>
-      <c r="T17" s="66" t="s">
+      <c r="Q17" s="69"/>
+      <c r="R17" s="69"/>
+      <c r="S17" s="69"/>
+      <c r="T17" s="69" t="s">
         <v>119</v>
       </c>
-      <c r="U17" s="66"/>
-      <c r="V17" s="66"/>
+      <c r="U17" s="69"/>
+      <c r="V17" s="69"/>
     </row>
     <row r="19" customHeight="1" spans="1:22">
-      <c r="A19" s="89" t="s">
+      <c r="A19" s="90" t="s">
         <v>124</v>
       </c>
-      <c r="B19" s="90"/>
-      <c r="C19" s="90"/>
-      <c r="D19" s="90"/>
-      <c r="E19" s="90"/>
-      <c r="F19" s="90"/>
-      <c r="G19" s="90"/>
-      <c r="H19" s="90"/>
-      <c r="I19" s="90"/>
-      <c r="J19" s="90"/>
-      <c r="K19" s="90"/>
-      <c r="L19" s="90"/>
-      <c r="M19" s="90"/>
-      <c r="N19" s="90"/>
-      <c r="O19" s="90"/>
-      <c r="P19" s="90"/>
-      <c r="Q19" s="90"/>
-      <c r="R19" s="90"/>
-      <c r="S19" s="90"/>
-      <c r="T19" s="90"/>
-      <c r="U19" s="90"/>
-      <c r="V19" s="96"/>
+      <c r="B19" s="91"/>
+      <c r="C19" s="91"/>
+      <c r="D19" s="91"/>
+      <c r="E19" s="91"/>
+      <c r="F19" s="91"/>
+      <c r="G19" s="91"/>
+      <c r="H19" s="91"/>
+      <c r="I19" s="91"/>
+      <c r="J19" s="91"/>
+      <c r="K19" s="91"/>
+      <c r="L19" s="91"/>
+      <c r="M19" s="91"/>
+      <c r="N19" s="91"/>
+      <c r="O19" s="91"/>
+      <c r="P19" s="91"/>
+      <c r="Q19" s="91"/>
+      <c r="R19" s="91"/>
+      <c r="S19" s="91"/>
+      <c r="T19" s="91"/>
+      <c r="U19" s="91"/>
+      <c r="V19" s="97"/>
     </row>
     <row r="20" customHeight="1" spans="1:22">
-      <c r="A20" s="84" t="s">
+      <c r="A20" s="85" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="84" t="s">
+      <c r="B20" s="85" t="s">
         <v>48</v>
       </c>
-      <c r="C20" s="84"/>
-      <c r="D20" s="84"/>
-      <c r="E20" s="84"/>
-      <c r="F20" s="84"/>
-      <c r="G20" s="84"/>
-      <c r="H20" s="84"/>
-      <c r="I20" s="84" t="s">
+      <c r="C20" s="85"/>
+      <c r="D20" s="85"/>
+      <c r="E20" s="85"/>
+      <c r="F20" s="85"/>
+      <c r="G20" s="85"/>
+      <c r="H20" s="85"/>
+      <c r="I20" s="85" t="s">
         <v>61</v>
       </c>
-      <c r="J20" s="84"/>
-      <c r="K20" s="84"/>
-      <c r="L20" s="84"/>
-      <c r="M20" s="84" t="s">
+      <c r="J20" s="85"/>
+      <c r="K20" s="85"/>
+      <c r="L20" s="85"/>
+      <c r="M20" s="85" t="s">
         <v>49</v>
       </c>
-      <c r="N20" s="84"/>
-      <c r="O20" s="84"/>
-      <c r="P20" s="92" t="s">
+      <c r="N20" s="85"/>
+      <c r="O20" s="85"/>
+      <c r="P20" s="93" t="s">
         <v>52</v>
       </c>
-      <c r="Q20" s="92"/>
-      <c r="R20" s="92"/>
-      <c r="S20" s="92"/>
+      <c r="Q20" s="93"/>
+      <c r="R20" s="93"/>
+      <c r="S20" s="93"/>
       <c r="T20" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="U20" s="94"/>
-      <c r="V20" s="95"/>
-    </row>
-    <row r="21" s="81" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A21" s="66">
+      <c r="U20" s="95"/>
+      <c r="V20" s="96"/>
+    </row>
+    <row r="21" s="82" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A21" s="69">
         <v>1</v>
       </c>
-      <c r="B21" s="85" t="s">
+      <c r="B21" s="86" t="s">
         <v>112</v>
       </c>
-      <c r="C21" s="86"/>
-      <c r="D21" s="86"/>
-      <c r="E21" s="86"/>
-      <c r="F21" s="86"/>
-      <c r="G21" s="86"/>
-      <c r="H21" s="86"/>
-      <c r="I21" s="67" t="s">
+      <c r="C21" s="87"/>
+      <c r="D21" s="87"/>
+      <c r="E21" s="87"/>
+      <c r="F21" s="87"/>
+      <c r="G21" s="87"/>
+      <c r="H21" s="87"/>
+      <c r="I21" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="J21" s="91"/>
-      <c r="K21" s="91"/>
-      <c r="L21" s="70"/>
-      <c r="M21" s="156" t="s">
+      <c r="J21" s="92"/>
+      <c r="K21" s="92"/>
+      <c r="L21" s="73"/>
+      <c r="M21" s="157" t="s">
         <v>55</v>
       </c>
-      <c r="N21" s="66"/>
-      <c r="O21" s="66"/>
-      <c r="P21" s="156" t="s">
+      <c r="N21" s="69"/>
+      <c r="O21" s="69"/>
+      <c r="P21" s="157" t="s">
         <v>113</v>
       </c>
-      <c r="Q21" s="66"/>
-      <c r="R21" s="66"/>
-      <c r="S21" s="66"/>
-      <c r="T21" s="66" t="s">
+      <c r="Q21" s="69"/>
+      <c r="R21" s="69"/>
+      <c r="S21" s="69"/>
+      <c r="T21" s="69" t="s">
         <v>121</v>
       </c>
-      <c r="U21" s="66"/>
-      <c r="V21" s="66"/>
-    </row>
-    <row r="22" s="81" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A22" s="66">
+      <c r="U21" s="69"/>
+      <c r="V21" s="69"/>
+    </row>
+    <row r="22" s="82" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A22" s="69">
         <v>2</v>
       </c>
-      <c r="B22" s="85" t="s">
+      <c r="B22" s="86" t="s">
         <v>115</v>
       </c>
       <c r="C22" s="52"/>
@@ -6365,136 +6362,136 @@
       <c r="F22" s="52"/>
       <c r="G22" s="52"/>
       <c r="H22" s="52"/>
-      <c r="I22" s="67" t="s">
+      <c r="I22" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="J22" s="91"/>
-      <c r="K22" s="91"/>
-      <c r="L22" s="70"/>
-      <c r="M22" s="156" t="s">
+      <c r="J22" s="92"/>
+      <c r="K22" s="92"/>
+      <c r="L22" s="73"/>
+      <c r="M22" s="157" t="s">
         <v>55</v>
       </c>
-      <c r="N22" s="66"/>
-      <c r="O22" s="66"/>
-      <c r="P22" s="156" t="s">
+      <c r="N22" s="69"/>
+      <c r="O22" s="69"/>
+      <c r="P22" s="157" t="s">
         <v>122</v>
       </c>
-      <c r="Q22" s="66"/>
-      <c r="R22" s="66"/>
-      <c r="S22" s="66"/>
-      <c r="T22" s="66" t="s">
+      <c r="Q22" s="69"/>
+      <c r="R22" s="69"/>
+      <c r="S22" s="69"/>
+      <c r="T22" s="69" t="s">
         <v>125</v>
       </c>
-      <c r="U22" s="66"/>
-      <c r="V22" s="66"/>
-    </row>
-    <row r="23" s="81" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A23" s="66">
+      <c r="U22" s="69"/>
+      <c r="V22" s="69"/>
+    </row>
+    <row r="23" s="82" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A23" s="69">
         <v>3</v>
       </c>
-      <c r="B23" s="67" t="s">
+      <c r="B23" s="70" t="s">
         <v>126</v>
       </c>
-      <c r="C23" s="91"/>
-      <c r="D23" s="91"/>
-      <c r="E23" s="91"/>
-      <c r="F23" s="91"/>
-      <c r="G23" s="91"/>
-      <c r="H23" s="70"/>
-      <c r="I23" s="67" t="s">
+      <c r="C23" s="92"/>
+      <c r="D23" s="92"/>
+      <c r="E23" s="92"/>
+      <c r="F23" s="92"/>
+      <c r="G23" s="92"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="J23" s="91"/>
-      <c r="K23" s="91"/>
-      <c r="L23" s="70"/>
-      <c r="M23" s="156" t="s">
+      <c r="J23" s="92"/>
+      <c r="K23" s="92"/>
+      <c r="L23" s="73"/>
+      <c r="M23" s="157" t="s">
         <v>55</v>
       </c>
-      <c r="N23" s="66"/>
-      <c r="O23" s="66"/>
-      <c r="P23" s="66" t="s">
+      <c r="N23" s="69"/>
+      <c r="O23" s="69"/>
+      <c r="P23" s="69" t="s">
         <v>127</v>
       </c>
-      <c r="Q23" s="66"/>
-      <c r="R23" s="66"/>
-      <c r="S23" s="66"/>
-      <c r="T23" s="156" t="s">
+      <c r="Q23" s="69"/>
+      <c r="R23" s="69"/>
+      <c r="S23" s="69"/>
+      <c r="T23" s="157" t="s">
         <v>128</v>
       </c>
-      <c r="U23" s="66"/>
-      <c r="V23" s="66"/>
-    </row>
-    <row r="24" s="81" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A24" s="66">
+      <c r="U23" s="69"/>
+      <c r="V23" s="69"/>
+    </row>
+    <row r="24" s="82" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A24" s="69">
         <v>4</v>
       </c>
-      <c r="B24" s="67" t="s">
+      <c r="B24" s="70" t="s">
         <v>129</v>
       </c>
-      <c r="C24" s="91"/>
-      <c r="D24" s="91"/>
-      <c r="E24" s="91"/>
-      <c r="F24" s="91"/>
-      <c r="G24" s="91"/>
-      <c r="H24" s="70"/>
-      <c r="I24" s="67" t="s">
+      <c r="C24" s="92"/>
+      <c r="D24" s="92"/>
+      <c r="E24" s="92"/>
+      <c r="F24" s="92"/>
+      <c r="G24" s="92"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="J24" s="91"/>
-      <c r="K24" s="91"/>
-      <c r="L24" s="70"/>
-      <c r="M24" s="156" t="s">
+      <c r="J24" s="92"/>
+      <c r="K24" s="92"/>
+      <c r="L24" s="73"/>
+      <c r="M24" s="157" t="s">
         <v>55</v>
       </c>
-      <c r="N24" s="66"/>
-      <c r="O24" s="66"/>
-      <c r="P24" s="66" t="s">
+      <c r="N24" s="69"/>
+      <c r="O24" s="69"/>
+      <c r="P24" s="69" t="s">
         <v>130</v>
       </c>
-      <c r="Q24" s="66"/>
-      <c r="R24" s="66"/>
-      <c r="S24" s="66"/>
-      <c r="T24" s="66" t="s">
+      <c r="Q24" s="69"/>
+      <c r="R24" s="69"/>
+      <c r="S24" s="69"/>
+      <c r="T24" s="69" t="s">
         <v>131</v>
       </c>
-      <c r="U24" s="66"/>
-      <c r="V24" s="66"/>
-    </row>
-    <row r="25" s="81" customFormat="1" customHeight="1" spans="1:22">
-      <c r="A25" s="66">
+      <c r="U24" s="69"/>
+      <c r="V24" s="69"/>
+    </row>
+    <row r="25" s="82" customFormat="1" customHeight="1" spans="1:22">
+      <c r="A25" s="69">
         <v>5</v>
       </c>
-      <c r="B25" s="67" t="s">
+      <c r="B25" s="70" t="s">
         <v>132</v>
       </c>
-      <c r="C25" s="91"/>
-      <c r="D25" s="91"/>
-      <c r="E25" s="91"/>
-      <c r="F25" s="91"/>
-      <c r="G25" s="91"/>
-      <c r="H25" s="70"/>
-      <c r="I25" s="67" t="s">
+      <c r="C25" s="92"/>
+      <c r="D25" s="92"/>
+      <c r="E25" s="92"/>
+      <c r="F25" s="92"/>
+      <c r="G25" s="92"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="70" t="s">
         <v>66</v>
       </c>
-      <c r="J25" s="91"/>
-      <c r="K25" s="91"/>
-      <c r="L25" s="70"/>
-      <c r="M25" s="156" t="s">
+      <c r="J25" s="92"/>
+      <c r="K25" s="92"/>
+      <c r="L25" s="73"/>
+      <c r="M25" s="157" t="s">
         <v>55</v>
       </c>
-      <c r="N25" s="66"/>
-      <c r="O25" s="66"/>
-      <c r="P25" s="66" t="s">
+      <c r="N25" s="69"/>
+      <c r="O25" s="69"/>
+      <c r="P25" s="69" t="s">
         <v>133</v>
       </c>
-      <c r="Q25" s="66"/>
-      <c r="R25" s="66"/>
-      <c r="S25" s="66"/>
-      <c r="T25" s="66" t="s">
+      <c r="Q25" s="69"/>
+      <c r="R25" s="69"/>
+      <c r="S25" s="69"/>
+      <c r="T25" s="69" t="s">
         <v>134</v>
       </c>
-      <c r="U25" s="66"/>
-      <c r="V25" s="66"/>
+      <c r="U25" s="69"/>
+      <c r="V25" s="69"/>
     </row>
   </sheetData>
   <mergeCells count="83">
@@ -6631,9 +6628,9 @@
       <c r="M1" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="N1" s="78"/>
-      <c r="O1" s="78"/>
-      <c r="P1" s="78"/>
+      <c r="N1" s="79"/>
+      <c r="O1" s="79"/>
+      <c r="P1" s="79"/>
       <c r="Q1" s="26" t="s">
         <v>3</v>
       </c>
@@ -6644,7 +6641,7 @@
       <c r="T1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="154" t="s">
+      <c r="U1" s="155" t="s">
         <v>12</v>
       </c>
       <c r="V1" s="30"/>
@@ -6663,12 +6660,12 @@
       <c r="K2" s="32"/>
       <c r="L2" s="32"/>
       <c r="M2" s="33"/>
-      <c r="N2" s="79"/>
-      <c r="O2" s="79"/>
-      <c r="P2" s="79"/>
+      <c r="N2" s="80"/>
+      <c r="O2" s="80"/>
+      <c r="P2" s="80"/>
       <c r="Q2" s="26"/>
       <c r="R2" s="34"/>
-      <c r="S2" s="80"/>
+      <c r="S2" s="81"/>
       <c r="T2" s="35"/>
       <c r="U2" s="36"/>
       <c r="V2" s="37"/>
@@ -6691,9 +6688,9 @@
       <c r="M3" s="25" t="s">
         <v>14</v>
       </c>
-      <c r="N3" s="78"/>
-      <c r="O3" s="78"/>
-      <c r="P3" s="78"/>
+      <c r="N3" s="79"/>
+      <c r="O3" s="79"/>
+      <c r="P3" s="79"/>
       <c r="Q3" s="26" t="s">
         <v>15</v>
       </c>
@@ -6704,7 +6701,7 @@
       <c r="T3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="U3" s="154" t="s">
+      <c r="U3" s="155" t="s">
         <v>18</v>
       </c>
       <c r="V3" s="30"/>
@@ -6723,12 +6720,12 @@
       <c r="K4" s="32"/>
       <c r="L4" s="32"/>
       <c r="M4" s="33"/>
-      <c r="N4" s="79"/>
-      <c r="O4" s="79"/>
-      <c r="P4" s="79"/>
+      <c r="N4" s="80"/>
+      <c r="O4" s="80"/>
+      <c r="P4" s="80"/>
       <c r="Q4" s="26"/>
       <c r="R4" s="34"/>
-      <c r="S4" s="80"/>
+      <c r="S4" s="81"/>
       <c r="T4" s="26"/>
       <c r="U4" s="36"/>
       <c r="V4" s="37"/>
@@ -6770,7 +6767,7 @@
       <c r="V5" s="11"/>
     </row>
     <row r="6" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A6" s="76"/>
+      <c r="A6" s="77"/>
       <c r="B6" s="18"/>
       <c r="C6" s="18"/>
       <c r="D6" s="18"/>
@@ -6794,7 +6791,7 @@
       <c r="V6" s="18"/>
     </row>
     <row r="7" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A7" s="76"/>
+      <c r="A7" s="77"/>
       <c r="B7" s="18"/>
       <c r="C7" s="18"/>
       <c r="D7" s="18"/>
@@ -6818,7 +6815,7 @@
       <c r="V7" s="18"/>
     </row>
     <row r="8" s="2" customFormat="1" ht="16.5" spans="1:22">
-      <c r="A8" s="77" t="s">
+      <c r="A8" s="78" t="s">
         <v>136</v>
       </c>
       <c r="B8" s="18"/>
@@ -6844,7 +6841,7 @@
       <c r="V8" s="18"/>
     </row>
     <row r="9" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A9" s="76"/>
+      <c r="A9" s="77"/>
       <c r="B9" s="18"/>
       <c r="C9" s="18"/>
       <c r="D9" s="18"/>
@@ -6868,7 +6865,7 @@
       <c r="V9" s="18"/>
     </row>
     <row r="10" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A10" s="76"/>
+      <c r="A10" s="77"/>
       <c r="B10" s="18"/>
       <c r="C10" s="18"/>
       <c r="D10" s="18"/>
@@ -6892,7 +6889,7 @@
       <c r="V10" s="18"/>
     </row>
     <row r="11" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A11" s="76"/>
+      <c r="A11" s="77"/>
       <c r="B11" s="18"/>
       <c r="C11" s="18"/>
       <c r="D11" s="18"/>
@@ -6916,7 +6913,7 @@
       <c r="V11" s="18"/>
     </row>
     <row r="12" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A12" s="76"/>
+      <c r="A12" s="77"/>
       <c r="B12" s="18"/>
       <c r="C12" s="18"/>
       <c r="D12" s="18"/>
@@ -6940,7 +6937,7 @@
       <c r="V12" s="18"/>
     </row>
     <row r="13" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A13" s="76"/>
+      <c r="A13" s="77"/>
       <c r="B13" s="18"/>
       <c r="C13" s="18"/>
       <c r="D13" s="18"/>
@@ -6964,7 +6961,7 @@
       <c r="V13" s="18"/>
     </row>
     <row r="14" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A14" s="76"/>
+      <c r="A14" s="77"/>
       <c r="B14" s="18"/>
       <c r="C14" s="18"/>
       <c r="D14" s="18"/>
@@ -6988,7 +6985,7 @@
       <c r="V14" s="18"/>
     </row>
     <row r="15" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A15" s="76"/>
+      <c r="A15" s="77"/>
       <c r="B15" s="18"/>
       <c r="C15" s="18"/>
       <c r="D15" s="18"/>
@@ -7012,7 +7009,7 @@
       <c r="V15" s="18"/>
     </row>
     <row r="16" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A16" s="76"/>
+      <c r="A16" s="77"/>
       <c r="B16" s="18"/>
       <c r="C16" s="18"/>
       <c r="D16" s="18"/>
@@ -7036,7 +7033,7 @@
       <c r="V16" s="18"/>
     </row>
     <row r="17" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A17" s="76"/>
+      <c r="A17" s="77"/>
       <c r="B17" s="18"/>
       <c r="C17" s="18"/>
       <c r="D17" s="18"/>
@@ -7060,7 +7057,7 @@
       <c r="V17" s="18"/>
     </row>
     <row r="18" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A18" s="76"/>
+      <c r="A18" s="77"/>
       <c r="B18" s="18"/>
       <c r="C18" s="18"/>
       <c r="D18" s="18"/>
@@ -7084,7 +7081,7 @@
       <c r="V18" s="18"/>
     </row>
     <row r="19" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A19" s="76"/>
+      <c r="A19" s="77"/>
       <c r="B19" s="18"/>
       <c r="C19" s="18"/>
       <c r="D19" s="18"/>
@@ -7108,7 +7105,7 @@
       <c r="V19" s="18"/>
     </row>
     <row r="20" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A20" s="76"/>
+      <c r="A20" s="77"/>
       <c r="B20" s="18"/>
       <c r="C20" s="18"/>
       <c r="D20" s="18"/>
@@ -7132,7 +7129,7 @@
       <c r="V20" s="18"/>
     </row>
     <row r="21" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A21" s="76"/>
+      <c r="A21" s="77"/>
       <c r="B21" s="18"/>
       <c r="C21" s="18"/>
       <c r="D21" s="18"/>
@@ -7156,7 +7153,7 @@
       <c r="V21" s="18"/>
     </row>
     <row r="22" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A22" s="76"/>
+      <c r="A22" s="77"/>
       <c r="B22" s="18"/>
       <c r="C22" s="18"/>
       <c r="D22" s="18"/>
@@ -7180,7 +7177,7 @@
       <c r="V22" s="18"/>
     </row>
     <row r="23" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A23" s="76"/>
+      <c r="A23" s="77"/>
       <c r="B23" s="18"/>
       <c r="C23" s="18"/>
       <c r="D23" s="18"/>
@@ -7204,7 +7201,7 @@
       <c r="V23" s="18"/>
     </row>
     <row r="24" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A24" s="76"/>
+      <c r="A24" s="77"/>
       <c r="B24" s="18"/>
       <c r="C24" s="18"/>
       <c r="D24" s="18"/>
@@ -7228,7 +7225,7 @@
       <c r="V24" s="18"/>
     </row>
     <row r="25" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A25" s="76"/>
+      <c r="A25" s="77"/>
       <c r="B25" s="18"/>
       <c r="C25" s="18"/>
       <c r="D25" s="18"/>
@@ -7252,7 +7249,7 @@
       <c r="V25" s="18"/>
     </row>
     <row r="26" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A26" s="76"/>
+      <c r="A26" s="77"/>
       <c r="B26" s="18"/>
       <c r="C26" s="18"/>
       <c r="D26" s="18"/>
@@ -7276,7 +7273,7 @@
       <c r="V26" s="18"/>
     </row>
     <row r="27" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A27" s="76"/>
+      <c r="A27" s="77"/>
       <c r="B27" s="18"/>
       <c r="C27" s="18"/>
       <c r="D27" s="18"/>
@@ -7300,7 +7297,7 @@
       <c r="V27" s="18"/>
     </row>
     <row r="28" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A28" s="76"/>
+      <c r="A28" s="77"/>
       <c r="B28" s="18"/>
       <c r="C28" s="18"/>
       <c r="D28" s="18"/>
@@ -7324,7 +7321,7 @@
       <c r="V28" s="18"/>
     </row>
     <row r="29" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A29" s="76"/>
+      <c r="A29" s="77"/>
       <c r="B29" s="18"/>
       <c r="C29" s="18"/>
       <c r="D29" s="18"/>
@@ -7348,7 +7345,7 @@
       <c r="V29" s="18"/>
     </row>
     <row r="30" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A30" s="76"/>
+      <c r="A30" s="77"/>
       <c r="B30" s="18"/>
       <c r="C30" s="18"/>
       <c r="D30" s="18"/>
@@ -7372,7 +7369,7 @@
       <c r="V30" s="18"/>
     </row>
     <row r="31" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A31" s="76"/>
+      <c r="A31" s="77"/>
       <c r="B31" s="18"/>
       <c r="C31" s="18"/>
       <c r="D31" s="18"/>
@@ -7396,7 +7393,7 @@
       <c r="V31" s="18"/>
     </row>
     <row r="32" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A32" s="76"/>
+      <c r="A32" s="77"/>
       <c r="B32" s="18"/>
       <c r="C32" s="18"/>
       <c r="D32" s="18"/>
@@ -7420,7 +7417,7 @@
       <c r="V32" s="18"/>
     </row>
     <row r="33" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A33" s="76"/>
+      <c r="A33" s="77"/>
       <c r="B33" s="18"/>
       <c r="C33" s="18"/>
       <c r="D33" s="18"/>
@@ -7444,7 +7441,7 @@
       <c r="V33" s="18"/>
     </row>
     <row r="34" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A34" s="76"/>
+      <c r="A34" s="77"/>
       <c r="B34" s="18"/>
       <c r="C34" s="18"/>
       <c r="D34" s="18"/>
@@ -7468,7 +7465,7 @@
       <c r="V34" s="18"/>
     </row>
     <row r="35" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A35" s="76"/>
+      <c r="A35" s="77"/>
       <c r="B35" s="18"/>
       <c r="C35" s="18"/>
       <c r="D35" s="18"/>
@@ -7492,7 +7489,7 @@
       <c r="V35" s="18"/>
     </row>
     <row r="36" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A36" s="76"/>
+      <c r="A36" s="77"/>
       <c r="B36" s="18"/>
       <c r="C36" s="18"/>
       <c r="D36" s="18"/>
@@ -7516,7 +7513,7 @@
       <c r="V36" s="18"/>
     </row>
     <row r="37" s="2" customFormat="1" ht="19.5" spans="1:22">
-      <c r="A37" s="76"/>
+      <c r="A37" s="77"/>
       <c r="B37" s="18"/>
       <c r="C37" s="18"/>
       <c r="D37" s="18"/>
@@ -7570,7 +7567,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:P134"/>
+  <dimension ref="A1:P127"/>
   <sheetFormatPr defaultColWidth="3.66666666666667" defaultRowHeight="20.1" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="6.44444444444444" style="3" customWidth="1"/>
@@ -7615,7 +7612,7 @@
       <c r="N1" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="O1" s="154" t="s">
+      <c r="O1" s="155" t="s">
         <v>12</v>
       </c>
       <c r="P1" s="30"/>
@@ -7663,7 +7660,7 @@
       <c r="N3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="O3" s="154" t="s">
+      <c r="O3" s="155" t="s">
         <v>18</v>
       </c>
       <c r="P3" s="30"/>
@@ -8273,7 +8270,7 @@
       <c r="H29" s="18"/>
       <c r="I29" s="39"/>
       <c r="J29" s="39" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="K29" s="18"/>
       <c r="L29" s="18"/>
@@ -8293,10 +8290,10 @@
       <c r="H30" s="18"/>
       <c r="I30" s="39"/>
       <c r="J30" s="45" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K30" s="45" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L30" s="45" t="s">
         <v>122</v>
@@ -8320,10 +8317,10 @@
         <v>65</v>
       </c>
       <c r="K31" s="47" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L31" s="48" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M31" s="48"/>
       <c r="N31" s="18"/>
@@ -8344,10 +8341,10 @@
         <v>70</v>
       </c>
       <c r="K32" s="48" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="L32" s="48" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="M32" s="48"/>
       <c r="N32" s="18"/>
@@ -8368,10 +8365,10 @@
         <v>75</v>
       </c>
       <c r="K33" s="48" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="L33" s="48" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="M33" s="48"/>
       <c r="N33" s="18"/>
@@ -8392,10 +8389,10 @@
         <v>79</v>
       </c>
       <c r="K34" s="48" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="L34" s="48" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="M34" s="48"/>
       <c r="N34" s="18"/>
@@ -8416,10 +8413,10 @@
         <v>82</v>
       </c>
       <c r="K35" s="48" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="L35" s="48" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="M35" s="48"/>
       <c r="N35" s="18"/>
@@ -8440,10 +8437,10 @@
         <v>86</v>
       </c>
       <c r="K36" s="51" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="L36" s="48" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="M36" s="48"/>
       <c r="N36" s="18"/>
@@ -8479,7 +8476,7 @@
       <c r="H38" s="18"/>
       <c r="I38" s="39"/>
       <c r="J38" s="56" t="s">
-        <v>147</v>
+        <v>186</v>
       </c>
       <c r="K38" s="57"/>
       <c r="L38" s="54"/>
@@ -8499,10 +8496,10 @@
       <c r="H39" s="18"/>
       <c r="I39" s="39"/>
       <c r="J39" s="45" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="K39" s="45" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="L39" s="45" t="s">
         <v>122</v>
@@ -8526,10 +8523,10 @@
         <v>96</v>
       </c>
       <c r="K40" s="58" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="L40" s="48" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="M40" s="48"/>
       <c r="N40" s="18"/>
@@ -8550,10 +8547,10 @@
         <v>96</v>
       </c>
       <c r="K41" s="46" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L41" s="48" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="M41" s="48"/>
       <c r="N41" s="18"/>
@@ -8574,10 +8571,10 @@
         <v>99</v>
       </c>
       <c r="K42" s="46" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="L42" s="48" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M42" s="48"/>
       <c r="N42" s="18"/>
@@ -8598,10 +8595,10 @@
         <v>99</v>
       </c>
       <c r="K43" s="46" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="L43" s="48" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="M43" s="48"/>
       <c r="N43" s="18"/>
@@ -8622,10 +8619,10 @@
         <v>101</v>
       </c>
       <c r="K44" s="46" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="L44" s="48" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="M44" s="48"/>
       <c r="N44" s="18"/>
@@ -8646,10 +8643,10 @@
         <v>104</v>
       </c>
       <c r="K45" s="46" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="L45" s="48" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="M45" s="48"/>
       <c r="N45" s="18"/>
@@ -8670,10 +8667,10 @@
         <v>104</v>
       </c>
       <c r="K46" s="46" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="L46" s="48" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="M46" s="48"/>
       <c r="N46" s="18"/>
@@ -8710,7 +8707,7 @@
       <c r="G48" s="20"/>
       <c r="H48" s="18"/>
       <c r="I48" s="38" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="J48" s="39"/>
       <c r="K48" s="18"/>
@@ -8722,7 +8719,7 @@
     </row>
     <row r="49" s="2" customFormat="1" ht="16.5" spans="1:16">
       <c r="A49" s="19" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B49" s="18"/>
       <c r="C49" s="18"/>
@@ -8732,8 +8729,8 @@
       <c r="G49" s="20"/>
       <c r="H49" s="18"/>
       <c r="I49" s="38"/>
-      <c r="J49" s="2" t="s">
-        <v>200</v>
+      <c r="J49" s="39" t="s">
+        <v>202</v>
       </c>
       <c r="K49" s="18"/>
       <c r="L49" s="18"/>
@@ -8753,7 +8750,7 @@
       <c r="H50" s="18"/>
       <c r="I50" s="38"/>
       <c r="J50" s="38" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="K50" s="18"/>
       <c r="L50" s="18"/>
@@ -8772,7 +8769,6 @@
       <c r="G51" s="20"/>
       <c r="H51" s="18"/>
       <c r="I51" s="38"/>
-      <c r="J51" s="38"/>
       <c r="K51" s="18"/>
       <c r="L51" s="18"/>
       <c r="M51" s="18"/>
@@ -8781,7 +8777,7 @@
       <c r="P51" s="20"/>
     </row>
     <row r="52" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A52" s="19"/>
+      <c r="A52" s="21"/>
       <c r="B52" s="18"/>
       <c r="C52" s="18"/>
       <c r="D52" s="18"/>
@@ -8789,19 +8785,19 @@
       <c r="F52" s="18"/>
       <c r="G52" s="20"/>
       <c r="H52" s="18"/>
-      <c r="I52" s="38"/>
+      <c r="I52" s="39"/>
       <c r="J52" s="39" t="s">
-        <v>202</v>
-      </c>
-      <c r="K52" s="18"/>
-      <c r="L52" s="18"/>
-      <c r="M52" s="18"/>
+        <v>204</v>
+      </c>
+      <c r="K52" s="59"/>
+      <c r="L52" s="59"/>
+      <c r="M52" s="59"/>
       <c r="N52" s="18"/>
       <c r="O52" s="42"/>
       <c r="P52" s="20"/>
     </row>
     <row r="53" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A53" s="19"/>
+      <c r="A53" s="21"/>
       <c r="B53" s="18"/>
       <c r="C53" s="18"/>
       <c r="D53" s="18"/>
@@ -8809,19 +8805,23 @@
       <c r="F53" s="18"/>
       <c r="G53" s="20"/>
       <c r="H53" s="18"/>
-      <c r="I53" s="38"/>
-      <c r="J53" s="38" t="s">
-        <v>203</v>
-      </c>
-      <c r="K53" s="18"/>
-      <c r="L53" s="18"/>
-      <c r="M53" s="18"/>
+      <c r="I53" s="39"/>
+      <c r="J53" s="40" t="s">
+        <v>205</v>
+      </c>
+      <c r="K53" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="L53" s="60" t="s">
+        <v>53</v>
+      </c>
+      <c r="M53" s="60"/>
       <c r="N53" s="18"/>
       <c r="O53" s="42"/>
       <c r="P53" s="20"/>
     </row>
     <row r="54" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A54" s="19"/>
+      <c r="A54" s="21"/>
       <c r="B54" s="18"/>
       <c r="C54" s="18"/>
       <c r="D54" s="18"/>
@@ -8829,10 +8829,17 @@
       <c r="F54" s="18"/>
       <c r="G54" s="20"/>
       <c r="H54" s="18"/>
-      <c r="I54" s="38"/>
-      <c r="K54" s="18"/>
-      <c r="L54" s="18"/>
-      <c r="M54" s="18"/>
+      <c r="I54" s="39"/>
+      <c r="J54" s="61" t="s">
+        <v>206</v>
+      </c>
+      <c r="K54" s="44" t="s">
+        <v>207</v>
+      </c>
+      <c r="L54" s="62" t="s">
+        <v>208</v>
+      </c>
+      <c r="M54" s="62"/>
       <c r="N54" s="18"/>
       <c r="O54" s="42"/>
       <c r="P54" s="20"/>
@@ -8847,18 +8854,18 @@
       <c r="G55" s="20"/>
       <c r="H55" s="18"/>
       <c r="I55" s="39"/>
-      <c r="J55" s="39" t="s">
-        <v>204</v>
-      </c>
-      <c r="K55" s="59"/>
-      <c r="L55" s="59"/>
-      <c r="M55" s="59"/>
+      <c r="J55" s="63"/>
+      <c r="K55" s="39"/>
+      <c r="L55" s="64"/>
+      <c r="M55" s="64"/>
       <c r="N55" s="18"/>
       <c r="O55" s="42"/>
       <c r="P55" s="20"/>
     </row>
     <row r="56" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A56" s="21"/>
+      <c r="A56" s="19" t="s">
+        <v>147</v>
+      </c>
       <c r="B56" s="18"/>
       <c r="C56" s="18"/>
       <c r="D56" s="18"/>
@@ -8866,23 +8873,19 @@
       <c r="F56" s="18"/>
       <c r="G56" s="20"/>
       <c r="H56" s="18"/>
-      <c r="I56" s="39"/>
-      <c r="J56" s="40" t="s">
-        <v>205</v>
-      </c>
-      <c r="K56" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="L56" s="60" t="s">
-        <v>53</v>
-      </c>
-      <c r="M56" s="60"/>
+      <c r="I56" s="38" t="s">
+        <v>209</v>
+      </c>
+      <c r="J56" s="39"/>
+      <c r="K56" s="18"/>
+      <c r="L56" s="18"/>
+      <c r="M56" s="18"/>
       <c r="N56" s="18"/>
       <c r="O56" s="42"/>
       <c r="P56" s="20"/>
     </row>
     <row r="57" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A57" s="21"/>
+      <c r="A57" s="19"/>
       <c r="B57" s="18"/>
       <c r="C57" s="18"/>
       <c r="D57" s="18"/>
@@ -8890,23 +8893,17 @@
       <c r="F57" s="18"/>
       <c r="G57" s="20"/>
       <c r="H57" s="18"/>
-      <c r="I57" s="39"/>
-      <c r="J57" s="61" t="s">
-        <v>206</v>
-      </c>
-      <c r="K57" s="44" t="s">
-        <v>207</v>
-      </c>
-      <c r="L57" s="62" t="s">
-        <v>208</v>
-      </c>
-      <c r="M57" s="62"/>
+      <c r="I57" s="38"/>
+      <c r="J57" s="38"/>
+      <c r="K57" s="18"/>
+      <c r="L57" s="18"/>
+      <c r="M57" s="18"/>
       <c r="N57" s="18"/>
       <c r="O57" s="42"/>
       <c r="P57" s="20"/>
     </row>
     <row r="58" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A58" s="21"/>
+      <c r="A58" s="19"/>
       <c r="B58" s="18"/>
       <c r="C58" s="18"/>
       <c r="D58" s="18"/>
@@ -8914,8 +8911,10 @@
       <c r="F58" s="18"/>
       <c r="G58" s="20"/>
       <c r="H58" s="18"/>
-      <c r="I58" s="39"/>
-      <c r="J58" s="39"/>
+      <c r="I58" s="38"/>
+      <c r="J58" s="38" t="s">
+        <v>210</v>
+      </c>
       <c r="K58" s="18"/>
       <c r="L58" s="18"/>
       <c r="M58" s="18"/>
@@ -8924,9 +8923,7 @@
       <c r="P58" s="20"/>
     </row>
     <row r="59" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A59" s="19" t="s">
-        <v>147</v>
-      </c>
+      <c r="A59" s="19"/>
       <c r="B59" s="18"/>
       <c r="C59" s="18"/>
       <c r="D59" s="18"/>
@@ -8934,10 +8931,10 @@
       <c r="F59" s="18"/>
       <c r="G59" s="20"/>
       <c r="H59" s="18"/>
-      <c r="I59" s="38" t="s">
-        <v>209</v>
-      </c>
-      <c r="J59" s="39"/>
+      <c r="I59" s="38"/>
+      <c r="J59" s="38" t="s">
+        <v>211</v>
+      </c>
       <c r="K59" s="18"/>
       <c r="L59" s="18"/>
       <c r="M59" s="18"/>
@@ -8955,9 +8952,7 @@
       <c r="G60" s="20"/>
       <c r="H60" s="18"/>
       <c r="I60" s="38"/>
-      <c r="J60" s="2" t="s">
-        <v>200</v>
-      </c>
+      <c r="J60" s="38"/>
       <c r="K60" s="18"/>
       <c r="L60" s="18"/>
       <c r="M60" s="18"/>
@@ -8976,7 +8971,7 @@
       <c r="H61" s="18"/>
       <c r="I61" s="38"/>
       <c r="J61" s="38" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="K61" s="18"/>
       <c r="L61" s="18"/>
@@ -8995,8 +8990,12 @@
       <c r="G62" s="20"/>
       <c r="H62" s="18"/>
       <c r="I62" s="38"/>
-      <c r="J62" s="38"/>
-      <c r="K62" s="18"/>
+      <c r="J62" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="K62" s="65" t="s">
+        <v>214</v>
+      </c>
       <c r="L62" s="18"/>
       <c r="M62" s="18"/>
       <c r="N62" s="18"/>
@@ -9014,9 +9013,11 @@
       <c r="H63" s="18"/>
       <c r="I63" s="38"/>
       <c r="J63" s="38" t="s">
-        <v>211</v>
-      </c>
-      <c r="K63" s="18"/>
+        <v>215</v>
+      </c>
+      <c r="K63" s="65" t="s">
+        <v>216</v>
+      </c>
       <c r="L63" s="18"/>
       <c r="M63" s="18"/>
       <c r="N63" s="18"/>
@@ -9033,9 +9034,7 @@
       <c r="G64" s="20"/>
       <c r="H64" s="18"/>
       <c r="I64" s="38"/>
-      <c r="J64" s="38" t="s">
-        <v>212</v>
-      </c>
+      <c r="J64" s="38"/>
       <c r="K64" s="18"/>
       <c r="L64" s="18"/>
       <c r="M64" s="18"/>
@@ -9052,8 +9051,10 @@
       <c r="F65" s="18"/>
       <c r="G65" s="20"/>
       <c r="H65" s="18"/>
-      <c r="I65" s="38"/>
-      <c r="J65" s="38"/>
+      <c r="I65" s="39"/>
+      <c r="J65" s="38" t="s">
+        <v>217</v>
+      </c>
       <c r="K65" s="18"/>
       <c r="L65" s="18"/>
       <c r="M65" s="18"/>
@@ -9070,9 +9071,9 @@
       <c r="F66" s="18"/>
       <c r="G66" s="20"/>
       <c r="H66" s="18"/>
-      <c r="I66" s="38"/>
+      <c r="I66" s="39"/>
       <c r="J66" s="38" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="K66" s="18"/>
       <c r="L66" s="18"/>
@@ -9090,15 +9091,17 @@
       <c r="F67" s="18"/>
       <c r="G67" s="20"/>
       <c r="H67" s="18"/>
-      <c r="I67" s="38"/>
-      <c r="J67" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="K67" s="63" t="s">
-        <v>215</v>
-      </c>
-      <c r="L67" s="18"/>
-      <c r="M67" s="18"/>
+      <c r="I67" s="39"/>
+      <c r="J67" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="K67" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="L67" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="M67" s="67"/>
       <c r="N67" s="18"/>
       <c r="O67" s="42"/>
       <c r="P67" s="20"/>
@@ -9112,15 +9115,17 @@
       <c r="F68" s="18"/>
       <c r="G68" s="20"/>
       <c r="H68" s="18"/>
-      <c r="I68" s="38"/>
-      <c r="J68" s="38" t="s">
-        <v>216</v>
-      </c>
-      <c r="K68" s="63" t="s">
-        <v>217</v>
-      </c>
-      <c r="L68" s="18"/>
-      <c r="M68" s="18"/>
+      <c r="I68" s="39"/>
+      <c r="J68" s="68" t="s">
+        <v>38</v>
+      </c>
+      <c r="K68" s="69" t="s">
+        <v>220</v>
+      </c>
+      <c r="L68" s="70" t="s">
+        <v>221</v>
+      </c>
+      <c r="M68" s="71"/>
       <c r="N68" s="18"/>
       <c r="O68" s="42"/>
       <c r="P68" s="20"/>
@@ -9134,11 +9139,15 @@
       <c r="F69" s="18"/>
       <c r="G69" s="20"/>
       <c r="H69" s="18"/>
-      <c r="I69" s="38"/>
-      <c r="J69" s="38"/>
-      <c r="K69" s="18"/>
-      <c r="L69" s="18"/>
-      <c r="M69" s="18"/>
+      <c r="I69" s="39"/>
+      <c r="J69" s="72"/>
+      <c r="K69" s="69" t="s">
+        <v>222</v>
+      </c>
+      <c r="L69" s="70" t="s">
+        <v>223</v>
+      </c>
+      <c r="M69" s="73"/>
       <c r="N69" s="18"/>
       <c r="O69" s="42"/>
       <c r="P69" s="20"/>
@@ -9153,12 +9162,14 @@
       <c r="G70" s="20"/>
       <c r="H70" s="18"/>
       <c r="I70" s="39"/>
-      <c r="J70" s="38" t="s">
-        <v>218</v>
-      </c>
-      <c r="K70" s="18"/>
-      <c r="L70" s="18"/>
-      <c r="M70" s="18"/>
+      <c r="J70" s="72"/>
+      <c r="K70" s="69" t="s">
+        <v>224</v>
+      </c>
+      <c r="L70" s="70" t="s">
+        <v>225</v>
+      </c>
+      <c r="M70" s="73"/>
       <c r="N70" s="18"/>
       <c r="O70" s="42"/>
       <c r="P70" s="20"/>
@@ -9173,12 +9184,14 @@
       <c r="G71" s="20"/>
       <c r="H71" s="18"/>
       <c r="I71" s="39"/>
-      <c r="J71" s="38" t="s">
-        <v>219</v>
-      </c>
-      <c r="K71" s="18"/>
-      <c r="L71" s="18"/>
-      <c r="M71" s="18"/>
+      <c r="J71" s="72"/>
+      <c r="K71" s="69" t="s">
+        <v>226</v>
+      </c>
+      <c r="L71" s="70" t="s">
+        <v>227</v>
+      </c>
+      <c r="M71" s="73"/>
       <c r="N71" s="18"/>
       <c r="O71" s="42"/>
       <c r="P71" s="20"/>
@@ -9193,16 +9206,14 @@
       <c r="G72" s="20"/>
       <c r="H72" s="18"/>
       <c r="I72" s="39"/>
-      <c r="J72" s="41" t="s">
-        <v>205</v>
-      </c>
-      <c r="K72" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="L72" s="40" t="s">
-        <v>220</v>
-      </c>
-      <c r="M72" s="64"/>
+      <c r="J72" s="72"/>
+      <c r="K72" s="69" t="s">
+        <v>228</v>
+      </c>
+      <c r="L72" s="70" t="s">
+        <v>229</v>
+      </c>
+      <c r="M72" s="73"/>
       <c r="N72" s="18"/>
       <c r="O72" s="42"/>
       <c r="P72" s="20"/>
@@ -9217,16 +9228,14 @@
       <c r="G73" s="20"/>
       <c r="H73" s="18"/>
       <c r="I73" s="39"/>
-      <c r="J73" s="65" t="s">
-        <v>38</v>
-      </c>
-      <c r="K73" s="66" t="s">
-        <v>221</v>
-      </c>
-      <c r="L73" s="67" t="s">
-        <v>222</v>
-      </c>
-      <c r="M73" s="68"/>
+      <c r="J73" s="72"/>
+      <c r="K73" s="69" t="s">
+        <v>230</v>
+      </c>
+      <c r="L73" s="70" t="s">
+        <v>231</v>
+      </c>
+      <c r="M73" s="73"/>
       <c r="N73" s="18"/>
       <c r="O73" s="42"/>
       <c r="P73" s="20"/>
@@ -9241,14 +9250,14 @@
       <c r="G74" s="20"/>
       <c r="H74" s="18"/>
       <c r="I74" s="39"/>
-      <c r="J74" s="69"/>
-      <c r="K74" s="66" t="s">
-        <v>223</v>
-      </c>
-      <c r="L74" s="67" t="s">
-        <v>224</v>
-      </c>
-      <c r="M74" s="70"/>
+      <c r="J74" s="72"/>
+      <c r="K74" s="69" t="s">
+        <v>232</v>
+      </c>
+      <c r="L74" s="70" t="s">
+        <v>233</v>
+      </c>
+      <c r="M74" s="71"/>
       <c r="N74" s="18"/>
       <c r="O74" s="42"/>
       <c r="P74" s="20"/>
@@ -9263,20 +9272,20 @@
       <c r="G75" s="20"/>
       <c r="H75" s="18"/>
       <c r="I75" s="39"/>
-      <c r="J75" s="69"/>
-      <c r="K75" s="66" t="s">
-        <v>225</v>
-      </c>
-      <c r="L75" s="67" t="s">
-        <v>226</v>
-      </c>
-      <c r="M75" s="70"/>
+      <c r="J75" s="72"/>
+      <c r="K75" s="69" t="s">
+        <v>234</v>
+      </c>
+      <c r="L75" s="70" t="s">
+        <v>235</v>
+      </c>
+      <c r="M75" s="71"/>
       <c r="N75" s="18"/>
       <c r="O75" s="42"/>
       <c r="P75" s="20"/>
     </row>
     <row r="76" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A76" s="19"/>
+      <c r="A76" s="21"/>
       <c r="B76" s="18"/>
       <c r="C76" s="18"/>
       <c r="D76" s="18"/>
@@ -9285,20 +9294,20 @@
       <c r="G76" s="20"/>
       <c r="H76" s="18"/>
       <c r="I76" s="39"/>
-      <c r="J76" s="69"/>
-      <c r="K76" s="66" t="s">
-        <v>227</v>
-      </c>
-      <c r="L76" s="67" t="s">
-        <v>228</v>
-      </c>
-      <c r="M76" s="70"/>
+      <c r="J76" s="74"/>
+      <c r="K76" s="69" t="s">
+        <v>236</v>
+      </c>
+      <c r="L76" s="70" t="s">
+        <v>235</v>
+      </c>
+      <c r="M76" s="73"/>
       <c r="N76" s="18"/>
       <c r="O76" s="42"/>
       <c r="P76" s="20"/>
     </row>
     <row r="77" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A77" s="19"/>
+      <c r="A77" s="21"/>
       <c r="B77" s="18"/>
       <c r="C77" s="18"/>
       <c r="D77" s="18"/>
@@ -9307,20 +9316,16 @@
       <c r="G77" s="20"/>
       <c r="H77" s="18"/>
       <c r="I77" s="39"/>
-      <c r="J77" s="69"/>
-      <c r="K77" s="66" t="s">
-        <v>229</v>
-      </c>
-      <c r="L77" s="67" t="s">
-        <v>230</v>
-      </c>
-      <c r="M77" s="70"/>
+      <c r="J77" s="39"/>
+      <c r="K77" s="18"/>
+      <c r="L77" s="18"/>
+      <c r="M77" s="18"/>
       <c r="N77" s="18"/>
       <c r="O77" s="42"/>
       <c r="P77" s="20"/>
     </row>
     <row r="78" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A78" s="19"/>
+      <c r="A78" s="21"/>
       <c r="B78" s="18"/>
       <c r="C78" s="18"/>
       <c r="D78" s="18"/>
@@ -9329,20 +9334,18 @@
       <c r="G78" s="20"/>
       <c r="H78" s="18"/>
       <c r="I78" s="39"/>
-      <c r="J78" s="69"/>
-      <c r="K78" s="66" t="s">
-        <v>231</v>
-      </c>
-      <c r="L78" s="67" t="s">
-        <v>232</v>
-      </c>
-      <c r="M78" s="70"/>
+      <c r="J78" s="39" t="s">
+        <v>237</v>
+      </c>
+      <c r="K78" s="18"/>
+      <c r="L78" s="18"/>
+      <c r="M78" s="18"/>
       <c r="N78" s="18"/>
       <c r="O78" s="42"/>
       <c r="P78" s="20"/>
     </row>
     <row r="79" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A79" s="19"/>
+      <c r="A79" s="21"/>
       <c r="B79" s="18"/>
       <c r="C79" s="18"/>
       <c r="D79" s="18"/>
@@ -9351,20 +9354,22 @@
       <c r="G79" s="20"/>
       <c r="H79" s="18"/>
       <c r="I79" s="39"/>
-      <c r="J79" s="69"/>
-      <c r="K79" s="66" t="s">
-        <v>233</v>
-      </c>
-      <c r="L79" s="67" t="s">
-        <v>234</v>
-      </c>
-      <c r="M79" s="68"/>
+      <c r="J79" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="K79" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="L79" s="40" t="s">
+        <v>219</v>
+      </c>
+      <c r="M79" s="67"/>
       <c r="N79" s="18"/>
       <c r="O79" s="42"/>
       <c r="P79" s="20"/>
     </row>
     <row r="80" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A80" s="19"/>
+      <c r="A80" s="21"/>
       <c r="B80" s="18"/>
       <c r="C80" s="18"/>
       <c r="D80" s="18"/>
@@ -9373,14 +9378,16 @@
       <c r="G80" s="20"/>
       <c r="H80" s="18"/>
       <c r="I80" s="39"/>
-      <c r="J80" s="69"/>
-      <c r="K80" s="66" t="s">
-        <v>235</v>
-      </c>
-      <c r="L80" s="67" t="s">
-        <v>236</v>
-      </c>
-      <c r="M80" s="68"/>
+      <c r="J80" s="69" t="s">
+        <v>38</v>
+      </c>
+      <c r="K80" s="69" t="s">
+        <v>230</v>
+      </c>
+      <c r="L80" s="70" t="s">
+        <v>238</v>
+      </c>
+      <c r="M80" s="73"/>
       <c r="N80" s="18"/>
       <c r="O80" s="42"/>
       <c r="P80" s="20"/>
@@ -9395,14 +9402,14 @@
       <c r="G81" s="20"/>
       <c r="H81" s="18"/>
       <c r="I81" s="39"/>
-      <c r="J81" s="71"/>
-      <c r="K81" s="66" t="s">
-        <v>237</v>
-      </c>
-      <c r="L81" s="67" t="s">
+      <c r="J81" s="69"/>
+      <c r="K81" s="69" t="s">
         <v>236</v>
       </c>
-      <c r="M81" s="70"/>
+      <c r="L81" s="70" t="s">
+        <v>235</v>
+      </c>
+      <c r="M81" s="73"/>
       <c r="N81" s="18"/>
       <c r="O81" s="42"/>
       <c r="P81" s="20"/>
@@ -9417,10 +9424,10 @@
       <c r="G82" s="20"/>
       <c r="H82" s="18"/>
       <c r="I82" s="39"/>
-      <c r="J82" s="39"/>
-      <c r="K82" s="18"/>
-      <c r="L82" s="18"/>
-      <c r="M82" s="18"/>
+      <c r="J82" s="65"/>
+      <c r="K82" s="65"/>
+      <c r="L82" s="65"/>
+      <c r="M82" s="65"/>
       <c r="N82" s="18"/>
       <c r="O82" s="42"/>
       <c r="P82" s="20"/>
@@ -9435,12 +9442,12 @@
       <c r="G83" s="20"/>
       <c r="H83" s="18"/>
       <c r="I83" s="39"/>
-      <c r="J83" s="39" t="s">
-        <v>238</v>
-      </c>
-      <c r="K83" s="18"/>
-      <c r="L83" s="18"/>
-      <c r="M83" s="18"/>
+      <c r="J83" s="65" t="s">
+        <v>239</v>
+      </c>
+      <c r="K83" s="65"/>
+      <c r="L83" s="65"/>
+      <c r="M83" s="65"/>
       <c r="N83" s="18"/>
       <c r="O83" s="42"/>
       <c r="P83" s="20"/>
@@ -9455,16 +9462,10 @@
       <c r="G84" s="20"/>
       <c r="H84" s="18"/>
       <c r="I84" s="39"/>
-      <c r="J84" s="41" t="s">
-        <v>205</v>
-      </c>
-      <c r="K84" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="L84" s="40" t="s">
-        <v>220</v>
-      </c>
-      <c r="M84" s="64"/>
+      <c r="J84" s="65"/>
+      <c r="K84" s="65"/>
+      <c r="L84" s="65"/>
+      <c r="M84" s="65"/>
       <c r="N84" s="18"/>
       <c r="O84" s="42"/>
       <c r="P84" s="20"/>
@@ -9479,16 +9480,12 @@
       <c r="G85" s="20"/>
       <c r="H85" s="18"/>
       <c r="I85" s="39"/>
-      <c r="J85" s="66" t="s">
-        <v>38</v>
-      </c>
-      <c r="K85" s="66" t="s">
-        <v>231</v>
-      </c>
-      <c r="L85" s="67" t="s">
-        <v>239</v>
-      </c>
-      <c r="M85" s="70"/>
+      <c r="J85" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="K85" s="65"/>
+      <c r="L85" s="65"/>
+      <c r="M85" s="65"/>
       <c r="N85" s="18"/>
       <c r="O85" s="42"/>
       <c r="P85" s="20"/>
@@ -9503,14 +9500,12 @@
       <c r="G86" s="20"/>
       <c r="H86" s="18"/>
       <c r="I86" s="39"/>
-      <c r="J86" s="66"/>
-      <c r="K86" s="66" t="s">
-        <v>237</v>
-      </c>
-      <c r="L86" s="67" t="s">
-        <v>236</v>
-      </c>
-      <c r="M86" s="70"/>
+      <c r="J86" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="K86" s="65"/>
+      <c r="L86" s="65"/>
+      <c r="M86" s="65"/>
       <c r="N86" s="18"/>
       <c r="O86" s="42"/>
       <c r="P86" s="20"/>
@@ -9525,10 +9520,12 @@
       <c r="G87" s="20"/>
       <c r="H87" s="18"/>
       <c r="I87" s="39"/>
-      <c r="J87" s="63"/>
-      <c r="K87" s="63"/>
-      <c r="L87" s="63"/>
-      <c r="M87" s="63"/>
+      <c r="J87" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="K87" s="65"/>
+      <c r="L87" s="65"/>
+      <c r="M87" s="65"/>
       <c r="N87" s="18"/>
       <c r="O87" s="42"/>
       <c r="P87" s="20"/>
@@ -9543,12 +9540,9 @@
       <c r="G88" s="20"/>
       <c r="H88" s="18"/>
       <c r="I88" s="39"/>
-      <c r="J88" s="63" t="s">
-        <v>240</v>
-      </c>
-      <c r="K88" s="63"/>
-      <c r="L88" s="63"/>
-      <c r="M88" s="63"/>
+      <c r="K88" s="65"/>
+      <c r="L88" s="65"/>
+      <c r="M88" s="65"/>
       <c r="N88" s="18"/>
       <c r="O88" s="42"/>
       <c r="P88" s="20"/>
@@ -9563,10 +9557,12 @@
       <c r="G89" s="20"/>
       <c r="H89" s="18"/>
       <c r="I89" s="39"/>
-      <c r="J89" s="63"/>
-      <c r="K89" s="63"/>
-      <c r="L89" s="63"/>
-      <c r="M89" s="63"/>
+      <c r="J89" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="K89" s="65"/>
+      <c r="L89" s="65"/>
+      <c r="M89" s="65"/>
       <c r="N89" s="18"/>
       <c r="O89" s="42"/>
       <c r="P89" s="20"/>
@@ -9582,17 +9578,16 @@
       <c r="H90" s="18"/>
       <c r="I90" s="39"/>
       <c r="J90" s="2" t="s">
-        <v>241</v>
-      </c>
-      <c r="K90" s="63"/>
-      <c r="L90" s="63"/>
-      <c r="M90" s="63"/>
+        <v>244</v>
+      </c>
+      <c r="K90" s="18"/>
+      <c r="L90" s="18"/>
+      <c r="M90" s="18"/>
       <c r="N90" s="18"/>
       <c r="O90" s="42"/>
       <c r="P90" s="20"/>
     </row>
-    <row r="91" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A91" s="21"/>
+    <row r="91" s="2" customFormat="1" ht="16.5" spans="2:16">
       <c r="B91" s="18"/>
       <c r="C91" s="18"/>
       <c r="D91" s="18"/>
@@ -9600,19 +9595,19 @@
       <c r="F91" s="18"/>
       <c r="G91" s="20"/>
       <c r="H91" s="18"/>
-      <c r="I91" s="39"/>
-      <c r="J91" s="2" t="s">
-        <v>242</v>
-      </c>
-      <c r="K91" s="63"/>
-      <c r="L91" s="63"/>
-      <c r="M91" s="63"/>
+      <c r="I91" s="18"/>
+      <c r="J91" s="18"/>
+      <c r="K91" s="18"/>
+      <c r="L91" s="18"/>
+      <c r="M91" s="18"/>
       <c r="N91" s="18"/>
       <c r="O91" s="42"/>
       <c r="P91" s="20"/>
     </row>
     <row r="92" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A92" s="21"/>
+      <c r="A92" s="19" t="s">
+        <v>144</v>
+      </c>
       <c r="B92" s="18"/>
       <c r="C92" s="18"/>
       <c r="D92" s="18"/>
@@ -9620,19 +9615,20 @@
       <c r="F92" s="18"/>
       <c r="G92" s="20"/>
       <c r="H92" s="18"/>
-      <c r="I92" s="39"/>
-      <c r="J92" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="K92" s="63"/>
-      <c r="L92" s="63"/>
-      <c r="M92" s="63"/>
+      <c r="I92" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="K92" s="39"/>
+      <c r="L92" s="18"/>
+      <c r="M92" s="18"/>
       <c r="N92" s="18"/>
       <c r="O92" s="42"/>
       <c r="P92" s="20"/>
     </row>
     <row r="93" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A93" s="21"/>
+      <c r="A93" s="19" t="s">
+        <v>147</v>
+      </c>
       <c r="B93" s="18"/>
       <c r="C93" s="18"/>
       <c r="D93" s="18"/>
@@ -9640,16 +9636,15 @@
       <c r="F93" s="18"/>
       <c r="G93" s="20"/>
       <c r="H93" s="18"/>
-      <c r="I93" s="39"/>
-      <c r="K93" s="63"/>
-      <c r="L93" s="63"/>
-      <c r="M93" s="63"/>
+      <c r="I93" s="38"/>
+      <c r="K93" s="39"/>
+      <c r="L93" s="18"/>
+      <c r="M93" s="18"/>
       <c r="N93" s="18"/>
       <c r="O93" s="42"/>
       <c r="P93" s="20"/>
     </row>
-    <row r="94" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A94" s="21"/>
+    <row r="94" s="2" customFormat="1" ht="16.5" spans="2:16">
       <c r="B94" s="18"/>
       <c r="C94" s="18"/>
       <c r="D94" s="18"/>
@@ -9657,19 +9652,19 @@
       <c r="F94" s="18"/>
       <c r="G94" s="20"/>
       <c r="H94" s="18"/>
-      <c r="I94" s="39"/>
+      <c r="I94" s="38"/>
       <c r="J94" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="K94" s="63"/>
-      <c r="L94" s="63"/>
-      <c r="M94" s="63"/>
+        <v>246</v>
+      </c>
+      <c r="K94" s="39"/>
+      <c r="L94" s="18"/>
+      <c r="M94" s="18"/>
       <c r="N94" s="18"/>
       <c r="O94" s="42"/>
       <c r="P94" s="20"/>
     </row>
     <row r="95" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A95" s="21"/>
+      <c r="A95" s="19"/>
       <c r="B95" s="18"/>
       <c r="C95" s="18"/>
       <c r="D95" s="18"/>
@@ -9677,11 +9672,11 @@
       <c r="F95" s="18"/>
       <c r="G95" s="20"/>
       <c r="H95" s="18"/>
-      <c r="I95" s="39"/>
+      <c r="I95" s="38"/>
       <c r="J95" s="2" t="s">
-        <v>245</v>
-      </c>
-      <c r="K95" s="18"/>
+        <v>247</v>
+      </c>
+      <c r="K95" s="39"/>
       <c r="L95" s="18"/>
       <c r="M95" s="18"/>
       <c r="N95" s="18"/>
@@ -9689,7 +9684,7 @@
       <c r="P95" s="20"/>
     </row>
     <row r="96" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A96" s="21"/>
+      <c r="A96" s="19"/>
       <c r="B96" s="18"/>
       <c r="C96" s="18"/>
       <c r="D96" s="18"/>
@@ -9697,9 +9692,11 @@
       <c r="F96" s="18"/>
       <c r="G96" s="20"/>
       <c r="H96" s="18"/>
-      <c r="I96" s="18"/>
-      <c r="J96" s="18"/>
-      <c r="K96" s="18"/>
+      <c r="I96" s="38"/>
+      <c r="J96" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="K96" s="39"/>
       <c r="L96" s="18"/>
       <c r="M96" s="18"/>
       <c r="N96" s="18"/>
@@ -9707,9 +9704,7 @@
       <c r="P96" s="20"/>
     </row>
     <row r="97" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A97" s="19" t="s">
-        <v>144</v>
-      </c>
+      <c r="A97" s="19"/>
       <c r="B97" s="18"/>
       <c r="C97" s="18"/>
       <c r="D97" s="18"/>
@@ -9717,9 +9712,7 @@
       <c r="F97" s="18"/>
       <c r="G97" s="20"/>
       <c r="H97" s="18"/>
-      <c r="I97" s="38" t="s">
-        <v>246</v>
-      </c>
+      <c r="I97" s="38"/>
       <c r="K97" s="39"/>
       <c r="L97" s="18"/>
       <c r="M97" s="18"/>
@@ -9727,10 +9720,7 @@
       <c r="O97" s="42"/>
       <c r="P97" s="20"/>
     </row>
-    <row r="98" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A98" s="19" t="s">
-        <v>147</v>
-      </c>
+    <row r="98" s="2" customFormat="1" ht="16.5" spans="2:16">
       <c r="B98" s="18"/>
       <c r="C98" s="18"/>
       <c r="D98" s="18"/>
@@ -9738,11 +9728,10 @@
       <c r="F98" s="18"/>
       <c r="G98" s="20"/>
       <c r="H98" s="18"/>
-      <c r="I98" s="38"/>
-      <c r="J98" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="K98" s="39"/>
+      <c r="I98" s="18"/>
+      <c r="J98" s="38" t="s">
+        <v>249</v>
+      </c>
       <c r="L98" s="18"/>
       <c r="M98" s="18"/>
       <c r="N98" s="18"/>
@@ -9750,7 +9739,7 @@
       <c r="P98" s="20"/>
     </row>
     <row r="99" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A99" s="19"/>
+      <c r="A99" s="21"/>
       <c r="B99" s="18"/>
       <c r="C99" s="18"/>
       <c r="D99" s="18"/>
@@ -9758,19 +9747,23 @@
       <c r="F99" s="18"/>
       <c r="G99" s="20"/>
       <c r="H99" s="18"/>
-      <c r="I99" s="38"/>
-      <c r="J99" s="2" t="s">
-        <v>247</v>
-      </c>
-      <c r="K99" s="39"/>
-      <c r="L99" s="18"/>
-      <c r="M99" s="18"/>
+      <c r="I99" s="18"/>
+      <c r="J99" s="41" t="s">
+        <v>205</v>
+      </c>
+      <c r="K99" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="L99" s="41" t="s">
+        <v>219</v>
+      </c>
+      <c r="M99" s="41"/>
       <c r="N99" s="18"/>
       <c r="O99" s="42"/>
       <c r="P99" s="20"/>
     </row>
     <row r="100" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A100" s="19"/>
+      <c r="A100" s="21"/>
       <c r="B100" s="18"/>
       <c r="C100" s="18"/>
       <c r="D100" s="18"/>
@@ -9778,15 +9771,23 @@
       <c r="F100" s="18"/>
       <c r="G100" s="20"/>
       <c r="H100" s="18"/>
-      <c r="I100" s="38"/>
-      <c r="K100" s="39"/>
-      <c r="L100" s="18"/>
-      <c r="M100" s="18"/>
+      <c r="I100" s="18"/>
+      <c r="J100" s="68" t="s">
+        <v>250</v>
+      </c>
+      <c r="K100" s="69" t="s">
+        <v>251</v>
+      </c>
+      <c r="L100" s="69" t="s">
+        <v>221</v>
+      </c>
+      <c r="M100" s="69"/>
       <c r="N100" s="18"/>
       <c r="O100" s="42"/>
       <c r="P100" s="20"/>
     </row>
-    <row r="101" s="2" customFormat="1" ht="16.5" spans="2:16">
+    <row r="101" s="2" customFormat="1" ht="16.5" spans="1:16">
+      <c r="A101" s="21"/>
       <c r="B101" s="18"/>
       <c r="C101" s="18"/>
       <c r="D101" s="18"/>
@@ -9794,19 +9795,21 @@
       <c r="F101" s="18"/>
       <c r="G101" s="20"/>
       <c r="H101" s="18"/>
-      <c r="I101" s="38"/>
-      <c r="J101" s="2" t="s">
-        <v>248</v>
-      </c>
-      <c r="K101" s="39"/>
-      <c r="L101" s="18"/>
-      <c r="M101" s="18"/>
+      <c r="I101" s="18"/>
+      <c r="J101" s="72"/>
+      <c r="K101" s="69" t="s">
+        <v>220</v>
+      </c>
+      <c r="L101" s="69" t="s">
+        <v>252</v>
+      </c>
+      <c r="M101" s="69"/>
       <c r="N101" s="18"/>
       <c r="O101" s="42"/>
       <c r="P101" s="20"/>
     </row>
     <row r="102" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A102" s="19"/>
+      <c r="A102" s="21"/>
       <c r="B102" s="18"/>
       <c r="C102" s="18"/>
       <c r="D102" s="18"/>
@@ -9814,19 +9817,21 @@
       <c r="F102" s="18"/>
       <c r="G102" s="20"/>
       <c r="H102" s="18"/>
-      <c r="I102" s="38"/>
-      <c r="J102" s="2" t="s">
-        <v>249</v>
-      </c>
-      <c r="K102" s="39"/>
-      <c r="L102" s="18"/>
-      <c r="M102" s="18"/>
+      <c r="I102" s="18"/>
+      <c r="J102" s="72"/>
+      <c r="K102" s="69" t="s">
+        <v>253</v>
+      </c>
+      <c r="L102" s="69" t="s">
+        <v>254</v>
+      </c>
+      <c r="M102" s="69"/>
       <c r="N102" s="18"/>
       <c r="O102" s="42"/>
       <c r="P102" s="20"/>
     </row>
     <row r="103" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A103" s="19"/>
+      <c r="A103" s="21"/>
       <c r="B103" s="18"/>
       <c r="C103" s="18"/>
       <c r="D103" s="18"/>
@@ -9834,19 +9839,21 @@
       <c r="F103" s="18"/>
       <c r="G103" s="20"/>
       <c r="H103" s="18"/>
-      <c r="I103" s="38"/>
-      <c r="J103" s="2" t="s">
-        <v>250</v>
-      </c>
-      <c r="K103" s="39"/>
-      <c r="L103" s="18"/>
-      <c r="M103" s="18"/>
+      <c r="I103" s="18"/>
+      <c r="J103" s="72"/>
+      <c r="K103" s="69" t="s">
+        <v>255</v>
+      </c>
+      <c r="L103" s="69" t="s">
+        <v>256</v>
+      </c>
+      <c r="M103" s="69"/>
       <c r="N103" s="18"/>
       <c r="O103" s="42"/>
       <c r="P103" s="20"/>
     </row>
     <row r="104" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A104" s="19"/>
+      <c r="A104" s="21"/>
       <c r="B104" s="18"/>
       <c r="C104" s="18"/>
       <c r="D104" s="18"/>
@@ -9854,15 +9861,21 @@
       <c r="F104" s="18"/>
       <c r="G104" s="20"/>
       <c r="H104" s="18"/>
-      <c r="I104" s="38"/>
-      <c r="K104" s="39"/>
-      <c r="L104" s="18"/>
-      <c r="M104" s="18"/>
+      <c r="I104" s="18"/>
+      <c r="J104" s="72"/>
+      <c r="K104" s="69" t="s">
+        <v>257</v>
+      </c>
+      <c r="L104" s="69" t="s">
+        <v>258</v>
+      </c>
+      <c r="M104" s="69"/>
       <c r="N104" s="18"/>
       <c r="O104" s="42"/>
       <c r="P104" s="20"/>
     </row>
-    <row r="105" s="2" customFormat="1" ht="16.5" spans="2:16">
+    <row r="105" s="2" customFormat="1" ht="16.5" spans="1:16">
+      <c r="A105" s="21"/>
       <c r="B105" s="18"/>
       <c r="C105" s="18"/>
       <c r="D105" s="18"/>
@@ -9871,11 +9884,14 @@
       <c r="G105" s="20"/>
       <c r="H105" s="18"/>
       <c r="I105" s="18"/>
-      <c r="J105" s="38" t="s">
-        <v>251</v>
-      </c>
-      <c r="L105" s="18"/>
-      <c r="M105" s="18"/>
+      <c r="J105" s="72"/>
+      <c r="K105" s="69" t="s">
+        <v>259</v>
+      </c>
+      <c r="L105" s="69" t="s">
+        <v>231</v>
+      </c>
+      <c r="M105" s="69"/>
       <c r="N105" s="18"/>
       <c r="O105" s="42"/>
       <c r="P105" s="20"/>
@@ -9890,16 +9906,14 @@
       <c r="G106" s="20"/>
       <c r="H106" s="18"/>
       <c r="I106" s="18"/>
-      <c r="J106" s="41" t="s">
-        <v>205</v>
-      </c>
-      <c r="K106" s="41" t="s">
-        <v>60</v>
-      </c>
-      <c r="L106" s="41" t="s">
-        <v>220</v>
-      </c>
-      <c r="M106" s="41"/>
+      <c r="J106" s="72"/>
+      <c r="K106" s="69" t="s">
+        <v>260</v>
+      </c>
+      <c r="L106" s="69" t="s">
+        <v>261</v>
+      </c>
+      <c r="M106" s="69"/>
       <c r="N106" s="18"/>
       <c r="O106" s="42"/>
       <c r="P106" s="20"/>
@@ -9914,16 +9928,14 @@
       <c r="G107" s="20"/>
       <c r="H107" s="18"/>
       <c r="I107" s="18"/>
-      <c r="J107" s="65" t="s">
-        <v>252</v>
-      </c>
-      <c r="K107" s="66" t="s">
-        <v>253</v>
-      </c>
-      <c r="L107" s="66" t="s">
-        <v>222</v>
-      </c>
-      <c r="M107" s="66"/>
+      <c r="J107" s="72"/>
+      <c r="K107" s="69" t="s">
+        <v>262</v>
+      </c>
+      <c r="L107" s="69" t="s">
+        <v>263</v>
+      </c>
+      <c r="M107" s="69"/>
       <c r="N107" s="18"/>
       <c r="O107" s="42"/>
       <c r="P107" s="20"/>
@@ -9938,14 +9950,14 @@
       <c r="G108" s="20"/>
       <c r="H108" s="18"/>
       <c r="I108" s="18"/>
-      <c r="J108" s="69"/>
-      <c r="K108" s="66" t="s">
-        <v>221</v>
-      </c>
-      <c r="L108" s="66" t="s">
-        <v>254</v>
-      </c>
-      <c r="M108" s="66"/>
+      <c r="J108" s="72"/>
+      <c r="K108" s="69" t="s">
+        <v>264</v>
+      </c>
+      <c r="L108" s="69" t="s">
+        <v>265</v>
+      </c>
+      <c r="M108" s="69"/>
       <c r="N108" s="18"/>
       <c r="O108" s="42"/>
       <c r="P108" s="20"/>
@@ -9960,14 +9972,14 @@
       <c r="G109" s="20"/>
       <c r="H109" s="18"/>
       <c r="I109" s="18"/>
-      <c r="J109" s="69"/>
-      <c r="K109" s="66" t="s">
-        <v>255</v>
-      </c>
-      <c r="L109" s="66" t="s">
-        <v>256</v>
-      </c>
-      <c r="M109" s="66"/>
+      <c r="J109" s="72"/>
+      <c r="K109" s="69" t="s">
+        <v>266</v>
+      </c>
+      <c r="L109" s="69" t="s">
+        <v>267</v>
+      </c>
+      <c r="M109" s="69"/>
       <c r="N109" s="18"/>
       <c r="O109" s="42"/>
       <c r="P109" s="20"/>
@@ -9982,14 +9994,14 @@
       <c r="G110" s="20"/>
       <c r="H110" s="18"/>
       <c r="I110" s="18"/>
-      <c r="J110" s="69"/>
-      <c r="K110" s="66" t="s">
-        <v>257</v>
-      </c>
-      <c r="L110" s="66" t="s">
-        <v>258</v>
-      </c>
-      <c r="M110" s="66"/>
+      <c r="J110" s="72"/>
+      <c r="K110" s="69" t="s">
+        <v>232</v>
+      </c>
+      <c r="L110" s="69" t="s">
+        <v>233</v>
+      </c>
+      <c r="M110" s="69"/>
       <c r="N110" s="18"/>
       <c r="O110" s="42"/>
       <c r="P110" s="20"/>
@@ -10004,14 +10016,14 @@
       <c r="G111" s="20"/>
       <c r="H111" s="18"/>
       <c r="I111" s="18"/>
-      <c r="J111" s="69"/>
-      <c r="K111" s="66" t="s">
-        <v>259</v>
-      </c>
-      <c r="L111" s="66" t="s">
-        <v>260</v>
-      </c>
-      <c r="M111" s="66"/>
+      <c r="J111" s="72"/>
+      <c r="K111" s="69" t="s">
+        <v>234</v>
+      </c>
+      <c r="L111" s="69" t="s">
+        <v>235</v>
+      </c>
+      <c r="M111" s="69"/>
       <c r="N111" s="18"/>
       <c r="O111" s="42"/>
       <c r="P111" s="20"/>
@@ -10026,14 +10038,14 @@
       <c r="G112" s="20"/>
       <c r="H112" s="18"/>
       <c r="I112" s="18"/>
-      <c r="J112" s="69"/>
-      <c r="K112" s="66" t="s">
-        <v>261</v>
-      </c>
-      <c r="L112" s="66" t="s">
-        <v>232</v>
-      </c>
-      <c r="M112" s="66"/>
+      <c r="J112" s="74"/>
+      <c r="K112" s="69" t="s">
+        <v>236</v>
+      </c>
+      <c r="L112" s="69" t="s">
+        <v>235</v>
+      </c>
+      <c r="M112" s="69"/>
       <c r="N112" s="18"/>
       <c r="O112" s="42"/>
       <c r="P112" s="20"/>
@@ -10048,14 +10060,10 @@
       <c r="G113" s="20"/>
       <c r="H113" s="18"/>
       <c r="I113" s="18"/>
-      <c r="J113" s="69"/>
-      <c r="K113" s="66" t="s">
-        <v>262</v>
-      </c>
-      <c r="L113" s="66" t="s">
-        <v>263</v>
-      </c>
-      <c r="M113" s="66"/>
+      <c r="J113" s="18"/>
+      <c r="K113" s="18"/>
+      <c r="L113" s="18"/>
+      <c r="M113" s="18"/>
       <c r="N113" s="18"/>
       <c r="O113" s="42"/>
       <c r="P113" s="20"/>
@@ -10069,15 +10077,10 @@
       <c r="F114" s="18"/>
       <c r="G114" s="20"/>
       <c r="H114" s="18"/>
-      <c r="I114" s="18"/>
-      <c r="J114" s="69"/>
-      <c r="K114" s="66" t="s">
-        <v>264</v>
-      </c>
-      <c r="L114" s="66" t="s">
-        <v>265</v>
-      </c>
-      <c r="M114" s="66"/>
+      <c r="J114" s="2" t="s">
+        <v>268</v>
+      </c>
+      <c r="M114" s="18"/>
       <c r="N114" s="18"/>
       <c r="O114" s="42"/>
       <c r="P114" s="20"/>
@@ -10091,15 +10094,10 @@
       <c r="F115" s="18"/>
       <c r="G115" s="20"/>
       <c r="H115" s="18"/>
-      <c r="I115" s="18"/>
-      <c r="J115" s="69"/>
-      <c r="K115" s="66" t="s">
-        <v>266</v>
-      </c>
-      <c r="L115" s="66" t="s">
-        <v>267</v>
-      </c>
-      <c r="M115" s="66"/>
+      <c r="J115" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="M115" s="18"/>
       <c r="N115" s="18"/>
       <c r="O115" s="42"/>
       <c r="P115" s="20"/>
@@ -10113,15 +10111,10 @@
       <c r="F116" s="18"/>
       <c r="G116" s="20"/>
       <c r="H116" s="18"/>
-      <c r="I116" s="18"/>
-      <c r="J116" s="69"/>
-      <c r="K116" s="66" t="s">
-        <v>268</v>
-      </c>
-      <c r="L116" s="66" t="s">
+      <c r="J116" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="M116" s="66"/>
+      <c r="M116" s="18"/>
       <c r="N116" s="18"/>
       <c r="O116" s="42"/>
       <c r="P116" s="20"/>
@@ -10135,15 +10128,7 @@
       <c r="F117" s="18"/>
       <c r="G117" s="20"/>
       <c r="H117" s="18"/>
-      <c r="I117" s="18"/>
-      <c r="J117" s="69"/>
-      <c r="K117" s="66" t="s">
-        <v>233</v>
-      </c>
-      <c r="L117" s="66" t="s">
-        <v>234</v>
-      </c>
-      <c r="M117" s="66"/>
+      <c r="M117" s="18"/>
       <c r="N117" s="18"/>
       <c r="O117" s="42"/>
       <c r="P117" s="20"/>
@@ -10157,15 +10142,10 @@
       <c r="F118" s="18"/>
       <c r="G118" s="20"/>
       <c r="H118" s="18"/>
-      <c r="I118" s="18"/>
-      <c r="J118" s="69"/>
-      <c r="K118" s="66" t="s">
-        <v>235</v>
-      </c>
-      <c r="L118" s="66" t="s">
-        <v>236</v>
-      </c>
-      <c r="M118" s="66"/>
+      <c r="J118" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="M118" s="18"/>
       <c r="N118" s="18"/>
       <c r="O118" s="42"/>
       <c r="P118" s="20"/>
@@ -10179,15 +10159,10 @@
       <c r="F119" s="18"/>
       <c r="G119" s="20"/>
       <c r="H119" s="18"/>
-      <c r="I119" s="18"/>
-      <c r="J119" s="71"/>
-      <c r="K119" s="66" t="s">
-        <v>237</v>
-      </c>
-      <c r="L119" s="66" t="s">
-        <v>236</v>
-      </c>
-      <c r="M119" s="66"/>
+      <c r="J119" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="M119" s="18"/>
       <c r="N119" s="18"/>
       <c r="O119" s="42"/>
       <c r="P119" s="20"/>
@@ -10202,7 +10177,7 @@
       <c r="G120" s="20"/>
       <c r="H120" s="18"/>
       <c r="I120" s="18"/>
-      <c r="J120" s="18"/>
+      <c r="J120" s="64"/>
       <c r="K120" s="18"/>
       <c r="L120" s="18"/>
       <c r="M120" s="18"/>
@@ -10219,12 +10194,17 @@
       <c r="F121" s="18"/>
       <c r="G121" s="20"/>
       <c r="H121" s="18"/>
-      <c r="J121" s="2" t="s">
-        <v>270</v>
-      </c>
+      <c r="I121" s="65" t="s">
+        <v>271</v>
+      </c>
+      <c r="J121" s="18"/>
+      <c r="K121" s="18"/>
+      <c r="L121" s="18"/>
       <c r="M121" s="18"/>
       <c r="N121" s="18"/>
-      <c r="O121" s="42"/>
+      <c r="O121" s="19" t="s">
+        <v>272</v>
+      </c>
       <c r="P121" s="20"/>
     </row>
     <row r="122" s="2" customFormat="1" ht="16.5" spans="1:16">
@@ -10236,9 +10216,12 @@
       <c r="F122" s="18"/>
       <c r="G122" s="20"/>
       <c r="H122" s="18"/>
-      <c r="J122" s="2" t="s">
-        <v>242</v>
-      </c>
+      <c r="I122" s="18"/>
+      <c r="J122" s="39" t="s">
+        <v>273</v>
+      </c>
+      <c r="K122" s="18"/>
+      <c r="L122" s="18"/>
       <c r="M122" s="18"/>
       <c r="N122" s="18"/>
       <c r="O122" s="42"/>
@@ -10253,9 +10236,14 @@
       <c r="F123" s="18"/>
       <c r="G123" s="20"/>
       <c r="H123" s="18"/>
-      <c r="J123" s="2" t="s">
-        <v>271</v>
-      </c>
+      <c r="I123" s="18"/>
+      <c r="J123" s="40" t="s">
+        <v>274</v>
+      </c>
+      <c r="K123" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="L123" s="67"/>
       <c r="M123" s="18"/>
       <c r="N123" s="18"/>
       <c r="O123" s="42"/>
@@ -10270,6 +10258,14 @@
       <c r="F124" s="18"/>
       <c r="G124" s="20"/>
       <c r="H124" s="18"/>
+      <c r="I124" s="18"/>
+      <c r="J124" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="K124" s="75" t="s">
+        <v>114</v>
+      </c>
+      <c r="L124" s="76"/>
       <c r="M124" s="18"/>
       <c r="N124" s="18"/>
       <c r="O124" s="42"/>
@@ -10284,9 +10280,14 @@
       <c r="F125" s="18"/>
       <c r="G125" s="20"/>
       <c r="H125" s="18"/>
-      <c r="J125" s="2" t="s">
-        <v>244</v>
-      </c>
+      <c r="I125" s="18"/>
+      <c r="J125" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="K125" s="75" t="s">
+        <v>117</v>
+      </c>
+      <c r="L125" s="76"/>
       <c r="M125" s="18"/>
       <c r="N125" s="18"/>
       <c r="O125" s="42"/>
@@ -10301,16 +10302,21 @@
       <c r="F126" s="18"/>
       <c r="G126" s="20"/>
       <c r="H126" s="18"/>
-      <c r="J126" s="2" t="s">
-        <v>272</v>
-      </c>
+      <c r="I126" s="18"/>
+      <c r="J126" s="62" t="s">
+        <v>275</v>
+      </c>
+      <c r="K126" s="75" t="s">
+        <v>119</v>
+      </c>
+      <c r="L126" s="76"/>
       <c r="M126" s="18"/>
       <c r="N126" s="18"/>
       <c r="O126" s="42"/>
       <c r="P126" s="20"/>
     </row>
-    <row r="127" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A127" s="21"/>
+    <row r="127" s="2" customFormat="1" ht="19.5" spans="1:16">
+      <c r="A127" s="66"/>
       <c r="B127" s="18"/>
       <c r="C127" s="18"/>
       <c r="D127" s="18"/>
@@ -10319,161 +10325,13 @@
       <c r="G127" s="20"/>
       <c r="H127" s="18"/>
       <c r="I127" s="18"/>
-      <c r="J127" s="72"/>
+      <c r="J127" s="39"/>
       <c r="K127" s="18"/>
       <c r="L127" s="18"/>
       <c r="M127" s="18"/>
       <c r="N127" s="18"/>
       <c r="O127" s="42"/>
       <c r="P127" s="20"/>
-    </row>
-    <row r="128" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A128" s="21"/>
-      <c r="B128" s="18"/>
-      <c r="C128" s="18"/>
-      <c r="D128" s="18"/>
-      <c r="E128" s="18"/>
-      <c r="F128" s="18"/>
-      <c r="G128" s="20"/>
-      <c r="H128" s="18"/>
-      <c r="I128" s="63" t="s">
-        <v>273</v>
-      </c>
-      <c r="J128" s="18"/>
-      <c r="K128" s="18"/>
-      <c r="L128" s="18"/>
-      <c r="M128" s="18"/>
-      <c r="N128" s="18"/>
-      <c r="O128" s="19" t="s">
-        <v>274</v>
-      </c>
-      <c r="P128" s="20"/>
-    </row>
-    <row r="129" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A129" s="21"/>
-      <c r="B129" s="18"/>
-      <c r="C129" s="18"/>
-      <c r="D129" s="18"/>
-      <c r="E129" s="18"/>
-      <c r="F129" s="18"/>
-      <c r="G129" s="20"/>
-      <c r="H129" s="18"/>
-      <c r="I129" s="18"/>
-      <c r="J129" s="39" t="s">
-        <v>275</v>
-      </c>
-      <c r="K129" s="18"/>
-      <c r="L129" s="18"/>
-      <c r="M129" s="18"/>
-      <c r="N129" s="18"/>
-      <c r="O129" s="42"/>
-      <c r="P129" s="20"/>
-    </row>
-    <row r="130" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A130" s="21"/>
-      <c r="B130" s="18"/>
-      <c r="C130" s="18"/>
-      <c r="D130" s="18"/>
-      <c r="E130" s="18"/>
-      <c r="F130" s="18"/>
-      <c r="G130" s="20"/>
-      <c r="H130" s="18"/>
-      <c r="I130" s="18"/>
-      <c r="J130" s="40" t="s">
-        <v>276</v>
-      </c>
-      <c r="K130" s="40" t="s">
-        <v>53</v>
-      </c>
-      <c r="L130" s="64"/>
-      <c r="M130" s="18"/>
-      <c r="N130" s="18"/>
-      <c r="O130" s="42"/>
-      <c r="P130" s="20"/>
-    </row>
-    <row r="131" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A131" s="21"/>
-      <c r="B131" s="18"/>
-      <c r="C131" s="18"/>
-      <c r="D131" s="18"/>
-      <c r="E131" s="18"/>
-      <c r="F131" s="18"/>
-      <c r="G131" s="20"/>
-      <c r="H131" s="18"/>
-      <c r="I131" s="18"/>
-      <c r="J131" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="K131" s="74" t="s">
-        <v>114</v>
-      </c>
-      <c r="L131" s="75"/>
-      <c r="M131" s="18"/>
-      <c r="N131" s="18"/>
-      <c r="O131" s="42"/>
-      <c r="P131" s="20"/>
-    </row>
-    <row r="132" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A132" s="21"/>
-      <c r="B132" s="18"/>
-      <c r="C132" s="18"/>
-      <c r="D132" s="18"/>
-      <c r="E132" s="18"/>
-      <c r="F132" s="18"/>
-      <c r="G132" s="20"/>
-      <c r="H132" s="18"/>
-      <c r="I132" s="18"/>
-      <c r="J132" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="K132" s="74" t="s">
-        <v>117</v>
-      </c>
-      <c r="L132" s="75"/>
-      <c r="M132" s="18"/>
-      <c r="N132" s="18"/>
-      <c r="O132" s="42"/>
-      <c r="P132" s="20"/>
-    </row>
-    <row r="133" s="2" customFormat="1" ht="16.5" spans="1:16">
-      <c r="A133" s="21"/>
-      <c r="B133" s="18"/>
-      <c r="C133" s="18"/>
-      <c r="D133" s="18"/>
-      <c r="E133" s="18"/>
-      <c r="F133" s="18"/>
-      <c r="G133" s="20"/>
-      <c r="H133" s="18"/>
-      <c r="I133" s="18"/>
-      <c r="J133" s="62" t="s">
-        <v>277</v>
-      </c>
-      <c r="K133" s="74" t="s">
-        <v>119</v>
-      </c>
-      <c r="L133" s="75"/>
-      <c r="M133" s="18"/>
-      <c r="N133" s="18"/>
-      <c r="O133" s="42"/>
-      <c r="P133" s="20"/>
-    </row>
-    <row r="134" s="2" customFormat="1" ht="19.5" spans="1:16">
-      <c r="A134" s="73"/>
-      <c r="B134" s="18"/>
-      <c r="C134" s="18"/>
-      <c r="D134" s="18"/>
-      <c r="E134" s="18"/>
-      <c r="F134" s="18"/>
-      <c r="G134" s="20"/>
-      <c r="H134" s="18"/>
-      <c r="I134" s="18"/>
-      <c r="J134" s="39"/>
-      <c r="K134" s="18"/>
-      <c r="L134" s="18"/>
-      <c r="M134" s="18"/>
-      <c r="N134" s="18"/>
-      <c r="O134" s="42"/>
-      <c r="P134" s="20"/>
     </row>
   </sheetData>
   <mergeCells count="71">
@@ -10499,21 +10357,28 @@
     <mergeCell ref="L44:M44"/>
     <mergeCell ref="L45:M45"/>
     <mergeCell ref="L46:M46"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="L57:M57"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="L54:M54"/>
+    <mergeCell ref="L67:M67"/>
+    <mergeCell ref="L68:M68"/>
+    <mergeCell ref="L69:M69"/>
+    <mergeCell ref="L70:M70"/>
+    <mergeCell ref="L71:M71"/>
     <mergeCell ref="L72:M72"/>
     <mergeCell ref="L73:M73"/>
     <mergeCell ref="L74:M74"/>
     <mergeCell ref="L75:M75"/>
     <mergeCell ref="L76:M76"/>
-    <mergeCell ref="L77:M77"/>
-    <mergeCell ref="L78:M78"/>
     <mergeCell ref="L79:M79"/>
     <mergeCell ref="L80:M80"/>
     <mergeCell ref="L81:M81"/>
-    <mergeCell ref="L84:M84"/>
-    <mergeCell ref="L85:M85"/>
-    <mergeCell ref="L86:M86"/>
+    <mergeCell ref="L99:M99"/>
+    <mergeCell ref="L100:M100"/>
+    <mergeCell ref="L101:M101"/>
+    <mergeCell ref="L102:M102"/>
+    <mergeCell ref="L103:M103"/>
+    <mergeCell ref="L104:M104"/>
+    <mergeCell ref="L105:M105"/>
     <mergeCell ref="L106:M106"/>
     <mergeCell ref="L107:M107"/>
     <mergeCell ref="L108:M108"/>
@@ -10521,20 +10386,13 @@
     <mergeCell ref="L110:M110"/>
     <mergeCell ref="L111:M111"/>
     <mergeCell ref="L112:M112"/>
-    <mergeCell ref="L113:M113"/>
-    <mergeCell ref="L114:M114"/>
-    <mergeCell ref="L115:M115"/>
-    <mergeCell ref="L116:M116"/>
-    <mergeCell ref="L117:M117"/>
-    <mergeCell ref="L118:M118"/>
-    <mergeCell ref="L119:M119"/>
-    <mergeCell ref="K130:L130"/>
-    <mergeCell ref="K131:L131"/>
-    <mergeCell ref="K132:L132"/>
-    <mergeCell ref="K133:L133"/>
-    <mergeCell ref="J73:J81"/>
-    <mergeCell ref="J85:J86"/>
-    <mergeCell ref="J107:J119"/>
+    <mergeCell ref="K123:L123"/>
+    <mergeCell ref="K124:L124"/>
+    <mergeCell ref="K125:L125"/>
+    <mergeCell ref="K126:L126"/>
+    <mergeCell ref="J68:J76"/>
+    <mergeCell ref="J80:J81"/>
+    <mergeCell ref="J100:J112"/>
     <mergeCell ref="K1:K2"/>
     <mergeCell ref="K3:K4"/>
     <mergeCell ref="L1:L2"/>
